--- a/data/GOOGL_data.xlsx
+++ b/data/GOOGL_data.xlsx
@@ -4839,7 +4839,7 @@
         <v>22.785429</v>
       </c>
       <c r="M2" t="n">
-        <v>19.93</v>
+        <v>19.94</v>
       </c>
       <c r="N2" t="n">
         <v>408.61</v>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-06 05:34:41</t>
+          <t>2026-09-06 05:41:42</t>
         </is>
       </c>
     </row>

--- a/data/GOOGL_data.xlsx
+++ b/data/GOOGL_data.xlsx
@@ -4652,7 +4652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4773,25 +4773,45 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>book_value</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>price_to_book</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>earnings_growth</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>shares_outstanding</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -4875,29 +4895,41 @@
       <c r="W2" t="n">
         <v>2.724</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" t="n">
+        <v>50.896</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.650031</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5867155790</v>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Internet Content &amp; Information</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>https://abc.xyz</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>2026-09-06 05:41:42</t>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2026-09-06 16:09:45</t>
         </is>
       </c>
     </row>

--- a/data/GOOGL_data.xlsx
+++ b/data/GOOGL_data.xlsx
@@ -4929,7 +4929,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:09:45</t>
+          <t>2026-09-06 16:24:21</t>
         </is>
       </c>
     </row>

--- a/data/GOOGL_data.xlsx
+++ b/data/GOOGL_data.xlsx
@@ -4929,7 +4929,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:24:21</t>
+          <t>2026-09-06 16:34:15</t>
         </is>
       </c>
     </row>

--- a/data/GOOGL_data.xlsx
+++ b/data/GOOGL_data.xlsx
@@ -4929,7 +4929,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:34:15</t>
+          <t>2026-09-06 16:48:50</t>
         </is>
       </c>
     </row>

--- a/data/GOOGL_data.xlsx
+++ b/data/GOOGL_data.xlsx
@@ -4873,15 +4873,11 @@
       <c r="Q2" t="n">
         <v>0.26</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="R2" t="n">
+        <v>0.54771</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.34033</v>
       </c>
       <c r="T2" t="n">
         <v>0.48676</v>
@@ -4929,7 +4925,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:48:50</t>
+          <t>2026-09-06 16:59:20</t>
         </is>
       </c>
     </row>

--- a/data/GOOGL_data.xlsx
+++ b/data/GOOGL_data.xlsx
@@ -4652,7 +4652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4793,25 +4793,40 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>total_revenue</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -4903,29 +4918,38 @@
       <c r="AA2" t="n">
         <v>5867155790</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" t="n">
+        <v>445865984000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4035705831424</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>173164003328</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Internet Content &amp; Information</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>https://abc.xyz</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>2026-09-06 16:59:20</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2026-09-06 22:20:25</t>
         </is>
       </c>
     </row>

--- a/data/GOOGL_data.xlsx
+++ b/data/GOOGL_data.xlsx
@@ -4949,7 +4949,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:20:25</t>
+          <t>2026-09-06 22:41:19</t>
         </is>
       </c>
     </row>

--- a/data/GOOGL_data.xlsx
+++ b/data/GOOGL_data.xlsx
@@ -4949,7 +4949,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:41:19</t>
+          <t>2026-09-06 22:59:14</t>
         </is>
       </c>
     </row>

--- a/data/GOOGL_data.xlsx
+++ b/data/GOOGL_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46239</v>
+        <v>45905</v>
       </c>
       <c r="B2" t="n">
-        <v>383.0937455186354</v>
+        <v>231.3907550155185</v>
       </c>
       <c r="C2" t="n">
-        <v>384.2330278418686</v>
+        <v>234.9383456001989</v>
       </c>
       <c r="D2" t="n">
-        <v>356.5408062961898</v>
+        <v>231.091797506623</v>
       </c>
       <c r="E2" t="n">
-        <v>362.1971740722656</v>
+        <v>234.1809997558594</v>
       </c>
       <c r="F2" t="n">
-        <v>46926300</v>
+        <v>46588900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,25 +495,25 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46240</v>
+        <v>45908</v>
       </c>
       <c r="B3" t="n">
-        <v>360.5382517887205</v>
+        <v>234.8592056813389</v>
       </c>
       <c r="C3" t="n">
-        <v>363.8961093831237</v>
+        <v>237.512309448077</v>
       </c>
       <c r="D3" t="n">
-        <v>356.6507663527499</v>
+        <v>233.0638717332001</v>
       </c>
       <c r="E3" t="n">
-        <v>357.5202026367188</v>
+        <v>233.4329071044922</v>
       </c>
       <c r="F3" t="n">
-        <v>25235900</v>
+        <v>32474700</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46241</v>
+        <v>45909</v>
       </c>
       <c r="B4" t="n">
-        <v>356.4908465215469</v>
+        <v>233.5625640692738</v>
       </c>
       <c r="C4" t="n">
-        <v>358.6694387836589</v>
+        <v>239.8462249904786</v>
       </c>
       <c r="D4" t="n">
-        <v>353.5527327193329</v>
+        <v>232.6249999826575</v>
       </c>
       <c r="E4" t="n">
-        <v>354.0723876953125</v>
+        <v>239.0084075927734</v>
       </c>
       <c r="F4" t="n">
-        <v>19859900</v>
+        <v>38061000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46244</v>
+        <v>45910</v>
       </c>
       <c r="B5" t="n">
-        <v>354.951850943437</v>
+        <v>238.2803024247839</v>
       </c>
       <c r="C5" t="n">
-        <v>357.3802827690857</v>
+        <v>241.0331528996711</v>
       </c>
       <c r="D5" t="n">
-        <v>352.4834362714388</v>
+        <v>237.2330382337294</v>
       </c>
       <c r="E5" t="n">
-        <v>357.2903442382812</v>
+        <v>238.5496063232422</v>
       </c>
       <c r="F5" t="n">
-        <v>18991400</v>
+        <v>35141100</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46245</v>
+        <v>45911</v>
       </c>
       <c r="B6" t="n">
-        <v>355.6613923515014</v>
+        <v>239.2577712479691</v>
       </c>
       <c r="C6" t="n">
-        <v>356.5807842683805</v>
+        <v>241.6216187469878</v>
       </c>
       <c r="D6" t="n">
-        <v>343.1694223006263</v>
+        <v>235.6371823693535</v>
       </c>
       <c r="E6" t="n">
-        <v>343.5791320800781</v>
+        <v>239.7464904785156</v>
       </c>
       <c r="F6" t="n">
-        <v>29081800</v>
+        <v>30599300</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46246</v>
+        <v>45912</v>
       </c>
       <c r="B7" t="n">
-        <v>346.0875456512855</v>
+        <v>239.7464919977143</v>
       </c>
       <c r="C7" t="n">
-        <v>346.2574498710514</v>
+        <v>241.4520630725996</v>
       </c>
       <c r="D7" t="n">
-        <v>340.661040926288</v>
+        <v>237.3826444837165</v>
       </c>
       <c r="E7" t="n">
-        <v>343.3193359375</v>
+        <v>240.1753845214844</v>
       </c>
       <c r="F7" t="n">
-        <v>25012000</v>
+        <v>26771600</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46247</v>
+        <v>45915</v>
       </c>
       <c r="B8" t="n">
-        <v>345.5478948342235</v>
+        <v>244.0253822711298</v>
       </c>
       <c r="C8" t="n">
-        <v>347.7065110877775</v>
+        <v>251.7552796155814</v>
       </c>
       <c r="D8" t="n">
-        <v>343.5392066313974</v>
+        <v>244.0253822711298</v>
       </c>
       <c r="E8" t="n">
-        <v>346.1375122070312</v>
+        <v>250.9573516845703</v>
       </c>
       <c r="F8" t="n">
-        <v>17866100</v>
+        <v>58383800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46248</v>
+        <v>45916</v>
       </c>
       <c r="B9" t="n">
-        <v>346.5772111705174</v>
+        <v>251.4261108558069</v>
       </c>
       <c r="C9" t="n">
-        <v>350.2248908898295</v>
+        <v>252.3836121103763</v>
       </c>
       <c r="D9" t="n">
-        <v>344.2787008387085</v>
+        <v>248.8228805399337</v>
       </c>
       <c r="E9" t="n">
-        <v>345.6777954101562</v>
+        <v>250.5084991455078</v>
       </c>
       <c r="F9" t="n">
-        <v>17808600</v>
+        <v>34109700</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46251</v>
+        <v>45917</v>
       </c>
       <c r="B10" t="n">
-        <v>346.0475530411078</v>
+        <v>250.5683549046871</v>
       </c>
       <c r="C10" t="n">
-        <v>347.0269344906474</v>
+        <v>250.9473740826164</v>
       </c>
       <c r="D10" t="n">
-        <v>341.7103446182459</v>
+        <v>245.6411664684413</v>
       </c>
       <c r="E10" t="n">
-        <v>343.7790222167969</v>
+        <v>248.8827362060547</v>
       </c>
       <c r="F10" t="n">
-        <v>18291300</v>
+        <v>34108000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46252</v>
+        <v>45918</v>
       </c>
       <c r="B11" t="n">
-        <v>342.1900536360575</v>
+        <v>251.0271530076639</v>
       </c>
       <c r="C11" t="n">
-        <v>344.6484648943574</v>
+        <v>253.3311738191467</v>
       </c>
       <c r="D11" t="n">
-        <v>339.9714784523309</v>
+        <v>249.1520399405299</v>
       </c>
       <c r="E11" t="n">
-        <v>343.9789123535156</v>
+        <v>251.3762512207031</v>
       </c>
       <c r="F11" t="n">
-        <v>19248800</v>
+        <v>31239500</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46253</v>
+        <v>45919</v>
       </c>
       <c r="B12" t="n">
-        <v>342.2400076559886</v>
+        <v>252.5930922260568</v>
       </c>
       <c r="C12" t="n">
-        <v>346.5072842825429</v>
+        <v>255.3359589728353</v>
       </c>
       <c r="D12" t="n">
-        <v>340.4411761094805</v>
+        <v>251.1568250217611</v>
       </c>
       <c r="E12" t="n">
-        <v>344.4985656738281</v>
+        <v>254.0592803955078</v>
       </c>
       <c r="F12" t="n">
-        <v>19733800</v>
+        <v>55571400</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46254</v>
+        <v>45922</v>
       </c>
       <c r="B13" t="n">
-        <v>342.8396207141765</v>
+        <v>253.7700350469374</v>
       </c>
       <c r="C13" t="n">
-        <v>343.6790774504127</v>
+        <v>255.1165394138156</v>
       </c>
       <c r="D13" t="n">
-        <v>338.3525147854226</v>
+        <v>249.6507580677981</v>
       </c>
       <c r="E13" t="n">
-        <v>340.451171875</v>
+        <v>251.8749694824219</v>
       </c>
       <c r="F13" t="n">
-        <v>18570400</v>
+        <v>32290500</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46255</v>
+        <v>45923</v>
       </c>
       <c r="B14" t="n">
-        <v>342.359928876986</v>
+        <v>252.38362744671</v>
       </c>
       <c r="C14" t="n">
-        <v>345.9776291730591</v>
+        <v>253.7002107757565</v>
       </c>
       <c r="D14" t="n">
-        <v>340.1813365286692</v>
+        <v>249.8302703204236</v>
       </c>
       <c r="E14" t="n">
-        <v>344.5985107421875</v>
+        <v>251.0072174072266</v>
       </c>
       <c r="F14" t="n">
-        <v>20849800</v>
+        <v>26628000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46258</v>
+        <v>45924</v>
       </c>
       <c r="B15" t="n">
-        <v>343.3992753172161</v>
+        <v>251.0072270537175</v>
       </c>
       <c r="C15" t="n">
-        <v>351.3741604480826</v>
+        <v>251.6954397095125</v>
       </c>
       <c r="D15" t="n">
-        <v>342.2699962782288</v>
+        <v>245.8007659055053</v>
       </c>
       <c r="E15" t="n">
-        <v>347.83642578125</v>
+        <v>246.4989471435547</v>
       </c>
       <c r="F15" t="n">
-        <v>26338200</v>
+        <v>28201000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46259</v>
+        <v>45925</v>
       </c>
       <c r="B16" t="n">
-        <v>349.4154232615459</v>
+        <v>243.76602627878</v>
       </c>
       <c r="C16" t="n">
-        <v>349.9350782600912</v>
+        <v>245.8506164364007</v>
       </c>
       <c r="D16" t="n">
-        <v>345.3780098175396</v>
+        <v>240.1155317960277</v>
       </c>
       <c r="E16" t="n">
-        <v>346.7371215820312</v>
+        <v>245.1524200439453</v>
       </c>
       <c r="F16" t="n">
-        <v>20649700</v>
+        <v>31020400</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46260</v>
+        <v>45926</v>
       </c>
       <c r="B17" t="n">
-        <v>346.3973312516375</v>
+        <v>246.429136680309</v>
       </c>
       <c r="C17" t="n">
-        <v>346.6571739906042</v>
+        <v>248.7730319241888</v>
       </c>
       <c r="D17" t="n">
-        <v>339.9614657782595</v>
+        <v>245.3319838637119</v>
       </c>
       <c r="E17" t="n">
-        <v>341.7803039550781</v>
+        <v>245.9004974365234</v>
       </c>
       <c r="F17" t="n">
-        <v>20420300</v>
+        <v>18503200</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46261</v>
+        <v>45929</v>
       </c>
       <c r="B18" t="n">
-        <v>339.4518318672431</v>
+        <v>247.2070923961575</v>
       </c>
       <c r="C18" t="n">
-        <v>341.4705233735174</v>
+        <v>250.4985201433971</v>
       </c>
       <c r="D18" t="n">
-        <v>338.3025461528343</v>
+        <v>242.1402679011131</v>
       </c>
       <c r="E18" t="n">
-        <v>340.4311828613281</v>
+        <v>243.4169464111328</v>
       </c>
       <c r="F18" t="n">
-        <v>23391400</v>
+        <v>32505800</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46262</v>
+        <v>45930</v>
       </c>
       <c r="B19" t="n">
-        <v>340.4911426360338</v>
+        <v>242.1801651040411</v>
       </c>
       <c r="C19" t="n">
-        <v>348.9157509584863</v>
+        <v>242.6589157556348</v>
       </c>
       <c r="D19" t="n">
-        <v>340.0514228221321</v>
+        <v>238.6294019345709</v>
       </c>
       <c r="E19" t="n">
-        <v>346.3673706054688</v>
+        <v>242.4694213867188</v>
       </c>
       <c r="F19" t="n">
-        <v>25347200</v>
+        <v>34724300</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46265</v>
+        <v>45931</v>
       </c>
       <c r="B20" t="n">
-        <v>343.609121722545</v>
+        <v>240.125510895299</v>
       </c>
       <c r="C20" t="n">
-        <v>344.3686432833908</v>
+        <v>245.661117617101</v>
       </c>
       <c r="D20" t="n">
-        <v>336.943423385668</v>
+        <v>237.9910625183314</v>
       </c>
       <c r="E20" t="n">
-        <v>339.1320190429688</v>
+        <v>244.2647399902344</v>
       </c>
       <c r="F20" t="n">
-        <v>33493600</v>
+        <v>31658200</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46266</v>
+        <v>45932</v>
       </c>
       <c r="B21" t="n">
-        <v>335.7841605001305</v>
+        <v>244.5140808226371</v>
       </c>
       <c r="C21" t="n">
-        <v>336.9834018439635</v>
+        <v>246.1697784759451</v>
       </c>
       <c r="D21" t="n">
-        <v>332.8360433203593</v>
+        <v>241.6714827842888</v>
       </c>
       <c r="E21" t="n">
-        <v>334.8047790527344</v>
+        <v>245.0526885986328</v>
       </c>
       <c r="F21" t="n">
-        <v>23342700</v>
+        <v>25483300</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46267</v>
+        <v>45933</v>
       </c>
       <c r="B22" t="n">
-        <v>333.845410447285</v>
+        <v>243.8558378805103</v>
       </c>
       <c r="C22" t="n">
-        <v>339.7815972628325</v>
+        <v>245.6611405975774</v>
       </c>
       <c r="D22" t="n">
-        <v>332.6062167342666</v>
+        <v>241.0331766174326</v>
       </c>
       <c r="E22" t="n">
-        <v>336.9034423828125</v>
+        <v>244.7136077880859</v>
       </c>
       <c r="F22" t="n">
-        <v>22582300</v>
+        <v>30249600</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46268</v>
+        <v>45936</v>
       </c>
       <c r="B23" t="n">
-        <v>340.3412297100126</v>
+        <v>244.145057284137</v>
       </c>
       <c r="C23" t="n">
-        <v>344.4585782378343</v>
+        <v>250.6681015230512</v>
       </c>
       <c r="D23" t="n">
-        <v>339.841550898423</v>
+        <v>243.9455791134174</v>
       </c>
       <c r="E23" t="n">
-        <v>342.260009765625</v>
+        <v>249.7803955078125</v>
       </c>
       <c r="F23" t="n">
-        <v>20726900</v>
+        <v>28894700</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,27 +1041,5981 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B24" t="n">
+        <v>247.6260272338786</v>
+      </c>
+      <c r="C24" t="n">
+        <v>249.7903967365714</v>
+      </c>
+      <c r="D24" t="n">
+        <v>244.8831603422913</v>
+      </c>
+      <c r="E24" t="n">
+        <v>245.1225280761719</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23181300</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B25" t="n">
+        <v>244.3245879910796</v>
+      </c>
+      <c r="C25" t="n">
+        <v>245.3718521480096</v>
+      </c>
+      <c r="D25" t="n">
+        <v>243.1875457247831</v>
+      </c>
+      <c r="E25" t="n">
+        <v>243.9854583740234</v>
+      </c>
+      <c r="F25" t="n">
+        <v>21307100</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B26" t="n">
+        <v>243.8358644557508</v>
+      </c>
+      <c r="C26" t="n">
+        <v>244.1251055211473</v>
+      </c>
+      <c r="D26" t="n">
+        <v>238.5296568297252</v>
+      </c>
+      <c r="E26" t="n">
+        <v>240.9034881591797</v>
+      </c>
+      <c r="F26" t="n">
+        <v>27892100</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B27" t="n">
+        <v>240.8037387238312</v>
+      </c>
+      <c r="C27" t="n">
+        <v>243.4568425066541</v>
+      </c>
+      <c r="D27" t="n">
+        <v>235.2282424787384</v>
+      </c>
+      <c r="E27" t="n">
+        <v>235.9563598632812</v>
+      </c>
+      <c r="F27" t="n">
+        <v>33180300</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B28" t="n">
+        <v>239.5869258671789</v>
+      </c>
+      <c r="C28" t="n">
+        <v>243.8657913377574</v>
+      </c>
+      <c r="D28" t="n">
+        <v>239.0882228174084</v>
+      </c>
+      <c r="E28" t="n">
+        <v>243.5166931152344</v>
+      </c>
+      <c r="F28" t="n">
+        <v>24995000</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B29" t="n">
+        <v>240.6042690189676</v>
+      </c>
+      <c r="C29" t="n">
+        <v>246.4789903337629</v>
+      </c>
+      <c r="D29" t="n">
+        <v>239.8861354100955</v>
+      </c>
+      <c r="E29" t="n">
+        <v>244.8133239746094</v>
+      </c>
+      <c r="F29" t="n">
+        <v>22111600</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B30" t="n">
+        <v>246.6086514775368</v>
+      </c>
+      <c r="C30" t="n">
+        <v>251.4560455996756</v>
+      </c>
+      <c r="D30" t="n">
+        <v>245.3519253048375</v>
+      </c>
+      <c r="E30" t="n">
+        <v>250.3788452148438</v>
+      </c>
+      <c r="F30" t="n">
+        <v>27007700</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B31" t="n">
+        <v>251.1169327071502</v>
+      </c>
+      <c r="C31" t="n">
+        <v>256.2934574717041</v>
+      </c>
+      <c r="D31" t="n">
+        <v>249.4512663819502</v>
+      </c>
+      <c r="E31" t="n">
+        <v>250.8077392578125</v>
+      </c>
+      <c r="F31" t="n">
+        <v>27997200</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B32" t="n">
+        <v>250.1095547697768</v>
+      </c>
+      <c r="C32" t="n">
+        <v>253.5605866634714</v>
+      </c>
+      <c r="D32" t="n">
+        <v>247.1672097408255</v>
+      </c>
+      <c r="E32" t="n">
+        <v>252.6429748535156</v>
+      </c>
+      <c r="F32" t="n">
+        <v>29671600</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B33" t="n">
+        <v>254.0293759063695</v>
+      </c>
+      <c r="C33" t="n">
+        <v>256.6625123260812</v>
+      </c>
+      <c r="D33" t="n">
+        <v>253.5705623788801</v>
+      </c>
+      <c r="E33" t="n">
+        <v>255.8845367431641</v>
+      </c>
+      <c r="F33" t="n">
+        <v>22350200</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B34" t="n">
+        <v>254.079230052693</v>
+      </c>
+      <c r="C34" t="n">
+        <v>254.2188662949897</v>
+      </c>
+      <c r="D34" t="n">
+        <v>243.5166881090968</v>
+      </c>
+      <c r="E34" t="n">
+        <v>249.8103332519531</v>
+      </c>
+      <c r="F34" t="n">
+        <v>47312100</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B35" t="n">
+        <v>253.7101963156115</v>
+      </c>
+      <c r="C35" t="n">
+        <v>255.6950248045094</v>
+      </c>
+      <c r="D35" t="n">
+        <v>248.6433712710665</v>
+      </c>
+      <c r="E35" t="n">
+        <v>251.0371551513672</v>
+      </c>
+      <c r="F35" t="n">
+        <v>35029400</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B36" t="n">
+        <v>252.3237915100895</v>
+      </c>
+      <c r="C36" t="n">
+        <v>254.3784456458486</v>
+      </c>
+      <c r="D36" t="n">
+        <v>251.196732963501</v>
+      </c>
+      <c r="E36" t="n">
+        <v>252.4235382080078</v>
+      </c>
+      <c r="F36" t="n">
+        <v>19901400</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B37" t="n">
+        <v>255.9144256499636</v>
+      </c>
+      <c r="C37" t="n">
+        <v>261.0012024879728</v>
+      </c>
+      <c r="D37" t="n">
+        <v>254.6577147509474</v>
+      </c>
+      <c r="E37" t="n">
+        <v>259.2457885742188</v>
+      </c>
+      <c r="F37" t="n">
+        <v>28655100</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B38" t="n">
+        <v>264.1330942614516</v>
+      </c>
+      <c r="C38" t="n">
+        <v>269.4393020900735</v>
+      </c>
+      <c r="D38" t="n">
+        <v>263.5944864374467</v>
+      </c>
+      <c r="E38" t="n">
+        <v>268.571533203125</v>
+      </c>
+      <c r="F38" t="n">
+        <v>35235200</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B39" t="n">
+        <v>268.9904266199372</v>
+      </c>
+      <c r="C39" t="n">
+        <v>270.0277373828665</v>
+      </c>
+      <c r="D39" t="n">
+        <v>265.8086990443333</v>
+      </c>
+      <c r="E39" t="n">
+        <v>266.7761840820312</v>
+      </c>
+      <c r="F39" t="n">
+        <v>29738600</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B40" t="n">
+        <v>267.055471479175</v>
+      </c>
+      <c r="C40" t="n">
+        <v>274.6257797911847</v>
+      </c>
+      <c r="D40" t="n">
+        <v>266.975692387603</v>
+      </c>
+      <c r="E40" t="n">
+        <v>273.8577880859375</v>
+      </c>
+      <c r="F40" t="n">
+        <v>43580300</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B41" t="n">
+        <v>290.8336389163956</v>
+      </c>
+      <c r="C41" t="n">
+        <v>290.8336389163956</v>
+      </c>
+      <c r="D41" t="n">
+        <v>279.3335478851562</v>
+      </c>
+      <c r="E41" t="n">
+        <v>280.7498779296875</v>
+      </c>
+      <c r="F41" t="n">
+        <v>74876000</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B42" t="n">
+        <v>282.4753817503845</v>
+      </c>
+      <c r="C42" t="n">
+        <v>285.2581533777714</v>
+      </c>
+      <c r="D42" t="n">
+        <v>276.3114191679317</v>
+      </c>
+      <c r="E42" t="n">
+        <v>280.4606323242188</v>
+      </c>
+      <c r="F42" t="n">
+        <v>39267900</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B43" t="n">
+        <v>281.4480558536455</v>
+      </c>
+      <c r="C43" t="n">
+        <v>284.7893724933962</v>
+      </c>
+      <c r="D43" t="n">
+        <v>279.0742243823285</v>
+      </c>
+      <c r="E43" t="n">
+        <v>282.9840698242188</v>
+      </c>
+      <c r="F43" t="n">
+        <v>29786000</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B44" t="n">
+        <v>276.0321395313242</v>
+      </c>
+      <c r="C44" t="n">
+        <v>280.5404041676455</v>
+      </c>
+      <c r="D44" t="n">
+        <v>275.5434202802167</v>
+      </c>
+      <c r="E44" t="n">
+        <v>276.8200988769531</v>
+      </c>
+      <c r="F44" t="n">
+        <v>30078400</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B45" t="n">
+        <v>278.1466184544242</v>
+      </c>
+      <c r="C45" t="n">
+        <v>285.677052345188</v>
+      </c>
+      <c r="D45" t="n">
+        <v>276.62058842555</v>
+      </c>
+      <c r="E45" t="n">
+        <v>283.572509765625</v>
+      </c>
+      <c r="F45" t="n">
+        <v>31010300</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B46" t="n">
+        <v>284.5898651937554</v>
+      </c>
+      <c r="C46" t="n">
+        <v>287.6020510547858</v>
+      </c>
+      <c r="D46" t="n">
+        <v>280.4107616957575</v>
+      </c>
+      <c r="E46" t="n">
+        <v>284.0113830566406</v>
+      </c>
+      <c r="F46" t="n">
+        <v>37173600</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B47" t="n">
+        <v>282.4753944065927</v>
+      </c>
+      <c r="C47" t="n">
+        <v>283.0439232317803</v>
+      </c>
+      <c r="D47" t="n">
+        <v>274.4762078378772</v>
+      </c>
+      <c r="E47" t="n">
+        <v>278.1067504882812</v>
+      </c>
+      <c r="F47" t="n">
+        <v>34479600</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B48" t="n">
+        <v>283.6822445549795</v>
+      </c>
+      <c r="C48" t="n">
+        <v>290.0456696400176</v>
+      </c>
+      <c r="D48" t="n">
+        <v>282.1262631003564</v>
+      </c>
+      <c r="E48" t="n">
+        <v>289.3475036621094</v>
+      </c>
+      <c r="F48" t="n">
+        <v>29557300</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B49" t="n">
+        <v>287.0035887304013</v>
+      </c>
+      <c r="C49" t="n">
+        <v>291.1627853205446</v>
+      </c>
+      <c r="D49" t="n">
+        <v>286.5747114373448</v>
+      </c>
+      <c r="E49" t="n">
+        <v>290.5543518066406</v>
+      </c>
+      <c r="F49" t="n">
+        <v>19842100</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B50" t="n">
+        <v>290.9234183741868</v>
+      </c>
+      <c r="C50" t="n">
+        <v>291.2525794490294</v>
+      </c>
+      <c r="D50" t="n">
+        <v>282.9541529801612</v>
+      </c>
+      <c r="E50" t="n">
+        <v>285.96630859375</v>
+      </c>
+      <c r="F50" t="n">
+        <v>24829900</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B51" t="n">
+        <v>281.6076529103283</v>
+      </c>
+      <c r="C51" t="n">
+        <v>282.1063559927165</v>
+      </c>
+      <c r="D51" t="n">
+        <v>276.5208753822851</v>
+      </c>
+      <c r="E51" t="n">
+        <v>277.8474426269531</v>
+      </c>
+      <c r="F51" t="n">
+        <v>29494000</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B52" t="n">
+        <v>270.705963217399</v>
+      </c>
+      <c r="C52" t="n">
+        <v>277.8374099534448</v>
+      </c>
+      <c r="D52" t="n">
+        <v>269.997813487729</v>
+      </c>
+      <c r="E52" t="n">
+        <v>275.6929931640625</v>
+      </c>
+      <c r="F52" t="n">
+        <v>31647200</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B53" t="n">
+        <v>285.0387085276487</v>
+      </c>
+      <c r="C53" t="n">
+        <v>293.1875295999499</v>
+      </c>
+      <c r="D53" t="n">
+        <v>282.8344496120375</v>
+      </c>
+      <c r="E53" t="n">
+        <v>284.2806701660156</v>
+      </c>
+      <c r="F53" t="n">
+        <v>52670200</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B54" t="n">
+        <v>287.1731753233953</v>
+      </c>
+      <c r="C54" t="n">
+        <v>288.0508671158451</v>
+      </c>
+      <c r="D54" t="n">
+        <v>277.4783868942568</v>
+      </c>
+      <c r="E54" t="n">
+        <v>283.5426025390625</v>
+      </c>
+      <c r="F54" t="n">
+        <v>49158700</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B55" t="n">
+        <v>286.4151377283875</v>
+      </c>
+      <c r="C55" t="n">
+        <v>303.0219431129204</v>
+      </c>
+      <c r="D55" t="n">
+        <v>285.8865137158778</v>
+      </c>
+      <c r="E55" t="n">
+        <v>292.0504760742188</v>
+      </c>
+      <c r="F55" t="n">
+        <v>68198900</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B56" t="n">
+        <v>303.7500416076266</v>
+      </c>
+      <c r="C56" t="n">
+        <v>305.625169818548</v>
+      </c>
+      <c r="D56" t="n">
+        <v>287.9212127447435</v>
+      </c>
+      <c r="E56" t="n">
+        <v>288.6991882324219</v>
+      </c>
+      <c r="F56" t="n">
+        <v>62025200</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B57" t="n">
+        <v>295.6511348655125</v>
+      </c>
+      <c r="C57" t="n">
+        <v>303.1316807498811</v>
+      </c>
+      <c r="D57" t="n">
+        <v>293.0877938372482</v>
+      </c>
+      <c r="E57" t="n">
+        <v>298.8827209472656</v>
+      </c>
+      <c r="F57" t="n">
+        <v>74137700</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B58" t="n">
+        <v>310.3229443803346</v>
+      </c>
+      <c r="C58" t="n">
+        <v>318.651290855991</v>
+      </c>
+      <c r="D58" t="n">
+        <v>308.796914365105</v>
+      </c>
+      <c r="E58" t="n">
+        <v>317.7536010742188</v>
+      </c>
+      <c r="F58" t="n">
+        <v>85165100</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B59" t="n">
+        <v>325.3638169665917</v>
+      </c>
+      <c r="C59" t="n">
+        <v>327.9770159307299</v>
+      </c>
+      <c r="D59" t="n">
+        <v>316.826023668276</v>
+      </c>
+      <c r="E59" t="n">
+        <v>322.6010131835938</v>
+      </c>
+      <c r="F59" t="n">
+        <v>88632100</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B60" t="n">
+        <v>319.8481736259059</v>
+      </c>
+      <c r="C60" t="n">
+        <v>323.6582721471574</v>
+      </c>
+      <c r="D60" t="n">
+        <v>315.9682798124272</v>
+      </c>
+      <c r="E60" t="n">
+        <v>319.1200866699219</v>
+      </c>
+      <c r="F60" t="n">
+        <v>51373400</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B61" t="n">
+        <v>322.5311844719001</v>
+      </c>
+      <c r="C61" t="n">
+        <v>326.0021684294219</v>
+      </c>
+      <c r="D61" t="n">
+        <v>315.9682661584897</v>
+      </c>
+      <c r="E61" t="n">
+        <v>319.3494567871094</v>
+      </c>
+      <c r="F61" t="n">
+        <v>26018600</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B62" t="n">
+        <v>316.8759510785769</v>
+      </c>
+      <c r="C62" t="n">
+        <v>319.020368247556</v>
+      </c>
+      <c r="D62" t="n">
+        <v>313.0758360216101</v>
+      </c>
+      <c r="E62" t="n">
+        <v>314.0732421875</v>
+      </c>
+      <c r="F62" t="n">
+        <v>41183000</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B63" t="n">
+        <v>315.9184251730286</v>
+      </c>
+      <c r="C63" t="n">
+        <v>317.5541859262309</v>
+      </c>
+      <c r="D63" t="n">
+        <v>313.095779063488</v>
+      </c>
+      <c r="E63" t="n">
+        <v>314.9908447265625</v>
+      </c>
+      <c r="F63" t="n">
+        <v>35854700</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B64" t="n">
+        <v>315.0706445626379</v>
+      </c>
+      <c r="C64" t="n">
+        <v>320.7458575749233</v>
+      </c>
+      <c r="D64" t="n">
+        <v>313.2852790244178</v>
+      </c>
+      <c r="E64" t="n">
+        <v>318.8009338378906</v>
+      </c>
+      <c r="F64" t="n">
+        <v>41838300</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B65" t="n">
+        <v>321.3941698854088</v>
+      </c>
+      <c r="C65" t="n">
+        <v>321.5238071066378</v>
+      </c>
+      <c r="D65" t="n">
+        <v>313.8837033726762</v>
+      </c>
+      <c r="E65" t="n">
+        <v>316.7961120605469</v>
+      </c>
+      <c r="F65" t="n">
+        <v>31240900</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B66" t="n">
+        <v>318.6612638744486</v>
+      </c>
+      <c r="C66" t="n">
+        <v>322.3217576397153</v>
+      </c>
+      <c r="D66" t="n">
+        <v>318.3421170569229</v>
+      </c>
+      <c r="E66" t="n">
+        <v>320.4366455078125</v>
+      </c>
+      <c r="F66" t="n">
+        <v>28851700</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B67" t="n">
+        <v>319.4285975207571</v>
+      </c>
+      <c r="C67" t="n">
+        <v>319.8178549396436</v>
+      </c>
+      <c r="D67" t="n">
+        <v>310.6157547321785</v>
+      </c>
+      <c r="E67" t="n">
+        <v>313.1109008789062</v>
+      </c>
+      <c r="F67" t="n">
+        <v>33909400</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B68" t="n">
+        <v>311.7635388280278</v>
+      </c>
+      <c r="C68" t="n">
+        <v>317.3726229056239</v>
+      </c>
+      <c r="D68" t="n">
+        <v>311.2944500995635</v>
+      </c>
+      <c r="E68" t="n">
+        <v>316.4643859863281</v>
+      </c>
+      <c r="F68" t="n">
+        <v>30194000</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B69" t="n">
+        <v>315.2168165746965</v>
+      </c>
+      <c r="C69" t="n">
+        <v>320.6861883612462</v>
+      </c>
+      <c r="D69" t="n">
+        <v>314.069055340672</v>
+      </c>
+      <c r="E69" t="n">
+        <v>319.5883178710938</v>
+      </c>
+      <c r="F69" t="n">
+        <v>33428900</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B70" t="n">
+        <v>319.4585671045538</v>
+      </c>
+      <c r="C70" t="n">
+        <v>320.4965565243085</v>
+      </c>
+      <c r="D70" t="n">
+        <v>308.0008744502611</v>
+      </c>
+      <c r="E70" t="n">
+        <v>311.8234252929688</v>
+      </c>
+      <c r="F70" t="n">
+        <v>42353700</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B71" t="n">
+        <v>313.0909556884665</v>
+      </c>
+      <c r="C71" t="n">
+        <v>314.2586670471713</v>
+      </c>
+      <c r="D71" t="n">
+        <v>304.9667450846255</v>
+      </c>
+      <c r="E71" t="n">
+        <v>308.6895141601562</v>
+      </c>
+      <c r="F71" t="n">
+        <v>35940200</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B72" t="n">
+        <v>310.7156001962807</v>
+      </c>
+      <c r="C72" t="n">
+        <v>310.8154121445851</v>
+      </c>
+      <c r="D72" t="n">
+        <v>304.2881005921093</v>
+      </c>
+      <c r="E72" t="n">
+        <v>307.6216125488281</v>
+      </c>
+      <c r="F72" t="n">
+        <v>29151900</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B73" t="n">
+        <v>304.3579426322819</v>
+      </c>
+      <c r="C73" t="n">
+        <v>310.1666197797816</v>
+      </c>
+      <c r="D73" t="n">
+        <v>302.0025088045779</v>
+      </c>
+      <c r="E73" t="n">
+        <v>305.9747924804688</v>
+      </c>
+      <c r="F73" t="n">
+        <v>30585000</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B74" t="n">
+        <v>307.4120099511304</v>
+      </c>
+      <c r="C74" t="n">
+        <v>307.4918412298865</v>
+      </c>
+      <c r="D74" t="n">
+        <v>295.5450797036171</v>
+      </c>
+      <c r="E74" t="n">
+        <v>296.1439208984375</v>
+      </c>
+      <c r="F74" t="n">
+        <v>43930400</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B75" t="n">
+        <v>301.1342186567393</v>
+      </c>
+      <c r="C75" t="n">
+        <v>303.3698600006946</v>
+      </c>
+      <c r="D75" t="n">
+        <v>298.6490626821344</v>
+      </c>
+      <c r="E75" t="n">
+        <v>301.8727722167969</v>
+      </c>
+      <c r="F75" t="n">
+        <v>33518000</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B76" t="n">
+        <v>301.1442091965169</v>
+      </c>
+      <c r="C76" t="n">
+        <v>306.6534812800651</v>
+      </c>
+      <c r="D76" t="n">
+        <v>300.3856749721532</v>
+      </c>
+      <c r="E76" t="n">
+        <v>306.5636596679688</v>
+      </c>
+      <c r="F76" t="n">
+        <v>59943200</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B77" t="n">
+        <v>309.278400817878</v>
+      </c>
+      <c r="C77" t="n">
+        <v>309.5279154654388</v>
+      </c>
+      <c r="D77" t="n">
+        <v>304.707275417899</v>
+      </c>
+      <c r="E77" t="n">
+        <v>309.1785888671875</v>
+      </c>
+      <c r="F77" t="n">
+        <v>26429900</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B78" t="n">
+        <v>309.0288478780406</v>
+      </c>
+      <c r="C78" t="n">
+        <v>314.328535898872</v>
+      </c>
+      <c r="D78" t="n">
+        <v>308.7194521900694</v>
+      </c>
+      <c r="E78" t="n">
+        <v>313.7396850585938</v>
+      </c>
+      <c r="F78" t="n">
+        <v>25478700</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B79" t="n">
+        <v>314.1588359856885</v>
+      </c>
+      <c r="C79" t="n">
+        <v>314.4682316573388</v>
+      </c>
+      <c r="D79" t="n">
+        <v>311.3143938726672</v>
+      </c>
+      <c r="E79" t="n">
+        <v>313.4801635742188</v>
+      </c>
+      <c r="F79" t="n">
+        <v>10097400</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B80" t="n">
+        <v>313.8694852656387</v>
+      </c>
+      <c r="C80" t="n">
+        <v>314.4782864028367</v>
+      </c>
+      <c r="D80" t="n">
+        <v>311.6737441219225</v>
+      </c>
+      <c r="E80" t="n">
+        <v>312.9013671875</v>
+      </c>
+      <c r="F80" t="n">
+        <v>10899000</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B81" t="n">
+        <v>310.7655125785055</v>
+      </c>
+      <c r="C81" t="n">
+        <v>313.410361871903</v>
+      </c>
+      <c r="D81" t="n">
+        <v>310.0169686016006</v>
+      </c>
+      <c r="E81" t="n">
+        <v>312.9512634277344</v>
+      </c>
+      <c r="F81" t="n">
+        <v>19621800</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B82" t="n">
+        <v>311.8932765746258</v>
+      </c>
+      <c r="C82" t="n">
+        <v>316.3346490163796</v>
+      </c>
+      <c r="D82" t="n">
+        <v>311.8533457068925</v>
+      </c>
+      <c r="E82" t="n">
+        <v>313.2406616210938</v>
+      </c>
+      <c r="F82" t="n">
+        <v>17380900</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B83" t="n">
+        <v>312.2426007868329</v>
+      </c>
+      <c r="C83" t="n">
+        <v>313.9692224596297</v>
+      </c>
+      <c r="D83" t="n">
+        <v>310.8353346785167</v>
+      </c>
+      <c r="E83" t="n">
+        <v>312.3923034667969</v>
+      </c>
+      <c r="F83" t="n">
+        <v>16377700</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B84" t="n">
+        <v>316.2847187538463</v>
+      </c>
+      <c r="C84" t="n">
+        <v>321.87385220157</v>
+      </c>
+      <c r="D84" t="n">
+        <v>309.7274673850438</v>
+      </c>
+      <c r="E84" t="n">
+        <v>314.5381164550781</v>
+      </c>
+      <c r="F84" t="n">
+        <v>32009400</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B85" t="n">
+        <v>317.0432662013207</v>
+      </c>
+      <c r="C85" t="n">
+        <v>318.4006111389099</v>
+      </c>
+      <c r="D85" t="n">
+        <v>314.0191501700305</v>
+      </c>
+      <c r="E85" t="n">
+        <v>315.9254455566406</v>
+      </c>
+      <c r="F85" t="n">
+        <v>30195600</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B86" t="n">
+        <v>315.7857038876524</v>
+      </c>
+      <c r="C86" t="n">
+        <v>320.3168980142969</v>
+      </c>
+      <c r="D86" t="n">
+        <v>311.1746784825258</v>
+      </c>
+      <c r="E86" t="n">
+        <v>313.7297058105469</v>
+      </c>
+      <c r="F86" t="n">
+        <v>31212100</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B87" t="n">
+        <v>313.7496873061683</v>
+      </c>
+      <c r="C87" t="n">
+        <v>325.5168067446344</v>
+      </c>
+      <c r="D87" t="n">
+        <v>313.5800344006012</v>
+      </c>
+      <c r="E87" t="n">
+        <v>321.3549194335938</v>
+      </c>
+      <c r="F87" t="n">
+        <v>35104400</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B88" t="n">
+        <v>328.3313118537803</v>
+      </c>
+      <c r="C88" t="n">
+        <v>329.6786969446188</v>
+      </c>
+      <c r="D88" t="n">
+        <v>320.8758135066914</v>
+      </c>
+      <c r="E88" t="n">
+        <v>324.8081665039062</v>
+      </c>
+      <c r="F88" t="n">
+        <v>31896100</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B89" t="n">
+        <v>326.4549607998293</v>
+      </c>
+      <c r="C89" t="n">
+        <v>330.1876899539591</v>
+      </c>
+      <c r="D89" t="n">
+        <v>325.1674567682817</v>
+      </c>
+      <c r="E89" t="n">
+        <v>327.9320983886719</v>
+      </c>
+      <c r="F89" t="n">
+        <v>26214200</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B90" t="n">
+        <v>325.1674658209474</v>
+      </c>
+      <c r="C90" t="n">
+        <v>333.3914890456728</v>
+      </c>
+      <c r="D90" t="n">
+        <v>324.3690311583512</v>
+      </c>
+      <c r="E90" t="n">
+        <v>331.2156982421875</v>
+      </c>
+      <c r="F90" t="n">
+        <v>33923900</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B91" t="n">
+        <v>334.2996793666924</v>
+      </c>
+      <c r="C91" t="n">
+        <v>339.8289010736461</v>
+      </c>
+      <c r="D91" t="n">
+        <v>332.9722446137951</v>
+      </c>
+      <c r="E91" t="n">
+        <v>335.3176879882812</v>
+      </c>
+      <c r="F91" t="n">
+        <v>33517600</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B92" t="n">
+        <v>334.4094733641317</v>
+      </c>
+      <c r="C92" t="n">
+        <v>335.8666302231012</v>
+      </c>
+      <c r="D92" t="n">
+        <v>329.8383789070015</v>
+      </c>
+      <c r="E92" t="n">
+        <v>335.1879577636719</v>
+      </c>
+      <c r="F92" t="n">
+        <v>28525600</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B93" t="n">
+        <v>336.9944512235705</v>
+      </c>
+      <c r="C93" t="n">
+        <v>337.03438209247</v>
+      </c>
+      <c r="D93" t="n">
+        <v>330.097863235539</v>
+      </c>
+      <c r="E93" t="n">
+        <v>332.1339111328125</v>
+      </c>
+      <c r="F93" t="n">
+        <v>28442400</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B94" t="n">
+        <v>333.7607557246461</v>
+      </c>
+      <c r="C94" t="n">
+        <v>334.0002800245007</v>
+      </c>
+      <c r="D94" t="n">
+        <v>327.0637915356931</v>
+      </c>
+      <c r="E94" t="n">
+        <v>329.3593139648438</v>
+      </c>
+      <c r="F94" t="n">
+        <v>40341600</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B95" t="n">
+        <v>320.2470363972373</v>
+      </c>
+      <c r="C95" t="n">
+        <v>327.0937337673917</v>
+      </c>
+      <c r="D95" t="n">
+        <v>319.8078882063433</v>
+      </c>
+      <c r="E95" t="n">
+        <v>321.3748474121094</v>
+      </c>
+      <c r="F95" t="n">
+        <v>35361000</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B96" t="n">
+        <v>320.2969541162656</v>
+      </c>
+      <c r="C96" t="n">
+        <v>331.8345081879527</v>
+      </c>
+      <c r="D96" t="n">
+        <v>318.729994927537</v>
+      </c>
+      <c r="E96" t="n">
+        <v>327.7424621582031</v>
+      </c>
+      <c r="F96" t="n">
+        <v>35386600</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B97" t="n">
+        <v>333.8006666576773</v>
+      </c>
+      <c r="C97" t="n">
+        <v>334.4992893099707</v>
+      </c>
+      <c r="D97" t="n">
+        <v>328.1117212092731</v>
+      </c>
+      <c r="E97" t="n">
+        <v>329.8982543945312</v>
+      </c>
+      <c r="F97" t="n">
+        <v>26253600</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B98" t="n">
+        <v>331.8444485977197</v>
+      </c>
+      <c r="C98" t="n">
+        <v>333.0421309365838</v>
+      </c>
+      <c r="D98" t="n">
+        <v>326.8142558744754</v>
+      </c>
+      <c r="E98" t="n">
+        <v>327.2933044433594</v>
+      </c>
+      <c r="F98" t="n">
+        <v>27280000</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B99" t="n">
+        <v>327.1735452193246</v>
+      </c>
+      <c r="C99" t="n">
+        <v>335.1879535299186</v>
+      </c>
+      <c r="D99" t="n">
+        <v>326.3651202937951</v>
+      </c>
+      <c r="E99" t="n">
+        <v>332.6129760742188</v>
+      </c>
+      <c r="F99" t="n">
+        <v>26042100</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B100" t="n">
+        <v>334.7188669221849</v>
+      </c>
+      <c r="C100" t="n">
+        <v>337.2539439848537</v>
+      </c>
+      <c r="D100" t="n">
+        <v>332.8325522369338</v>
+      </c>
+      <c r="E100" t="n">
+        <v>333.9004516601562</v>
+      </c>
+      <c r="F100" t="n">
+        <v>21636200</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B101" t="n">
+        <v>335.4075262381039</v>
+      </c>
+      <c r="C101" t="n">
+        <v>336.8846637353836</v>
+      </c>
+      <c r="D101" t="n">
+        <v>331.2955302242731</v>
+      </c>
+      <c r="E101" t="n">
+        <v>335.3576354980469</v>
+      </c>
+      <c r="F101" t="n">
+        <v>27434400</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B102" t="n">
+        <v>339.6393000059441</v>
+      </c>
+      <c r="C102" t="n">
+        <v>341.625457159737</v>
+      </c>
+      <c r="D102" t="n">
+        <v>325.9060355700189</v>
+      </c>
+      <c r="E102" t="n">
+        <v>337.5932922363281</v>
+      </c>
+      <c r="F102" t="n">
+        <v>39785600</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B103" t="n">
+        <v>339.3398975620609</v>
+      </c>
+      <c r="C103" t="n">
+        <v>339.3398975620609</v>
+      </c>
+      <c r="D103" t="n">
+        <v>331.6448748839121</v>
+      </c>
+      <c r="E103" t="n">
+        <v>337.3437805175781</v>
+      </c>
+      <c r="F103" t="n">
+        <v>31024000</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B104" t="n">
+        <v>335.5672073695487</v>
+      </c>
+      <c r="C104" t="n">
+        <v>344.1604758527643</v>
+      </c>
+      <c r="D104" t="n">
+        <v>334.9783565494149</v>
+      </c>
+      <c r="E104" t="n">
+        <v>343.022705078125</v>
+      </c>
+      <c r="F104" t="n">
+        <v>32006100</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B105" t="n">
+        <v>346.6656368085559</v>
+      </c>
+      <c r="C105" t="n">
+        <v>348.322417578686</v>
+      </c>
+      <c r="D105" t="n">
+        <v>336.8148042563823</v>
+      </c>
+      <c r="E105" t="n">
+        <v>339.0504455566406</v>
+      </c>
+      <c r="F105" t="n">
+        <v>36506700</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B106" t="n">
+        <v>342.2941565134455</v>
+      </c>
+      <c r="C106" t="n">
+        <v>342.6434831024425</v>
+      </c>
+      <c r="D106" t="n">
+        <v>327.8821884154679</v>
+      </c>
+      <c r="E106" t="n">
+        <v>332.3934326171875</v>
+      </c>
+      <c r="F106" t="n">
+        <v>70618400</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B107" t="n">
+        <v>311.6138496060838</v>
+      </c>
+      <c r="C107" t="n">
+        <v>332.0441098613053</v>
+      </c>
+      <c r="D107" t="n">
+        <v>305.8650224655501</v>
+      </c>
+      <c r="E107" t="n">
+        <v>330.6069030761719</v>
+      </c>
+      <c r="F107" t="n">
+        <v>88205800</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B108" t="n">
+        <v>326.5447743483745</v>
+      </c>
+      <c r="C108" t="n">
+        <v>329.7385737476322</v>
+      </c>
+      <c r="D108" t="n">
+        <v>319.2988903139048</v>
+      </c>
+      <c r="E108" t="n">
+        <v>322.233154296875</v>
+      </c>
+      <c r="F108" t="n">
+        <v>56380500</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B109" t="n">
+        <v>320.3069052195784</v>
+      </c>
+      <c r="C109" t="n">
+        <v>327.0637807183464</v>
+      </c>
+      <c r="D109" t="n">
+        <v>316.6440476026885</v>
+      </c>
+      <c r="E109" t="n">
+        <v>323.6903381347656</v>
+      </c>
+      <c r="F109" t="n">
+        <v>39640100</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B110" t="n">
+        <v>320.3468306795893</v>
+      </c>
+      <c r="C110" t="n">
+        <v>321.0454837970353</v>
+      </c>
+      <c r="D110" t="n">
+        <v>313.9991629255859</v>
+      </c>
+      <c r="E110" t="n">
+        <v>317.9614562988281</v>
+      </c>
+      <c r="F110" t="n">
+        <v>39170000</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B111" t="n">
+        <v>318.3506892240785</v>
+      </c>
+      <c r="C111" t="n">
+        <v>320.4366276261131</v>
+      </c>
+      <c r="D111" t="n">
+        <v>309.0587679521403</v>
+      </c>
+      <c r="E111" t="n">
+        <v>310.3562316894531</v>
+      </c>
+      <c r="F111" t="n">
+        <v>45406400</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B112" t="n">
+        <v>311.4840826487114</v>
+      </c>
+      <c r="C112" t="n">
+        <v>315.6260194522374</v>
+      </c>
+      <c r="D112" t="n">
+        <v>306.603592280419</v>
+      </c>
+      <c r="E112" t="n">
+        <v>308.4000854492188</v>
+      </c>
+      <c r="F112" t="n">
+        <v>47761300</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B113" t="n">
+        <v>307.1325415821482</v>
+      </c>
+      <c r="C113" t="n">
+        <v>308.0307881065925</v>
+      </c>
+      <c r="D113" t="n">
+        <v>303.1203270701956</v>
+      </c>
+      <c r="E113" t="n">
+        <v>305.1264343261719</v>
+      </c>
+      <c r="F113" t="n">
+        <v>38499700</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B114" t="n">
+        <v>299.4574575670962</v>
+      </c>
+      <c r="C114" t="n">
+        <v>303.8489085337251</v>
+      </c>
+      <c r="D114" t="n">
+        <v>295.674807618098</v>
+      </c>
+      <c r="E114" t="n">
+        <v>301.43359375</v>
+      </c>
+      <c r="F114" t="n">
+        <v>39247600</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B115" t="n">
+        <v>301.5035060024616</v>
+      </c>
+      <c r="C115" t="n">
+        <v>304.7871271852118</v>
+      </c>
+      <c r="D115" t="n">
+        <v>300.6651404690992</v>
+      </c>
+      <c r="E115" t="n">
+        <v>302.7410888671875</v>
+      </c>
+      <c r="F115" t="n">
+        <v>28482100</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B116" t="n">
+        <v>301.2340248853423</v>
+      </c>
+      <c r="C116" t="n">
+        <v>304.8769323320439</v>
+      </c>
+      <c r="D116" t="n">
+        <v>299.4574819671566</v>
+      </c>
+      <c r="E116" t="n">
+        <v>302.2620239257812</v>
+      </c>
+      <c r="F116" t="n">
+        <v>25834400</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B117" t="n">
+        <v>303.7291917307074</v>
+      </c>
+      <c r="C117" t="n">
+        <v>315.8855378192499</v>
+      </c>
+      <c r="D117" t="n">
+        <v>303.3099937290923</v>
+      </c>
+      <c r="E117" t="n">
+        <v>314.3684997558594</v>
+      </c>
+      <c r="F117" t="n">
+        <v>53210800</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B118" t="n">
+        <v>318.4305429928518</v>
+      </c>
+      <c r="C118" t="n">
+        <v>318.8996316925602</v>
+      </c>
+      <c r="D118" t="n">
+        <v>309.2683735389658</v>
+      </c>
+      <c r="E118" t="n">
+        <v>310.8852233886719</v>
+      </c>
+      <c r="F118" t="n">
+        <v>31423000</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B119" t="n">
+        <v>309.91711960911</v>
+      </c>
+      <c r="C119" t="n">
+        <v>311.6637220131571</v>
+      </c>
+      <c r="D119" t="n">
+        <v>305.3360346729232</v>
+      </c>
+      <c r="E119" t="n">
+        <v>310.29638671875</v>
+      </c>
+      <c r="F119" t="n">
+        <v>25615600</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B120" t="n">
+        <v>311.4541454679639</v>
+      </c>
+      <c r="C120" t="n">
+        <v>313.031095017384</v>
+      </c>
+      <c r="D120" t="n">
+        <v>308.8392369672335</v>
+      </c>
+      <c r="E120" t="n">
+        <v>312.2925109863281</v>
+      </c>
+      <c r="F120" t="n">
+        <v>29963600</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B121" t="n">
+        <v>312.0330001798944</v>
+      </c>
+      <c r="C121" t="n">
+        <v>312.5320293917034</v>
+      </c>
+      <c r="D121" t="n">
+        <v>301.762970472535</v>
+      </c>
+      <c r="E121" t="n">
+        <v>306.783203125</v>
+      </c>
+      <c r="F121" t="n">
+        <v>36431200</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B122" t="n">
+        <v>303.5495233120643</v>
+      </c>
+      <c r="C122" t="n">
+        <v>311.7635251790807</v>
+      </c>
+      <c r="D122" t="n">
+        <v>303.2101566226461</v>
+      </c>
+      <c r="E122" t="n">
+        <v>311.1547241210938</v>
+      </c>
+      <c r="F122" t="n">
+        <v>44640600</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B123" t="n">
+        <v>302.6413055358027</v>
+      </c>
+      <c r="C123" t="n">
+        <v>307.8910728050191</v>
+      </c>
+      <c r="D123" t="n">
+        <v>300.7150293830805</v>
+      </c>
+      <c r="E123" t="n">
+        <v>305.9248962402344</v>
+      </c>
+      <c r="F123" t="n">
+        <v>34790200</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B124" t="n">
+        <v>298.0102681623609</v>
+      </c>
+      <c r="C124" t="n">
+        <v>303.3498869477631</v>
+      </c>
+      <c r="D124" t="n">
+        <v>296.1339134078651</v>
+      </c>
+      <c r="E124" t="n">
+        <v>302.9905700683594</v>
+      </c>
+      <c r="F124" t="n">
+        <v>35497000</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B125" t="n">
+        <v>302.3019795923877</v>
+      </c>
+      <c r="C125" t="n">
+        <v>304.8769573413998</v>
+      </c>
+      <c r="D125" t="n">
+        <v>300.1661195993462</v>
+      </c>
+      <c r="E125" t="n">
+        <v>302.54150390625</v>
+      </c>
+      <c r="F125" t="n">
+        <v>29536200</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B126" t="n">
+        <v>302.4516780897468</v>
+      </c>
+      <c r="C126" t="n">
+        <v>302.7111526067185</v>
+      </c>
+      <c r="D126" t="n">
+        <v>297.4114640277728</v>
+      </c>
+      <c r="E126" t="n">
+        <v>300.2958679199219</v>
+      </c>
+      <c r="F126" t="n">
+        <v>35752300</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B127" t="n">
+        <v>295.5151547022239</v>
+      </c>
+      <c r="C127" t="n">
+        <v>299.9465371351957</v>
+      </c>
+      <c r="D127" t="n">
+        <v>294.6069177596933</v>
+      </c>
+      <c r="E127" t="n">
+        <v>297.9404296875</v>
+      </c>
+      <c r="F127" t="n">
+        <v>25576900</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B128" t="n">
+        <v>293.9952756214191</v>
+      </c>
+      <c r="C128" t="n">
+        <v>306.4198649966507</v>
+      </c>
+      <c r="D128" t="n">
+        <v>293.7156237584298</v>
+      </c>
+      <c r="E128" t="n">
+        <v>305.9804077148438</v>
+      </c>
+      <c r="F128" t="n">
+        <v>29312100</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B129" t="n">
+        <v>305.7906896809686</v>
+      </c>
+      <c r="C129" t="n">
+        <v>309.1265479913924</v>
+      </c>
+      <c r="D129" t="n">
+        <v>305.1914269440574</v>
+      </c>
+      <c r="E129" t="n">
+        <v>306.6596069335938</v>
+      </c>
+      <c r="F129" t="n">
+        <v>23239700</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B130" t="n">
+        <v>306.3699695674413</v>
+      </c>
+      <c r="C130" t="n">
+        <v>311.0341973481569</v>
+      </c>
+      <c r="D130" t="n">
+        <v>305.5410112597431</v>
+      </c>
+      <c r="E130" t="n">
+        <v>308.3175659179688</v>
+      </c>
+      <c r="F130" t="n">
+        <v>24125700</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B131" t="n">
+        <v>306.4398571350748</v>
+      </c>
+      <c r="C131" t="n">
+        <v>308.5572255769297</v>
+      </c>
+      <c r="D131" t="n">
+        <v>300.6570224145156</v>
+      </c>
+      <c r="E131" t="n">
+        <v>303.1738891601562</v>
+      </c>
+      <c r="F131" t="n">
+        <v>24928300</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B132" t="n">
+        <v>306.6296377698095</v>
+      </c>
+      <c r="C132" t="n">
+        <v>307.3087879643589</v>
+      </c>
+      <c r="D132" t="n">
+        <v>300.0677703977713</v>
+      </c>
+      <c r="E132" t="n">
+        <v>301.9054870605469</v>
+      </c>
+      <c r="F132" t="n">
+        <v>23693100</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B133" t="n">
+        <v>303.9729346538992</v>
+      </c>
+      <c r="C133" t="n">
+        <v>306.1102674724465</v>
+      </c>
+      <c r="D133" t="n">
+        <v>302.6445653756606</v>
+      </c>
+      <c r="E133" t="n">
+        <v>305.1814270019531</v>
+      </c>
+      <c r="F133" t="n">
+        <v>23519700</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B134" t="n">
+        <v>305.481031231764</v>
+      </c>
+      <c r="C134" t="n">
+        <v>311.0341705495281</v>
+      </c>
+      <c r="D134" t="n">
+        <v>305.1214918945171</v>
+      </c>
+      <c r="E134" t="n">
+        <v>310.5347900390625</v>
+      </c>
+      <c r="F134" t="n">
+        <v>21955200</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B135" t="n">
+        <v>308.8868058363209</v>
+      </c>
+      <c r="C135" t="n">
+        <v>312.0828532524296</v>
+      </c>
+      <c r="D135" t="n">
+        <v>306.5497087361953</v>
+      </c>
+      <c r="E135" t="n">
+        <v>307.3087768554688</v>
+      </c>
+      <c r="F135" t="n">
+        <v>20009800</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B136" t="n">
+        <v>303.6333516523425</v>
+      </c>
+      <c r="C136" t="n">
+        <v>307.6783216475022</v>
+      </c>
+      <c r="D136" t="n">
+        <v>301.9754046785898</v>
+      </c>
+      <c r="E136" t="n">
+        <v>306.7494812011719</v>
+      </c>
+      <c r="F136" t="n">
+        <v>25075800</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B137" t="n">
+        <v>305.0815409313132</v>
+      </c>
+      <c r="C137" t="n">
+        <v>305.620880431115</v>
+      </c>
+      <c r="D137" t="n">
+        <v>297.9004465638477</v>
+      </c>
+      <c r="E137" t="n">
+        <v>300.6270751953125</v>
+      </c>
+      <c r="F137" t="n">
+        <v>44364100</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B138" t="n">
+        <v>301.7357168812967</v>
+      </c>
+      <c r="C138" t="n">
+        <v>305.6009481410186</v>
+      </c>
+      <c r="D138" t="n">
+        <v>300.5571860375472</v>
+      </c>
+      <c r="E138" t="n">
+        <v>301.685791015625</v>
+      </c>
+      <c r="F138" t="n">
+        <v>29326900</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B139" t="n">
+        <v>298.8293264668504</v>
+      </c>
+      <c r="C139" t="n">
+        <v>299.5484356615691</v>
+      </c>
+      <c r="D139" t="n">
+        <v>289.9702901097709</v>
+      </c>
+      <c r="E139" t="n">
+        <v>290.0801696777344</v>
+      </c>
+      <c r="F139" t="n">
+        <v>36864300</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B140" t="n">
+        <v>293.0764495892524</v>
+      </c>
+      <c r="C140" t="n">
+        <v>295.6332754793409</v>
+      </c>
+      <c r="D140" t="n">
+        <v>288.8816409209488</v>
+      </c>
+      <c r="E140" t="n">
+        <v>290.5695495605469</v>
+      </c>
+      <c r="F140" t="n">
+        <v>29460700</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B141" t="n">
+        <v>287.5532902578335</v>
+      </c>
+      <c r="C141" t="n">
+        <v>287.5932492331535</v>
+      </c>
+      <c r="D141" t="n">
+        <v>278.1549453585245</v>
+      </c>
+      <c r="E141" t="n">
+        <v>280.5719604492188</v>
+      </c>
+      <c r="F141" t="n">
+        <v>39080600</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B142" t="n">
+        <v>276.9364822022131</v>
+      </c>
+      <c r="C142" t="n">
+        <v>279.0238892859517</v>
+      </c>
+      <c r="D142" t="n">
+        <v>273.6106210828978</v>
+      </c>
+      <c r="E142" t="n">
+        <v>274.0001220703125</v>
+      </c>
+      <c r="F142" t="n">
+        <v>35890600</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B143" t="n">
+        <v>276.0775591796553</v>
+      </c>
+      <c r="C143" t="n">
+        <v>276.7467120540596</v>
+      </c>
+      <c r="D143" t="n">
+        <v>271.772870758184</v>
+      </c>
+      <c r="E143" t="n">
+        <v>273.1611633300781</v>
+      </c>
+      <c r="F143" t="n">
+        <v>35141200</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B144" t="n">
+        <v>277.6955407888773</v>
+      </c>
+      <c r="C144" t="n">
+        <v>287.7230801433843</v>
+      </c>
+      <c r="D144" t="n">
+        <v>276.7467055656006</v>
+      </c>
+      <c r="E144" t="n">
+        <v>287.2037353515625</v>
+      </c>
+      <c r="F144" t="n">
+        <v>43875400</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B145" t="n">
+        <v>290.4796724840224</v>
+      </c>
+      <c r="C145" t="n">
+        <v>300.1476725442409</v>
+      </c>
+      <c r="D145" t="n">
+        <v>290.0502125293938</v>
+      </c>
+      <c r="E145" t="n">
+        <v>297.0215759277344</v>
+      </c>
+      <c r="F145" t="n">
+        <v>37684500</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B146" t="n">
+        <v>290.3298713924274</v>
+      </c>
+      <c r="C146" t="n">
+        <v>297.7107001938477</v>
+      </c>
+      <c r="D146" t="n">
+        <v>289.0914173614996</v>
+      </c>
+      <c r="E146" t="n">
+        <v>295.403564453125</v>
+      </c>
+      <c r="F146" t="n">
+        <v>21666500</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B147" t="n">
+        <v>295.5034260146894</v>
+      </c>
+      <c r="C147" t="n">
+        <v>300.2475409865838</v>
+      </c>
+      <c r="D147" t="n">
+        <v>294.8142784540748</v>
+      </c>
+      <c r="E147" t="n">
+        <v>299.6183166503906</v>
+      </c>
+      <c r="F147" t="n">
+        <v>16945500</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B148" t="n">
+        <v>302.3549447988444</v>
+      </c>
+      <c r="C148" t="n">
+        <v>305.2513457589993</v>
+      </c>
+      <c r="D148" t="n">
+        <v>297.3511421656273</v>
+      </c>
+      <c r="E148" t="n">
+        <v>305.08154296875</v>
+      </c>
+      <c r="F148" t="n">
+        <v>23205400</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B149" t="n">
+        <v>320.0530070056894</v>
+      </c>
+      <c r="C149" t="n">
+        <v>321.6809619973042</v>
+      </c>
+      <c r="D149" t="n">
+        <v>314.6297110626625</v>
+      </c>
+      <c r="E149" t="n">
+        <v>316.9268798828125</v>
+      </c>
+      <c r="F149" t="n">
+        <v>33547100</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B150" t="n">
+        <v>315.5186078441214</v>
+      </c>
+      <c r="C150" t="n">
+        <v>319.1441153425082</v>
+      </c>
+      <c r="D150" t="n">
+        <v>310.6746106421415</v>
+      </c>
+      <c r="E150" t="n">
+        <v>318.0953979492188</v>
+      </c>
+      <c r="F150" t="n">
+        <v>23739200</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B151" t="n">
+        <v>319.6235089208506</v>
+      </c>
+      <c r="C151" t="n">
+        <v>321.4312640320202</v>
+      </c>
+      <c r="D151" t="n">
+        <v>315.9281112234418</v>
+      </c>
+      <c r="E151" t="n">
+        <v>316.8469543457031</v>
+      </c>
+      <c r="F151" t="n">
+        <v>19152600</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B152" t="n">
+        <v>316.7471095555252</v>
+      </c>
+      <c r="C152" t="n">
+        <v>321.2315371363443</v>
+      </c>
+      <c r="D152" t="n">
+        <v>315.0791651091577</v>
+      </c>
+      <c r="E152" t="n">
+        <v>320.9119262695312</v>
+      </c>
+      <c r="F152" t="n">
+        <v>18866400</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B153" t="n">
+        <v>324.3876234083889</v>
+      </c>
+      <c r="C153" t="n">
+        <v>332.8770926852431</v>
+      </c>
+      <c r="D153" t="n">
+        <v>323.3489033390031</v>
+      </c>
+      <c r="E153" t="n">
+        <v>332.49755859375</v>
+      </c>
+      <c r="F153" t="n">
+        <v>27721400</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B154" t="n">
+        <v>332.4775916674409</v>
+      </c>
+      <c r="C154" t="n">
+        <v>337.0619013824557</v>
+      </c>
+      <c r="D154" t="n">
+        <v>330.4900363853266</v>
+      </c>
+      <c r="E154" t="n">
+        <v>336.7023315429688</v>
+      </c>
+      <c r="F154" t="n">
+        <v>24918800</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B155" t="n">
+        <v>338.3302967803236</v>
+      </c>
+      <c r="C155" t="n">
+        <v>339.458901613874</v>
+      </c>
+      <c r="D155" t="n">
+        <v>334.105526677332</v>
+      </c>
+      <c r="E155" t="n">
+        <v>335.6036682128906</v>
+      </c>
+      <c r="F155" t="n">
+        <v>20541500</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B156" t="n">
+        <v>337.2316773591919</v>
+      </c>
+      <c r="C156" t="n">
+        <v>341.895905080184</v>
+      </c>
+      <c r="D156" t="n">
+        <v>335.8234205588037</v>
+      </c>
+      <c r="E156" t="n">
+        <v>341.2566833496094</v>
+      </c>
+      <c r="F156" t="n">
+        <v>25581900</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B157" t="n">
+        <v>340.3378420577138</v>
+      </c>
+      <c r="C157" t="n">
+        <v>340.9770333119858</v>
+      </c>
+      <c r="D157" t="n">
+        <v>336.1929591105031</v>
+      </c>
+      <c r="E157" t="n">
+        <v>337.0019836425781</v>
+      </c>
+      <c r="F157" t="n">
+        <v>18784200</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B158" t="n">
+        <v>337.2716301294484</v>
+      </c>
+      <c r="C158" t="n">
+        <v>338.9195798085849</v>
+      </c>
+      <c r="D158" t="n">
+        <v>330.9394885663705</v>
+      </c>
+      <c r="E158" t="n">
+        <v>331.8783264160156</v>
+      </c>
+      <c r="F158" t="n">
+        <v>23123800</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B159" t="n">
+        <v>336.6024588411248</v>
+      </c>
+      <c r="C159" t="n">
+        <v>339.3990082413208</v>
+      </c>
+      <c r="D159" t="n">
+        <v>334.7547751685775</v>
+      </c>
+      <c r="E159" t="n">
+        <v>338.8996276855469</v>
+      </c>
+      <c r="F159" t="n">
+        <v>20293000</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B160" t="n">
+        <v>340.7572947145818</v>
+      </c>
+      <c r="C160" t="n">
+        <v>341.5363271303731</v>
+      </c>
+      <c r="D160" t="n">
+        <v>335.7634893621326</v>
+      </c>
+      <c r="E160" t="n">
+        <v>338.4701538085938</v>
+      </c>
+      <c r="F160" t="n">
+        <v>18650300</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B161" t="n">
+        <v>338.3103390739037</v>
+      </c>
+      <c r="C161" t="n">
+        <v>344.8422143498026</v>
+      </c>
+      <c r="D161" t="n">
+        <v>334.9744808477988</v>
+      </c>
+      <c r="E161" t="n">
+        <v>343.9732971191406</v>
+      </c>
+      <c r="F161" t="n">
+        <v>26426100</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B162" t="n">
+        <v>345.55136124882</v>
+      </c>
+      <c r="C162" t="n">
+        <v>352.7424225666816</v>
+      </c>
+      <c r="D162" t="n">
+        <v>342.3053878156813</v>
+      </c>
+      <c r="E162" t="n">
+        <v>349.9059448242188</v>
+      </c>
+      <c r="F162" t="n">
+        <v>28576900</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B163" t="n">
+        <v>348.1181620694143</v>
+      </c>
+      <c r="C163" t="n">
+        <v>351.9833930501032</v>
+      </c>
+      <c r="D163" t="n">
+        <v>345.6911799613628</v>
+      </c>
+      <c r="E163" t="n">
+        <v>349.3466491699219</v>
+      </c>
+      <c r="F163" t="n">
+        <v>27824100</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B164" t="n">
+        <v>347.1394107424554</v>
+      </c>
+      <c r="C164" t="n">
+        <v>355.3492283904879</v>
+      </c>
+      <c r="D164" t="n">
+        <v>343.7835575206014</v>
+      </c>
+      <c r="E164" t="n">
+        <v>349.5064697265625</v>
+      </c>
+      <c r="F164" t="n">
+        <v>35376300</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B165" t="n">
+        <v>373.6065555628184</v>
+      </c>
+      <c r="C165" t="n">
+        <v>385.3619622201579</v>
+      </c>
+      <c r="D165" t="n">
+        <v>365.3667768501622</v>
+      </c>
+      <c r="E165" t="n">
+        <v>384.3232421875</v>
+      </c>
+      <c r="F165" t="n">
+        <v>72040000</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B166" t="n">
+        <v>381.1572209075714</v>
+      </c>
+      <c r="C166" t="n">
+        <v>386.2808704617397</v>
+      </c>
+      <c r="D166" t="n">
+        <v>378.5804000830116</v>
+      </c>
+      <c r="E166" t="n">
+        <v>385.2121887207031</v>
+      </c>
+      <c r="F166" t="n">
+        <v>30105200</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B167" t="n">
+        <v>385.1522332062169</v>
+      </c>
+      <c r="C167" t="n">
+        <v>386.9000650646732</v>
+      </c>
+      <c r="D167" t="n">
+        <v>379.3194722618546</v>
+      </c>
+      <c r="E167" t="n">
+        <v>382.7751770019531</v>
+      </c>
+      <c r="F167" t="n">
+        <v>26298600</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B168" t="n">
+        <v>385.7515048868787</v>
+      </c>
+      <c r="C168" t="n">
+        <v>392.3333367803882</v>
+      </c>
+      <c r="D168" t="n">
+        <v>383.5442209432822</v>
+      </c>
+      <c r="E168" t="n">
+        <v>387.9487609863281</v>
+      </c>
+      <c r="F168" t="n">
+        <v>23878600</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B169" t="n">
+        <v>393.7615619135972</v>
+      </c>
+      <c r="C169" t="n">
+        <v>399.3546301445318</v>
+      </c>
+      <c r="D169" t="n">
+        <v>392.2734176347804</v>
+      </c>
+      <c r="E169" t="n">
+        <v>397.546875</v>
+      </c>
+      <c r="F169" t="n">
+        <v>31308500</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B170" t="n">
+        <v>399.4245497990884</v>
+      </c>
+      <c r="C170" t="n">
+        <v>399.6043194807176</v>
+      </c>
+      <c r="D170" t="n">
+        <v>392.1934987581594</v>
+      </c>
+      <c r="E170" t="n">
+        <v>397.4969177246094</v>
+      </c>
+      <c r="F170" t="n">
+        <v>24433500</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B171" t="n">
+        <v>396.5081562950806</v>
+      </c>
+      <c r="C171" t="n">
+        <v>401.5019617899809</v>
+      </c>
+      <c r="D171" t="n">
+        <v>395.8689345614438</v>
+      </c>
+      <c r="E171" t="n">
+        <v>400.3034362792969</v>
+      </c>
+      <c r="F171" t="n">
+        <v>21461800</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B172" t="n">
+        <v>393.1622804247065</v>
+      </c>
+      <c r="C172" t="n">
+        <v>396.9475933307253</v>
+      </c>
+      <c r="D172" t="n">
+        <v>387.9887055115338</v>
+      </c>
+      <c r="E172" t="n">
+        <v>388.1585083007812</v>
+      </c>
+      <c r="F172" t="n">
+        <v>30753700</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B173" t="n">
+        <v>386.8601198229993</v>
+      </c>
+      <c r="C173" t="n">
+        <v>388.0386506028281</v>
+      </c>
+      <c r="D173" t="n">
+        <v>382.2957742925754</v>
+      </c>
+      <c r="E173" t="n">
+        <v>386.8701171875</v>
+      </c>
+      <c r="F173" t="n">
+        <v>26017500</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B174" t="n">
+        <v>385.1222825184223</v>
+      </c>
+      <c r="C174" t="n">
+        <v>403.1998643489371</v>
+      </c>
+      <c r="D174" t="n">
+        <v>384.5230197682841</v>
+      </c>
+      <c r="E174" t="n">
+        <v>402.1211853027344</v>
+      </c>
+      <c r="F174" t="n">
+        <v>28144600</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B175" t="n">
+        <v>396.7878070287349</v>
+      </c>
+      <c r="C175" t="n">
+        <v>402.430801125594</v>
+      </c>
+      <c r="D175" t="n">
+        <v>395.349588612008</v>
+      </c>
+      <c r="E175" t="n">
+        <v>400.5731201171875</v>
+      </c>
+      <c r="F175" t="n">
+        <v>21136700</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B176" t="n">
+        <v>395.8290000666237</v>
+      </c>
+      <c r="C176" t="n">
+        <v>399.0450119758119</v>
+      </c>
+      <c r="D176" t="n">
+        <v>392.692875633045</v>
+      </c>
+      <c r="E176" t="n">
+        <v>396.2884216308594</v>
+      </c>
+      <c r="F176" t="n">
+        <v>20309700</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B177" t="n">
+        <v>395.1997907850553</v>
+      </c>
+      <c r="C177" t="n">
+        <v>408.1037674120522</v>
+      </c>
+      <c r="D177" t="n">
+        <v>394.0412242260142</v>
+      </c>
+      <c r="E177" t="n">
+        <v>396.4482421875</v>
+      </c>
+      <c r="F177" t="n">
+        <v>26837200</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B178" t="n">
+        <v>396.4681837278221</v>
+      </c>
+      <c r="C178" t="n">
+        <v>396.6579507685057</v>
+      </c>
+      <c r="D178" t="n">
+        <v>385.6316200793582</v>
+      </c>
+      <c r="E178" t="n">
+        <v>387.1797180175781</v>
+      </c>
+      <c r="F178" t="n">
+        <v>39545700</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B179" t="n">
+        <v>387.2196997137571</v>
+      </c>
+      <c r="C179" t="n">
+        <v>393.3720414113799</v>
+      </c>
+      <c r="D179" t="n">
+        <v>382.4256280338265</v>
+      </c>
+      <c r="E179" t="n">
+        <v>388.4281921386719</v>
+      </c>
+      <c r="F179" t="n">
+        <v>31744400</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B180" t="n">
+        <v>385.2221548650083</v>
+      </c>
+      <c r="C180" t="n">
+        <v>392.0137179133836</v>
+      </c>
+      <c r="D180" t="n">
+        <v>382.5454520468608</v>
+      </c>
+      <c r="E180" t="n">
+        <v>387.1797180175781</v>
+      </c>
+      <c r="F180" t="n">
+        <v>24852800</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B181" t="n">
+        <v>386.8701229826527</v>
+      </c>
+      <c r="C181" t="n">
+        <v>388.258385079403</v>
+      </c>
+      <c r="D181" t="n">
+        <v>381.2970189068101</v>
+      </c>
+      <c r="E181" t="n">
+        <v>382.4955444335938</v>
+      </c>
+      <c r="F181" t="n">
+        <v>20442100</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B182" t="n">
+        <v>384.0336125447445</v>
+      </c>
+      <c r="C182" t="n">
+        <v>388.7777274266938</v>
+      </c>
+      <c r="D182" t="n">
+        <v>382.125975324115</v>
+      </c>
+      <c r="E182" t="n">
+        <v>388.398193359375</v>
+      </c>
+      <c r="F182" t="n">
+        <v>27747400</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B183" t="n">
+        <v>386.1909390913781</v>
+      </c>
+      <c r="C183" t="n">
+        <v>393.3919975499695</v>
+      </c>
+      <c r="D183" t="n">
+        <v>385.421873594791</v>
+      </c>
+      <c r="E183" t="n">
+        <v>388.3482360839844</v>
+      </c>
+      <c r="F183" t="n">
+        <v>23087300</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B184" t="n">
+        <v>387.5193014898567</v>
+      </c>
+      <c r="C184" t="n">
+        <v>391.384502017129</v>
+      </c>
+      <c r="D184" t="n">
+        <v>384.682823662297</v>
+      </c>
+      <c r="E184" t="n">
+        <v>389.6466674804688</v>
+      </c>
+      <c r="F184" t="n">
+        <v>24357500</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B185" t="n">
+        <v>384.7626974671623</v>
+      </c>
+      <c r="C185" t="n">
+        <v>384.7626974671623</v>
+      </c>
+      <c r="D185" t="n">
+        <v>377.9910987617443</v>
+      </c>
+      <c r="E185" t="n">
+        <v>379.8687744140625</v>
+      </c>
+      <c r="F185" t="n">
+        <v>44415800</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B186" t="n">
+        <v>376.0535251127361</v>
+      </c>
+      <c r="C186" t="n">
+        <v>378.0910063274455</v>
+      </c>
+      <c r="D186" t="n">
+        <v>373.0572417592452</v>
+      </c>
+      <c r="E186" t="n">
+        <v>375.9037170410156</v>
+      </c>
+      <c r="F186" t="n">
+        <v>28672100</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B187" t="n">
+        <v>366.1358206463617</v>
+      </c>
+      <c r="C187" t="n">
+        <v>373.0772223440179</v>
+      </c>
+      <c r="D187" t="n">
+        <v>357.9959239406105</v>
+      </c>
+      <c r="E187" t="n">
+        <v>361.4017028808594</v>
+      </c>
+      <c r="F187" t="n">
+        <v>50412300</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B188" t="n">
+        <v>361.5814692403301</v>
+      </c>
+      <c r="C188" t="n">
+        <v>365.9960065843375</v>
+      </c>
+      <c r="D188" t="n">
+        <v>357.6363508187865</v>
+      </c>
+      <c r="E188" t="n">
+        <v>358.5452270507812</v>
+      </c>
+      <c r="F188" t="n">
+        <v>55441600</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B189" t="n">
+        <v>358.4553682250688</v>
+      </c>
+      <c r="C189" t="n">
+        <v>372.7875967270043</v>
+      </c>
+      <c r="D189" t="n">
+        <v>357.7662205978281</v>
+      </c>
+      <c r="E189" t="n">
+        <v>371.7289123535156</v>
+      </c>
+      <c r="F189" t="n">
+        <v>44055500</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B190" t="n">
+        <v>365.8861360555161</v>
+      </c>
+      <c r="C190" t="n">
+        <v>371.6190149899659</v>
+      </c>
+      <c r="D190" t="n">
+        <v>363.6688852043904</v>
+      </c>
+      <c r="E190" t="n">
+        <v>368.0734252929688</v>
+      </c>
+      <c r="F190" t="n">
+        <v>37471200</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B191" t="n">
+        <v>364.9454235864071</v>
+      </c>
+      <c r="C191" t="n">
+        <v>365.9647879200631</v>
+      </c>
+      <c r="D191" t="n">
+        <v>360.2984165590168</v>
+      </c>
+      <c r="E191" t="n">
+        <v>363.0766296386719</v>
+      </c>
+      <c r="F191" t="n">
+        <v>27942500</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B192" t="n">
+        <v>366.8542002567407</v>
+      </c>
+      <c r="C192" t="n">
+        <v>371.8409852276818</v>
+      </c>
+      <c r="D192" t="n">
+        <v>357.0704802123837</v>
+      </c>
+      <c r="E192" t="n">
+        <v>364.0260314941406</v>
+      </c>
+      <c r="F192" t="n">
+        <v>29535100</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B193" t="n">
+        <v>362.9567158453764</v>
+      </c>
+      <c r="C193" t="n">
+        <v>368.3232616719084</v>
+      </c>
+      <c r="D193" t="n">
+        <v>354.9718577941881</v>
+      </c>
+      <c r="E193" t="n">
+        <v>356.1510925292969</v>
+      </c>
+      <c r="F193" t="n">
+        <v>32357100</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B194" t="n">
+        <v>355.7013467902599</v>
+      </c>
+      <c r="C194" t="n">
+        <v>358.5694982511428</v>
+      </c>
+      <c r="D194" t="n">
+        <v>346.1374871435174</v>
+      </c>
+      <c r="E194" t="n">
+        <v>357.5401611328125</v>
+      </c>
+      <c r="F194" t="n">
+        <v>35538200</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B195" t="n">
+        <v>362.3870579560934</v>
+      </c>
+      <c r="C195" t="n">
+        <v>366.3345327833823</v>
+      </c>
+      <c r="D195" t="n">
+        <v>354.7119986974298</v>
+      </c>
+      <c r="E195" t="n">
+        <v>359.4489440917969</v>
+      </c>
+      <c r="F195" t="n">
+        <v>24704600</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B196" t="n">
+        <v>367.6936611370598</v>
+      </c>
+      <c r="C196" t="n">
+        <v>372.7504085202595</v>
+      </c>
+      <c r="D196" t="n">
+        <v>366.3145426692825</v>
+      </c>
+      <c r="E196" t="n">
+        <v>369.1127624511719</v>
+      </c>
+      <c r="F196" t="n">
+        <v>27727500</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B197" t="n">
+        <v>369.3626044753487</v>
+      </c>
+      <c r="C197" t="n">
+        <v>375.7584875251172</v>
+      </c>
+      <c r="D197" t="n">
+        <v>366.8242274297617</v>
+      </c>
+      <c r="E197" t="n">
+        <v>373.01025390625</v>
+      </c>
+      <c r="F197" t="n">
+        <v>24876100</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B198" t="n">
+        <v>368.8929017493238</v>
+      </c>
+      <c r="C198" t="n">
+        <v>372.0908279957741</v>
+      </c>
+      <c r="D198" t="n">
+        <v>361.7874528539307</v>
+      </c>
+      <c r="E198" t="n">
+        <v>363.5563354492188</v>
+      </c>
+      <c r="F198" t="n">
+        <v>24543600</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B199" t="n">
+        <v>365.5150449761754</v>
+      </c>
+      <c r="C199" t="n">
+        <v>369.2426598317581</v>
+      </c>
+      <c r="D199" t="n">
+        <v>358.4396065335441</v>
+      </c>
+      <c r="E199" t="n">
+        <v>367.7935791015625</v>
+      </c>
+      <c r="F199" t="n">
+        <v>44470100</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B200" t="n">
+        <v>357.7200907639775</v>
+      </c>
+      <c r="C200" t="n">
+        <v>358.6894689253907</v>
+      </c>
+      <c r="D200" t="n">
+        <v>341.5005047739323</v>
+      </c>
+      <c r="E200" t="n">
+        <v>349.4553833007812</v>
+      </c>
+      <c r="F200" t="n">
+        <v>52814800</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B201" t="n">
+        <v>340.4711459801061</v>
+      </c>
+      <c r="C201" t="n">
+        <v>349.0656275102868</v>
+      </c>
+      <c r="D201" t="n">
+        <v>339.981470511436</v>
+      </c>
+      <c r="E201" t="n">
+        <v>345.9076538085938</v>
+      </c>
+      <c r="F201" t="n">
+        <v>34007700</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B202" t="n">
+        <v>348.8157979233392</v>
+      </c>
+      <c r="C202" t="n">
+        <v>353.2529482684732</v>
+      </c>
+      <c r="D202" t="n">
+        <v>341.7103492701006</v>
+      </c>
+      <c r="E202" t="n">
+        <v>345.0682067871094</v>
+      </c>
+      <c r="F202" t="n">
+        <v>44997300</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B203" t="n">
+        <v>336.5137001542092</v>
+      </c>
+      <c r="C203" t="n">
+        <v>345.3480177972958</v>
+      </c>
+      <c r="D203" t="n">
+        <v>335.6242572392167</v>
+      </c>
+      <c r="E203" t="n">
+        <v>343.4891967773438</v>
+      </c>
+      <c r="F203" t="n">
+        <v>44491400</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B204" t="n">
+        <v>342.3299372399903</v>
+      </c>
+      <c r="C204" t="n">
+        <v>346.1374872957393</v>
+      </c>
+      <c r="D204" t="n">
+        <v>329.98789515005</v>
+      </c>
+      <c r="E204" t="n">
+        <v>337.1732788085938</v>
+      </c>
+      <c r="F204" t="n">
+        <v>114706300</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B205" t="n">
+        <v>341.6104064955248</v>
+      </c>
+      <c r="C205" t="n">
+        <v>354.122383587675</v>
+      </c>
+      <c r="D205" t="n">
+        <v>340.4511784786947</v>
+      </c>
+      <c r="E205" t="n">
+        <v>353.4228210449219</v>
+      </c>
+      <c r="F205" t="n">
+        <v>34213900</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B206" t="n">
+        <v>353.6426900862941</v>
+      </c>
+      <c r="C206" t="n">
+        <v>358.3896389689017</v>
+      </c>
+      <c r="D206" t="n">
+        <v>350.1749177879227</v>
+      </c>
+      <c r="E206" t="n">
+        <v>357.1404418945312</v>
+      </c>
+      <c r="F206" t="n">
+        <v>35237200</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B207" t="n">
+        <v>358.1397942573561</v>
+      </c>
+      <c r="C207" t="n">
+        <v>362.7368455226467</v>
+      </c>
+      <c r="D207" t="n">
+        <v>356.2010379867681</v>
+      </c>
+      <c r="E207" t="n">
+        <v>360.9779663085938</v>
+      </c>
+      <c r="F207" t="n">
+        <v>26736400</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B208" t="n">
+        <v>359.2490860357571</v>
+      </c>
+      <c r="C208" t="n">
+        <v>363.9760280309549</v>
+      </c>
+      <c r="D208" t="n">
+        <v>353.1929813351636</v>
+      </c>
+      <c r="E208" t="n">
+        <v>359.6788024902344</v>
+      </c>
+      <c r="F208" t="n">
+        <v>25974800</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B209" t="n">
+        <v>361.3177293642356</v>
+      </c>
+      <c r="C209" t="n">
+        <v>367.693635754559</v>
+      </c>
+      <c r="D209" t="n">
+        <v>357.1504252362982</v>
+      </c>
+      <c r="E209" t="n">
+        <v>366.2245788574219</v>
+      </c>
+      <c r="F209" t="n">
+        <v>26915800</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B210" t="n">
+        <v>368.8329180211536</v>
+      </c>
+      <c r="C210" t="n">
+        <v>372.9202869594668</v>
+      </c>
+      <c r="D210" t="n">
+        <v>365.2652040573587</v>
+      </c>
+      <c r="E210" t="n">
+        <v>366.7942199707031</v>
+      </c>
+      <c r="F210" t="n">
+        <v>24045600</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B211" t="n">
+        <v>364.525702555654</v>
+      </c>
+      <c r="C211" t="n">
+        <v>367.6037106679975</v>
+      </c>
+      <c r="D211" t="n">
+        <v>357.7900113228786</v>
+      </c>
+      <c r="E211" t="n">
+        <v>361.6875305175781</v>
+      </c>
+      <c r="F211" t="n">
+        <v>22094800</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B212" t="n">
+        <v>354.0824097063769</v>
+      </c>
+      <c r="C212" t="n">
+        <v>359.4189759454678</v>
+      </c>
+      <c r="D212" t="n">
+        <v>350.8544734886641</v>
+      </c>
+      <c r="E212" t="n">
+        <v>358.6594848632812</v>
+      </c>
+      <c r="F212" t="n">
+        <v>24729100</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B213" t="n">
+        <v>357.3003428038799</v>
+      </c>
+      <c r="C213" t="n">
+        <v>357.5901650645865</v>
+      </c>
+      <c r="D213" t="n">
+        <v>352.5234144110846</v>
+      </c>
+      <c r="E213" t="n">
+        <v>356.9505615234375</v>
+      </c>
+      <c r="F213" t="n">
+        <v>18146100</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B214" t="n">
+        <v>355.9611981097028</v>
+      </c>
+      <c r="C214" t="n">
+        <v>357.8999543595846</v>
+      </c>
+      <c r="D214" t="n">
+        <v>351.5240477747128</v>
+      </c>
+      <c r="E214" t="n">
+        <v>352.2835693359375</v>
+      </c>
+      <c r="F214" t="n">
+        <v>15901700</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B215" t="n">
+        <v>350.9744235107016</v>
+      </c>
+      <c r="C215" t="n">
+        <v>359.92865963343</v>
+      </c>
+      <c r="D215" t="n">
+        <v>350.8644783088037</v>
+      </c>
+      <c r="E215" t="n">
+        <v>359.2790832519531</v>
+      </c>
+      <c r="F215" t="n">
+        <v>18259400</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B216" t="n">
+        <v>357.7400685886304</v>
+      </c>
+      <c r="C216" t="n">
+        <v>373.4099896327818</v>
+      </c>
+      <c r="D216" t="n">
+        <v>357.5302120160503</v>
+      </c>
+      <c r="E216" t="n">
+        <v>370.6817626953125</v>
+      </c>
+      <c r="F216" t="n">
+        <v>28284600</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B217" t="n">
+        <v>372.8203579699616</v>
+      </c>
+      <c r="C217" t="n">
+        <v>375.0289298103755</v>
+      </c>
+      <c r="D217" t="n">
+        <v>352.0736836469807</v>
+      </c>
+      <c r="E217" t="n">
+        <v>354.2322998046875</v>
+      </c>
+      <c r="F217" t="n">
+        <v>41158500</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B218" t="n">
+        <v>345.7777467999313</v>
+      </c>
+      <c r="C218" t="n">
+        <v>348.2961170979314</v>
+      </c>
+      <c r="D218" t="n">
+        <v>341.1407126662452</v>
+      </c>
+      <c r="E218" t="n">
+        <v>346.5472412109375</v>
+      </c>
+      <c r="F218" t="n">
+        <v>29959300</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B219" t="n">
+        <v>350.6546131580819</v>
+      </c>
+      <c r="C219" t="n">
+        <v>359.4489481797366</v>
+      </c>
+      <c r="D219" t="n">
+        <v>350.2948285491913</v>
+      </c>
+      <c r="E219" t="n">
+        <v>351.7638854980469</v>
+      </c>
+      <c r="F219" t="n">
+        <v>24736600</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B220" t="n">
+        <v>351.094336770995</v>
+      </c>
+      <c r="C220" t="n">
+        <v>351.094336770995</v>
+      </c>
+      <c r="D220" t="n">
+        <v>346.7771044052826</v>
+      </c>
+      <c r="E220" t="n">
+        <v>346.927001953125</v>
+      </c>
+      <c r="F220" t="n">
+        <v>23369800</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B221" t="n">
+        <v>347.9363472365376</v>
+      </c>
+      <c r="C221" t="n">
+        <v>349.7152025525983</v>
+      </c>
+      <c r="D221" t="n">
+        <v>341.5104851592261</v>
+      </c>
+      <c r="E221" t="n">
+        <v>341.8702392578125</v>
+      </c>
+      <c r="F221" t="n">
+        <v>39334100</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B222" t="n">
+        <v>320.9237241212255</v>
+      </c>
+      <c r="C222" t="n">
+        <v>324.2815511558238</v>
+      </c>
+      <c r="D222" t="n">
+        <v>314.6977150387725</v>
+      </c>
+      <c r="E222" t="n">
+        <v>317.4859313964844</v>
+      </c>
+      <c r="F222" t="n">
+        <v>69419700</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B223" t="n">
+        <v>318.2154780071113</v>
+      </c>
+      <c r="C223" t="n">
+        <v>323.9717573627877</v>
+      </c>
+      <c r="D223" t="n">
+        <v>317.1161784867298</v>
+      </c>
+      <c r="E223" t="n">
+        <v>319.5346069335938</v>
+      </c>
+      <c r="F223" t="n">
+        <v>31806600</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B224" t="n">
+        <v>324.83120713377</v>
+      </c>
+      <c r="C224" t="n">
+        <v>330.2077559724587</v>
+      </c>
+      <c r="D224" t="n">
+        <v>324.2415898017393</v>
+      </c>
+      <c r="E224" t="n">
+        <v>326.3502197265625</v>
+      </c>
+      <c r="F224" t="n">
+        <v>28471600</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B225" t="n">
+        <v>327.6893704249235</v>
+      </c>
+      <c r="C225" t="n">
+        <v>335.6642555263833</v>
+      </c>
+      <c r="D225" t="n">
+        <v>324.2316014627561</v>
+      </c>
+      <c r="E225" t="n">
+        <v>333.4956359863281</v>
+      </c>
+      <c r="F225" t="n">
+        <v>29511900</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B226" t="n">
+        <v>334.455045685483</v>
+      </c>
+      <c r="C226" t="n">
+        <v>342.2800028423013</v>
+      </c>
+      <c r="D226" t="n">
+        <v>331.4069864854741</v>
+      </c>
+      <c r="E226" t="n">
+        <v>336.4937133789062</v>
+      </c>
+      <c r="F226" t="n">
+        <v>27501600</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B227" t="n">
+        <v>333.9853403838827</v>
+      </c>
+      <c r="C227" t="n">
+        <v>336.2938541262907</v>
+      </c>
+      <c r="D227" t="n">
+        <v>330.1278039779788</v>
+      </c>
+      <c r="E227" t="n">
+        <v>333.4456787109375</v>
+      </c>
+      <c r="F227" t="n">
+        <v>30168000</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B228" t="n">
+        <v>340.611054758666</v>
+      </c>
+      <c r="C228" t="n">
+        <v>358.3496530632621</v>
+      </c>
+      <c r="D228" t="n">
+        <v>339.7816013274756</v>
+      </c>
+      <c r="E228" t="n">
+        <v>355.9012451171875</v>
+      </c>
+      <c r="F228" t="n">
+        <v>46498000</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B229" t="n">
+        <v>365.2152604560987</v>
+      </c>
+      <c r="C229" t="n">
+        <v>376.4480305309448</v>
+      </c>
+      <c r="D229" t="n">
+        <v>363.1166033198653</v>
+      </c>
+      <c r="E229" t="n">
+        <v>373.2700805664062</v>
+      </c>
+      <c r="F229" t="n">
+        <v>38669700</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B230" t="n">
+        <v>367.9834743668337</v>
+      </c>
+      <c r="C230" t="n">
+        <v>380.2755612380555</v>
+      </c>
+      <c r="D230" t="n">
+        <v>367.263935640354</v>
+      </c>
+      <c r="E230" t="n">
+        <v>377.4074096679688</v>
+      </c>
+      <c r="F230" t="n">
+        <v>35705700</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B231" t="n">
+        <v>383.0937455186354</v>
+      </c>
+      <c r="C231" t="n">
+        <v>384.2330278418686</v>
+      </c>
+      <c r="D231" t="n">
+        <v>356.5408062961898</v>
+      </c>
+      <c r="E231" t="n">
+        <v>362.1971740722656</v>
+      </c>
+      <c r="F231" t="n">
+        <v>46926300</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B232" t="n">
+        <v>360.5382517887205</v>
+      </c>
+      <c r="C232" t="n">
+        <v>363.8961093831237</v>
+      </c>
+      <c r="D232" t="n">
+        <v>356.6507663527499</v>
+      </c>
+      <c r="E232" t="n">
+        <v>357.5202026367188</v>
+      </c>
+      <c r="F232" t="n">
+        <v>25235900</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B233" t="n">
+        <v>356.4908465215469</v>
+      </c>
+      <c r="C233" t="n">
+        <v>358.6694387836589</v>
+      </c>
+      <c r="D233" t="n">
+        <v>353.5527327193329</v>
+      </c>
+      <c r="E233" t="n">
+        <v>354.0723876953125</v>
+      </c>
+      <c r="F233" t="n">
+        <v>19859900</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B234" t="n">
+        <v>354.951850943437</v>
+      </c>
+      <c r="C234" t="n">
+        <v>357.3802827690857</v>
+      </c>
+      <c r="D234" t="n">
+        <v>352.4834362714388</v>
+      </c>
+      <c r="E234" t="n">
+        <v>357.2903442382812</v>
+      </c>
+      <c r="F234" t="n">
+        <v>18991400</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B235" t="n">
+        <v>355.6613923515014</v>
+      </c>
+      <c r="C235" t="n">
+        <v>356.5807842683805</v>
+      </c>
+      <c r="D235" t="n">
+        <v>343.1694223006263</v>
+      </c>
+      <c r="E235" t="n">
+        <v>343.5791320800781</v>
+      </c>
+      <c r="F235" t="n">
+        <v>29081800</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B236" t="n">
+        <v>346.0875456512855</v>
+      </c>
+      <c r="C236" t="n">
+        <v>346.2574498710514</v>
+      </c>
+      <c r="D236" t="n">
+        <v>340.661040926288</v>
+      </c>
+      <c r="E236" t="n">
+        <v>343.3193359375</v>
+      </c>
+      <c r="F236" t="n">
+        <v>25012000</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B237" t="n">
+        <v>345.5478948342235</v>
+      </c>
+      <c r="C237" t="n">
+        <v>347.7065110877775</v>
+      </c>
+      <c r="D237" t="n">
+        <v>343.5392066313974</v>
+      </c>
+      <c r="E237" t="n">
+        <v>346.1375122070312</v>
+      </c>
+      <c r="F237" t="n">
+        <v>17866100</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B238" t="n">
+        <v>346.5772111705174</v>
+      </c>
+      <c r="C238" t="n">
+        <v>350.2248908898295</v>
+      </c>
+      <c r="D238" t="n">
+        <v>344.2787008387085</v>
+      </c>
+      <c r="E238" t="n">
+        <v>345.6777954101562</v>
+      </c>
+      <c r="F238" t="n">
+        <v>17808600</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B239" t="n">
+        <v>346.0475530411078</v>
+      </c>
+      <c r="C239" t="n">
+        <v>347.0269344906474</v>
+      </c>
+      <c r="D239" t="n">
+        <v>341.7103446182459</v>
+      </c>
+      <c r="E239" t="n">
+        <v>343.7790222167969</v>
+      </c>
+      <c r="F239" t="n">
+        <v>18291300</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B240" t="n">
+        <v>342.1900536360575</v>
+      </c>
+      <c r="C240" t="n">
+        <v>344.6484648943574</v>
+      </c>
+      <c r="D240" t="n">
+        <v>339.9714784523309</v>
+      </c>
+      <c r="E240" t="n">
+        <v>343.9789123535156</v>
+      </c>
+      <c r="F240" t="n">
+        <v>19248800</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B241" t="n">
+        <v>342.2400076559886</v>
+      </c>
+      <c r="C241" t="n">
+        <v>346.5072842825429</v>
+      </c>
+      <c r="D241" t="n">
+        <v>340.4411761094805</v>
+      </c>
+      <c r="E241" t="n">
+        <v>344.4985656738281</v>
+      </c>
+      <c r="F241" t="n">
+        <v>19733800</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B242" t="n">
+        <v>342.8396207141765</v>
+      </c>
+      <c r="C242" t="n">
+        <v>343.6790774504127</v>
+      </c>
+      <c r="D242" t="n">
+        <v>338.3525147854226</v>
+      </c>
+      <c r="E242" t="n">
+        <v>340.451171875</v>
+      </c>
+      <c r="F242" t="n">
+        <v>18570400</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B243" t="n">
+        <v>342.359928876986</v>
+      </c>
+      <c r="C243" t="n">
+        <v>345.9776291730591</v>
+      </c>
+      <c r="D243" t="n">
+        <v>340.1813365286692</v>
+      </c>
+      <c r="E243" t="n">
+        <v>344.5985107421875</v>
+      </c>
+      <c r="F243" t="n">
+        <v>20849800</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B244" t="n">
+        <v>343.3992753172161</v>
+      </c>
+      <c r="C244" t="n">
+        <v>351.3741604480826</v>
+      </c>
+      <c r="D244" t="n">
+        <v>342.2699962782288</v>
+      </c>
+      <c r="E244" t="n">
+        <v>347.83642578125</v>
+      </c>
+      <c r="F244" t="n">
+        <v>26338200</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B245" t="n">
+        <v>349.4154232615459</v>
+      </c>
+      <c r="C245" t="n">
+        <v>349.9350782600912</v>
+      </c>
+      <c r="D245" t="n">
+        <v>345.3780098175396</v>
+      </c>
+      <c r="E245" t="n">
+        <v>346.7371215820312</v>
+      </c>
+      <c r="F245" t="n">
+        <v>20649700</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B246" t="n">
+        <v>346.3973312516375</v>
+      </c>
+      <c r="C246" t="n">
+        <v>346.6571739906042</v>
+      </c>
+      <c r="D246" t="n">
+        <v>339.9614657782595</v>
+      </c>
+      <c r="E246" t="n">
+        <v>341.7803039550781</v>
+      </c>
+      <c r="F246" t="n">
+        <v>20420300</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B247" t="n">
+        <v>339.4518318672431</v>
+      </c>
+      <c r="C247" t="n">
+        <v>341.4705233735174</v>
+      </c>
+      <c r="D247" t="n">
+        <v>338.3025461528343</v>
+      </c>
+      <c r="E247" t="n">
+        <v>340.4311828613281</v>
+      </c>
+      <c r="F247" t="n">
+        <v>23391400</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B248" t="n">
+        <v>340.4911426360338</v>
+      </c>
+      <c r="C248" t="n">
+        <v>348.9157509584863</v>
+      </c>
+      <c r="D248" t="n">
+        <v>340.0514228221321</v>
+      </c>
+      <c r="E248" t="n">
+        <v>346.3673706054688</v>
+      </c>
+      <c r="F248" t="n">
+        <v>25347200</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B249" t="n">
+        <v>343.609121722545</v>
+      </c>
+      <c r="C249" t="n">
+        <v>344.3686432833908</v>
+      </c>
+      <c r="D249" t="n">
+        <v>336.943423385668</v>
+      </c>
+      <c r="E249" t="n">
+        <v>339.1320190429688</v>
+      </c>
+      <c r="F249" t="n">
+        <v>33493600</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B250" t="n">
+        <v>335.7841605001305</v>
+      </c>
+      <c r="C250" t="n">
+        <v>336.9834018439635</v>
+      </c>
+      <c r="D250" t="n">
+        <v>332.8360433203593</v>
+      </c>
+      <c r="E250" t="n">
+        <v>334.8047790527344</v>
+      </c>
+      <c r="F250" t="n">
+        <v>23342700</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B251" t="n">
+        <v>333.845410447285</v>
+      </c>
+      <c r="C251" t="n">
+        <v>339.7815972628325</v>
+      </c>
+      <c r="D251" t="n">
+        <v>332.6062167342666</v>
+      </c>
+      <c r="E251" t="n">
+        <v>336.9034423828125</v>
+      </c>
+      <c r="F251" t="n">
+        <v>22582300</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B252" t="n">
+        <v>340.3412297100126</v>
+      </c>
+      <c r="C252" t="n">
+        <v>344.4585782378343</v>
+      </c>
+      <c r="D252" t="n">
+        <v>339.841550898423</v>
+      </c>
+      <c r="E252" t="n">
+        <v>342.260009765625</v>
+      </c>
+      <c r="F252" t="n">
+        <v>20726900</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
         <v>46269</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B253" t="n">
         <v>342.4700012207031</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C253" t="n">
         <v>343.5299987792969</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D253" t="n">
         <v>337.0899963378906</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E253" t="n">
         <v>338.4599914550781</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F253" t="n">
         <v>23157700</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G253" t="n">
         <v>0.22</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4856,10 +10810,10 @@
         <v>343.53</v>
       </c>
       <c r="G2" t="n">
-        <v>337.1</v>
+        <v>337.09</v>
       </c>
       <c r="H2" t="n">
-        <v>20841990</v>
+        <v>23189321</v>
       </c>
       <c r="I2" t="n">
         <v>30102998</v>
@@ -4949,7 +10903,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:59:14</t>
+          <t>2026-09-07 03:08:04</t>
         </is>
       </c>
     </row>

--- a/data/GOOGL_data.xlsx
+++ b/data/GOOGL_data.xlsx
@@ -472,16 +472,16 @@
         <v>45905</v>
       </c>
       <c r="B2" t="n">
-        <v>231.3907550155185</v>
+        <v>231.3907399385365</v>
       </c>
       <c r="C2" t="n">
-        <v>234.9383456001989</v>
+        <v>234.9383302920627</v>
       </c>
       <c r="D2" t="n">
-        <v>231.091797506623</v>
+        <v>231.0917824491205</v>
       </c>
       <c r="E2" t="n">
-        <v>234.1809997558594</v>
+        <v>234.1809844970703</v>
       </c>
       <c r="F2" t="n">
         <v>46588900</v>
@@ -498,16 +498,16 @@
         <v>45908</v>
       </c>
       <c r="B3" t="n">
-        <v>234.8592056813389</v>
+        <v>234.8592210333607</v>
       </c>
       <c r="C3" t="n">
-        <v>237.512309448077</v>
+        <v>237.512324973524</v>
       </c>
       <c r="D3" t="n">
-        <v>233.0638717332001</v>
+        <v>233.0638869678665</v>
       </c>
       <c r="E3" t="n">
-        <v>233.4329071044922</v>
+        <v>233.4329223632812</v>
       </c>
       <c r="F3" t="n">
         <v>32474700</v>
@@ -524,16 +524,16 @@
         <v>45909</v>
       </c>
       <c r="B4" t="n">
-        <v>233.5625640692738</v>
+        <v>233.562578980389</v>
       </c>
       <c r="C4" t="n">
-        <v>239.8462249904786</v>
+        <v>239.8462403027557</v>
       </c>
       <c r="D4" t="n">
-        <v>232.6249999826575</v>
+        <v>232.6250148339166</v>
       </c>
       <c r="E4" t="n">
-        <v>239.0084075927734</v>
+        <v>239.0084228515625</v>
       </c>
       <c r="F4" t="n">
         <v>38061000</v>
@@ -576,16 +576,16 @@
         <v>45911</v>
       </c>
       <c r="B6" t="n">
-        <v>239.2577712479691</v>
+        <v>239.2577864756533</v>
       </c>
       <c r="C6" t="n">
-        <v>241.6216187469878</v>
+        <v>241.6216341251204</v>
       </c>
       <c r="D6" t="n">
-        <v>235.6371823693535</v>
+        <v>235.6371973666035</v>
       </c>
       <c r="E6" t="n">
-        <v>239.7464904785156</v>
+        <v>239.7465057373047</v>
       </c>
       <c r="F6" t="n">
         <v>30599300</v>
@@ -628,16 +628,16 @@
         <v>45915</v>
       </c>
       <c r="B8" t="n">
-        <v>244.0253822711298</v>
+        <v>244.0253674338205</v>
       </c>
       <c r="C8" t="n">
-        <v>251.7552796155814</v>
+        <v>251.7552643082765</v>
       </c>
       <c r="D8" t="n">
-        <v>244.0253822711298</v>
+        <v>244.0253674338205</v>
       </c>
       <c r="E8" t="n">
-        <v>250.9573516845703</v>
+        <v>250.9573364257812</v>
       </c>
       <c r="F8" t="n">
         <v>58383800</v>
@@ -654,16 +654,16 @@
         <v>45916</v>
       </c>
       <c r="B9" t="n">
-        <v>251.4261108558069</v>
+        <v>251.4261261704888</v>
       </c>
       <c r="C9" t="n">
-        <v>252.3836121103763</v>
+        <v>252.3836274833809</v>
       </c>
       <c r="D9" t="n">
-        <v>248.8228805399337</v>
+        <v>248.8228956960496</v>
       </c>
       <c r="E9" t="n">
-        <v>250.5084991455078</v>
+        <v>250.5085144042969</v>
       </c>
       <c r="F9" t="n">
         <v>34109700</v>
@@ -706,16 +706,16 @@
         <v>45918</v>
       </c>
       <c r="B11" t="n">
-        <v>251.0271530076639</v>
+        <v>251.0271682452624</v>
       </c>
       <c r="C11" t="n">
-        <v>253.3311738191467</v>
+        <v>253.3311891966015</v>
       </c>
       <c r="D11" t="n">
-        <v>249.1520399405299</v>
+        <v>249.1520550643071</v>
       </c>
       <c r="E11" t="n">
-        <v>251.3762512207031</v>
+        <v>251.3762664794922</v>
       </c>
       <c r="F11" t="n">
         <v>31239500</v>
@@ -732,16 +732,16 @@
         <v>45919</v>
       </c>
       <c r="B12" t="n">
-        <v>252.5930922260568</v>
+        <v>252.5931073967866</v>
       </c>
       <c r="C12" t="n">
-        <v>255.3359589728353</v>
+        <v>255.3359743083016</v>
       </c>
       <c r="D12" t="n">
-        <v>251.1568250217611</v>
+        <v>251.1568401062288</v>
       </c>
       <c r="E12" t="n">
-        <v>254.0592803955078</v>
+        <v>254.0592956542969</v>
       </c>
       <c r="F12" t="n">
         <v>55571400</v>
@@ -914,16 +914,16 @@
         <v>45930</v>
       </c>
       <c r="B19" t="n">
-        <v>242.1801651040411</v>
+        <v>242.180180344627</v>
       </c>
       <c r="C19" t="n">
-        <v>242.6589157556348</v>
+        <v>242.6589310263489</v>
       </c>
       <c r="D19" t="n">
-        <v>238.6294019345709</v>
+        <v>238.6294169517045</v>
       </c>
       <c r="E19" t="n">
-        <v>242.4694213867188</v>
+        <v>242.4694366455078</v>
       </c>
       <c r="F19" t="n">
         <v>34724300</v>
@@ -966,16 +966,16 @@
         <v>45932</v>
       </c>
       <c r="B21" t="n">
-        <v>244.5140808226371</v>
+        <v>244.5140960478885</v>
       </c>
       <c r="C21" t="n">
-        <v>246.1697784759451</v>
+        <v>246.1697938042925</v>
       </c>
       <c r="D21" t="n">
-        <v>241.6714827842888</v>
+        <v>241.671497832539</v>
       </c>
       <c r="E21" t="n">
-        <v>245.0526885986328</v>
+        <v>245.0527038574219</v>
       </c>
       <c r="F21" t="n">
         <v>25483300</v>
@@ -992,16 +992,16 @@
         <v>45933</v>
       </c>
       <c r="B22" t="n">
-        <v>243.8558378805103</v>
+        <v>243.8558226752064</v>
       </c>
       <c r="C22" t="n">
-        <v>245.6611405975774</v>
+        <v>245.6611252797062</v>
       </c>
       <c r="D22" t="n">
-        <v>241.0331766174326</v>
+        <v>241.0331615881319</v>
       </c>
       <c r="E22" t="n">
-        <v>244.7136077880859</v>
+        <v>244.7135925292969</v>
       </c>
       <c r="F22" t="n">
         <v>30249600</v>
@@ -1044,16 +1044,16 @@
         <v>45937</v>
       </c>
       <c r="B24" t="n">
-        <v>247.6260272338786</v>
+        <v>247.6260118192477</v>
       </c>
       <c r="C24" t="n">
-        <v>249.7903967365714</v>
+        <v>249.7903811872092</v>
       </c>
       <c r="D24" t="n">
-        <v>244.8831603422913</v>
+        <v>244.8831450984028</v>
       </c>
       <c r="E24" t="n">
-        <v>245.1225280761719</v>
+        <v>245.1225128173828</v>
       </c>
       <c r="F24" t="n">
         <v>23181300</v>
@@ -1070,16 +1070,16 @@
         <v>45938</v>
       </c>
       <c r="B25" t="n">
-        <v>244.3245879910796</v>
+        <v>244.3246032710778</v>
       </c>
       <c r="C25" t="n">
-        <v>245.3718521480096</v>
+        <v>245.3718674935034</v>
       </c>
       <c r="D25" t="n">
-        <v>243.1875457247831</v>
+        <v>243.187560933671</v>
       </c>
       <c r="E25" t="n">
-        <v>243.9854583740234</v>
+        <v>243.9854736328125</v>
       </c>
       <c r="F25" t="n">
         <v>21307100</v>
@@ -1148,16 +1148,16 @@
         <v>45943</v>
       </c>
       <c r="B28" t="n">
-        <v>239.5869258671789</v>
+        <v>239.5869408797282</v>
       </c>
       <c r="C28" t="n">
-        <v>243.8657913377574</v>
+        <v>243.865806618421</v>
       </c>
       <c r="D28" t="n">
-        <v>239.0882228174084</v>
+        <v>239.0882377987089</v>
       </c>
       <c r="E28" t="n">
-        <v>243.5166931152344</v>
+        <v>243.5167083740234</v>
       </c>
       <c r="F28" t="n">
         <v>24995000</v>
@@ -1200,16 +1200,16 @@
         <v>45945</v>
       </c>
       <c r="B30" t="n">
-        <v>246.6086514775368</v>
+        <v>246.6086665065597</v>
       </c>
       <c r="C30" t="n">
-        <v>251.4560455996756</v>
+        <v>251.4560609241123</v>
       </c>
       <c r="D30" t="n">
-        <v>245.3519253048375</v>
+        <v>245.3519402572719</v>
       </c>
       <c r="E30" t="n">
-        <v>250.3788452148438</v>
+        <v>250.3788604736328</v>
       </c>
       <c r="F30" t="n">
         <v>27007700</v>
@@ -1252,16 +1252,16 @@
         <v>45947</v>
       </c>
       <c r="B32" t="n">
-        <v>250.1095547697768</v>
+        <v>250.1095396639979</v>
       </c>
       <c r="C32" t="n">
-        <v>253.5605866634714</v>
+        <v>253.5605713492617</v>
       </c>
       <c r="D32" t="n">
-        <v>247.1672097408255</v>
+        <v>247.1671948127543</v>
       </c>
       <c r="E32" t="n">
-        <v>252.6429748535156</v>
+        <v>252.6429595947266</v>
       </c>
       <c r="F32" t="n">
         <v>29671600</v>
@@ -1330,16 +1330,16 @@
         <v>45952</v>
       </c>
       <c r="B35" t="n">
-        <v>253.7101963156115</v>
+        <v>253.710180894347</v>
       </c>
       <c r="C35" t="n">
-        <v>255.6950248045094</v>
+        <v>255.6950092626011</v>
       </c>
       <c r="D35" t="n">
-        <v>248.6433712710665</v>
+        <v>248.6433561577788</v>
       </c>
       <c r="E35" t="n">
-        <v>251.0371551513672</v>
+        <v>251.0371398925781</v>
       </c>
       <c r="F35" t="n">
         <v>35029400</v>
@@ -1382,16 +1382,16 @@
         <v>45954</v>
       </c>
       <c r="B37" t="n">
-        <v>255.9144256499636</v>
+        <v>255.9144859008052</v>
       </c>
       <c r="C37" t="n">
-        <v>261.0012024879728</v>
+        <v>261.0012639364123</v>
       </c>
       <c r="D37" t="n">
-        <v>254.6577147509474</v>
+        <v>254.6577747059171</v>
       </c>
       <c r="E37" t="n">
-        <v>259.2457885742188</v>
+        <v>259.245849609375</v>
       </c>
       <c r="F37" t="n">
         <v>28655100</v>
@@ -1408,16 +1408,16 @@
         <v>45957</v>
       </c>
       <c r="B38" t="n">
-        <v>264.1330942614516</v>
+        <v>264.1330642482098</v>
       </c>
       <c r="C38" t="n">
-        <v>269.4393020900735</v>
+        <v>269.4392714738914</v>
       </c>
       <c r="D38" t="n">
-        <v>263.5944864374467</v>
+        <v>263.5944564854066</v>
       </c>
       <c r="E38" t="n">
-        <v>268.571533203125</v>
+        <v>268.5715026855469</v>
       </c>
       <c r="F38" t="n">
         <v>35235200</v>
@@ -1434,16 +1434,16 @@
         <v>45958</v>
       </c>
       <c r="B39" t="n">
-        <v>268.9904266199372</v>
+        <v>268.9904573908112</v>
       </c>
       <c r="C39" t="n">
-        <v>270.0277373828665</v>
+        <v>270.0277682724026</v>
       </c>
       <c r="D39" t="n">
-        <v>265.8086990443333</v>
+        <v>265.808729451237</v>
       </c>
       <c r="E39" t="n">
-        <v>266.7761840820312</v>
+        <v>266.7762145996094</v>
       </c>
       <c r="F39" t="n">
         <v>29738600</v>
@@ -1460,16 +1460,16 @@
         <v>45959</v>
       </c>
       <c r="B40" t="n">
-        <v>267.055471479175</v>
+        <v>267.0555012387311</v>
       </c>
       <c r="C40" t="n">
-        <v>274.6257797911847</v>
+        <v>274.6258103943446</v>
       </c>
       <c r="D40" t="n">
-        <v>266.975692387603</v>
+        <v>266.9757221382688</v>
       </c>
       <c r="E40" t="n">
-        <v>273.8577880859375</v>
+        <v>273.8578186035156</v>
       </c>
       <c r="F40" t="n">
         <v>43580300</v>
@@ -1486,16 +1486,16 @@
         <v>45960</v>
       </c>
       <c r="B41" t="n">
-        <v>290.8336389163956</v>
+        <v>290.8336705300809</v>
       </c>
       <c r="C41" t="n">
-        <v>290.8336389163956</v>
+        <v>290.8336705300809</v>
       </c>
       <c r="D41" t="n">
-        <v>279.3335478851562</v>
+        <v>279.3335782487789</v>
       </c>
       <c r="E41" t="n">
-        <v>280.7498779296875</v>
+        <v>280.7499084472656</v>
       </c>
       <c r="F41" t="n">
         <v>74876000</v>
@@ -1564,16 +1564,16 @@
         <v>45965</v>
       </c>
       <c r="B44" t="n">
-        <v>276.0321395313242</v>
+        <v>276.032169962035</v>
       </c>
       <c r="C44" t="n">
-        <v>280.5404041676455</v>
+        <v>280.5404350953626</v>
       </c>
       <c r="D44" t="n">
-        <v>275.5434202802167</v>
+        <v>275.5434506570495</v>
       </c>
       <c r="E44" t="n">
-        <v>276.8200988769531</v>
+        <v>276.8201293945312</v>
       </c>
       <c r="F44" t="n">
         <v>30078400</v>
@@ -1616,16 +1616,16 @@
         <v>45967</v>
       </c>
       <c r="B46" t="n">
-        <v>284.5898651937554</v>
+        <v>284.5898957734926</v>
       </c>
       <c r="C46" t="n">
-        <v>287.6020510547858</v>
+        <v>287.6020819581881</v>
       </c>
       <c r="D46" t="n">
-        <v>280.4107616957575</v>
+        <v>280.4107918264418</v>
       </c>
       <c r="E46" t="n">
-        <v>284.0113830566406</v>
+        <v>284.0114135742188</v>
       </c>
       <c r="F46" t="n">
         <v>37173600</v>
@@ -1642,16 +1642,16 @@
         <v>45968</v>
       </c>
       <c r="B47" t="n">
-        <v>282.4753944065927</v>
+        <v>282.4753324126648</v>
       </c>
       <c r="C47" t="n">
-        <v>283.0439232317803</v>
+        <v>283.0438611130793</v>
       </c>
       <c r="D47" t="n">
-        <v>274.4762078378772</v>
+        <v>274.4761475995039</v>
       </c>
       <c r="E47" t="n">
-        <v>278.1067504882812</v>
+        <v>278.106689453125</v>
       </c>
       <c r="F47" t="n">
         <v>34479600</v>
@@ -1720,16 +1720,16 @@
         <v>45973</v>
       </c>
       <c r="B50" t="n">
-        <v>290.9234183741868</v>
+        <v>290.9233873275988</v>
       </c>
       <c r="C50" t="n">
-        <v>291.2525794490294</v>
+        <v>291.2525483673142</v>
       </c>
       <c r="D50" t="n">
-        <v>282.9541529801612</v>
+        <v>282.9541227840324</v>
       </c>
       <c r="E50" t="n">
-        <v>285.96630859375</v>
+        <v>285.9662780761719</v>
       </c>
       <c r="F50" t="n">
         <v>24829900</v>
@@ -1746,16 +1746,16 @@
         <v>45974</v>
       </c>
       <c r="B51" t="n">
-        <v>281.6076529103283</v>
+        <v>281.6076219797447</v>
       </c>
       <c r="C51" t="n">
-        <v>282.1063559927165</v>
+        <v>282.1063250073575</v>
       </c>
       <c r="D51" t="n">
-        <v>276.5208753822851</v>
+        <v>276.5208450104115</v>
       </c>
       <c r="E51" t="n">
-        <v>277.8474426269531</v>
+        <v>277.847412109375</v>
       </c>
       <c r="F51" t="n">
         <v>29494000</v>
@@ -1772,16 +1772,16 @@
         <v>45975</v>
       </c>
       <c r="B52" t="n">
-        <v>270.705963217399</v>
+        <v>270.7059931829425</v>
       </c>
       <c r="C52" t="n">
-        <v>277.8374099534448</v>
+        <v>277.8374407083971</v>
       </c>
       <c r="D52" t="n">
-        <v>269.997813487729</v>
+        <v>269.9978433748846</v>
       </c>
       <c r="E52" t="n">
-        <v>275.6929931640625</v>
+        <v>275.6930236816406</v>
       </c>
       <c r="F52" t="n">
         <v>31647200</v>
@@ -1798,16 +1798,16 @@
         <v>45978</v>
       </c>
       <c r="B53" t="n">
-        <v>285.0387085276487</v>
+        <v>285.038677928695</v>
       </c>
       <c r="C53" t="n">
-        <v>293.1875295999499</v>
+        <v>293.1874981262189</v>
       </c>
       <c r="D53" t="n">
-        <v>282.8344496120375</v>
+        <v>282.8344192497114</v>
       </c>
       <c r="E53" t="n">
-        <v>284.2806701660156</v>
+        <v>284.2806396484375</v>
       </c>
       <c r="F53" t="n">
         <v>52670200</v>
@@ -1902,16 +1902,16 @@
         <v>45982</v>
       </c>
       <c r="B57" t="n">
-        <v>295.6511348655125</v>
+        <v>295.6511046778972</v>
       </c>
       <c r="C57" t="n">
-        <v>303.1316807498811</v>
+        <v>303.1316497984607</v>
       </c>
       <c r="D57" t="n">
-        <v>293.0877938372482</v>
+        <v>293.0877639113642</v>
       </c>
       <c r="E57" t="n">
-        <v>298.8827209472656</v>
+        <v>298.8826904296875</v>
       </c>
       <c r="F57" t="n">
         <v>74137700</v>
@@ -1980,16 +1980,16 @@
         <v>45987</v>
       </c>
       <c r="B60" t="n">
-        <v>319.8481736259059</v>
+        <v>319.8482042131112</v>
       </c>
       <c r="C60" t="n">
-        <v>323.6582721471574</v>
+        <v>323.658303098724</v>
       </c>
       <c r="D60" t="n">
-        <v>315.9682798124272</v>
+        <v>315.9683100285969</v>
       </c>
       <c r="E60" t="n">
-        <v>319.1200866699219</v>
+        <v>319.1201171875</v>
       </c>
       <c r="F60" t="n">
         <v>51373400</v>
@@ -2006,16 +2006,16 @@
         <v>45989</v>
       </c>
       <c r="B61" t="n">
-        <v>322.5311844719001</v>
+        <v>322.5312152935296</v>
       </c>
       <c r="C61" t="n">
-        <v>326.0021684294219</v>
+        <v>326.0021995827445</v>
       </c>
       <c r="D61" t="n">
-        <v>315.9682661584897</v>
+        <v>315.9682963529555</v>
       </c>
       <c r="E61" t="n">
-        <v>319.3494567871094</v>
+        <v>319.3494873046875</v>
       </c>
       <c r="F61" t="n">
         <v>26018600</v>
@@ -2032,16 +2032,16 @@
         <v>45992</v>
       </c>
       <c r="B62" t="n">
-        <v>316.8759510785769</v>
+        <v>316.8759202886677</v>
       </c>
       <c r="C62" t="n">
-        <v>319.020368247556</v>
+        <v>319.02033724928</v>
       </c>
       <c r="D62" t="n">
-        <v>313.0758360216101</v>
+        <v>313.075805600947</v>
       </c>
       <c r="E62" t="n">
-        <v>314.0732421875</v>
+        <v>314.0732116699219</v>
       </c>
       <c r="F62" t="n">
         <v>41183000</v>
@@ -2058,16 +2058,16 @@
         <v>45993</v>
       </c>
       <c r="B63" t="n">
-        <v>315.9184251730286</v>
+        <v>315.9183945655827</v>
       </c>
       <c r="C63" t="n">
-        <v>317.5541859262309</v>
+        <v>317.554155160306</v>
       </c>
       <c r="D63" t="n">
-        <v>313.095779063488</v>
+        <v>313.0957487295115</v>
       </c>
       <c r="E63" t="n">
-        <v>314.9908447265625</v>
+        <v>314.9908142089844</v>
       </c>
       <c r="F63" t="n">
         <v>35854700</v>
@@ -2084,16 +2084,16 @@
         <v>45994</v>
       </c>
       <c r="B64" t="n">
-        <v>315.0706445626379</v>
+        <v>315.0706144021458</v>
       </c>
       <c r="C64" t="n">
-        <v>320.7458575749233</v>
+        <v>320.7458268711651</v>
       </c>
       <c r="D64" t="n">
-        <v>313.2852790244178</v>
+        <v>313.2852490348319</v>
       </c>
       <c r="E64" t="n">
-        <v>318.8009338378906</v>
+        <v>318.8009033203125</v>
       </c>
       <c r="F64" t="n">
         <v>41838300</v>
@@ -2110,16 +2110,16 @@
         <v>45995</v>
       </c>
       <c r="B65" t="n">
-        <v>321.3941698854088</v>
+        <v>321.3942008459266</v>
       </c>
       <c r="C65" t="n">
-        <v>321.5238071066378</v>
+        <v>321.5238380796439</v>
       </c>
       <c r="D65" t="n">
-        <v>313.8837033726762</v>
+        <v>313.8837336096964</v>
       </c>
       <c r="E65" t="n">
-        <v>316.7961120605469</v>
+        <v>316.796142578125</v>
       </c>
       <c r="F65" t="n">
         <v>31240900</v>
@@ -2136,16 +2136,16 @@
         <v>45996</v>
       </c>
       <c r="B66" t="n">
-        <v>318.6612638744486</v>
+        <v>318.6612335259534</v>
       </c>
       <c r="C66" t="n">
-        <v>322.3217576397153</v>
+        <v>322.3217269426038</v>
       </c>
       <c r="D66" t="n">
-        <v>318.3421170569229</v>
+        <v>318.3420867388224</v>
       </c>
       <c r="E66" t="n">
-        <v>320.4366455078125</v>
+        <v>320.4366149902344</v>
       </c>
       <c r="F66" t="n">
         <v>28851700</v>
@@ -2162,16 +2162,16 @@
         <v>45999</v>
       </c>
       <c r="B67" t="n">
-        <v>319.4285975207571</v>
+        <v>319.428628654094</v>
       </c>
       <c r="C67" t="n">
-        <v>319.8178549396436</v>
+        <v>319.8178861109197</v>
       </c>
       <c r="D67" t="n">
-        <v>310.6157547321785</v>
+        <v>310.6157850065654</v>
       </c>
       <c r="E67" t="n">
-        <v>313.1109008789062</v>
+        <v>313.1109313964844</v>
       </c>
       <c r="F67" t="n">
         <v>33909400</v>
@@ -2240,16 +2240,16 @@
         <v>46002</v>
       </c>
       <c r="B70" t="n">
-        <v>319.4585671045538</v>
+        <v>319.4585358397385</v>
       </c>
       <c r="C70" t="n">
-        <v>320.4965565243085</v>
+        <v>320.4965251579071</v>
       </c>
       <c r="D70" t="n">
-        <v>308.0008744502611</v>
+        <v>308.0008443067889</v>
       </c>
       <c r="E70" t="n">
-        <v>311.8234252929688</v>
+        <v>311.8233947753906</v>
       </c>
       <c r="F70" t="n">
         <v>42353700</v>
@@ -2292,16 +2292,16 @@
         <v>46006</v>
       </c>
       <c r="B72" t="n">
-        <v>310.7156001962807</v>
+        <v>310.7155693717638</v>
       </c>
       <c r="C72" t="n">
-        <v>310.8154121445851</v>
+        <v>310.8153813101663</v>
       </c>
       <c r="D72" t="n">
-        <v>304.2881005921093</v>
+        <v>304.288070405232</v>
       </c>
       <c r="E72" t="n">
-        <v>307.6216125488281</v>
+        <v>307.62158203125</v>
       </c>
       <c r="F72" t="n">
         <v>29151900</v>
@@ -2422,16 +2422,16 @@
         <v>46013</v>
       </c>
       <c r="B77" t="n">
-        <v>309.278400817878</v>
+        <v>309.2783702904479</v>
       </c>
       <c r="C77" t="n">
-        <v>309.5279154654388</v>
+        <v>309.5278849133803</v>
       </c>
       <c r="D77" t="n">
-        <v>304.707275417899</v>
+        <v>304.7072453416635</v>
       </c>
       <c r="E77" t="n">
-        <v>309.1785888671875</v>
+        <v>309.1785583496094</v>
       </c>
       <c r="F77" t="n">
         <v>26429900</v>
@@ -2474,16 +2474,16 @@
         <v>46015</v>
       </c>
       <c r="B79" t="n">
-        <v>314.1588359856885</v>
+        <v>314.1588665693361</v>
       </c>
       <c r="C79" t="n">
-        <v>314.4682316573388</v>
+        <v>314.4682622711062</v>
       </c>
       <c r="D79" t="n">
-        <v>311.3143938726672</v>
+        <v>311.3144241794057</v>
       </c>
       <c r="E79" t="n">
-        <v>313.4801635742188</v>
+        <v>313.4801940917969</v>
       </c>
       <c r="F79" t="n">
         <v>10097400</v>
@@ -2500,16 +2500,16 @@
         <v>46017</v>
       </c>
       <c r="B80" t="n">
-        <v>313.8694852656387</v>
+        <v>313.8694546536391</v>
       </c>
       <c r="C80" t="n">
-        <v>314.4782864028367</v>
+        <v>314.4782557314601</v>
       </c>
       <c r="D80" t="n">
-        <v>311.6737441219225</v>
+        <v>311.6737137240756</v>
       </c>
       <c r="E80" t="n">
-        <v>312.9013671875</v>
+        <v>312.9013366699219</v>
       </c>
       <c r="F80" t="n">
         <v>10899000</v>
@@ -2526,16 +2526,16 @@
         <v>46020</v>
       </c>
       <c r="B81" t="n">
-        <v>310.7655125785055</v>
+        <v>310.7654822740718</v>
       </c>
       <c r="C81" t="n">
-        <v>313.410361871903</v>
+        <v>313.4103313095557</v>
       </c>
       <c r="D81" t="n">
-        <v>310.0169686016006</v>
+        <v>310.0169383701615</v>
       </c>
       <c r="E81" t="n">
-        <v>312.9512634277344</v>
+        <v>312.9512329101562</v>
       </c>
       <c r="F81" t="n">
         <v>19621800</v>
@@ -2604,16 +2604,16 @@
         <v>46024</v>
       </c>
       <c r="B84" t="n">
-        <v>316.2847187538463</v>
+        <v>316.2847494408858</v>
       </c>
       <c r="C84" t="n">
-        <v>321.87385220157</v>
+        <v>321.8738834308866</v>
       </c>
       <c r="D84" t="n">
-        <v>309.7274673850438</v>
+        <v>309.727497435876</v>
       </c>
       <c r="E84" t="n">
-        <v>314.5381164550781</v>
+        <v>314.5381469726562</v>
       </c>
       <c r="F84" t="n">
         <v>32009400</v>
@@ -2630,16 +2630,16 @@
         <v>46027</v>
       </c>
       <c r="B85" t="n">
-        <v>317.0432662013207</v>
+        <v>317.0432968268774</v>
       </c>
       <c r="C85" t="n">
-        <v>318.4006111389099</v>
+        <v>318.4006418955826</v>
       </c>
       <c r="D85" t="n">
-        <v>314.0191501700305</v>
+        <v>314.0191805034655</v>
       </c>
       <c r="E85" t="n">
-        <v>315.9254455566406</v>
+        <v>315.9254760742188</v>
       </c>
       <c r="F85" t="n">
         <v>30195600</v>
@@ -2682,16 +2682,16 @@
         <v>46029</v>
       </c>
       <c r="B87" t="n">
-        <v>313.7496873061683</v>
+        <v>313.7496575108236</v>
       </c>
       <c r="C87" t="n">
-        <v>325.5168067446344</v>
+        <v>325.5167758318212</v>
       </c>
       <c r="D87" t="n">
-        <v>313.5800344006012</v>
+        <v>313.5800046213677</v>
       </c>
       <c r="E87" t="n">
-        <v>321.3549194335938</v>
+        <v>321.3548889160156</v>
       </c>
       <c r="F87" t="n">
         <v>35104400</v>
@@ -2760,16 +2760,16 @@
         <v>46034</v>
       </c>
       <c r="B90" t="n">
-        <v>325.1674658209474</v>
+        <v>325.1674358606418</v>
       </c>
       <c r="C90" t="n">
-        <v>333.3914890456728</v>
+        <v>333.3914583276215</v>
       </c>
       <c r="D90" t="n">
-        <v>324.3690311583512</v>
+        <v>324.3690012716118</v>
       </c>
       <c r="E90" t="n">
-        <v>331.2156982421875</v>
+        <v>331.2156677246094</v>
       </c>
       <c r="F90" t="n">
         <v>33923900</v>
@@ -2786,16 +2786,16 @@
         <v>46035</v>
       </c>
       <c r="B91" t="n">
-        <v>334.2996793666924</v>
+        <v>334.2997097916206</v>
       </c>
       <c r="C91" t="n">
-        <v>339.8289010736461</v>
+        <v>339.828932001794</v>
       </c>
       <c r="D91" t="n">
-        <v>332.9722446137951</v>
+        <v>332.9722749179122</v>
       </c>
       <c r="E91" t="n">
-        <v>335.3176879882812</v>
+        <v>335.3177185058594</v>
       </c>
       <c r="F91" t="n">
         <v>33517600</v>
@@ -2838,16 +2838,16 @@
         <v>46037</v>
       </c>
       <c r="B93" t="n">
-        <v>336.9944512235705</v>
+        <v>336.9944202593897</v>
       </c>
       <c r="C93" t="n">
-        <v>337.03438209247</v>
+        <v>337.0343511246202</v>
       </c>
       <c r="D93" t="n">
-        <v>330.097863235539</v>
+        <v>330.0978329050398</v>
       </c>
       <c r="E93" t="n">
-        <v>332.1339111328125</v>
+        <v>332.1338806152344</v>
       </c>
       <c r="F93" t="n">
         <v>28442400</v>
@@ -2942,16 +2942,16 @@
         <v>46044</v>
       </c>
       <c r="B97" t="n">
-        <v>333.8006666576773</v>
+        <v>333.8006975362521</v>
       </c>
       <c r="C97" t="n">
-        <v>334.4992893099707</v>
+        <v>334.4993202531722</v>
       </c>
       <c r="D97" t="n">
-        <v>328.1117212092731</v>
+        <v>328.1117515615861</v>
       </c>
       <c r="E97" t="n">
-        <v>329.8982543945312</v>
+        <v>329.8982849121094</v>
       </c>
       <c r="F97" t="n">
         <v>26253600</v>
@@ -3046,16 +3046,16 @@
         <v>46050</v>
       </c>
       <c r="B101" t="n">
-        <v>335.4075262381039</v>
+        <v>335.4075567602221</v>
       </c>
       <c r="C101" t="n">
-        <v>336.8846637353836</v>
+        <v>336.8846943919215</v>
       </c>
       <c r="D101" t="n">
-        <v>331.2955302242731</v>
+        <v>331.2955603721992</v>
       </c>
       <c r="E101" t="n">
-        <v>335.3576354980469</v>
+        <v>335.357666015625</v>
       </c>
       <c r="F101" t="n">
         <v>27434400</v>
@@ -3072,16 +3072,16 @@
         <v>46051</v>
       </c>
       <c r="B102" t="n">
-        <v>339.6393000059441</v>
+        <v>339.639269303412</v>
       </c>
       <c r="C102" t="n">
-        <v>341.625457159737</v>
+        <v>341.6254262776615</v>
       </c>
       <c r="D102" t="n">
-        <v>325.9060355700189</v>
+        <v>325.9060061089392</v>
       </c>
       <c r="E102" t="n">
-        <v>337.5932922363281</v>
+        <v>337.59326171875</v>
       </c>
       <c r="F102" t="n">
         <v>39785600</v>
@@ -3124,16 +3124,16 @@
         <v>46055</v>
       </c>
       <c r="B104" t="n">
-        <v>335.5672073695487</v>
+        <v>335.5672372238362</v>
       </c>
       <c r="C104" t="n">
-        <v>344.1604758527643</v>
+        <v>344.160506471566</v>
       </c>
       <c r="D104" t="n">
-        <v>334.9783565494149</v>
+        <v>334.9783863513143</v>
       </c>
       <c r="E104" t="n">
-        <v>343.022705078125</v>
+        <v>343.0227355957031</v>
       </c>
       <c r="F104" t="n">
         <v>32006100</v>
@@ -3176,16 +3176,16 @@
         <v>46057</v>
       </c>
       <c r="B106" t="n">
-        <v>342.2941565134455</v>
+        <v>342.2941250868659</v>
       </c>
       <c r="C106" t="n">
-        <v>342.6434831024425</v>
+        <v>342.6434516437907</v>
       </c>
       <c r="D106" t="n">
-        <v>327.8821884154679</v>
+        <v>327.8821583120744</v>
       </c>
       <c r="E106" t="n">
-        <v>332.3934326171875</v>
+        <v>332.3934020996094</v>
       </c>
       <c r="F106" t="n">
         <v>70618400</v>
@@ -3202,16 +3202,16 @@
         <v>46058</v>
       </c>
       <c r="B107" t="n">
-        <v>311.6138496060838</v>
+        <v>311.6138208417116</v>
       </c>
       <c r="C107" t="n">
-        <v>332.0441098613053</v>
+        <v>332.0440792110618</v>
       </c>
       <c r="D107" t="n">
-        <v>305.8650224655501</v>
+        <v>305.8649942318392</v>
       </c>
       <c r="E107" t="n">
-        <v>330.6069030761719</v>
+        <v>330.6068725585938</v>
       </c>
       <c r="F107" t="n">
         <v>88205800</v>
@@ -3306,16 +3306,16 @@
         <v>46064</v>
       </c>
       <c r="B111" t="n">
-        <v>318.3506892240785</v>
+        <v>318.3507205277581</v>
       </c>
       <c r="C111" t="n">
-        <v>320.4366276261131</v>
+        <v>320.4366591349046</v>
       </c>
       <c r="D111" t="n">
-        <v>309.0587679521403</v>
+        <v>309.0587983421378</v>
       </c>
       <c r="E111" t="n">
-        <v>310.3562316894531</v>
+        <v>310.3562622070312</v>
       </c>
       <c r="F111" t="n">
         <v>45406400</v>
@@ -3332,16 +3332,16 @@
         <v>46065</v>
       </c>
       <c r="B112" t="n">
-        <v>311.4840826487114</v>
+        <v>311.4840518259579</v>
       </c>
       <c r="C112" t="n">
-        <v>315.6260194522374</v>
+        <v>315.6259882196205</v>
       </c>
       <c r="D112" t="n">
-        <v>306.603592280419</v>
+        <v>306.603561940612</v>
       </c>
       <c r="E112" t="n">
-        <v>308.4000854492188</v>
+        <v>308.4000549316406</v>
       </c>
       <c r="F112" t="n">
         <v>47761300</v>
@@ -3462,16 +3462,16 @@
         <v>46073</v>
       </c>
       <c r="B117" t="n">
-        <v>303.7291917307074</v>
+        <v>303.7291622459488</v>
       </c>
       <c r="C117" t="n">
-        <v>315.8855378192499</v>
+        <v>315.885507154404</v>
       </c>
       <c r="D117" t="n">
-        <v>303.3099937290923</v>
+        <v>303.3099642850277</v>
       </c>
       <c r="E117" t="n">
-        <v>314.3684997558594</v>
+        <v>314.3684692382812</v>
       </c>
       <c r="F117" t="n">
         <v>53210800</v>
@@ -3540,16 +3540,16 @@
         <v>46078</v>
       </c>
       <c r="B120" t="n">
-        <v>311.4541454679639</v>
+        <v>311.4541150323118</v>
       </c>
       <c r="C120" t="n">
-        <v>313.031095017384</v>
+        <v>313.0310644276307</v>
       </c>
       <c r="D120" t="n">
-        <v>308.8392369672335</v>
+        <v>308.8392067871133</v>
       </c>
       <c r="E120" t="n">
-        <v>312.2925109863281</v>
+        <v>312.29248046875</v>
       </c>
       <c r="F120" t="n">
         <v>29963600</v>
@@ -3566,16 +3566,16 @@
         <v>46079</v>
       </c>
       <c r="B121" t="n">
-        <v>312.0330001798944</v>
+        <v>312.0330312197015</v>
       </c>
       <c r="C121" t="n">
-        <v>312.5320293917034</v>
+        <v>312.5320604811519</v>
       </c>
       <c r="D121" t="n">
-        <v>301.762970472535</v>
+        <v>301.7630004907203</v>
       </c>
       <c r="E121" t="n">
-        <v>306.783203125</v>
+        <v>306.7832336425781</v>
       </c>
       <c r="F121" t="n">
         <v>36431200</v>
@@ -3696,16 +3696,16 @@
         <v>46086</v>
       </c>
       <c r="B126" t="n">
-        <v>302.4516780897468</v>
+        <v>302.4516473530844</v>
       </c>
       <c r="C126" t="n">
-        <v>302.7111526067185</v>
+        <v>302.711121843687</v>
       </c>
       <c r="D126" t="n">
-        <v>297.4114640277728</v>
+        <v>297.4114338033223</v>
       </c>
       <c r="E126" t="n">
-        <v>300.2958679199219</v>
+        <v>300.2958374023438</v>
       </c>
       <c r="F126" t="n">
         <v>35752300</v>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-07 03:08:04</t>
+          <t>2026-09-08 08:51:55</t>
         </is>
       </c>
     </row>

--- a/data/GOOGL_data.xlsx
+++ b/data/GOOGL_data.xlsx
@@ -433,22 +433,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Open</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Close</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -469,25 +469,17 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45905</v>
-      </c>
-      <c r="B2" t="n">
-        <v>231.3907399385365</v>
-      </c>
-      <c r="C2" t="n">
-        <v>234.9383302920627</v>
-      </c>
-      <c r="D2" t="n">
-        <v>231.0917824491205</v>
-      </c>
-      <c r="E2" t="n">
-        <v>234.1809844970703</v>
-      </c>
+        <v>45908</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>46588900</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -495,25 +487,25 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45908</v>
+        <v>45909</v>
       </c>
       <c r="B3" t="n">
-        <v>234.8592210333607</v>
+        <v>239.0084228515625</v>
       </c>
       <c r="C3" t="n">
-        <v>237.512324973524</v>
+        <v>239.8462403027557</v>
       </c>
       <c r="D3" t="n">
-        <v>233.0638869678665</v>
+        <v>232.6250148339166</v>
       </c>
       <c r="E3" t="n">
-        <v>233.4329223632812</v>
+        <v>233.562578980389</v>
       </c>
       <c r="F3" t="n">
-        <v>32474700</v>
+        <v>38061000</v>
       </c>
       <c r="G3" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -521,22 +513,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="B4" t="n">
-        <v>233.562578980389</v>
+        <v>238.5495910644531</v>
       </c>
       <c r="C4" t="n">
-        <v>239.8462403027557</v>
+        <v>241.0331374820224</v>
       </c>
       <c r="D4" t="n">
-        <v>232.6250148339166</v>
+        <v>237.2330230591544</v>
       </c>
       <c r="E4" t="n">
-        <v>239.0084228515625</v>
+        <v>238.2802871832208</v>
       </c>
       <c r="F4" t="n">
-        <v>38061000</v>
+        <v>35141100</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +539,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B5" t="n">
-        <v>238.2803024247839</v>
+        <v>239.7464904785156</v>
       </c>
       <c r="C5" t="n">
-        <v>241.0331528996711</v>
+        <v>241.6216187469878</v>
       </c>
       <c r="D5" t="n">
-        <v>237.2330382337294</v>
+        <v>235.6371823693535</v>
       </c>
       <c r="E5" t="n">
-        <v>238.5496063232422</v>
+        <v>239.2577712479691</v>
       </c>
       <c r="F5" t="n">
-        <v>35141100</v>
+        <v>30599300</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +565,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B6" t="n">
-        <v>239.2577864756533</v>
+        <v>240.1753997802734</v>
       </c>
       <c r="C6" t="n">
-        <v>241.6216341251204</v>
+        <v>241.4520784124984</v>
       </c>
       <c r="D6" t="n">
-        <v>235.6371973666035</v>
+        <v>237.3826595650776</v>
       </c>
       <c r="E6" t="n">
-        <v>239.7465057373047</v>
+        <v>239.746507229255</v>
       </c>
       <c r="F6" t="n">
-        <v>30599300</v>
+        <v>26771600</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +591,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B7" t="n">
-        <v>239.7464919977143</v>
+        <v>250.9573364257812</v>
       </c>
       <c r="C7" t="n">
-        <v>241.4520630725996</v>
+        <v>251.7552643082765</v>
       </c>
       <c r="D7" t="n">
-        <v>237.3826444837165</v>
+        <v>244.0253674338205</v>
       </c>
       <c r="E7" t="n">
-        <v>240.1753845214844</v>
+        <v>244.0253674338205</v>
       </c>
       <c r="F7" t="n">
-        <v>26771600</v>
+        <v>58383800</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +617,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B8" t="n">
-        <v>244.0253674338205</v>
+        <v>250.5084991455078</v>
       </c>
       <c r="C8" t="n">
-        <v>251.7552643082765</v>
+        <v>252.3836121103763</v>
       </c>
       <c r="D8" t="n">
-        <v>244.0253674338205</v>
+        <v>248.8228805399337</v>
       </c>
       <c r="E8" t="n">
-        <v>250.9573364257812</v>
+        <v>251.4261108558069</v>
       </c>
       <c r="F8" t="n">
-        <v>58383800</v>
+        <v>34109700</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +643,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B9" t="n">
-        <v>251.4261261704888</v>
+        <v>248.8827362060547</v>
       </c>
       <c r="C9" t="n">
-        <v>252.3836274833809</v>
+        <v>250.9473740826164</v>
       </c>
       <c r="D9" t="n">
-        <v>248.8228956960496</v>
+        <v>245.6411664684413</v>
       </c>
       <c r="E9" t="n">
-        <v>250.5085144042969</v>
+        <v>250.5683549046871</v>
       </c>
       <c r="F9" t="n">
-        <v>34109700</v>
+        <v>34108000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +669,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B10" t="n">
-        <v>250.5683549046871</v>
+        <v>251.3762512207031</v>
       </c>
       <c r="C10" t="n">
-        <v>250.9473740826164</v>
+        <v>253.3311738191467</v>
       </c>
       <c r="D10" t="n">
-        <v>245.6411664684413</v>
+        <v>249.1520399405299</v>
       </c>
       <c r="E10" t="n">
-        <v>248.8827362060547</v>
+        <v>251.0271530076639</v>
       </c>
       <c r="F10" t="n">
-        <v>34108000</v>
+        <v>31239500</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +695,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B11" t="n">
-        <v>251.0271682452624</v>
+        <v>254.0592803955078</v>
       </c>
       <c r="C11" t="n">
-        <v>253.3311891966015</v>
+        <v>255.3359589728353</v>
       </c>
       <c r="D11" t="n">
-        <v>249.1520550643071</v>
+        <v>251.1568250217611</v>
       </c>
       <c r="E11" t="n">
-        <v>251.3762664794922</v>
+        <v>252.5930922260568</v>
       </c>
       <c r="F11" t="n">
-        <v>31239500</v>
+        <v>55571400</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +721,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B12" t="n">
-        <v>252.5931073967866</v>
+        <v>251.8749694824219</v>
       </c>
       <c r="C12" t="n">
-        <v>255.3359743083016</v>
+        <v>255.1165394138156</v>
       </c>
       <c r="D12" t="n">
-        <v>251.1568401062288</v>
+        <v>249.6507580677981</v>
       </c>
       <c r="E12" t="n">
-        <v>254.0592956542969</v>
+        <v>253.7700350469374</v>
       </c>
       <c r="F12" t="n">
-        <v>55571400</v>
+        <v>32290500</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +747,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B13" t="n">
-        <v>253.7700350469374</v>
+        <v>251.0072174072266</v>
       </c>
       <c r="C13" t="n">
-        <v>255.1165394138156</v>
+        <v>253.7002107757565</v>
       </c>
       <c r="D13" t="n">
-        <v>249.6507580677981</v>
+        <v>249.8302703204236</v>
       </c>
       <c r="E13" t="n">
-        <v>251.8749694824219</v>
+        <v>252.38362744671</v>
       </c>
       <c r="F13" t="n">
-        <v>32290500</v>
+        <v>26628000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +773,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B14" t="n">
-        <v>252.38362744671</v>
+        <v>246.4989318847656</v>
       </c>
       <c r="C14" t="n">
-        <v>253.7002107757565</v>
+        <v>251.6954241290499</v>
       </c>
       <c r="D14" t="n">
-        <v>249.8302703204236</v>
+        <v>245.8007506899351</v>
       </c>
       <c r="E14" t="n">
-        <v>251.0072174072266</v>
+        <v>251.0072115158567</v>
       </c>
       <c r="F14" t="n">
-        <v>26628000</v>
+        <v>28201000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +799,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B15" t="n">
-        <v>251.0072270537175</v>
+        <v>245.1524200439453</v>
       </c>
       <c r="C15" t="n">
-        <v>251.6954397095125</v>
+        <v>245.8506164364007</v>
       </c>
       <c r="D15" t="n">
-        <v>245.8007659055053</v>
+        <v>240.1155317960277</v>
       </c>
       <c r="E15" t="n">
-        <v>246.4989471435547</v>
+        <v>243.76602627878</v>
       </c>
       <c r="F15" t="n">
-        <v>28201000</v>
+        <v>31020400</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +825,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B16" t="n">
-        <v>243.76602627878</v>
+        <v>245.9004974365234</v>
       </c>
       <c r="C16" t="n">
-        <v>245.8506164364007</v>
+        <v>248.7730319241888</v>
       </c>
       <c r="D16" t="n">
-        <v>240.1155317960277</v>
+        <v>245.3319838637119</v>
       </c>
       <c r="E16" t="n">
-        <v>245.1524200439453</v>
+        <v>246.429136680309</v>
       </c>
       <c r="F16" t="n">
-        <v>31020400</v>
+        <v>18503200</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +851,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B17" t="n">
-        <v>246.429136680309</v>
+        <v>243.4169616699219</v>
       </c>
       <c r="C17" t="n">
-        <v>248.7730319241888</v>
+        <v>250.4985358461003</v>
       </c>
       <c r="D17" t="n">
-        <v>245.3319838637119</v>
+        <v>242.1402830798725</v>
       </c>
       <c r="E17" t="n">
-        <v>245.9004974365234</v>
+        <v>247.2071078925349</v>
       </c>
       <c r="F17" t="n">
-        <v>18503200</v>
+        <v>32505800</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +877,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B18" t="n">
-        <v>247.2070923961575</v>
+        <v>242.4694213867188</v>
       </c>
       <c r="C18" t="n">
-        <v>250.4985201433971</v>
+        <v>242.6589157556348</v>
       </c>
       <c r="D18" t="n">
-        <v>242.1402679011131</v>
+        <v>238.6294019345709</v>
       </c>
       <c r="E18" t="n">
-        <v>243.4169464111328</v>
+        <v>242.1801651040411</v>
       </c>
       <c r="F18" t="n">
-        <v>32505800</v>
+        <v>34724300</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +903,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B19" t="n">
-        <v>242.180180344627</v>
+        <v>244.2647247314453</v>
       </c>
       <c r="C19" t="n">
-        <v>242.6589310263489</v>
+        <v>245.6611022710827</v>
       </c>
       <c r="D19" t="n">
-        <v>238.6294169517045</v>
+        <v>237.991047651448</v>
       </c>
       <c r="E19" t="n">
-        <v>242.4694366455078</v>
+        <v>240.1254958950803</v>
       </c>
       <c r="F19" t="n">
-        <v>34724300</v>
+        <v>31658200</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +929,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B20" t="n">
-        <v>240.125510895299</v>
+        <v>245.0526885986328</v>
       </c>
       <c r="C20" t="n">
-        <v>245.661117617101</v>
+        <v>246.1697784759451</v>
       </c>
       <c r="D20" t="n">
-        <v>237.9910625183314</v>
+        <v>241.6714827842888</v>
       </c>
       <c r="E20" t="n">
-        <v>244.2647399902344</v>
+        <v>244.5140808226371</v>
       </c>
       <c r="F20" t="n">
-        <v>31658200</v>
+        <v>25483300</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +955,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B21" t="n">
-        <v>244.5140960478885</v>
+        <v>244.7136077880859</v>
       </c>
       <c r="C21" t="n">
-        <v>246.1697938042925</v>
+        <v>245.6611405975774</v>
       </c>
       <c r="D21" t="n">
-        <v>241.671497832539</v>
+        <v>241.0331766174326</v>
       </c>
       <c r="E21" t="n">
-        <v>245.0527038574219</v>
+        <v>243.8558378805103</v>
       </c>
       <c r="F21" t="n">
-        <v>25483300</v>
+        <v>30249600</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +981,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B22" t="n">
-        <v>243.8558226752064</v>
+        <v>249.7804107666016</v>
       </c>
       <c r="C22" t="n">
-        <v>245.6611252797062</v>
+        <v>250.6681168360691</v>
       </c>
       <c r="D22" t="n">
-        <v>241.0331615881319</v>
+        <v>243.9455940157645</v>
       </c>
       <c r="E22" t="n">
-        <v>244.7135925292969</v>
+        <v>244.1450721986699</v>
       </c>
       <c r="F22" t="n">
-        <v>30249600</v>
+        <v>28894700</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1007,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B23" t="n">
-        <v>244.145057284137</v>
+        <v>245.1225128173828</v>
       </c>
       <c r="C23" t="n">
-        <v>250.6681015230512</v>
+        <v>249.7903811872092</v>
       </c>
       <c r="D23" t="n">
-        <v>243.9455791134174</v>
+        <v>244.8831450984028</v>
       </c>
       <c r="E23" t="n">
-        <v>249.7803955078125</v>
+        <v>247.6260118192477</v>
       </c>
       <c r="F23" t="n">
-        <v>28894700</v>
+        <v>23181300</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1033,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B24" t="n">
-        <v>247.6260118192477</v>
+        <v>243.9854583740234</v>
       </c>
       <c r="C24" t="n">
-        <v>249.7903811872092</v>
+        <v>245.3718521480096</v>
       </c>
       <c r="D24" t="n">
-        <v>244.8831450984028</v>
+        <v>243.1875457247831</v>
       </c>
       <c r="E24" t="n">
-        <v>245.1225128173828</v>
+        <v>244.3245879910796</v>
       </c>
       <c r="F24" t="n">
-        <v>23181300</v>
+        <v>21307100</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1059,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B25" t="n">
-        <v>244.3246032710778</v>
+        <v>240.9034881591797</v>
       </c>
       <c r="C25" t="n">
-        <v>245.3718674935034</v>
+        <v>244.1251055211473</v>
       </c>
       <c r="D25" t="n">
-        <v>243.187560933671</v>
+        <v>238.5296568297252</v>
       </c>
       <c r="E25" t="n">
-        <v>243.9854736328125</v>
+        <v>243.8358644557508</v>
       </c>
       <c r="F25" t="n">
-        <v>21307100</v>
+        <v>27892100</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1085,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B26" t="n">
-        <v>243.8358644557508</v>
+        <v>235.9563598632812</v>
       </c>
       <c r="C26" t="n">
-        <v>244.1251055211473</v>
+        <v>243.4568425066541</v>
       </c>
       <c r="D26" t="n">
-        <v>238.5296568297252</v>
+        <v>235.2282424787384</v>
       </c>
       <c r="E26" t="n">
-        <v>240.9034881591797</v>
+        <v>240.8037387238312</v>
       </c>
       <c r="F26" t="n">
-        <v>27892100</v>
+        <v>33180300</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1111,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B27" t="n">
-        <v>240.8037387238312</v>
+        <v>243.5166931152344</v>
       </c>
       <c r="C27" t="n">
-        <v>243.4568425066541</v>
+        <v>243.8657913377574</v>
       </c>
       <c r="D27" t="n">
-        <v>235.2282424787384</v>
+        <v>239.0882228174084</v>
       </c>
       <c r="E27" t="n">
-        <v>235.9563598632812</v>
+        <v>239.5869258671789</v>
       </c>
       <c r="F27" t="n">
-        <v>33180300</v>
+        <v>24995000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1137,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B28" t="n">
-        <v>239.5869408797282</v>
+        <v>244.8133239746094</v>
       </c>
       <c r="C28" t="n">
-        <v>243.865806618421</v>
+        <v>246.4789903337629</v>
       </c>
       <c r="D28" t="n">
-        <v>239.0882377987089</v>
+        <v>239.8861354100955</v>
       </c>
       <c r="E28" t="n">
-        <v>243.5167083740234</v>
+        <v>240.6042690189676</v>
       </c>
       <c r="F28" t="n">
-        <v>24995000</v>
+        <v>22111600</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1163,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B29" t="n">
-        <v>240.6042690189676</v>
+        <v>250.3788452148438</v>
       </c>
       <c r="C29" t="n">
-        <v>246.4789903337629</v>
+        <v>251.4560455996756</v>
       </c>
       <c r="D29" t="n">
-        <v>239.8861354100955</v>
+        <v>245.3519253048375</v>
       </c>
       <c r="E29" t="n">
-        <v>244.8133239746094</v>
+        <v>246.6086514775368</v>
       </c>
       <c r="F29" t="n">
-        <v>22111600</v>
+        <v>27007700</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1189,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B30" t="n">
-        <v>246.6086665065597</v>
+        <v>250.8077392578125</v>
       </c>
       <c r="C30" t="n">
-        <v>251.4560609241123</v>
+        <v>256.2934574717041</v>
       </c>
       <c r="D30" t="n">
-        <v>245.3519402572719</v>
+        <v>249.4512663819502</v>
       </c>
       <c r="E30" t="n">
-        <v>250.3788604736328</v>
+        <v>251.1169327071502</v>
       </c>
       <c r="F30" t="n">
-        <v>27007700</v>
+        <v>27997200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1215,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B31" t="n">
-        <v>251.1169327071502</v>
+        <v>252.6429595947266</v>
       </c>
       <c r="C31" t="n">
-        <v>256.2934574717041</v>
+        <v>253.5605713492617</v>
       </c>
       <c r="D31" t="n">
-        <v>249.4512663819502</v>
+        <v>247.1671948127543</v>
       </c>
       <c r="E31" t="n">
-        <v>250.8077392578125</v>
+        <v>250.1095396639979</v>
       </c>
       <c r="F31" t="n">
-        <v>27997200</v>
+        <v>29671600</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1241,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B32" t="n">
-        <v>250.1095396639979</v>
+        <v>255.8845367431641</v>
       </c>
       <c r="C32" t="n">
-        <v>253.5605713492617</v>
+        <v>256.6625123260812</v>
       </c>
       <c r="D32" t="n">
-        <v>247.1671948127543</v>
+        <v>253.5705623788801</v>
       </c>
       <c r="E32" t="n">
-        <v>252.6429595947266</v>
+        <v>254.0293759063695</v>
       </c>
       <c r="F32" t="n">
-        <v>29671600</v>
+        <v>22350200</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1267,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B33" t="n">
-        <v>254.0293759063695</v>
+        <v>249.8103332519531</v>
       </c>
       <c r="C33" t="n">
-        <v>256.6625123260812</v>
+        <v>254.2188662949897</v>
       </c>
       <c r="D33" t="n">
-        <v>253.5705623788801</v>
+        <v>243.5166881090968</v>
       </c>
       <c r="E33" t="n">
-        <v>255.8845367431641</v>
+        <v>254.079230052693</v>
       </c>
       <c r="F33" t="n">
-        <v>22350200</v>
+        <v>47312100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1293,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B34" t="n">
-        <v>254.079230052693</v>
+        <v>251.0371551513672</v>
       </c>
       <c r="C34" t="n">
-        <v>254.2188662949897</v>
+        <v>255.6950248045094</v>
       </c>
       <c r="D34" t="n">
-        <v>243.5166881090968</v>
+        <v>248.6433712710665</v>
       </c>
       <c r="E34" t="n">
-        <v>249.8103332519531</v>
+        <v>253.7101963156115</v>
       </c>
       <c r="F34" t="n">
-        <v>47312100</v>
+        <v>35029400</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1319,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B35" t="n">
-        <v>253.710180894347</v>
+        <v>252.4235382080078</v>
       </c>
       <c r="C35" t="n">
-        <v>255.6950092626011</v>
+        <v>254.3784456458486</v>
       </c>
       <c r="D35" t="n">
-        <v>248.6433561577788</v>
+        <v>251.196732963501</v>
       </c>
       <c r="E35" t="n">
-        <v>251.0371398925781</v>
+        <v>252.3237915100895</v>
       </c>
       <c r="F35" t="n">
-        <v>35029400</v>
+        <v>19901400</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1345,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B36" t="n">
-        <v>252.3237915100895</v>
+        <v>259.2458190917969</v>
       </c>
       <c r="C36" t="n">
-        <v>254.3784456458486</v>
+        <v>261.0012332121926</v>
       </c>
       <c r="D36" t="n">
-        <v>251.196732963501</v>
+        <v>254.6577447284323</v>
       </c>
       <c r="E36" t="n">
-        <v>252.4235382080078</v>
+        <v>255.9144557753844</v>
       </c>
       <c r="F36" t="n">
-        <v>19901400</v>
+        <v>28655100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1371,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B37" t="n">
-        <v>255.9144859008052</v>
+        <v>268.571533203125</v>
       </c>
       <c r="C37" t="n">
-        <v>261.0012639364123</v>
+        <v>269.4393020900735</v>
       </c>
       <c r="D37" t="n">
-        <v>254.6577747059171</v>
+        <v>263.5944864374467</v>
       </c>
       <c r="E37" t="n">
-        <v>259.245849609375</v>
+        <v>264.1330942614516</v>
       </c>
       <c r="F37" t="n">
-        <v>28655100</v>
+        <v>35235200</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1397,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B38" t="n">
-        <v>264.1330642482098</v>
+        <v>266.7761840820312</v>
       </c>
       <c r="C38" t="n">
-        <v>269.4392714738914</v>
+        <v>270.0277373828665</v>
       </c>
       <c r="D38" t="n">
-        <v>263.5944564854066</v>
+        <v>265.8086990443333</v>
       </c>
       <c r="E38" t="n">
-        <v>268.5715026855469</v>
+        <v>268.9904266199372</v>
       </c>
       <c r="F38" t="n">
-        <v>35235200</v>
+        <v>29738600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1423,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B39" t="n">
-        <v>268.9904573908112</v>
+        <v>273.8577880859375</v>
       </c>
       <c r="C39" t="n">
-        <v>270.0277682724026</v>
+        <v>274.6257797911847</v>
       </c>
       <c r="D39" t="n">
-        <v>265.808729451237</v>
+        <v>266.975692387603</v>
       </c>
       <c r="E39" t="n">
-        <v>266.7762145996094</v>
+        <v>267.055471479175</v>
       </c>
       <c r="F39" t="n">
-        <v>29738600</v>
+        <v>43580300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1449,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B40" t="n">
-        <v>267.0555012387311</v>
+        <v>280.7499084472656</v>
       </c>
       <c r="C40" t="n">
-        <v>274.6258103943446</v>
+        <v>290.8336705300809</v>
       </c>
       <c r="D40" t="n">
-        <v>266.9757221382688</v>
+        <v>279.3335782487789</v>
       </c>
       <c r="E40" t="n">
-        <v>273.8578186035156</v>
+        <v>290.8336705300809</v>
       </c>
       <c r="F40" t="n">
-        <v>43580300</v>
+        <v>74876000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1475,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B41" t="n">
-        <v>290.8336705300809</v>
+        <v>280.4606323242188</v>
       </c>
       <c r="C41" t="n">
-        <v>290.8336705300809</v>
+        <v>285.2581533777714</v>
       </c>
       <c r="D41" t="n">
-        <v>279.3335782487789</v>
+        <v>276.3114191679317</v>
       </c>
       <c r="E41" t="n">
-        <v>280.7499084472656</v>
+        <v>282.4753817503845</v>
       </c>
       <c r="F41" t="n">
-        <v>74876000</v>
+        <v>39267900</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1501,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B42" t="n">
-        <v>282.4753817503845</v>
+        <v>282.9840698242188</v>
       </c>
       <c r="C42" t="n">
-        <v>285.2581533777714</v>
+        <v>284.7893724933962</v>
       </c>
       <c r="D42" t="n">
-        <v>276.3114191679317</v>
+        <v>279.0742243823285</v>
       </c>
       <c r="E42" t="n">
-        <v>280.4606323242188</v>
+        <v>281.4480558536455</v>
       </c>
       <c r="F42" t="n">
-        <v>39267900</v>
+        <v>29786000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1527,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B43" t="n">
-        <v>281.4480558536455</v>
+        <v>276.8200988769531</v>
       </c>
       <c r="C43" t="n">
-        <v>284.7893724933962</v>
+        <v>280.5404041676455</v>
       </c>
       <c r="D43" t="n">
-        <v>279.0742243823285</v>
+        <v>275.5434202802167</v>
       </c>
       <c r="E43" t="n">
-        <v>282.9840698242188</v>
+        <v>276.0321395313242</v>
       </c>
       <c r="F43" t="n">
-        <v>29786000</v>
+        <v>30078400</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1553,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B44" t="n">
-        <v>276.032169962035</v>
+        <v>283.572509765625</v>
       </c>
       <c r="C44" t="n">
-        <v>280.5404350953626</v>
+        <v>285.677052345188</v>
       </c>
       <c r="D44" t="n">
-        <v>275.5434506570495</v>
+        <v>276.62058842555</v>
       </c>
       <c r="E44" t="n">
-        <v>276.8201293945312</v>
+        <v>278.1466184544242</v>
       </c>
       <c r="F44" t="n">
-        <v>30078400</v>
+        <v>31010300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1579,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B45" t="n">
-        <v>278.1466184544242</v>
+        <v>284.0113830566406</v>
       </c>
       <c r="C45" t="n">
-        <v>285.677052345188</v>
+        <v>287.6020510547858</v>
       </c>
       <c r="D45" t="n">
-        <v>276.62058842555</v>
+        <v>280.4107616957575</v>
       </c>
       <c r="E45" t="n">
-        <v>283.572509765625</v>
+        <v>284.5898651937554</v>
       </c>
       <c r="F45" t="n">
-        <v>31010300</v>
+        <v>37173600</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1605,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B46" t="n">
-        <v>284.5898957734926</v>
+        <v>278.1067199707031</v>
       </c>
       <c r="C46" t="n">
-        <v>287.6020819581881</v>
+        <v>283.0438921724298</v>
       </c>
       <c r="D46" t="n">
-        <v>280.4107918264418</v>
+        <v>274.4761777186906</v>
       </c>
       <c r="E46" t="n">
-        <v>284.0114135742188</v>
+        <v>282.4753634096288</v>
       </c>
       <c r="F46" t="n">
-        <v>37173600</v>
+        <v>34479600</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1631,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B47" t="n">
-        <v>282.4753324126648</v>
+        <v>289.3475036621094</v>
       </c>
       <c r="C47" t="n">
-        <v>283.0438611130793</v>
+        <v>290.0456696400176</v>
       </c>
       <c r="D47" t="n">
-        <v>274.4761475995039</v>
+        <v>282.1262631003564</v>
       </c>
       <c r="E47" t="n">
-        <v>278.106689453125</v>
+        <v>283.6822445549795</v>
       </c>
       <c r="F47" t="n">
-        <v>34479600</v>
+        <v>29557300</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1657,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B48" t="n">
-        <v>283.6822445549795</v>
+        <v>290.5543518066406</v>
       </c>
       <c r="C48" t="n">
-        <v>290.0456696400176</v>
+        <v>291.1627853205446</v>
       </c>
       <c r="D48" t="n">
-        <v>282.1262631003564</v>
+        <v>286.5747114373448</v>
       </c>
       <c r="E48" t="n">
-        <v>289.3475036621094</v>
+        <v>287.0035887304013</v>
       </c>
       <c r="F48" t="n">
-        <v>29557300</v>
+        <v>19842100</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1683,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B49" t="n">
-        <v>287.0035887304013</v>
+        <v>285.96630859375</v>
       </c>
       <c r="C49" t="n">
-        <v>291.1627853205446</v>
+        <v>291.2525794490294</v>
       </c>
       <c r="D49" t="n">
-        <v>286.5747114373448</v>
+        <v>282.9541529801612</v>
       </c>
       <c r="E49" t="n">
-        <v>290.5543518066406</v>
+        <v>290.9234183741868</v>
       </c>
       <c r="F49" t="n">
-        <v>19842100</v>
+        <v>24829900</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1709,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B50" t="n">
-        <v>290.9233873275988</v>
+        <v>277.8474426269531</v>
       </c>
       <c r="C50" t="n">
-        <v>291.2525483673142</v>
+        <v>282.1063559927165</v>
       </c>
       <c r="D50" t="n">
-        <v>282.9541227840324</v>
+        <v>276.5208753822851</v>
       </c>
       <c r="E50" t="n">
-        <v>285.9662780761719</v>
+        <v>281.6076529103283</v>
       </c>
       <c r="F50" t="n">
-        <v>24829900</v>
+        <v>29494000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1735,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B51" t="n">
-        <v>281.6076219797447</v>
+        <v>275.6929931640625</v>
       </c>
       <c r="C51" t="n">
-        <v>282.1063250073575</v>
+        <v>277.8374099534448</v>
       </c>
       <c r="D51" t="n">
-        <v>276.5208450104115</v>
+        <v>269.997813487729</v>
       </c>
       <c r="E51" t="n">
-        <v>277.847412109375</v>
+        <v>270.705963217399</v>
       </c>
       <c r="F51" t="n">
-        <v>29494000</v>
+        <v>31647200</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1761,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B52" t="n">
-        <v>270.7059931829425</v>
+        <v>284.2806701660156</v>
       </c>
       <c r="C52" t="n">
-        <v>277.8374407083971</v>
+        <v>293.1875295999499</v>
       </c>
       <c r="D52" t="n">
-        <v>269.9978433748846</v>
+        <v>282.8344496120375</v>
       </c>
       <c r="E52" t="n">
-        <v>275.6930236816406</v>
+        <v>285.0387085276487</v>
       </c>
       <c r="F52" t="n">
-        <v>31647200</v>
+        <v>52670200</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1787,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B53" t="n">
-        <v>285.038677928695</v>
+        <v>283.5426025390625</v>
       </c>
       <c r="C53" t="n">
-        <v>293.1874981262189</v>
+        <v>288.0508671158451</v>
       </c>
       <c r="D53" t="n">
-        <v>282.8344192497114</v>
+        <v>277.4783868942568</v>
       </c>
       <c r="E53" t="n">
-        <v>284.2806396484375</v>
+        <v>287.1731753233953</v>
       </c>
       <c r="F53" t="n">
-        <v>52670200</v>
+        <v>49158700</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1813,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B54" t="n">
-        <v>287.1731753233953</v>
+        <v>292.0504760742188</v>
       </c>
       <c r="C54" t="n">
-        <v>288.0508671158451</v>
+        <v>303.0219431129204</v>
       </c>
       <c r="D54" t="n">
-        <v>277.4783868942568</v>
+        <v>285.8865137158778</v>
       </c>
       <c r="E54" t="n">
-        <v>283.5426025390625</v>
+        <v>286.4151377283875</v>
       </c>
       <c r="F54" t="n">
-        <v>49158700</v>
+        <v>68198900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1839,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B55" t="n">
-        <v>286.4151377283875</v>
+        <v>288.6991882324219</v>
       </c>
       <c r="C55" t="n">
-        <v>303.0219431129204</v>
+        <v>305.625169818548</v>
       </c>
       <c r="D55" t="n">
-        <v>285.8865137158778</v>
+        <v>287.9212127447435</v>
       </c>
       <c r="E55" t="n">
-        <v>292.0504760742188</v>
+        <v>303.7500416076266</v>
       </c>
       <c r="F55" t="n">
-        <v>68198900</v>
+        <v>62025200</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1865,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B56" t="n">
-        <v>303.7500416076266</v>
+        <v>298.8827209472656</v>
       </c>
       <c r="C56" t="n">
-        <v>305.625169818548</v>
+        <v>303.1316807498811</v>
       </c>
       <c r="D56" t="n">
-        <v>287.9212127447435</v>
+        <v>293.0877938372482</v>
       </c>
       <c r="E56" t="n">
-        <v>288.6991882324219</v>
+        <v>295.6511348655125</v>
       </c>
       <c r="F56" t="n">
-        <v>62025200</v>
+        <v>74137700</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1891,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B57" t="n">
-        <v>295.6511046778972</v>
+        <v>317.7536010742188</v>
       </c>
       <c r="C57" t="n">
-        <v>303.1316497984607</v>
+        <v>318.651290855991</v>
       </c>
       <c r="D57" t="n">
-        <v>293.0877639113642</v>
+        <v>308.796914365105</v>
       </c>
       <c r="E57" t="n">
-        <v>298.8826904296875</v>
+        <v>310.3229443803346</v>
       </c>
       <c r="F57" t="n">
-        <v>74137700</v>
+        <v>85165100</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1917,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B58" t="n">
-        <v>310.3229443803346</v>
+        <v>322.6010131835938</v>
       </c>
       <c r="C58" t="n">
-        <v>318.651290855991</v>
+        <v>327.9770159307299</v>
       </c>
       <c r="D58" t="n">
-        <v>308.796914365105</v>
+        <v>316.826023668276</v>
       </c>
       <c r="E58" t="n">
-        <v>317.7536010742188</v>
+        <v>325.3638169665917</v>
       </c>
       <c r="F58" t="n">
-        <v>85165100</v>
+        <v>88632100</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1943,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B59" t="n">
-        <v>325.3638169665917</v>
+        <v>319.1201171875</v>
       </c>
       <c r="C59" t="n">
-        <v>327.9770159307299</v>
+        <v>323.658303098724</v>
       </c>
       <c r="D59" t="n">
-        <v>316.826023668276</v>
+        <v>315.9683100285969</v>
       </c>
       <c r="E59" t="n">
-        <v>322.6010131835938</v>
+        <v>319.8482042131112</v>
       </c>
       <c r="F59" t="n">
-        <v>88632100</v>
+        <v>51373400</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1969,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B60" t="n">
-        <v>319.8482042131112</v>
+        <v>319.3494873046875</v>
       </c>
       <c r="C60" t="n">
-        <v>323.658303098724</v>
+        <v>326.0021995827445</v>
       </c>
       <c r="D60" t="n">
-        <v>315.9683100285969</v>
+        <v>315.9682963529555</v>
       </c>
       <c r="E60" t="n">
-        <v>319.1201171875</v>
+        <v>322.5312152935296</v>
       </c>
       <c r="F60" t="n">
-        <v>51373400</v>
+        <v>26018600</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +1995,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B61" t="n">
-        <v>322.5312152935296</v>
+        <v>314.0732421875</v>
       </c>
       <c r="C61" t="n">
-        <v>326.0021995827445</v>
+        <v>319.020368247556</v>
       </c>
       <c r="D61" t="n">
-        <v>315.9682963529555</v>
+        <v>313.0758360216101</v>
       </c>
       <c r="E61" t="n">
-        <v>319.3494873046875</v>
+        <v>316.8759510785769</v>
       </c>
       <c r="F61" t="n">
-        <v>26018600</v>
+        <v>41183000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2021,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B62" t="n">
-        <v>316.8759202886677</v>
+        <v>314.9908447265625</v>
       </c>
       <c r="C62" t="n">
-        <v>319.02033724928</v>
+        <v>317.5541859262309</v>
       </c>
       <c r="D62" t="n">
-        <v>313.075805600947</v>
+        <v>313.095779063488</v>
       </c>
       <c r="E62" t="n">
-        <v>314.0732116699219</v>
+        <v>315.9184251730286</v>
       </c>
       <c r="F62" t="n">
-        <v>41183000</v>
+        <v>35854700</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2047,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B63" t="n">
-        <v>315.9183945655827</v>
+        <v>318.8009033203125</v>
       </c>
       <c r="C63" t="n">
-        <v>317.554155160306</v>
+        <v>320.7458268711651</v>
       </c>
       <c r="D63" t="n">
-        <v>313.0957487295115</v>
+        <v>313.2852490348319</v>
       </c>
       <c r="E63" t="n">
-        <v>314.9908142089844</v>
+        <v>315.0706144021458</v>
       </c>
       <c r="F63" t="n">
-        <v>35854700</v>
+        <v>41838300</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2073,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B64" t="n">
-        <v>315.0706144021458</v>
+        <v>316.7961120605469</v>
       </c>
       <c r="C64" t="n">
-        <v>320.7458268711651</v>
+        <v>321.5238071066378</v>
       </c>
       <c r="D64" t="n">
-        <v>313.2852490348319</v>
+        <v>313.8837033726762</v>
       </c>
       <c r="E64" t="n">
-        <v>318.8009033203125</v>
+        <v>321.3941698854088</v>
       </c>
       <c r="F64" t="n">
-        <v>41838300</v>
+        <v>31240900</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2099,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B65" t="n">
-        <v>321.3942008459266</v>
+        <v>320.4366455078125</v>
       </c>
       <c r="C65" t="n">
-        <v>321.5238380796439</v>
+        <v>322.3217576397153</v>
       </c>
       <c r="D65" t="n">
-        <v>313.8837336096964</v>
+        <v>318.3421170569229</v>
       </c>
       <c r="E65" t="n">
-        <v>316.796142578125</v>
+        <v>318.6612638744486</v>
       </c>
       <c r="F65" t="n">
-        <v>31240900</v>
+        <v>28851700</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,25 +2125,25 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B66" t="n">
-        <v>318.6612335259534</v>
+        <v>313.1109008789062</v>
       </c>
       <c r="C66" t="n">
-        <v>322.3217269426038</v>
+        <v>319.8178549396436</v>
       </c>
       <c r="D66" t="n">
-        <v>318.3420867388224</v>
+        <v>310.6157547321785</v>
       </c>
       <c r="E66" t="n">
-        <v>320.4366149902344</v>
+        <v>319.4285975207571</v>
       </c>
       <c r="F66" t="n">
-        <v>28851700</v>
+        <v>33909400</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2159,25 +2151,25 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B67" t="n">
-        <v>319.428628654094</v>
+        <v>316.4643859863281</v>
       </c>
       <c r="C67" t="n">
-        <v>319.8178861109197</v>
+        <v>317.3726229056239</v>
       </c>
       <c r="D67" t="n">
-        <v>310.6157850065654</v>
+        <v>311.2944500995635</v>
       </c>
       <c r="E67" t="n">
-        <v>313.1109313964844</v>
+        <v>311.7635388280278</v>
       </c>
       <c r="F67" t="n">
-        <v>33909400</v>
+        <v>30194000</v>
       </c>
       <c r="G67" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2185,22 +2177,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B68" t="n">
-        <v>311.7635388280278</v>
+        <v>319.5883178710938</v>
       </c>
       <c r="C68" t="n">
-        <v>317.3726229056239</v>
+        <v>320.6861883612462</v>
       </c>
       <c r="D68" t="n">
-        <v>311.2944500995635</v>
+        <v>314.069055340672</v>
       </c>
       <c r="E68" t="n">
-        <v>316.4643859863281</v>
+        <v>315.2168165746965</v>
       </c>
       <c r="F68" t="n">
-        <v>30194000</v>
+        <v>33428900</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2203,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B69" t="n">
-        <v>315.2168165746965</v>
+        <v>311.8234252929688</v>
       </c>
       <c r="C69" t="n">
-        <v>320.6861883612462</v>
+        <v>320.4965565243085</v>
       </c>
       <c r="D69" t="n">
-        <v>314.069055340672</v>
+        <v>308.0008744502611</v>
       </c>
       <c r="E69" t="n">
-        <v>319.5883178710938</v>
+        <v>319.4585671045538</v>
       </c>
       <c r="F69" t="n">
-        <v>33428900</v>
+        <v>42353700</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2229,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B70" t="n">
-        <v>319.4585358397385</v>
+        <v>308.6895141601562</v>
       </c>
       <c r="C70" t="n">
-        <v>320.4965251579071</v>
+        <v>314.2586670471713</v>
       </c>
       <c r="D70" t="n">
-        <v>308.0008443067889</v>
+        <v>304.9667450846255</v>
       </c>
       <c r="E70" t="n">
-        <v>311.8233947753906</v>
+        <v>313.0909556884665</v>
       </c>
       <c r="F70" t="n">
-        <v>42353700</v>
+        <v>35940200</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2255,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B71" t="n">
-        <v>313.0909556884665</v>
+        <v>307.6216125488281</v>
       </c>
       <c r="C71" t="n">
-        <v>314.2586670471713</v>
+        <v>310.8154121445851</v>
       </c>
       <c r="D71" t="n">
-        <v>304.9667450846255</v>
+        <v>304.2881005921093</v>
       </c>
       <c r="E71" t="n">
-        <v>308.6895141601562</v>
+        <v>310.7156001962807</v>
       </c>
       <c r="F71" t="n">
-        <v>35940200</v>
+        <v>29151900</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2281,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B72" t="n">
-        <v>310.7155693717638</v>
+        <v>305.9747924804688</v>
       </c>
       <c r="C72" t="n">
-        <v>310.8153813101663</v>
+        <v>310.1666197797816</v>
       </c>
       <c r="D72" t="n">
-        <v>304.288070405232</v>
+        <v>302.0025088045779</v>
       </c>
       <c r="E72" t="n">
-        <v>307.62158203125</v>
+        <v>304.3579426322819</v>
       </c>
       <c r="F72" t="n">
-        <v>29151900</v>
+        <v>30585000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2307,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B73" t="n">
-        <v>304.3579426322819</v>
+        <v>296.1439208984375</v>
       </c>
       <c r="C73" t="n">
-        <v>310.1666197797816</v>
+        <v>307.4918412298865</v>
       </c>
       <c r="D73" t="n">
-        <v>302.0025088045779</v>
+        <v>295.5450797036171</v>
       </c>
       <c r="E73" t="n">
-        <v>305.9747924804688</v>
+        <v>307.4120099511304</v>
       </c>
       <c r="F73" t="n">
-        <v>30585000</v>
+        <v>43930400</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2333,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B74" t="n">
-        <v>307.4120099511304</v>
+        <v>301.8727722167969</v>
       </c>
       <c r="C74" t="n">
-        <v>307.4918412298865</v>
+        <v>303.3698600006946</v>
       </c>
       <c r="D74" t="n">
-        <v>295.5450797036171</v>
+        <v>298.6490626821344</v>
       </c>
       <c r="E74" t="n">
-        <v>296.1439208984375</v>
+        <v>301.1342186567393</v>
       </c>
       <c r="F74" t="n">
-        <v>43930400</v>
+        <v>33518000</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2359,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B75" t="n">
-        <v>301.1342186567393</v>
+        <v>306.5636596679688</v>
       </c>
       <c r="C75" t="n">
-        <v>303.3698600006946</v>
+        <v>306.6534812800651</v>
       </c>
       <c r="D75" t="n">
-        <v>298.6490626821344</v>
+        <v>300.3856749721532</v>
       </c>
       <c r="E75" t="n">
-        <v>301.8727722167969</v>
+        <v>301.1442091965169</v>
       </c>
       <c r="F75" t="n">
-        <v>33518000</v>
+        <v>59943200</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2385,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B76" t="n">
-        <v>301.1442091965169</v>
+        <v>309.1785888671875</v>
       </c>
       <c r="C76" t="n">
-        <v>306.6534812800651</v>
+        <v>309.5279154654388</v>
       </c>
       <c r="D76" t="n">
-        <v>300.3856749721532</v>
+        <v>304.707275417899</v>
       </c>
       <c r="E76" t="n">
-        <v>306.5636596679688</v>
+        <v>309.278400817878</v>
       </c>
       <c r="F76" t="n">
-        <v>59943200</v>
+        <v>26429900</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2411,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B77" t="n">
-        <v>309.2783702904479</v>
+        <v>313.7396850585938</v>
       </c>
       <c r="C77" t="n">
-        <v>309.5278849133803</v>
+        <v>314.328535898872</v>
       </c>
       <c r="D77" t="n">
-        <v>304.7072453416635</v>
+        <v>308.7194521900694</v>
       </c>
       <c r="E77" t="n">
-        <v>309.1785583496094</v>
+        <v>309.0288478780406</v>
       </c>
       <c r="F77" t="n">
-        <v>26429900</v>
+        <v>25478700</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2437,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B78" t="n">
-        <v>309.0288478780406</v>
+        <v>313.4801635742188</v>
       </c>
       <c r="C78" t="n">
-        <v>314.328535898872</v>
+        <v>314.4682316573388</v>
       </c>
       <c r="D78" t="n">
-        <v>308.7194521900694</v>
+        <v>311.3143938726672</v>
       </c>
       <c r="E78" t="n">
-        <v>313.7396850585938</v>
+        <v>314.1588359856885</v>
       </c>
       <c r="F78" t="n">
-        <v>25478700</v>
+        <v>10097400</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2463,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B79" t="n">
-        <v>314.1588665693361</v>
+        <v>312.9013671875</v>
       </c>
       <c r="C79" t="n">
-        <v>314.4682622711062</v>
+        <v>314.4782864028367</v>
       </c>
       <c r="D79" t="n">
-        <v>311.3144241794057</v>
+        <v>311.6737441219225</v>
       </c>
       <c r="E79" t="n">
-        <v>313.4801940917969</v>
+        <v>313.8694852656387</v>
       </c>
       <c r="F79" t="n">
-        <v>10097400</v>
+        <v>10899000</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2489,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B80" t="n">
-        <v>313.8694546536391</v>
+        <v>312.9512634277344</v>
       </c>
       <c r="C80" t="n">
-        <v>314.4782557314601</v>
+        <v>313.410361871903</v>
       </c>
       <c r="D80" t="n">
-        <v>311.6737137240756</v>
+        <v>310.0169686016006</v>
       </c>
       <c r="E80" t="n">
-        <v>312.9013366699219</v>
+        <v>310.7655125785055</v>
       </c>
       <c r="F80" t="n">
-        <v>10899000</v>
+        <v>19621800</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2515,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B81" t="n">
-        <v>310.7654822740718</v>
+        <v>313.2406616210938</v>
       </c>
       <c r="C81" t="n">
-        <v>313.4103313095557</v>
+        <v>316.3346490163796</v>
       </c>
       <c r="D81" t="n">
-        <v>310.0169383701615</v>
+        <v>311.8533457068925</v>
       </c>
       <c r="E81" t="n">
-        <v>312.9512329101562</v>
+        <v>311.8932765746258</v>
       </c>
       <c r="F81" t="n">
-        <v>19621800</v>
+        <v>17380900</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2541,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B82" t="n">
-        <v>311.8932765746258</v>
+        <v>312.3923034667969</v>
       </c>
       <c r="C82" t="n">
-        <v>316.3346490163796</v>
+        <v>313.9692224596297</v>
       </c>
       <c r="D82" t="n">
-        <v>311.8533457068925</v>
+        <v>310.8353346785167</v>
       </c>
       <c r="E82" t="n">
-        <v>313.2406616210938</v>
+        <v>312.2426007868329</v>
       </c>
       <c r="F82" t="n">
-        <v>17380900</v>
+        <v>16377700</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2567,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B83" t="n">
-        <v>312.2426007868329</v>
+        <v>314.5381164550781</v>
       </c>
       <c r="C83" t="n">
-        <v>313.9692224596297</v>
+        <v>321.87385220157</v>
       </c>
       <c r="D83" t="n">
-        <v>310.8353346785167</v>
+        <v>309.7274673850438</v>
       </c>
       <c r="E83" t="n">
-        <v>312.3923034667969</v>
+        <v>316.2847187538463</v>
       </c>
       <c r="F83" t="n">
-        <v>16377700</v>
+        <v>32009400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2593,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B84" t="n">
-        <v>316.2847494408858</v>
+        <v>315.9254455566406</v>
       </c>
       <c r="C84" t="n">
-        <v>321.8738834308866</v>
+        <v>318.4006111389099</v>
       </c>
       <c r="D84" t="n">
-        <v>309.727497435876</v>
+        <v>314.0191501700305</v>
       </c>
       <c r="E84" t="n">
-        <v>314.5381469726562</v>
+        <v>317.0432662013207</v>
       </c>
       <c r="F84" t="n">
-        <v>32009400</v>
+        <v>30195600</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2619,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B85" t="n">
-        <v>317.0432968268774</v>
+        <v>313.7297058105469</v>
       </c>
       <c r="C85" t="n">
-        <v>318.4006418955826</v>
+        <v>320.3168980142969</v>
       </c>
       <c r="D85" t="n">
-        <v>314.0191805034655</v>
+        <v>311.1746784825258</v>
       </c>
       <c r="E85" t="n">
-        <v>315.9254760742188</v>
+        <v>315.7857038876524</v>
       </c>
       <c r="F85" t="n">
-        <v>30195600</v>
+        <v>31212100</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2645,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B86" t="n">
-        <v>315.7857038876524</v>
+        <v>321.3549194335938</v>
       </c>
       <c r="C86" t="n">
-        <v>320.3168980142969</v>
+        <v>325.5168067446344</v>
       </c>
       <c r="D86" t="n">
-        <v>311.1746784825258</v>
+        <v>313.5800344006012</v>
       </c>
       <c r="E86" t="n">
-        <v>313.7297058105469</v>
+        <v>313.7496873061683</v>
       </c>
       <c r="F86" t="n">
-        <v>31212100</v>
+        <v>35104400</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2671,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B87" t="n">
-        <v>313.7496575108236</v>
+        <v>324.8081665039062</v>
       </c>
       <c r="C87" t="n">
-        <v>325.5167758318212</v>
+        <v>329.6786969446188</v>
       </c>
       <c r="D87" t="n">
-        <v>313.5800046213677</v>
+        <v>320.8758135066914</v>
       </c>
       <c r="E87" t="n">
-        <v>321.3548889160156</v>
+        <v>328.3313118537803</v>
       </c>
       <c r="F87" t="n">
-        <v>35104400</v>
+        <v>31896100</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2697,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B88" t="n">
-        <v>328.3313118537803</v>
+        <v>327.9320983886719</v>
       </c>
       <c r="C88" t="n">
-        <v>329.6786969446188</v>
+        <v>330.1876899539591</v>
       </c>
       <c r="D88" t="n">
-        <v>320.8758135066914</v>
+        <v>325.1674567682817</v>
       </c>
       <c r="E88" t="n">
-        <v>324.8081665039062</v>
+        <v>326.4549607998293</v>
       </c>
       <c r="F88" t="n">
-        <v>31896100</v>
+        <v>26214200</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2723,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B89" t="n">
-        <v>326.4549607998293</v>
+        <v>331.2156982421875</v>
       </c>
       <c r="C89" t="n">
-        <v>330.1876899539591</v>
+        <v>333.3914890456728</v>
       </c>
       <c r="D89" t="n">
-        <v>325.1674567682817</v>
+        <v>324.3690311583512</v>
       </c>
       <c r="E89" t="n">
-        <v>327.9320983886719</v>
+        <v>325.1674658209474</v>
       </c>
       <c r="F89" t="n">
-        <v>26214200</v>
+        <v>33923900</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2749,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B90" t="n">
-        <v>325.1674358606418</v>
+        <v>335.3176879882812</v>
       </c>
       <c r="C90" t="n">
-        <v>333.3914583276215</v>
+        <v>339.8289010736461</v>
       </c>
       <c r="D90" t="n">
-        <v>324.3690012716118</v>
+        <v>332.9722446137951</v>
       </c>
       <c r="E90" t="n">
-        <v>331.2156677246094</v>
+        <v>334.2996793666924</v>
       </c>
       <c r="F90" t="n">
-        <v>33923900</v>
+        <v>33517600</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2775,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B91" t="n">
-        <v>334.2997097916206</v>
+        <v>335.1879577636719</v>
       </c>
       <c r="C91" t="n">
-        <v>339.828932001794</v>
+        <v>335.8666302231012</v>
       </c>
       <c r="D91" t="n">
-        <v>332.9722749179122</v>
+        <v>329.8383789070015</v>
       </c>
       <c r="E91" t="n">
-        <v>335.3177185058594</v>
+        <v>334.4094733641317</v>
       </c>
       <c r="F91" t="n">
-        <v>33517600</v>
+        <v>28525600</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2801,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B92" t="n">
-        <v>334.4094733641317</v>
+        <v>332.1339111328125</v>
       </c>
       <c r="C92" t="n">
-        <v>335.8666302231012</v>
+        <v>337.03438209247</v>
       </c>
       <c r="D92" t="n">
-        <v>329.8383789070015</v>
+        <v>330.097863235539</v>
       </c>
       <c r="E92" t="n">
-        <v>335.1879577636719</v>
+        <v>336.9944512235705</v>
       </c>
       <c r="F92" t="n">
-        <v>28525600</v>
+        <v>28442400</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2827,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B93" t="n">
-        <v>336.9944202593897</v>
+        <v>329.3593139648438</v>
       </c>
       <c r="C93" t="n">
-        <v>337.0343511246202</v>
+        <v>334.0002800245007</v>
       </c>
       <c r="D93" t="n">
-        <v>330.0978329050398</v>
+        <v>327.0637915356931</v>
       </c>
       <c r="E93" t="n">
-        <v>332.1338806152344</v>
+        <v>333.7607557246461</v>
       </c>
       <c r="F93" t="n">
-        <v>28442400</v>
+        <v>40341600</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2853,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B94" t="n">
-        <v>333.7607557246461</v>
+        <v>321.3748474121094</v>
       </c>
       <c r="C94" t="n">
-        <v>334.0002800245007</v>
+        <v>327.0937337673917</v>
       </c>
       <c r="D94" t="n">
-        <v>327.0637915356931</v>
+        <v>319.8078882063433</v>
       </c>
       <c r="E94" t="n">
-        <v>329.3593139648438</v>
+        <v>320.2470363972373</v>
       </c>
       <c r="F94" t="n">
-        <v>40341600</v>
+        <v>35361000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2879,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B95" t="n">
-        <v>320.2470363972373</v>
+        <v>327.7424621582031</v>
       </c>
       <c r="C95" t="n">
-        <v>327.0937337673917</v>
+        <v>331.8345081879527</v>
       </c>
       <c r="D95" t="n">
-        <v>319.8078882063433</v>
+        <v>318.729994927537</v>
       </c>
       <c r="E95" t="n">
-        <v>321.3748474121094</v>
+        <v>320.2969541162656</v>
       </c>
       <c r="F95" t="n">
-        <v>35361000</v>
+        <v>35386600</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2905,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B96" t="n">
-        <v>320.2969541162656</v>
+        <v>329.8982543945312</v>
       </c>
       <c r="C96" t="n">
-        <v>331.8345081879527</v>
+        <v>334.4992893099707</v>
       </c>
       <c r="D96" t="n">
-        <v>318.729994927537</v>
+        <v>328.1117212092731</v>
       </c>
       <c r="E96" t="n">
-        <v>327.7424621582031</v>
+        <v>333.8006666576773</v>
       </c>
       <c r="F96" t="n">
-        <v>35386600</v>
+        <v>26253600</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2931,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B97" t="n">
-        <v>333.8006975362521</v>
+        <v>327.2933044433594</v>
       </c>
       <c r="C97" t="n">
-        <v>334.4993202531722</v>
+        <v>333.0421309365838</v>
       </c>
       <c r="D97" t="n">
-        <v>328.1117515615861</v>
+        <v>326.8142558744754</v>
       </c>
       <c r="E97" t="n">
-        <v>329.8982849121094</v>
+        <v>331.8444485977197</v>
       </c>
       <c r="F97" t="n">
-        <v>26253600</v>
+        <v>27280000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2957,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B98" t="n">
-        <v>331.8444485977197</v>
+        <v>332.6129760742188</v>
       </c>
       <c r="C98" t="n">
-        <v>333.0421309365838</v>
+        <v>335.1879535299186</v>
       </c>
       <c r="D98" t="n">
-        <v>326.8142558744754</v>
+        <v>326.3651202937951</v>
       </c>
       <c r="E98" t="n">
-        <v>327.2933044433594</v>
+        <v>327.1735452193246</v>
       </c>
       <c r="F98" t="n">
-        <v>27280000</v>
+        <v>26042100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2983,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B99" t="n">
-        <v>327.1735452193246</v>
+        <v>333.9004516601562</v>
       </c>
       <c r="C99" t="n">
-        <v>335.1879535299186</v>
+        <v>337.2539439848537</v>
       </c>
       <c r="D99" t="n">
-        <v>326.3651202937951</v>
+        <v>332.8325522369338</v>
       </c>
       <c r="E99" t="n">
-        <v>332.6129760742188</v>
+        <v>334.7188669221849</v>
       </c>
       <c r="F99" t="n">
-        <v>26042100</v>
+        <v>21636200</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3009,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B100" t="n">
-        <v>334.7188669221849</v>
+        <v>335.3576354980469</v>
       </c>
       <c r="C100" t="n">
-        <v>337.2539439848537</v>
+        <v>336.8846637353836</v>
       </c>
       <c r="D100" t="n">
-        <v>332.8325522369338</v>
+        <v>331.2955302242731</v>
       </c>
       <c r="E100" t="n">
-        <v>333.9004516601562</v>
+        <v>335.4075262381039</v>
       </c>
       <c r="F100" t="n">
-        <v>21636200</v>
+        <v>27434400</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3035,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B101" t="n">
-        <v>335.4075567602221</v>
+        <v>337.5932922363281</v>
       </c>
       <c r="C101" t="n">
-        <v>336.8846943919215</v>
+        <v>341.625457159737</v>
       </c>
       <c r="D101" t="n">
-        <v>331.2955603721992</v>
+        <v>325.9060355700189</v>
       </c>
       <c r="E101" t="n">
-        <v>335.357666015625</v>
+        <v>339.6393000059441</v>
       </c>
       <c r="F101" t="n">
-        <v>27434400</v>
+        <v>39785600</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3061,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B102" t="n">
-        <v>339.639269303412</v>
+        <v>337.3437805175781</v>
       </c>
       <c r="C102" t="n">
-        <v>341.6254262776615</v>
+        <v>339.3398975620609</v>
       </c>
       <c r="D102" t="n">
-        <v>325.9060061089392</v>
+        <v>331.6448748839121</v>
       </c>
       <c r="E102" t="n">
-        <v>337.59326171875</v>
+        <v>339.3398975620609</v>
       </c>
       <c r="F102" t="n">
-        <v>39785600</v>
+        <v>31024000</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3087,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B103" t="n">
-        <v>339.3398975620609</v>
+        <v>343.022705078125</v>
       </c>
       <c r="C103" t="n">
-        <v>339.3398975620609</v>
+        <v>344.1604758527643</v>
       </c>
       <c r="D103" t="n">
-        <v>331.6448748839121</v>
+        <v>334.9783565494149</v>
       </c>
       <c r="E103" t="n">
-        <v>337.3437805175781</v>
+        <v>335.5672073695487</v>
       </c>
       <c r="F103" t="n">
-        <v>31024000</v>
+        <v>32006100</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3113,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B104" t="n">
-        <v>335.5672372238362</v>
+        <v>339.0504455566406</v>
       </c>
       <c r="C104" t="n">
-        <v>344.160506471566</v>
+        <v>348.322417578686</v>
       </c>
       <c r="D104" t="n">
-        <v>334.9783863513143</v>
+        <v>336.8148042563823</v>
       </c>
       <c r="E104" t="n">
-        <v>343.0227355957031</v>
+        <v>346.6656368085559</v>
       </c>
       <c r="F104" t="n">
-        <v>32006100</v>
+        <v>36506700</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3139,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B105" t="n">
-        <v>346.6656368085559</v>
+        <v>332.3934326171875</v>
       </c>
       <c r="C105" t="n">
-        <v>348.322417578686</v>
+        <v>342.6434831024425</v>
       </c>
       <c r="D105" t="n">
-        <v>336.8148042563823</v>
+        <v>327.8821884154679</v>
       </c>
       <c r="E105" t="n">
-        <v>339.0504455566406</v>
+        <v>342.2941565134455</v>
       </c>
       <c r="F105" t="n">
-        <v>36506700</v>
+        <v>70618400</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3165,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B106" t="n">
-        <v>342.2941250868659</v>
+        <v>330.6069030761719</v>
       </c>
       <c r="C106" t="n">
-        <v>342.6434516437907</v>
+        <v>332.0441098613053</v>
       </c>
       <c r="D106" t="n">
-        <v>327.8821583120744</v>
+        <v>305.8650224655501</v>
       </c>
       <c r="E106" t="n">
-        <v>332.3934020996094</v>
+        <v>311.6138496060838</v>
       </c>
       <c r="F106" t="n">
-        <v>70618400</v>
+        <v>88205800</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3191,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B107" t="n">
-        <v>311.6138208417116</v>
+        <v>322.233154296875</v>
       </c>
       <c r="C107" t="n">
-        <v>332.0440792110618</v>
+        <v>329.7385737476322</v>
       </c>
       <c r="D107" t="n">
-        <v>305.8649942318392</v>
+        <v>319.2988903139048</v>
       </c>
       <c r="E107" t="n">
-        <v>330.6068725585938</v>
+        <v>326.5447743483745</v>
       </c>
       <c r="F107" t="n">
-        <v>88205800</v>
+        <v>56380500</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3217,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B108" t="n">
-        <v>326.5447743483745</v>
+        <v>323.6903381347656</v>
       </c>
       <c r="C108" t="n">
-        <v>329.7385737476322</v>
+        <v>327.0637807183464</v>
       </c>
       <c r="D108" t="n">
-        <v>319.2988903139048</v>
+        <v>316.6440476026885</v>
       </c>
       <c r="E108" t="n">
-        <v>322.233154296875</v>
+        <v>320.3069052195784</v>
       </c>
       <c r="F108" t="n">
-        <v>56380500</v>
+        <v>39640100</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3243,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B109" t="n">
-        <v>320.3069052195784</v>
+        <v>317.9614562988281</v>
       </c>
       <c r="C109" t="n">
-        <v>327.0637807183464</v>
+        <v>321.0454837970353</v>
       </c>
       <c r="D109" t="n">
-        <v>316.6440476026885</v>
+        <v>313.9991629255859</v>
       </c>
       <c r="E109" t="n">
-        <v>323.6903381347656</v>
+        <v>320.3468306795893</v>
       </c>
       <c r="F109" t="n">
-        <v>39640100</v>
+        <v>39170000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3269,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B110" t="n">
-        <v>320.3468306795893</v>
+        <v>310.3562316894531</v>
       </c>
       <c r="C110" t="n">
-        <v>321.0454837970353</v>
+        <v>320.4366276261131</v>
       </c>
       <c r="D110" t="n">
-        <v>313.9991629255859</v>
+        <v>309.0587679521403</v>
       </c>
       <c r="E110" t="n">
-        <v>317.9614562988281</v>
+        <v>318.3506892240785</v>
       </c>
       <c r="F110" t="n">
-        <v>39170000</v>
+        <v>45406400</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3295,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B111" t="n">
-        <v>318.3507205277581</v>
+        <v>308.4000854492188</v>
       </c>
       <c r="C111" t="n">
-        <v>320.4366591349046</v>
+        <v>315.6260194522374</v>
       </c>
       <c r="D111" t="n">
-        <v>309.0587983421378</v>
+        <v>306.603592280419</v>
       </c>
       <c r="E111" t="n">
-        <v>310.3562622070312</v>
+        <v>311.4840826487114</v>
       </c>
       <c r="F111" t="n">
-        <v>45406400</v>
+        <v>47761300</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3321,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B112" t="n">
-        <v>311.4840518259579</v>
+        <v>305.1264343261719</v>
       </c>
       <c r="C112" t="n">
-        <v>315.6259882196205</v>
+        <v>308.0307881065925</v>
       </c>
       <c r="D112" t="n">
-        <v>306.603561940612</v>
+        <v>303.1203270701956</v>
       </c>
       <c r="E112" t="n">
-        <v>308.4000549316406</v>
+        <v>307.1325415821482</v>
       </c>
       <c r="F112" t="n">
-        <v>47761300</v>
+        <v>38499700</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3347,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B113" t="n">
-        <v>307.1325415821482</v>
+        <v>301.43359375</v>
       </c>
       <c r="C113" t="n">
-        <v>308.0307881065925</v>
+        <v>303.8489085337251</v>
       </c>
       <c r="D113" t="n">
-        <v>303.1203270701956</v>
+        <v>295.674807618098</v>
       </c>
       <c r="E113" t="n">
-        <v>305.1264343261719</v>
+        <v>299.4574575670962</v>
       </c>
       <c r="F113" t="n">
-        <v>38499700</v>
+        <v>39247600</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3373,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B114" t="n">
-        <v>299.4574575670962</v>
+        <v>302.7410888671875</v>
       </c>
       <c r="C114" t="n">
-        <v>303.8489085337251</v>
+        <v>304.7871271852118</v>
       </c>
       <c r="D114" t="n">
-        <v>295.674807618098</v>
+        <v>300.6651404690992</v>
       </c>
       <c r="E114" t="n">
-        <v>301.43359375</v>
+        <v>301.5035060024616</v>
       </c>
       <c r="F114" t="n">
-        <v>39247600</v>
+        <v>28482100</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3399,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B115" t="n">
-        <v>301.5035060024616</v>
+        <v>302.2620239257812</v>
       </c>
       <c r="C115" t="n">
-        <v>304.7871271852118</v>
+        <v>304.8769323320439</v>
       </c>
       <c r="D115" t="n">
-        <v>300.6651404690992</v>
+        <v>299.4574819671566</v>
       </c>
       <c r="E115" t="n">
-        <v>302.7410888671875</v>
+        <v>301.2340248853423</v>
       </c>
       <c r="F115" t="n">
-        <v>28482100</v>
+        <v>25834400</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3425,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B116" t="n">
-        <v>301.2340248853423</v>
+        <v>314.3684997558594</v>
       </c>
       <c r="C116" t="n">
-        <v>304.8769323320439</v>
+        <v>315.8855378192499</v>
       </c>
       <c r="D116" t="n">
-        <v>299.4574819671566</v>
+        <v>303.3099937290923</v>
       </c>
       <c r="E116" t="n">
-        <v>302.2620239257812</v>
+        <v>303.7291917307074</v>
       </c>
       <c r="F116" t="n">
-        <v>25834400</v>
+        <v>53210800</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3451,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B117" t="n">
-        <v>303.7291622459488</v>
+        <v>310.8852233886719</v>
       </c>
       <c r="C117" t="n">
-        <v>315.885507154404</v>
+        <v>318.8996316925602</v>
       </c>
       <c r="D117" t="n">
-        <v>303.3099642850277</v>
+        <v>309.2683735389658</v>
       </c>
       <c r="E117" t="n">
-        <v>314.3684692382812</v>
+        <v>318.4305429928518</v>
       </c>
       <c r="F117" t="n">
-        <v>53210800</v>
+        <v>31423000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3477,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B118" t="n">
-        <v>318.4305429928518</v>
+        <v>310.29638671875</v>
       </c>
       <c r="C118" t="n">
-        <v>318.8996316925602</v>
+        <v>311.6637220131571</v>
       </c>
       <c r="D118" t="n">
-        <v>309.2683735389658</v>
+        <v>305.3360346729232</v>
       </c>
       <c r="E118" t="n">
-        <v>310.8852233886719</v>
+        <v>309.91711960911</v>
       </c>
       <c r="F118" t="n">
-        <v>31423000</v>
+        <v>25615600</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3503,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B119" t="n">
-        <v>309.91711960911</v>
+        <v>312.2925109863281</v>
       </c>
       <c r="C119" t="n">
-        <v>311.6637220131571</v>
+        <v>313.031095017384</v>
       </c>
       <c r="D119" t="n">
-        <v>305.3360346729232</v>
+        <v>308.8392369672335</v>
       </c>
       <c r="E119" t="n">
-        <v>310.29638671875</v>
+        <v>311.4541454679639</v>
       </c>
       <c r="F119" t="n">
-        <v>25615600</v>
+        <v>29963600</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3529,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B120" t="n">
-        <v>311.4541150323118</v>
+        <v>306.783203125</v>
       </c>
       <c r="C120" t="n">
-        <v>313.0310644276307</v>
+        <v>312.5320293917034</v>
       </c>
       <c r="D120" t="n">
-        <v>308.8392067871133</v>
+        <v>301.762970472535</v>
       </c>
       <c r="E120" t="n">
-        <v>312.29248046875</v>
+        <v>312.0330001798944</v>
       </c>
       <c r="F120" t="n">
-        <v>29963600</v>
+        <v>36431200</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3555,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B121" t="n">
-        <v>312.0330312197015</v>
+        <v>311.1547241210938</v>
       </c>
       <c r="C121" t="n">
-        <v>312.5320604811519</v>
+        <v>311.7635251790807</v>
       </c>
       <c r="D121" t="n">
-        <v>301.7630004907203</v>
+        <v>303.2101566226461</v>
       </c>
       <c r="E121" t="n">
-        <v>306.7832336425781</v>
+        <v>303.5495233120643</v>
       </c>
       <c r="F121" t="n">
-        <v>36431200</v>
+        <v>44640600</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3581,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B122" t="n">
-        <v>303.5495233120643</v>
+        <v>305.9248962402344</v>
       </c>
       <c r="C122" t="n">
-        <v>311.7635251790807</v>
+        <v>307.8910728050191</v>
       </c>
       <c r="D122" t="n">
-        <v>303.2101566226461</v>
+        <v>300.7150293830805</v>
       </c>
       <c r="E122" t="n">
-        <v>311.1547241210938</v>
+        <v>302.6413055358027</v>
       </c>
       <c r="F122" t="n">
-        <v>44640600</v>
+        <v>34790200</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3607,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B123" t="n">
-        <v>302.6413055358027</v>
+        <v>302.9905700683594</v>
       </c>
       <c r="C123" t="n">
-        <v>307.8910728050191</v>
+        <v>303.3498869477631</v>
       </c>
       <c r="D123" t="n">
-        <v>300.7150293830805</v>
+        <v>296.1339134078651</v>
       </c>
       <c r="E123" t="n">
-        <v>305.9248962402344</v>
+        <v>298.0102681623609</v>
       </c>
       <c r="F123" t="n">
-        <v>34790200</v>
+        <v>35497000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3633,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B124" t="n">
-        <v>298.0102681623609</v>
+        <v>302.54150390625</v>
       </c>
       <c r="C124" t="n">
-        <v>303.3498869477631</v>
+        <v>304.8769573413998</v>
       </c>
       <c r="D124" t="n">
-        <v>296.1339134078651</v>
+        <v>300.1661195993462</v>
       </c>
       <c r="E124" t="n">
-        <v>302.9905700683594</v>
+        <v>302.3019795923877</v>
       </c>
       <c r="F124" t="n">
-        <v>35497000</v>
+        <v>29536200</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3659,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B125" t="n">
-        <v>302.3019795923877</v>
+        <v>300.2958679199219</v>
       </c>
       <c r="C125" t="n">
-        <v>304.8769573413998</v>
+        <v>302.7111526067185</v>
       </c>
       <c r="D125" t="n">
-        <v>300.1661195993462</v>
+        <v>297.4114640277728</v>
       </c>
       <c r="E125" t="n">
-        <v>302.54150390625</v>
+        <v>302.4516780897468</v>
       </c>
       <c r="F125" t="n">
-        <v>29536200</v>
+        <v>35752300</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3685,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B126" t="n">
-        <v>302.4516473530844</v>
+        <v>297.9404296875</v>
       </c>
       <c r="C126" t="n">
-        <v>302.711121843687</v>
+        <v>299.9465371351957</v>
       </c>
       <c r="D126" t="n">
-        <v>297.4114338033223</v>
+        <v>294.6069177596933</v>
       </c>
       <c r="E126" t="n">
-        <v>300.2958374023438</v>
+        <v>295.5151547022239</v>
       </c>
       <c r="F126" t="n">
-        <v>35752300</v>
+        <v>25576900</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,25 +3711,25 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B127" t="n">
-        <v>295.5151547022239</v>
+        <v>305.9804077148438</v>
       </c>
       <c r="C127" t="n">
-        <v>299.9465371351957</v>
+        <v>306.4198649966507</v>
       </c>
       <c r="D127" t="n">
-        <v>294.6069177596933</v>
+        <v>293.7156237584298</v>
       </c>
       <c r="E127" t="n">
-        <v>297.9404296875</v>
+        <v>293.9952756214191</v>
       </c>
       <c r="F127" t="n">
-        <v>25576900</v>
+        <v>29312100</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -3745,25 +3737,25 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B128" t="n">
-        <v>293.9952756214191</v>
+        <v>306.6596069335938</v>
       </c>
       <c r="C128" t="n">
-        <v>306.4198649966507</v>
+        <v>309.1265479913924</v>
       </c>
       <c r="D128" t="n">
-        <v>293.7156237584298</v>
+        <v>305.1914269440574</v>
       </c>
       <c r="E128" t="n">
-        <v>305.9804077148438</v>
+        <v>305.7906896809686</v>
       </c>
       <c r="F128" t="n">
-        <v>29312100</v>
+        <v>23239700</v>
       </c>
       <c r="G128" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -3771,22 +3763,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B129" t="n">
-        <v>305.7906896809686</v>
+        <v>308.3175659179688</v>
       </c>
       <c r="C129" t="n">
-        <v>309.1265479913924</v>
+        <v>311.0341973481569</v>
       </c>
       <c r="D129" t="n">
-        <v>305.1914269440574</v>
+        <v>305.5410112597431</v>
       </c>
       <c r="E129" t="n">
-        <v>306.6596069335938</v>
+        <v>306.3699695674413</v>
       </c>
       <c r="F129" t="n">
-        <v>23239700</v>
+        <v>24125700</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3789,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B130" t="n">
-        <v>306.3699695674413</v>
+        <v>303.1738891601562</v>
       </c>
       <c r="C130" t="n">
-        <v>311.0341973481569</v>
+        <v>308.5572255769297</v>
       </c>
       <c r="D130" t="n">
-        <v>305.5410112597431</v>
+        <v>300.6570224145156</v>
       </c>
       <c r="E130" t="n">
-        <v>308.3175659179688</v>
+        <v>306.4398571350748</v>
       </c>
       <c r="F130" t="n">
-        <v>24125700</v>
+        <v>24928300</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3815,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B131" t="n">
-        <v>306.4398571350748</v>
+        <v>301.9054870605469</v>
       </c>
       <c r="C131" t="n">
-        <v>308.5572255769297</v>
+        <v>307.3087879643589</v>
       </c>
       <c r="D131" t="n">
-        <v>300.6570224145156</v>
+        <v>300.0677703977713</v>
       </c>
       <c r="E131" t="n">
-        <v>303.1738891601562</v>
+        <v>306.6296377698095</v>
       </c>
       <c r="F131" t="n">
-        <v>24928300</v>
+        <v>23693100</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3841,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B132" t="n">
-        <v>306.6296377698095</v>
+        <v>305.1814270019531</v>
       </c>
       <c r="C132" t="n">
-        <v>307.3087879643589</v>
+        <v>306.1102674724465</v>
       </c>
       <c r="D132" t="n">
-        <v>300.0677703977713</v>
+        <v>302.6445653756606</v>
       </c>
       <c r="E132" t="n">
-        <v>301.9054870605469</v>
+        <v>303.9729346538992</v>
       </c>
       <c r="F132" t="n">
-        <v>23693100</v>
+        <v>23519700</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3867,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B133" t="n">
-        <v>303.9729346538992</v>
+        <v>310.5347900390625</v>
       </c>
       <c r="C133" t="n">
-        <v>306.1102674724465</v>
+        <v>311.0341705495281</v>
       </c>
       <c r="D133" t="n">
-        <v>302.6445653756606</v>
+        <v>305.1214918945171</v>
       </c>
       <c r="E133" t="n">
-        <v>305.1814270019531</v>
+        <v>305.481031231764</v>
       </c>
       <c r="F133" t="n">
-        <v>23519700</v>
+        <v>21955200</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3893,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B134" t="n">
-        <v>305.481031231764</v>
+        <v>307.3087768554688</v>
       </c>
       <c r="C134" t="n">
-        <v>311.0341705495281</v>
+        <v>312.0828532524296</v>
       </c>
       <c r="D134" t="n">
-        <v>305.1214918945171</v>
+        <v>306.5497087361953</v>
       </c>
       <c r="E134" t="n">
-        <v>310.5347900390625</v>
+        <v>308.8868058363209</v>
       </c>
       <c r="F134" t="n">
-        <v>21955200</v>
+        <v>20009800</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3919,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B135" t="n">
-        <v>308.8868058363209</v>
+        <v>306.7494812011719</v>
       </c>
       <c r="C135" t="n">
-        <v>312.0828532524296</v>
+        <v>307.6783216475022</v>
       </c>
       <c r="D135" t="n">
-        <v>306.5497087361953</v>
+        <v>301.9754046785898</v>
       </c>
       <c r="E135" t="n">
-        <v>307.3087768554688</v>
+        <v>303.6333516523425</v>
       </c>
       <c r="F135" t="n">
-        <v>20009800</v>
+        <v>25075800</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3945,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B136" t="n">
-        <v>303.6333516523425</v>
+        <v>300.6270751953125</v>
       </c>
       <c r="C136" t="n">
-        <v>307.6783216475022</v>
+        <v>305.620880431115</v>
       </c>
       <c r="D136" t="n">
-        <v>301.9754046785898</v>
+        <v>297.9004465638477</v>
       </c>
       <c r="E136" t="n">
-        <v>306.7494812011719</v>
+        <v>305.0815409313132</v>
       </c>
       <c r="F136" t="n">
-        <v>25075800</v>
+        <v>44364100</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3971,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B137" t="n">
-        <v>305.0815409313132</v>
+        <v>301.685791015625</v>
       </c>
       <c r="C137" t="n">
-        <v>305.620880431115</v>
+        <v>305.6009481410186</v>
       </c>
       <c r="D137" t="n">
-        <v>297.9004465638477</v>
+        <v>300.5571860375472</v>
       </c>
       <c r="E137" t="n">
-        <v>300.6270751953125</v>
+        <v>301.7357168812967</v>
       </c>
       <c r="F137" t="n">
-        <v>44364100</v>
+        <v>29326900</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +3997,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B138" t="n">
-        <v>301.7357168812967</v>
+        <v>290.0801696777344</v>
       </c>
       <c r="C138" t="n">
-        <v>305.6009481410186</v>
+        <v>299.5484356615691</v>
       </c>
       <c r="D138" t="n">
-        <v>300.5571860375472</v>
+        <v>289.9702901097709</v>
       </c>
       <c r="E138" t="n">
-        <v>301.685791015625</v>
+        <v>298.8293264668504</v>
       </c>
       <c r="F138" t="n">
-        <v>29326900</v>
+        <v>36864300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4023,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B139" t="n">
-        <v>298.8293264668504</v>
+        <v>290.5695495605469</v>
       </c>
       <c r="C139" t="n">
-        <v>299.5484356615691</v>
+        <v>295.6332754793409</v>
       </c>
       <c r="D139" t="n">
-        <v>289.9702901097709</v>
+        <v>288.8816409209488</v>
       </c>
       <c r="E139" t="n">
-        <v>290.0801696777344</v>
+        <v>293.0764495892524</v>
       </c>
       <c r="F139" t="n">
-        <v>36864300</v>
+        <v>29460700</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4049,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B140" t="n">
-        <v>293.0764495892524</v>
+        <v>280.5719604492188</v>
       </c>
       <c r="C140" t="n">
-        <v>295.6332754793409</v>
+        <v>287.5932492331535</v>
       </c>
       <c r="D140" t="n">
-        <v>288.8816409209488</v>
+        <v>278.1549453585245</v>
       </c>
       <c r="E140" t="n">
-        <v>290.5695495605469</v>
+        <v>287.5532902578335</v>
       </c>
       <c r="F140" t="n">
-        <v>29460700</v>
+        <v>39080600</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4075,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B141" t="n">
-        <v>287.5532902578335</v>
+        <v>274.0001220703125</v>
       </c>
       <c r="C141" t="n">
-        <v>287.5932492331535</v>
+        <v>279.0238892859517</v>
       </c>
       <c r="D141" t="n">
-        <v>278.1549453585245</v>
+        <v>273.6106210828978</v>
       </c>
       <c r="E141" t="n">
-        <v>280.5719604492188</v>
+        <v>276.9364822022131</v>
       </c>
       <c r="F141" t="n">
-        <v>39080600</v>
+        <v>35890600</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4101,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B142" t="n">
-        <v>276.9364822022131</v>
+        <v>273.1611633300781</v>
       </c>
       <c r="C142" t="n">
-        <v>279.0238892859517</v>
+        <v>276.7467120540596</v>
       </c>
       <c r="D142" t="n">
-        <v>273.6106210828978</v>
+        <v>271.772870758184</v>
       </c>
       <c r="E142" t="n">
-        <v>274.0001220703125</v>
+        <v>276.0775591796553</v>
       </c>
       <c r="F142" t="n">
-        <v>35890600</v>
+        <v>35141200</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4127,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B143" t="n">
-        <v>276.0775591796553</v>
+        <v>287.2037353515625</v>
       </c>
       <c r="C143" t="n">
-        <v>276.7467120540596</v>
+        <v>287.7230801433843</v>
       </c>
       <c r="D143" t="n">
-        <v>271.772870758184</v>
+        <v>276.7467055656006</v>
       </c>
       <c r="E143" t="n">
-        <v>273.1611633300781</v>
+        <v>277.6955407888773</v>
       </c>
       <c r="F143" t="n">
-        <v>35141200</v>
+        <v>43875400</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4153,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B144" t="n">
-        <v>277.6955407888773</v>
+        <v>297.0215759277344</v>
       </c>
       <c r="C144" t="n">
-        <v>287.7230801433843</v>
+        <v>300.1476725442409</v>
       </c>
       <c r="D144" t="n">
-        <v>276.7467055656006</v>
+        <v>290.0502125293938</v>
       </c>
       <c r="E144" t="n">
-        <v>287.2037353515625</v>
+        <v>290.4796724840224</v>
       </c>
       <c r="F144" t="n">
-        <v>43875400</v>
+        <v>37684500</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4179,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B145" t="n">
-        <v>290.4796724840224</v>
+        <v>295.403564453125</v>
       </c>
       <c r="C145" t="n">
-        <v>300.1476725442409</v>
+        <v>297.7107001938477</v>
       </c>
       <c r="D145" t="n">
-        <v>290.0502125293938</v>
+        <v>289.0914173614996</v>
       </c>
       <c r="E145" t="n">
-        <v>297.0215759277344</v>
+        <v>290.3298713924274</v>
       </c>
       <c r="F145" t="n">
-        <v>37684500</v>
+        <v>21666500</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4205,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B146" t="n">
-        <v>290.3298713924274</v>
+        <v>299.6183166503906</v>
       </c>
       <c r="C146" t="n">
-        <v>297.7107001938477</v>
+        <v>300.2475409865838</v>
       </c>
       <c r="D146" t="n">
-        <v>289.0914173614996</v>
+        <v>294.8142784540748</v>
       </c>
       <c r="E146" t="n">
-        <v>295.403564453125</v>
+        <v>295.5034260146894</v>
       </c>
       <c r="F146" t="n">
-        <v>21666500</v>
+        <v>16945500</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4231,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B147" t="n">
-        <v>295.5034260146894</v>
+        <v>305.08154296875</v>
       </c>
       <c r="C147" t="n">
-        <v>300.2475409865838</v>
+        <v>305.2513457589993</v>
       </c>
       <c r="D147" t="n">
-        <v>294.8142784540748</v>
+        <v>297.3511421656273</v>
       </c>
       <c r="E147" t="n">
-        <v>299.6183166503906</v>
+        <v>302.3549447988444</v>
       </c>
       <c r="F147" t="n">
-        <v>16945500</v>
+        <v>23205400</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4257,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B148" t="n">
-        <v>302.3549447988444</v>
+        <v>316.9268798828125</v>
       </c>
       <c r="C148" t="n">
-        <v>305.2513457589993</v>
+        <v>321.6809619973042</v>
       </c>
       <c r="D148" t="n">
-        <v>297.3511421656273</v>
+        <v>314.6297110626625</v>
       </c>
       <c r="E148" t="n">
-        <v>305.08154296875</v>
+        <v>320.0530070056894</v>
       </c>
       <c r="F148" t="n">
-        <v>23205400</v>
+        <v>33547100</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4283,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B149" t="n">
-        <v>320.0530070056894</v>
+        <v>318.0953979492188</v>
       </c>
       <c r="C149" t="n">
-        <v>321.6809619973042</v>
+        <v>319.1441153425082</v>
       </c>
       <c r="D149" t="n">
-        <v>314.6297110626625</v>
+        <v>310.6746106421415</v>
       </c>
       <c r="E149" t="n">
-        <v>316.9268798828125</v>
+        <v>315.5186078441214</v>
       </c>
       <c r="F149" t="n">
-        <v>33547100</v>
+        <v>23739200</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4309,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B150" t="n">
-        <v>315.5186078441214</v>
+        <v>316.8469543457031</v>
       </c>
       <c r="C150" t="n">
-        <v>319.1441153425082</v>
+        <v>321.4312640320202</v>
       </c>
       <c r="D150" t="n">
-        <v>310.6746106421415</v>
+        <v>315.9281112234418</v>
       </c>
       <c r="E150" t="n">
-        <v>318.0953979492188</v>
+        <v>319.6235089208506</v>
       </c>
       <c r="F150" t="n">
-        <v>23739200</v>
+        <v>19152600</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4335,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B151" t="n">
-        <v>319.6235089208506</v>
+        <v>320.9119262695312</v>
       </c>
       <c r="C151" t="n">
-        <v>321.4312640320202</v>
+        <v>321.2315371363443</v>
       </c>
       <c r="D151" t="n">
-        <v>315.9281112234418</v>
+        <v>315.0791651091577</v>
       </c>
       <c r="E151" t="n">
-        <v>316.8469543457031</v>
+        <v>316.7471095555252</v>
       </c>
       <c r="F151" t="n">
-        <v>19152600</v>
+        <v>18866400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4361,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B152" t="n">
-        <v>316.7471095555252</v>
+        <v>332.49755859375</v>
       </c>
       <c r="C152" t="n">
-        <v>321.2315371363443</v>
+        <v>332.8770926852431</v>
       </c>
       <c r="D152" t="n">
-        <v>315.0791651091577</v>
+        <v>323.3489033390031</v>
       </c>
       <c r="E152" t="n">
-        <v>320.9119262695312</v>
+        <v>324.3876234083889</v>
       </c>
       <c r="F152" t="n">
-        <v>18866400</v>
+        <v>27721400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4387,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B153" t="n">
-        <v>324.3876234083889</v>
+        <v>336.7023315429688</v>
       </c>
       <c r="C153" t="n">
-        <v>332.8770926852431</v>
+        <v>337.0619013824557</v>
       </c>
       <c r="D153" t="n">
-        <v>323.3489033390031</v>
+        <v>330.4900363853266</v>
       </c>
       <c r="E153" t="n">
-        <v>332.49755859375</v>
+        <v>332.4775916674409</v>
       </c>
       <c r="F153" t="n">
-        <v>27721400</v>
+        <v>24918800</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4413,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B154" t="n">
-        <v>332.4775916674409</v>
+        <v>335.6036682128906</v>
       </c>
       <c r="C154" t="n">
-        <v>337.0619013824557</v>
+        <v>339.458901613874</v>
       </c>
       <c r="D154" t="n">
-        <v>330.4900363853266</v>
+        <v>334.105526677332</v>
       </c>
       <c r="E154" t="n">
-        <v>336.7023315429688</v>
+        <v>338.3302967803236</v>
       </c>
       <c r="F154" t="n">
-        <v>24918800</v>
+        <v>20541500</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4439,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B155" t="n">
-        <v>338.3302967803236</v>
+        <v>341.2566833496094</v>
       </c>
       <c r="C155" t="n">
-        <v>339.458901613874</v>
+        <v>341.895905080184</v>
       </c>
       <c r="D155" t="n">
-        <v>334.105526677332</v>
+        <v>335.8234205588037</v>
       </c>
       <c r="E155" t="n">
-        <v>335.6036682128906</v>
+        <v>337.2316773591919</v>
       </c>
       <c r="F155" t="n">
-        <v>20541500</v>
+        <v>25581900</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4465,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B156" t="n">
-        <v>337.2316773591919</v>
+        <v>337.0019836425781</v>
       </c>
       <c r="C156" t="n">
-        <v>341.895905080184</v>
+        <v>340.9770333119858</v>
       </c>
       <c r="D156" t="n">
-        <v>335.8234205588037</v>
+        <v>336.1929591105031</v>
       </c>
       <c r="E156" t="n">
-        <v>341.2566833496094</v>
+        <v>340.3378420577138</v>
       </c>
       <c r="F156" t="n">
-        <v>25581900</v>
+        <v>18784200</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4491,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B157" t="n">
-        <v>340.3378420577138</v>
+        <v>331.8783264160156</v>
       </c>
       <c r="C157" t="n">
-        <v>340.9770333119858</v>
+        <v>338.9195798085849</v>
       </c>
       <c r="D157" t="n">
-        <v>336.1929591105031</v>
+        <v>330.9394885663705</v>
       </c>
       <c r="E157" t="n">
-        <v>337.0019836425781</v>
+        <v>337.2716301294484</v>
       </c>
       <c r="F157" t="n">
-        <v>18784200</v>
+        <v>23123800</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4517,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B158" t="n">
-        <v>337.2716301294484</v>
+        <v>338.8996276855469</v>
       </c>
       <c r="C158" t="n">
-        <v>338.9195798085849</v>
+        <v>339.3990082413208</v>
       </c>
       <c r="D158" t="n">
-        <v>330.9394885663705</v>
+        <v>334.7547751685775</v>
       </c>
       <c r="E158" t="n">
-        <v>331.8783264160156</v>
+        <v>336.6024588411248</v>
       </c>
       <c r="F158" t="n">
-        <v>23123800</v>
+        <v>20293000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4543,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B159" t="n">
-        <v>336.6024588411248</v>
+        <v>338.4701538085938</v>
       </c>
       <c r="C159" t="n">
-        <v>339.3990082413208</v>
+        <v>341.5363271303731</v>
       </c>
       <c r="D159" t="n">
-        <v>334.7547751685775</v>
+        <v>335.7634893621326</v>
       </c>
       <c r="E159" t="n">
-        <v>338.8996276855469</v>
+        <v>340.7572947145818</v>
       </c>
       <c r="F159" t="n">
-        <v>20293000</v>
+        <v>18650300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4569,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B160" t="n">
-        <v>340.7572947145818</v>
+        <v>343.9732971191406</v>
       </c>
       <c r="C160" t="n">
-        <v>341.5363271303731</v>
+        <v>344.8422143498026</v>
       </c>
       <c r="D160" t="n">
-        <v>335.7634893621326</v>
+        <v>334.9744808477988</v>
       </c>
       <c r="E160" t="n">
-        <v>338.4701538085938</v>
+        <v>338.3103390739037</v>
       </c>
       <c r="F160" t="n">
-        <v>18650300</v>
+        <v>26426100</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4595,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B161" t="n">
-        <v>338.3103390739037</v>
+        <v>349.9059448242188</v>
       </c>
       <c r="C161" t="n">
-        <v>344.8422143498026</v>
+        <v>352.7424225666816</v>
       </c>
       <c r="D161" t="n">
-        <v>334.9744808477988</v>
+        <v>342.3053878156813</v>
       </c>
       <c r="E161" t="n">
-        <v>343.9732971191406</v>
+        <v>345.55136124882</v>
       </c>
       <c r="F161" t="n">
-        <v>26426100</v>
+        <v>28576900</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4621,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B162" t="n">
-        <v>345.55136124882</v>
+        <v>349.3466491699219</v>
       </c>
       <c r="C162" t="n">
-        <v>352.7424225666816</v>
+        <v>351.9833930501032</v>
       </c>
       <c r="D162" t="n">
-        <v>342.3053878156813</v>
+        <v>345.6911799613628</v>
       </c>
       <c r="E162" t="n">
-        <v>349.9059448242188</v>
+        <v>348.1181620694143</v>
       </c>
       <c r="F162" t="n">
-        <v>28576900</v>
+        <v>27824100</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4647,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B163" t="n">
-        <v>348.1181620694143</v>
+        <v>349.5064697265625</v>
       </c>
       <c r="C163" t="n">
-        <v>351.9833930501032</v>
+        <v>355.3492283904879</v>
       </c>
       <c r="D163" t="n">
-        <v>345.6911799613628</v>
+        <v>343.7835575206014</v>
       </c>
       <c r="E163" t="n">
-        <v>349.3466491699219</v>
+        <v>347.1394107424554</v>
       </c>
       <c r="F163" t="n">
-        <v>27824100</v>
+        <v>35376300</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4673,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B164" t="n">
-        <v>347.1394107424554</v>
+        <v>384.3232421875</v>
       </c>
       <c r="C164" t="n">
-        <v>355.3492283904879</v>
+        <v>385.3619622201579</v>
       </c>
       <c r="D164" t="n">
-        <v>343.7835575206014</v>
+        <v>365.3667768501622</v>
       </c>
       <c r="E164" t="n">
-        <v>349.5064697265625</v>
+        <v>373.6065555628184</v>
       </c>
       <c r="F164" t="n">
-        <v>35376300</v>
+        <v>72040000</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4699,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B165" t="n">
-        <v>373.6065555628184</v>
+        <v>385.2121887207031</v>
       </c>
       <c r="C165" t="n">
-        <v>385.3619622201579</v>
+        <v>386.2808704617397</v>
       </c>
       <c r="D165" t="n">
-        <v>365.3667768501622</v>
+        <v>378.5804000830116</v>
       </c>
       <c r="E165" t="n">
-        <v>384.3232421875</v>
+        <v>381.1572209075714</v>
       </c>
       <c r="F165" t="n">
-        <v>72040000</v>
+        <v>30105200</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4725,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B166" t="n">
-        <v>381.1572209075714</v>
+        <v>382.7751770019531</v>
       </c>
       <c r="C166" t="n">
-        <v>386.2808704617397</v>
+        <v>386.9000650646732</v>
       </c>
       <c r="D166" t="n">
-        <v>378.5804000830116</v>
+        <v>379.3194722618546</v>
       </c>
       <c r="E166" t="n">
-        <v>385.2121887207031</v>
+        <v>385.1522332062169</v>
       </c>
       <c r="F166" t="n">
-        <v>30105200</v>
+        <v>26298600</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4751,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B167" t="n">
-        <v>385.1522332062169</v>
+        <v>387.9487609863281</v>
       </c>
       <c r="C167" t="n">
-        <v>386.9000650646732</v>
+        <v>392.3333367803882</v>
       </c>
       <c r="D167" t="n">
-        <v>379.3194722618546</v>
+        <v>383.5442209432822</v>
       </c>
       <c r="E167" t="n">
-        <v>382.7751770019531</v>
+        <v>385.7515048868787</v>
       </c>
       <c r="F167" t="n">
-        <v>26298600</v>
+        <v>23878600</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4777,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B168" t="n">
-        <v>385.7515048868787</v>
+        <v>397.546875</v>
       </c>
       <c r="C168" t="n">
-        <v>392.3333367803882</v>
+        <v>399.3546301445318</v>
       </c>
       <c r="D168" t="n">
-        <v>383.5442209432822</v>
+        <v>392.2734176347804</v>
       </c>
       <c r="E168" t="n">
-        <v>387.9487609863281</v>
+        <v>393.7615619135972</v>
       </c>
       <c r="F168" t="n">
-        <v>23878600</v>
+        <v>31308500</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4803,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B169" t="n">
-        <v>393.7615619135972</v>
+        <v>397.4969177246094</v>
       </c>
       <c r="C169" t="n">
-        <v>399.3546301445318</v>
+        <v>399.6043194807176</v>
       </c>
       <c r="D169" t="n">
-        <v>392.2734176347804</v>
+        <v>392.1934987581594</v>
       </c>
       <c r="E169" t="n">
-        <v>397.546875</v>
+        <v>399.4245497990884</v>
       </c>
       <c r="F169" t="n">
-        <v>31308500</v>
+        <v>24433500</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4829,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B170" t="n">
-        <v>399.4245497990884</v>
+        <v>400.3034362792969</v>
       </c>
       <c r="C170" t="n">
-        <v>399.6043194807176</v>
+        <v>401.5019617899809</v>
       </c>
       <c r="D170" t="n">
-        <v>392.1934987581594</v>
+        <v>395.8689345614438</v>
       </c>
       <c r="E170" t="n">
-        <v>397.4969177246094</v>
+        <v>396.5081562950806</v>
       </c>
       <c r="F170" t="n">
-        <v>24433500</v>
+        <v>21461800</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4855,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B171" t="n">
-        <v>396.5081562950806</v>
+        <v>388.1585083007812</v>
       </c>
       <c r="C171" t="n">
-        <v>401.5019617899809</v>
+        <v>396.9475933307253</v>
       </c>
       <c r="D171" t="n">
-        <v>395.8689345614438</v>
+        <v>387.9887055115338</v>
       </c>
       <c r="E171" t="n">
-        <v>400.3034362792969</v>
+        <v>393.1622804247065</v>
       </c>
       <c r="F171" t="n">
-        <v>21461800</v>
+        <v>30753700</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4881,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B172" t="n">
-        <v>393.1622804247065</v>
+        <v>386.8701171875</v>
       </c>
       <c r="C172" t="n">
-        <v>396.9475933307253</v>
+        <v>388.0386506028281</v>
       </c>
       <c r="D172" t="n">
-        <v>387.9887055115338</v>
+        <v>382.2957742925754</v>
       </c>
       <c r="E172" t="n">
-        <v>388.1585083007812</v>
+        <v>386.8601198229993</v>
       </c>
       <c r="F172" t="n">
-        <v>30753700</v>
+        <v>26017500</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4907,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B173" t="n">
-        <v>386.8601198229993</v>
+        <v>402.1211853027344</v>
       </c>
       <c r="C173" t="n">
-        <v>388.0386506028281</v>
+        <v>403.1998643489371</v>
       </c>
       <c r="D173" t="n">
-        <v>382.2957742925754</v>
+        <v>384.5230197682841</v>
       </c>
       <c r="E173" t="n">
-        <v>386.8701171875</v>
+        <v>385.1222825184223</v>
       </c>
       <c r="F173" t="n">
-        <v>26017500</v>
+        <v>28144600</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4933,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B174" t="n">
-        <v>385.1222825184223</v>
+        <v>400.5731201171875</v>
       </c>
       <c r="C174" t="n">
-        <v>403.1998643489371</v>
+        <v>402.430801125594</v>
       </c>
       <c r="D174" t="n">
-        <v>384.5230197682841</v>
+        <v>395.349588612008</v>
       </c>
       <c r="E174" t="n">
-        <v>402.1211853027344</v>
+        <v>396.7878070287349</v>
       </c>
       <c r="F174" t="n">
-        <v>28144600</v>
+        <v>21136700</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4959,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B175" t="n">
-        <v>396.7878070287349</v>
+        <v>396.2884216308594</v>
       </c>
       <c r="C175" t="n">
-        <v>402.430801125594</v>
+        <v>399.0450119758119</v>
       </c>
       <c r="D175" t="n">
-        <v>395.349588612008</v>
+        <v>392.692875633045</v>
       </c>
       <c r="E175" t="n">
-        <v>400.5731201171875</v>
+        <v>395.8290000666237</v>
       </c>
       <c r="F175" t="n">
-        <v>21136700</v>
+        <v>20309700</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4985,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B176" t="n">
-        <v>395.8290000666237</v>
+        <v>396.4482421875</v>
       </c>
       <c r="C176" t="n">
-        <v>399.0450119758119</v>
+        <v>408.1037674120522</v>
       </c>
       <c r="D176" t="n">
-        <v>392.692875633045</v>
+        <v>394.0412242260142</v>
       </c>
       <c r="E176" t="n">
-        <v>396.2884216308594</v>
+        <v>395.1997907850553</v>
       </c>
       <c r="F176" t="n">
-        <v>20309700</v>
+        <v>26837200</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5011,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B177" t="n">
-        <v>395.1997907850553</v>
+        <v>387.1797180175781</v>
       </c>
       <c r="C177" t="n">
-        <v>408.1037674120522</v>
+        <v>396.6579507685057</v>
       </c>
       <c r="D177" t="n">
-        <v>394.0412242260142</v>
+        <v>385.6316200793582</v>
       </c>
       <c r="E177" t="n">
-        <v>396.4482421875</v>
+        <v>396.4681837278221</v>
       </c>
       <c r="F177" t="n">
-        <v>26837200</v>
+        <v>39545700</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5037,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B178" t="n">
-        <v>396.4681837278221</v>
+        <v>388.4281921386719</v>
       </c>
       <c r="C178" t="n">
-        <v>396.6579507685057</v>
+        <v>393.3720414113799</v>
       </c>
       <c r="D178" t="n">
-        <v>385.6316200793582</v>
+        <v>382.4256280338265</v>
       </c>
       <c r="E178" t="n">
-        <v>387.1797180175781</v>
+        <v>387.2196997137571</v>
       </c>
       <c r="F178" t="n">
-        <v>39545700</v>
+        <v>31744400</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5063,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B179" t="n">
-        <v>387.2196997137571</v>
+        <v>387.1797180175781</v>
       </c>
       <c r="C179" t="n">
-        <v>393.3720414113799</v>
+        <v>392.0137179133836</v>
       </c>
       <c r="D179" t="n">
-        <v>382.4256280338265</v>
+        <v>382.5454520468608</v>
       </c>
       <c r="E179" t="n">
-        <v>388.4281921386719</v>
+        <v>385.2221548650083</v>
       </c>
       <c r="F179" t="n">
-        <v>31744400</v>
+        <v>24852800</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5089,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B180" t="n">
-        <v>385.2221548650083</v>
+        <v>382.4955444335938</v>
       </c>
       <c r="C180" t="n">
-        <v>392.0137179133836</v>
+        <v>388.258385079403</v>
       </c>
       <c r="D180" t="n">
-        <v>382.5454520468608</v>
+        <v>381.2970189068101</v>
       </c>
       <c r="E180" t="n">
-        <v>387.1797180175781</v>
+        <v>386.8701229826527</v>
       </c>
       <c r="F180" t="n">
-        <v>24852800</v>
+        <v>20442100</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5115,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B181" t="n">
-        <v>386.8701229826527</v>
+        <v>388.398193359375</v>
       </c>
       <c r="C181" t="n">
-        <v>388.258385079403</v>
+        <v>388.7777274266938</v>
       </c>
       <c r="D181" t="n">
-        <v>381.2970189068101</v>
+        <v>382.125975324115</v>
       </c>
       <c r="E181" t="n">
-        <v>382.4955444335938</v>
+        <v>384.0336125447445</v>
       </c>
       <c r="F181" t="n">
-        <v>20442100</v>
+        <v>27747400</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5141,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B182" t="n">
-        <v>384.0336125447445</v>
+        <v>388.3482360839844</v>
       </c>
       <c r="C182" t="n">
-        <v>388.7777274266938</v>
+        <v>393.3919975499695</v>
       </c>
       <c r="D182" t="n">
-        <v>382.125975324115</v>
+        <v>385.421873594791</v>
       </c>
       <c r="E182" t="n">
-        <v>388.398193359375</v>
+        <v>386.1909390913781</v>
       </c>
       <c r="F182" t="n">
-        <v>27747400</v>
+        <v>23087300</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5167,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B183" t="n">
-        <v>386.1909390913781</v>
+        <v>389.6466674804688</v>
       </c>
       <c r="C183" t="n">
-        <v>393.3919975499695</v>
+        <v>391.384502017129</v>
       </c>
       <c r="D183" t="n">
-        <v>385.421873594791</v>
+        <v>384.682823662297</v>
       </c>
       <c r="E183" t="n">
-        <v>388.3482360839844</v>
+        <v>387.5193014898567</v>
       </c>
       <c r="F183" t="n">
-        <v>23087300</v>
+        <v>24357500</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5193,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B184" t="n">
-        <v>387.5193014898567</v>
+        <v>379.8687744140625</v>
       </c>
       <c r="C184" t="n">
-        <v>391.384502017129</v>
+        <v>384.7626974671623</v>
       </c>
       <c r="D184" t="n">
-        <v>384.682823662297</v>
+        <v>377.9910987617443</v>
       </c>
       <c r="E184" t="n">
-        <v>389.6466674804688</v>
+        <v>384.7626974671623</v>
       </c>
       <c r="F184" t="n">
-        <v>24357500</v>
+        <v>44415800</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5219,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B185" t="n">
-        <v>384.7626974671623</v>
+        <v>375.9037170410156</v>
       </c>
       <c r="C185" t="n">
-        <v>384.7626974671623</v>
+        <v>378.0910063274455</v>
       </c>
       <c r="D185" t="n">
-        <v>377.9910987617443</v>
+        <v>373.0572417592452</v>
       </c>
       <c r="E185" t="n">
-        <v>379.8687744140625</v>
+        <v>376.0535251127361</v>
       </c>
       <c r="F185" t="n">
-        <v>44415800</v>
+        <v>28672100</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5245,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B186" t="n">
-        <v>376.0535251127361</v>
+        <v>361.4017028808594</v>
       </c>
       <c r="C186" t="n">
-        <v>378.0910063274455</v>
+        <v>373.0772223440179</v>
       </c>
       <c r="D186" t="n">
-        <v>373.0572417592452</v>
+        <v>357.9959239406105</v>
       </c>
       <c r="E186" t="n">
-        <v>375.9037170410156</v>
+        <v>366.1358206463617</v>
       </c>
       <c r="F186" t="n">
-        <v>28672100</v>
+        <v>50412300</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5271,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B187" t="n">
-        <v>366.1358206463617</v>
+        <v>358.5452270507812</v>
       </c>
       <c r="C187" t="n">
-        <v>373.0772223440179</v>
+        <v>365.9960065843375</v>
       </c>
       <c r="D187" t="n">
-        <v>357.9959239406105</v>
+        <v>357.6363508187865</v>
       </c>
       <c r="E187" t="n">
-        <v>361.4017028808594</v>
+        <v>361.5814692403301</v>
       </c>
       <c r="F187" t="n">
-        <v>50412300</v>
+        <v>55441600</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5297,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B188" t="n">
-        <v>361.5814692403301</v>
+        <v>371.7289123535156</v>
       </c>
       <c r="C188" t="n">
-        <v>365.9960065843375</v>
+        <v>372.7875967270043</v>
       </c>
       <c r="D188" t="n">
-        <v>357.6363508187865</v>
+        <v>357.7662205978281</v>
       </c>
       <c r="E188" t="n">
-        <v>358.5452270507812</v>
+        <v>358.4553682250688</v>
       </c>
       <c r="F188" t="n">
-        <v>55441600</v>
+        <v>44055500</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5323,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B189" t="n">
-        <v>358.4553682250688</v>
+        <v>368.0734252929688</v>
       </c>
       <c r="C189" t="n">
-        <v>372.7875967270043</v>
+        <v>371.6190149899659</v>
       </c>
       <c r="D189" t="n">
-        <v>357.7662205978281</v>
+        <v>363.6688852043904</v>
       </c>
       <c r="E189" t="n">
-        <v>371.7289123535156</v>
+        <v>365.8861360555161</v>
       </c>
       <c r="F189" t="n">
-        <v>44055500</v>
+        <v>37471200</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,25 +5349,25 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B190" t="n">
-        <v>365.8861360555161</v>
+        <v>363.0766296386719</v>
       </c>
       <c r="C190" t="n">
-        <v>371.6190149899659</v>
+        <v>365.9647879200631</v>
       </c>
       <c r="D190" t="n">
-        <v>363.6688852043904</v>
+        <v>360.2984165590168</v>
       </c>
       <c r="E190" t="n">
-        <v>368.0734252929688</v>
+        <v>364.9454235864071</v>
       </c>
       <c r="F190" t="n">
-        <v>37471200</v>
+        <v>27942500</v>
       </c>
       <c r="G190" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5383,25 +5375,25 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B191" t="n">
-        <v>364.9454235864071</v>
+        <v>364.0260314941406</v>
       </c>
       <c r="C191" t="n">
-        <v>365.9647879200631</v>
+        <v>371.8409852276818</v>
       </c>
       <c r="D191" t="n">
-        <v>360.2984165590168</v>
+        <v>357.0704802123837</v>
       </c>
       <c r="E191" t="n">
-        <v>363.0766296386719</v>
+        <v>366.8542002567407</v>
       </c>
       <c r="F191" t="n">
-        <v>27942500</v>
+        <v>29535100</v>
       </c>
       <c r="G191" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5409,22 +5401,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B192" t="n">
-        <v>366.8542002567407</v>
+        <v>356.1510925292969</v>
       </c>
       <c r="C192" t="n">
-        <v>371.8409852276818</v>
+        <v>368.3232616719084</v>
       </c>
       <c r="D192" t="n">
-        <v>357.0704802123837</v>
+        <v>354.9718577941881</v>
       </c>
       <c r="E192" t="n">
-        <v>364.0260314941406</v>
+        <v>362.9567158453764</v>
       </c>
       <c r="F192" t="n">
-        <v>29535100</v>
+        <v>32357100</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5427,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B193" t="n">
-        <v>362.9567158453764</v>
+        <v>357.5401611328125</v>
       </c>
       <c r="C193" t="n">
-        <v>368.3232616719084</v>
+        <v>358.5694982511428</v>
       </c>
       <c r="D193" t="n">
-        <v>354.9718577941881</v>
+        <v>346.1374871435174</v>
       </c>
       <c r="E193" t="n">
-        <v>356.1510925292969</v>
+        <v>355.7013467902599</v>
       </c>
       <c r="F193" t="n">
-        <v>32357100</v>
+        <v>35538200</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5453,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B194" t="n">
-        <v>355.7013467902599</v>
+        <v>359.4489440917969</v>
       </c>
       <c r="C194" t="n">
-        <v>358.5694982511428</v>
+        <v>366.3345327833823</v>
       </c>
       <c r="D194" t="n">
-        <v>346.1374871435174</v>
+        <v>354.7119986974298</v>
       </c>
       <c r="E194" t="n">
-        <v>357.5401611328125</v>
+        <v>362.3870579560934</v>
       </c>
       <c r="F194" t="n">
-        <v>35538200</v>
+        <v>24704600</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5479,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B195" t="n">
-        <v>362.3870579560934</v>
+        <v>369.1127624511719</v>
       </c>
       <c r="C195" t="n">
-        <v>366.3345327833823</v>
+        <v>372.7504085202595</v>
       </c>
       <c r="D195" t="n">
-        <v>354.7119986974298</v>
+        <v>366.3145426692825</v>
       </c>
       <c r="E195" t="n">
-        <v>359.4489440917969</v>
+        <v>367.6936611370598</v>
       </c>
       <c r="F195" t="n">
-        <v>24704600</v>
+        <v>27727500</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5505,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B196" t="n">
-        <v>367.6936611370598</v>
+        <v>373.01025390625</v>
       </c>
       <c r="C196" t="n">
-        <v>372.7504085202595</v>
+        <v>375.7584875251172</v>
       </c>
       <c r="D196" t="n">
-        <v>366.3145426692825</v>
+        <v>366.8242274297617</v>
       </c>
       <c r="E196" t="n">
-        <v>369.1127624511719</v>
+        <v>369.3626044753487</v>
       </c>
       <c r="F196" t="n">
-        <v>27727500</v>
+        <v>24876100</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5531,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B197" t="n">
-        <v>369.3626044753487</v>
+        <v>363.5563354492188</v>
       </c>
       <c r="C197" t="n">
-        <v>375.7584875251172</v>
+        <v>372.0908279957741</v>
       </c>
       <c r="D197" t="n">
-        <v>366.8242274297617</v>
+        <v>361.7874528539307</v>
       </c>
       <c r="E197" t="n">
-        <v>373.01025390625</v>
+        <v>368.8929017493238</v>
       </c>
       <c r="F197" t="n">
-        <v>24876100</v>
+        <v>24543600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5557,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B198" t="n">
-        <v>368.8929017493238</v>
+        <v>367.7935791015625</v>
       </c>
       <c r="C198" t="n">
-        <v>372.0908279957741</v>
+        <v>369.2426598317581</v>
       </c>
       <c r="D198" t="n">
-        <v>361.7874528539307</v>
+        <v>358.4396065335441</v>
       </c>
       <c r="E198" t="n">
-        <v>363.5563354492188</v>
+        <v>365.5150449761754</v>
       </c>
       <c r="F198" t="n">
-        <v>24543600</v>
+        <v>44470100</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5583,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B199" t="n">
-        <v>365.5150449761754</v>
+        <v>349.4553833007812</v>
       </c>
       <c r="C199" t="n">
-        <v>369.2426598317581</v>
+        <v>358.6894689253907</v>
       </c>
       <c r="D199" t="n">
-        <v>358.4396065335441</v>
+        <v>341.5005047739323</v>
       </c>
       <c r="E199" t="n">
-        <v>367.7935791015625</v>
+        <v>357.7200907639775</v>
       </c>
       <c r="F199" t="n">
-        <v>44470100</v>
+        <v>52814800</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5609,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B200" t="n">
-        <v>357.7200907639775</v>
+        <v>345.9076538085938</v>
       </c>
       <c r="C200" t="n">
-        <v>358.6894689253907</v>
+        <v>349.0656275102868</v>
       </c>
       <c r="D200" t="n">
-        <v>341.5005047739323</v>
+        <v>339.981470511436</v>
       </c>
       <c r="E200" t="n">
-        <v>349.4553833007812</v>
+        <v>340.4711459801061</v>
       </c>
       <c r="F200" t="n">
-        <v>52814800</v>
+        <v>34007700</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5635,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B201" t="n">
-        <v>340.4711459801061</v>
+        <v>345.0682067871094</v>
       </c>
       <c r="C201" t="n">
-        <v>349.0656275102868</v>
+        <v>353.2529482684732</v>
       </c>
       <c r="D201" t="n">
-        <v>339.981470511436</v>
+        <v>341.7103492701006</v>
       </c>
       <c r="E201" t="n">
-        <v>345.9076538085938</v>
+        <v>348.8157979233392</v>
       </c>
       <c r="F201" t="n">
-        <v>34007700</v>
+        <v>44997300</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5661,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B202" t="n">
-        <v>348.8157979233392</v>
+        <v>343.4891967773438</v>
       </c>
       <c r="C202" t="n">
-        <v>353.2529482684732</v>
+        <v>345.3480177972958</v>
       </c>
       <c r="D202" t="n">
-        <v>341.7103492701006</v>
+        <v>335.6242572392167</v>
       </c>
       <c r="E202" t="n">
-        <v>345.0682067871094</v>
+        <v>336.5137001542092</v>
       </c>
       <c r="F202" t="n">
-        <v>44997300</v>
+        <v>44491400</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5687,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B203" t="n">
-        <v>336.5137001542092</v>
+        <v>337.1732788085938</v>
       </c>
       <c r="C203" t="n">
-        <v>345.3480177972958</v>
+        <v>346.1374872957393</v>
       </c>
       <c r="D203" t="n">
-        <v>335.6242572392167</v>
+        <v>329.98789515005</v>
       </c>
       <c r="E203" t="n">
-        <v>343.4891967773438</v>
+        <v>342.3299372399903</v>
       </c>
       <c r="F203" t="n">
-        <v>44491400</v>
+        <v>114706300</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5713,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B204" t="n">
-        <v>342.3299372399903</v>
+        <v>353.4228210449219</v>
       </c>
       <c r="C204" t="n">
-        <v>346.1374872957393</v>
+        <v>354.122383587675</v>
       </c>
       <c r="D204" t="n">
-        <v>329.98789515005</v>
+        <v>340.4511784786947</v>
       </c>
       <c r="E204" t="n">
-        <v>337.1732788085938</v>
+        <v>341.6104064955248</v>
       </c>
       <c r="F204" t="n">
-        <v>114706300</v>
+        <v>34213900</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5739,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B205" t="n">
-        <v>341.6104064955248</v>
+        <v>357.1404418945312</v>
       </c>
       <c r="C205" t="n">
-        <v>354.122383587675</v>
+        <v>358.3896389689017</v>
       </c>
       <c r="D205" t="n">
-        <v>340.4511784786947</v>
+        <v>350.1749177879227</v>
       </c>
       <c r="E205" t="n">
-        <v>353.4228210449219</v>
+        <v>353.6426900862941</v>
       </c>
       <c r="F205" t="n">
-        <v>34213900</v>
+        <v>35237200</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5765,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B206" t="n">
-        <v>353.6426900862941</v>
+        <v>360.9779663085938</v>
       </c>
       <c r="C206" t="n">
-        <v>358.3896389689017</v>
+        <v>362.7368455226467</v>
       </c>
       <c r="D206" t="n">
-        <v>350.1749177879227</v>
+        <v>356.2010379867681</v>
       </c>
       <c r="E206" t="n">
-        <v>357.1404418945312</v>
+        <v>358.1397942573561</v>
       </c>
       <c r="F206" t="n">
-        <v>35237200</v>
+        <v>26736400</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5791,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B207" t="n">
-        <v>358.1397942573561</v>
+        <v>359.6788024902344</v>
       </c>
       <c r="C207" t="n">
-        <v>362.7368455226467</v>
+        <v>363.9760280309549</v>
       </c>
       <c r="D207" t="n">
-        <v>356.2010379867681</v>
+        <v>353.1929813351636</v>
       </c>
       <c r="E207" t="n">
-        <v>360.9779663085938</v>
+        <v>359.2490860357571</v>
       </c>
       <c r="F207" t="n">
-        <v>26736400</v>
+        <v>25974800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5817,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B208" t="n">
-        <v>359.2490860357571</v>
+        <v>366.2245788574219</v>
       </c>
       <c r="C208" t="n">
-        <v>363.9760280309549</v>
+        <v>367.693635754559</v>
       </c>
       <c r="D208" t="n">
-        <v>353.1929813351636</v>
+        <v>357.1504252362982</v>
       </c>
       <c r="E208" t="n">
-        <v>359.6788024902344</v>
+        <v>361.3177293642356</v>
       </c>
       <c r="F208" t="n">
-        <v>25974800</v>
+        <v>26915800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5843,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B209" t="n">
-        <v>361.3177293642356</v>
+        <v>366.7942199707031</v>
       </c>
       <c r="C209" t="n">
-        <v>367.693635754559</v>
+        <v>372.9202869594668</v>
       </c>
       <c r="D209" t="n">
-        <v>357.1504252362982</v>
+        <v>365.2652040573587</v>
       </c>
       <c r="E209" t="n">
-        <v>366.2245788574219</v>
+        <v>368.8329180211536</v>
       </c>
       <c r="F209" t="n">
-        <v>26915800</v>
+        <v>24045600</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5869,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B210" t="n">
-        <v>368.8329180211536</v>
+        <v>361.6875305175781</v>
       </c>
       <c r="C210" t="n">
-        <v>372.9202869594668</v>
+        <v>367.6037106679975</v>
       </c>
       <c r="D210" t="n">
-        <v>365.2652040573587</v>
+        <v>357.7900113228786</v>
       </c>
       <c r="E210" t="n">
-        <v>366.7942199707031</v>
+        <v>364.525702555654</v>
       </c>
       <c r="F210" t="n">
-        <v>24045600</v>
+        <v>22094800</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5895,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B211" t="n">
-        <v>364.525702555654</v>
+        <v>358.6594848632812</v>
       </c>
       <c r="C211" t="n">
-        <v>367.6037106679975</v>
+        <v>359.4189759454678</v>
       </c>
       <c r="D211" t="n">
-        <v>357.7900113228786</v>
+        <v>350.8544734886641</v>
       </c>
       <c r="E211" t="n">
-        <v>361.6875305175781</v>
+        <v>354.0824097063769</v>
       </c>
       <c r="F211" t="n">
-        <v>22094800</v>
+        <v>24729100</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5921,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B212" t="n">
-        <v>354.0824097063769</v>
+        <v>356.9505615234375</v>
       </c>
       <c r="C212" t="n">
-        <v>359.4189759454678</v>
+        <v>357.5901650645865</v>
       </c>
       <c r="D212" t="n">
-        <v>350.8544734886641</v>
+        <v>352.5234144110846</v>
       </c>
       <c r="E212" t="n">
-        <v>358.6594848632812</v>
+        <v>357.3003428038799</v>
       </c>
       <c r="F212" t="n">
-        <v>24729100</v>
+        <v>18146100</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5947,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B213" t="n">
-        <v>357.3003428038799</v>
+        <v>352.2835693359375</v>
       </c>
       <c r="C213" t="n">
-        <v>357.5901650645865</v>
+        <v>357.8999543595846</v>
       </c>
       <c r="D213" t="n">
-        <v>352.5234144110846</v>
+        <v>351.5240477747128</v>
       </c>
       <c r="E213" t="n">
-        <v>356.9505615234375</v>
+        <v>355.9611981097028</v>
       </c>
       <c r="F213" t="n">
-        <v>18146100</v>
+        <v>15901700</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5973,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B214" t="n">
-        <v>355.9611981097028</v>
+        <v>359.2790832519531</v>
       </c>
       <c r="C214" t="n">
-        <v>357.8999543595846</v>
+        <v>359.92865963343</v>
       </c>
       <c r="D214" t="n">
-        <v>351.5240477747128</v>
+        <v>350.8644783088037</v>
       </c>
       <c r="E214" t="n">
-        <v>352.2835693359375</v>
+        <v>350.9744235107016</v>
       </c>
       <c r="F214" t="n">
-        <v>15901700</v>
+        <v>18259400</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +5999,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B215" t="n">
-        <v>350.9744235107016</v>
+        <v>370.6817626953125</v>
       </c>
       <c r="C215" t="n">
-        <v>359.92865963343</v>
+        <v>373.4099896327818</v>
       </c>
       <c r="D215" t="n">
-        <v>350.8644783088037</v>
+        <v>357.5302120160503</v>
       </c>
       <c r="E215" t="n">
-        <v>359.2790832519531</v>
+        <v>357.7400685886304</v>
       </c>
       <c r="F215" t="n">
-        <v>18259400</v>
+        <v>28284600</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6025,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B216" t="n">
-        <v>357.7400685886304</v>
+        <v>354.2322998046875</v>
       </c>
       <c r="C216" t="n">
-        <v>373.4099896327818</v>
+        <v>375.0289298103755</v>
       </c>
       <c r="D216" t="n">
-        <v>357.5302120160503</v>
+        <v>352.0736836469807</v>
       </c>
       <c r="E216" t="n">
-        <v>370.6817626953125</v>
+        <v>372.8203579699616</v>
       </c>
       <c r="F216" t="n">
-        <v>28284600</v>
+        <v>41158500</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6051,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B217" t="n">
-        <v>372.8203579699616</v>
+        <v>346.5472412109375</v>
       </c>
       <c r="C217" t="n">
-        <v>375.0289298103755</v>
+        <v>348.2961170979314</v>
       </c>
       <c r="D217" t="n">
-        <v>352.0736836469807</v>
+        <v>341.1407126662452</v>
       </c>
       <c r="E217" t="n">
-        <v>354.2322998046875</v>
+        <v>345.7777467999313</v>
       </c>
       <c r="F217" t="n">
-        <v>41158500</v>
+        <v>29959300</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6077,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B218" t="n">
-        <v>345.7777467999313</v>
+        <v>351.7638854980469</v>
       </c>
       <c r="C218" t="n">
-        <v>348.2961170979314</v>
+        <v>359.4489481797366</v>
       </c>
       <c r="D218" t="n">
-        <v>341.1407126662452</v>
+        <v>350.2948285491913</v>
       </c>
       <c r="E218" t="n">
-        <v>346.5472412109375</v>
+        <v>350.6546131580819</v>
       </c>
       <c r="F218" t="n">
-        <v>29959300</v>
+        <v>24736600</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6103,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B219" t="n">
-        <v>350.6546131580819</v>
+        <v>346.927001953125</v>
       </c>
       <c r="C219" t="n">
-        <v>359.4489481797366</v>
+        <v>351.094336770995</v>
       </c>
       <c r="D219" t="n">
-        <v>350.2948285491913</v>
+        <v>346.7771044052826</v>
       </c>
       <c r="E219" t="n">
-        <v>351.7638854980469</v>
+        <v>351.094336770995</v>
       </c>
       <c r="F219" t="n">
-        <v>24736600</v>
+        <v>23369800</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6129,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B220" t="n">
-        <v>351.094336770995</v>
+        <v>341.8702392578125</v>
       </c>
       <c r="C220" t="n">
-        <v>351.094336770995</v>
+        <v>349.7152025525983</v>
       </c>
       <c r="D220" t="n">
-        <v>346.7771044052826</v>
+        <v>341.5104851592261</v>
       </c>
       <c r="E220" t="n">
-        <v>346.927001953125</v>
+        <v>347.9363472365376</v>
       </c>
       <c r="F220" t="n">
-        <v>23369800</v>
+        <v>39334100</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6155,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B221" t="n">
-        <v>347.9363472365376</v>
+        <v>317.4859313964844</v>
       </c>
       <c r="C221" t="n">
-        <v>349.7152025525983</v>
+        <v>324.2815511558238</v>
       </c>
       <c r="D221" t="n">
-        <v>341.5104851592261</v>
+        <v>314.6977150387725</v>
       </c>
       <c r="E221" t="n">
-        <v>341.8702392578125</v>
+        <v>320.9237241212255</v>
       </c>
       <c r="F221" t="n">
-        <v>39334100</v>
+        <v>69419700</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6181,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B222" t="n">
-        <v>320.9237241212255</v>
+        <v>319.5346069335938</v>
       </c>
       <c r="C222" t="n">
-        <v>324.2815511558238</v>
+        <v>323.9717573627877</v>
       </c>
       <c r="D222" t="n">
-        <v>314.6977150387725</v>
+        <v>317.1161784867298</v>
       </c>
       <c r="E222" t="n">
-        <v>317.4859313964844</v>
+        <v>318.2154780071113</v>
       </c>
       <c r="F222" t="n">
-        <v>69419700</v>
+        <v>31806600</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6207,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B223" t="n">
-        <v>318.2154780071113</v>
+        <v>326.3502197265625</v>
       </c>
       <c r="C223" t="n">
-        <v>323.9717573627877</v>
+        <v>330.2077559724587</v>
       </c>
       <c r="D223" t="n">
-        <v>317.1161784867298</v>
+        <v>324.2415898017393</v>
       </c>
       <c r="E223" t="n">
-        <v>319.5346069335938</v>
+        <v>324.83120713377</v>
       </c>
       <c r="F223" t="n">
-        <v>31806600</v>
+        <v>28471600</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6233,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B224" t="n">
-        <v>324.83120713377</v>
+        <v>333.4956359863281</v>
       </c>
       <c r="C224" t="n">
-        <v>330.2077559724587</v>
+        <v>335.6642555263833</v>
       </c>
       <c r="D224" t="n">
-        <v>324.2415898017393</v>
+        <v>324.2316014627561</v>
       </c>
       <c r="E224" t="n">
-        <v>326.3502197265625</v>
+        <v>327.6893704249235</v>
       </c>
       <c r="F224" t="n">
-        <v>28471600</v>
+        <v>29511900</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6259,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B225" t="n">
-        <v>327.6893704249235</v>
+        <v>336.4937133789062</v>
       </c>
       <c r="C225" t="n">
-        <v>335.6642555263833</v>
+        <v>342.2800028423013</v>
       </c>
       <c r="D225" t="n">
-        <v>324.2316014627561</v>
+        <v>331.4069864854741</v>
       </c>
       <c r="E225" t="n">
-        <v>333.4956359863281</v>
+        <v>334.455045685483</v>
       </c>
       <c r="F225" t="n">
-        <v>29511900</v>
+        <v>27501600</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6285,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B226" t="n">
-        <v>334.455045685483</v>
+        <v>333.4456787109375</v>
       </c>
       <c r="C226" t="n">
-        <v>342.2800028423013</v>
+        <v>336.2938541262907</v>
       </c>
       <c r="D226" t="n">
-        <v>331.4069864854741</v>
+        <v>330.1278039779788</v>
       </c>
       <c r="E226" t="n">
-        <v>336.4937133789062</v>
+        <v>333.9853403838827</v>
       </c>
       <c r="F226" t="n">
-        <v>27501600</v>
+        <v>30168000</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6311,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B227" t="n">
-        <v>333.9853403838827</v>
+        <v>355.9012451171875</v>
       </c>
       <c r="C227" t="n">
-        <v>336.2938541262907</v>
+        <v>358.3496530632621</v>
       </c>
       <c r="D227" t="n">
-        <v>330.1278039779788</v>
+        <v>339.7816013274756</v>
       </c>
       <c r="E227" t="n">
-        <v>333.4456787109375</v>
+        <v>340.611054758666</v>
       </c>
       <c r="F227" t="n">
-        <v>30168000</v>
+        <v>46498000</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6337,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B228" t="n">
-        <v>340.611054758666</v>
+        <v>373.2700805664062</v>
       </c>
       <c r="C228" t="n">
-        <v>358.3496530632621</v>
+        <v>376.4480305309448</v>
       </c>
       <c r="D228" t="n">
-        <v>339.7816013274756</v>
+        <v>363.1166033198653</v>
       </c>
       <c r="E228" t="n">
-        <v>355.9012451171875</v>
+        <v>365.2152604560987</v>
       </c>
       <c r="F228" t="n">
-        <v>46498000</v>
+        <v>38669700</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6363,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B229" t="n">
-        <v>365.2152604560987</v>
+        <v>377.4074096679688</v>
       </c>
       <c r="C229" t="n">
-        <v>376.4480305309448</v>
+        <v>380.2755612380555</v>
       </c>
       <c r="D229" t="n">
-        <v>363.1166033198653</v>
+        <v>367.263935640354</v>
       </c>
       <c r="E229" t="n">
-        <v>373.2700805664062</v>
+        <v>367.9834743668337</v>
       </c>
       <c r="F229" t="n">
-        <v>38669700</v>
+        <v>35705700</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6389,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B230" t="n">
-        <v>367.9834743668337</v>
+        <v>362.1971740722656</v>
       </c>
       <c r="C230" t="n">
-        <v>380.2755612380555</v>
+        <v>384.2330278418686</v>
       </c>
       <c r="D230" t="n">
-        <v>367.263935640354</v>
+        <v>356.5408062961898</v>
       </c>
       <c r="E230" t="n">
-        <v>377.4074096679688</v>
+        <v>383.0937455186354</v>
       </c>
       <c r="F230" t="n">
-        <v>35705700</v>
+        <v>46926300</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6415,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B231" t="n">
-        <v>383.0937455186354</v>
+        <v>357.5202026367188</v>
       </c>
       <c r="C231" t="n">
-        <v>384.2330278418686</v>
+        <v>363.8961093831237</v>
       </c>
       <c r="D231" t="n">
-        <v>356.5408062961898</v>
+        <v>356.6507663527499</v>
       </c>
       <c r="E231" t="n">
-        <v>362.1971740722656</v>
+        <v>360.5382517887205</v>
       </c>
       <c r="F231" t="n">
-        <v>46926300</v>
+        <v>25235900</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6441,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B232" t="n">
-        <v>360.5382517887205</v>
+        <v>354.0723876953125</v>
       </c>
       <c r="C232" t="n">
-        <v>363.8961093831237</v>
+        <v>358.6694387836589</v>
       </c>
       <c r="D232" t="n">
-        <v>356.6507663527499</v>
+        <v>353.5527327193329</v>
       </c>
       <c r="E232" t="n">
-        <v>357.5202026367188</v>
+        <v>356.4908465215469</v>
       </c>
       <c r="F232" t="n">
-        <v>25235900</v>
+        <v>19859900</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6467,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B233" t="n">
-        <v>356.4908465215469</v>
+        <v>357.2903442382812</v>
       </c>
       <c r="C233" t="n">
-        <v>358.6694387836589</v>
+        <v>357.3802827690857</v>
       </c>
       <c r="D233" t="n">
-        <v>353.5527327193329</v>
+        <v>352.4834362714388</v>
       </c>
       <c r="E233" t="n">
-        <v>354.0723876953125</v>
+        <v>354.951850943437</v>
       </c>
       <c r="F233" t="n">
-        <v>19859900</v>
+        <v>18991400</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6493,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B234" t="n">
-        <v>354.951850943437</v>
+        <v>343.5791320800781</v>
       </c>
       <c r="C234" t="n">
-        <v>357.3802827690857</v>
+        <v>356.5807842683805</v>
       </c>
       <c r="D234" t="n">
-        <v>352.4834362714388</v>
+        <v>343.1694223006263</v>
       </c>
       <c r="E234" t="n">
-        <v>357.2903442382812</v>
+        <v>355.6613923515014</v>
       </c>
       <c r="F234" t="n">
-        <v>18991400</v>
+        <v>29081800</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6519,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B235" t="n">
-        <v>355.6613923515014</v>
+        <v>343.3193359375</v>
       </c>
       <c r="C235" t="n">
-        <v>356.5807842683805</v>
+        <v>346.2574498710514</v>
       </c>
       <c r="D235" t="n">
-        <v>343.1694223006263</v>
+        <v>340.661040926288</v>
       </c>
       <c r="E235" t="n">
-        <v>343.5791320800781</v>
+        <v>346.0875456512855</v>
       </c>
       <c r="F235" t="n">
-        <v>29081800</v>
+        <v>25012000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6545,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B236" t="n">
-        <v>346.0875456512855</v>
+        <v>346.1375122070312</v>
       </c>
       <c r="C236" t="n">
-        <v>346.2574498710514</v>
+        <v>347.7065110877775</v>
       </c>
       <c r="D236" t="n">
-        <v>340.661040926288</v>
+        <v>343.5392066313974</v>
       </c>
       <c r="E236" t="n">
-        <v>343.3193359375</v>
+        <v>345.5478948342235</v>
       </c>
       <c r="F236" t="n">
-        <v>25012000</v>
+        <v>17866100</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6571,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B237" t="n">
-        <v>345.5478948342235</v>
+        <v>345.6777954101562</v>
       </c>
       <c r="C237" t="n">
-        <v>347.7065110877775</v>
+        <v>350.2248908898295</v>
       </c>
       <c r="D237" t="n">
-        <v>343.5392066313974</v>
+        <v>344.2787008387085</v>
       </c>
       <c r="E237" t="n">
-        <v>346.1375122070312</v>
+        <v>346.5772111705174</v>
       </c>
       <c r="F237" t="n">
-        <v>17866100</v>
+        <v>17808600</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6597,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B238" t="n">
-        <v>346.5772111705174</v>
+        <v>343.7790222167969</v>
       </c>
       <c r="C238" t="n">
-        <v>350.2248908898295</v>
+        <v>347.0269344906474</v>
       </c>
       <c r="D238" t="n">
-        <v>344.2787008387085</v>
+        <v>341.7103446182459</v>
       </c>
       <c r="E238" t="n">
-        <v>345.6777954101562</v>
+        <v>346.0475530411078</v>
       </c>
       <c r="F238" t="n">
-        <v>17808600</v>
+        <v>18291300</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6623,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B239" t="n">
-        <v>346.0475530411078</v>
+        <v>343.9789123535156</v>
       </c>
       <c r="C239" t="n">
-        <v>347.0269344906474</v>
+        <v>344.6484648943574</v>
       </c>
       <c r="D239" t="n">
-        <v>341.7103446182459</v>
+        <v>339.9714784523309</v>
       </c>
       <c r="E239" t="n">
-        <v>343.7790222167969</v>
+        <v>342.1900536360575</v>
       </c>
       <c r="F239" t="n">
-        <v>18291300</v>
+        <v>19248800</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6649,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B240" t="n">
-        <v>342.1900536360575</v>
+        <v>344.4985656738281</v>
       </c>
       <c r="C240" t="n">
-        <v>344.6484648943574</v>
+        <v>346.5072842825429</v>
       </c>
       <c r="D240" t="n">
-        <v>339.9714784523309</v>
+        <v>340.4411761094805</v>
       </c>
       <c r="E240" t="n">
-        <v>343.9789123535156</v>
+        <v>342.2400076559886</v>
       </c>
       <c r="F240" t="n">
-        <v>19248800</v>
+        <v>19733800</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6675,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B241" t="n">
-        <v>342.2400076559886</v>
+        <v>340.451171875</v>
       </c>
       <c r="C241" t="n">
-        <v>346.5072842825429</v>
+        <v>343.6790774504127</v>
       </c>
       <c r="D241" t="n">
-        <v>340.4411761094805</v>
+        <v>338.3525147854226</v>
       </c>
       <c r="E241" t="n">
-        <v>344.4985656738281</v>
+        <v>342.8396207141765</v>
       </c>
       <c r="F241" t="n">
-        <v>19733800</v>
+        <v>18570400</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6701,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B242" t="n">
-        <v>342.8396207141765</v>
+        <v>344.5985107421875</v>
       </c>
       <c r="C242" t="n">
-        <v>343.6790774504127</v>
+        <v>345.9776291730591</v>
       </c>
       <c r="D242" t="n">
-        <v>338.3525147854226</v>
+        <v>340.1813365286692</v>
       </c>
       <c r="E242" t="n">
-        <v>340.451171875</v>
+        <v>342.359928876986</v>
       </c>
       <c r="F242" t="n">
-        <v>18570400</v>
+        <v>20849800</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6727,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B243" t="n">
-        <v>342.359928876986</v>
+        <v>347.83642578125</v>
       </c>
       <c r="C243" t="n">
-        <v>345.9776291730591</v>
+        <v>351.3741604480826</v>
       </c>
       <c r="D243" t="n">
-        <v>340.1813365286692</v>
+        <v>342.2699962782288</v>
       </c>
       <c r="E243" t="n">
-        <v>344.5985107421875</v>
+        <v>343.3992753172161</v>
       </c>
       <c r="F243" t="n">
-        <v>20849800</v>
+        <v>26338200</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6753,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B244" t="n">
-        <v>343.3992753172161</v>
+        <v>346.7371215820312</v>
       </c>
       <c r="C244" t="n">
-        <v>351.3741604480826</v>
+        <v>349.9350782600912</v>
       </c>
       <c r="D244" t="n">
-        <v>342.2699962782288</v>
+        <v>345.3780098175396</v>
       </c>
       <c r="E244" t="n">
-        <v>347.83642578125</v>
+        <v>349.4154232615459</v>
       </c>
       <c r="F244" t="n">
-        <v>26338200</v>
+        <v>20649700</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6779,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B245" t="n">
-        <v>349.4154232615459</v>
+        <v>341.7803039550781</v>
       </c>
       <c r="C245" t="n">
-        <v>349.9350782600912</v>
+        <v>346.6571739906042</v>
       </c>
       <c r="D245" t="n">
-        <v>345.3780098175396</v>
+        <v>339.9614657782595</v>
       </c>
       <c r="E245" t="n">
-        <v>346.7371215820312</v>
+        <v>346.3973312516375</v>
       </c>
       <c r="F245" t="n">
-        <v>20649700</v>
+        <v>20420300</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6805,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B246" t="n">
-        <v>346.3973312516375</v>
+        <v>340.4311828613281</v>
       </c>
       <c r="C246" t="n">
-        <v>346.6571739906042</v>
+        <v>341.4705233735174</v>
       </c>
       <c r="D246" t="n">
-        <v>339.9614657782595</v>
+        <v>338.3025461528343</v>
       </c>
       <c r="E246" t="n">
-        <v>341.7803039550781</v>
+        <v>339.4518318672431</v>
       </c>
       <c r="F246" t="n">
-        <v>20420300</v>
+        <v>23391400</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6831,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B247" t="n">
-        <v>339.4518318672431</v>
+        <v>346.3673706054688</v>
       </c>
       <c r="C247" t="n">
-        <v>341.4705233735174</v>
+        <v>348.9157509584863</v>
       </c>
       <c r="D247" t="n">
-        <v>338.3025461528343</v>
+        <v>340.0514228221321</v>
       </c>
       <c r="E247" t="n">
-        <v>340.4311828613281</v>
+        <v>340.4911426360338</v>
       </c>
       <c r="F247" t="n">
-        <v>23391400</v>
+        <v>25347200</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6857,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B248" t="n">
-        <v>340.4911426360338</v>
+        <v>339.1320190429688</v>
       </c>
       <c r="C248" t="n">
-        <v>348.9157509584863</v>
+        <v>344.3686432833908</v>
       </c>
       <c r="D248" t="n">
-        <v>340.0514228221321</v>
+        <v>336.943423385668</v>
       </c>
       <c r="E248" t="n">
-        <v>346.3673706054688</v>
+        <v>343.609121722545</v>
       </c>
       <c r="F248" t="n">
-        <v>25347200</v>
+        <v>33493600</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6883,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B249" t="n">
-        <v>343.609121722545</v>
+        <v>334.8047790527344</v>
       </c>
       <c r="C249" t="n">
-        <v>344.3686432833908</v>
+        <v>336.9834018439635</v>
       </c>
       <c r="D249" t="n">
-        <v>336.943423385668</v>
+        <v>332.8360433203593</v>
       </c>
       <c r="E249" t="n">
-        <v>339.1320190429688</v>
+        <v>335.7841605001305</v>
       </c>
       <c r="F249" t="n">
-        <v>33493600</v>
+        <v>23342700</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6909,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B250" t="n">
-        <v>335.7841605001305</v>
+        <v>336.9034423828125</v>
       </c>
       <c r="C250" t="n">
-        <v>336.9834018439635</v>
+        <v>339.7815972628325</v>
       </c>
       <c r="D250" t="n">
-        <v>332.8360433203593</v>
+        <v>332.6062167342666</v>
       </c>
       <c r="E250" t="n">
-        <v>334.8047790527344</v>
+        <v>333.845410447285</v>
       </c>
       <c r="F250" t="n">
-        <v>23342700</v>
+        <v>22582300</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6935,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B251" t="n">
-        <v>333.845410447285</v>
+        <v>342.260009765625</v>
       </c>
       <c r="C251" t="n">
-        <v>339.7815972628325</v>
+        <v>344.4585782378343</v>
       </c>
       <c r="D251" t="n">
-        <v>332.6062167342666</v>
+        <v>339.841550898423</v>
       </c>
       <c r="E251" t="n">
-        <v>336.9034423828125</v>
+        <v>340.3412297100126</v>
       </c>
       <c r="F251" t="n">
-        <v>22582300</v>
+        <v>20726900</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,25 +6961,25 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B252" t="n">
-        <v>340.3412297100126</v>
+        <v>338.4599914550781</v>
       </c>
       <c r="C252" t="n">
-        <v>344.4585782378343</v>
+        <v>343.5299987792969</v>
       </c>
       <c r="D252" t="n">
-        <v>339.841550898423</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="E252" t="n">
-        <v>342.260009765625</v>
+        <v>342.4700012207031</v>
       </c>
       <c r="F252" t="n">
-        <v>20726900</v>
+        <v>23157700</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -6995,25 +6987,17 @@
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B253" t="n">
-        <v>342.4700012207031</v>
-      </c>
-      <c r="C253" t="n">
-        <v>343.5299987792969</v>
-      </c>
-      <c r="D253" t="n">
-        <v>337.0899963378906</v>
-      </c>
-      <c r="E253" t="n">
-        <v>338.4599914550781</v>
-      </c>
+        <v>46273</v>
+      </c>
+      <c r="B253" t="inlineStr"/>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="n">
-        <v>23157700</v>
+        <v>22262778</v>
       </c>
       <c r="G253" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -10798,34 +10782,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>338.36</v>
+      </c>
+      <c r="D2" t="n">
         <v>338.46</v>
       </c>
-      <c r="D2" t="n">
-        <v>342.26</v>
-      </c>
       <c r="E2" t="n">
-        <v>342.575</v>
+        <v>335.38</v>
       </c>
       <c r="F2" t="n">
-        <v>343.53</v>
+        <v>339.665</v>
       </c>
       <c r="G2" t="n">
-        <v>337.09</v>
+        <v>333.22</v>
       </c>
       <c r="H2" t="n">
-        <v>23189321</v>
+        <v>22262778</v>
       </c>
       <c r="I2" t="n">
-        <v>30102998</v>
+        <v>30137845</v>
       </c>
       <c r="J2" t="n">
-        <v>4139343675392</v>
+        <v>4138120773632</v>
       </c>
       <c r="K2" t="n">
-        <v>16.97392</v>
+        <v>16.968906</v>
       </c>
       <c r="L2" t="n">
-        <v>22.785429</v>
+        <v>22.779003</v>
       </c>
       <c r="M2" t="n">
         <v>19.94</v>
@@ -10864,7 +10848,7 @@
         <v>50.896</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.650031</v>
+        <v>6.6480665</v>
       </c>
       <c r="Z2" t="n">
         <v>2.94</v>
@@ -10876,7 +10860,7 @@
         <v>445865984000</v>
       </c>
       <c r="AC2" t="n">
-        <v>4035705831424</v>
+        <v>4034482929664</v>
       </c>
       <c r="AD2" t="n">
         <v>173164003328</v>
@@ -10903,7 +10887,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-08 08:51:55</t>
+          <t>2026-09-09 09:14:51</t>
         </is>
       </c>
     </row>

--- a/data/GOOGL_data.xlsx
+++ b/data/GOOGL_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,22 +433,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Close</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Open</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -469,17 +469,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45908</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+        <v>45910</v>
+      </c>
+      <c r="B2" t="n">
+        <v>238.2803024247839</v>
+      </c>
+      <c r="C2" t="n">
+        <v>241.0331528996711</v>
+      </c>
+      <c r="D2" t="n">
+        <v>237.2330382337294</v>
+      </c>
+      <c r="E2" t="n">
+        <v>238.5496063232422</v>
+      </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>35141100</v>
       </c>
       <c r="G2" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -487,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45909</v>
+        <v>45911</v>
       </c>
       <c r="B3" t="n">
-        <v>239.0084228515625</v>
+        <v>239.2577864756533</v>
       </c>
       <c r="C3" t="n">
-        <v>239.8462403027557</v>
+        <v>241.6216341251204</v>
       </c>
       <c r="D3" t="n">
-        <v>232.6250148339166</v>
+        <v>235.6371973666035</v>
       </c>
       <c r="E3" t="n">
-        <v>233.562578980389</v>
+        <v>239.7465057373047</v>
       </c>
       <c r="F3" t="n">
-        <v>38061000</v>
+        <v>30599300</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -513,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45910</v>
+        <v>45912</v>
       </c>
       <c r="B4" t="n">
-        <v>238.5495910644531</v>
+        <v>239.7464919977143</v>
       </c>
       <c r="C4" t="n">
-        <v>241.0331374820224</v>
+        <v>241.4520630725996</v>
       </c>
       <c r="D4" t="n">
-        <v>237.2330230591544</v>
+        <v>237.3826444837165</v>
       </c>
       <c r="E4" t="n">
-        <v>238.2802871832208</v>
+        <v>240.1753845214844</v>
       </c>
       <c r="F4" t="n">
-        <v>35141100</v>
+        <v>26771600</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -539,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45911</v>
+        <v>45915</v>
       </c>
       <c r="B5" t="n">
-        <v>239.7464904785156</v>
+        <v>244.0253674338205</v>
       </c>
       <c r="C5" t="n">
-        <v>241.6216187469878</v>
+        <v>251.7552643082765</v>
       </c>
       <c r="D5" t="n">
-        <v>235.6371823693535</v>
+        <v>244.0253674338205</v>
       </c>
       <c r="E5" t="n">
-        <v>239.2577712479691</v>
+        <v>250.9573364257812</v>
       </c>
       <c r="F5" t="n">
-        <v>30599300</v>
+        <v>58383800</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -565,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45912</v>
+        <v>45916</v>
       </c>
       <c r="B6" t="n">
-        <v>240.1753997802734</v>
+        <v>251.4261261704888</v>
       </c>
       <c r="C6" t="n">
-        <v>241.4520784124984</v>
+        <v>252.3836274833809</v>
       </c>
       <c r="D6" t="n">
-        <v>237.3826595650776</v>
+        <v>248.8228956960496</v>
       </c>
       <c r="E6" t="n">
-        <v>239.746507229255</v>
+        <v>250.5085144042969</v>
       </c>
       <c r="F6" t="n">
-        <v>26771600</v>
+        <v>34109700</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -591,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="B7" t="n">
-        <v>250.9573364257812</v>
+        <v>250.56837026682</v>
       </c>
       <c r="C7" t="n">
-        <v>251.7552643082765</v>
+        <v>250.9473894679867</v>
       </c>
       <c r="D7" t="n">
-        <v>244.0253674338205</v>
+        <v>245.6411815284925</v>
       </c>
       <c r="E7" t="n">
-        <v>244.0253674338205</v>
+        <v>248.8827514648438</v>
       </c>
       <c r="F7" t="n">
-        <v>58383800</v>
+        <v>34108000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -617,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="B8" t="n">
-        <v>250.5084991455078</v>
+        <v>251.0271682452624</v>
       </c>
       <c r="C8" t="n">
-        <v>252.3836121103763</v>
+        <v>253.3311891966015</v>
       </c>
       <c r="D8" t="n">
-        <v>248.8228805399337</v>
+        <v>249.1520550643071</v>
       </c>
       <c r="E8" t="n">
-        <v>251.4261108558069</v>
+        <v>251.3762664794922</v>
       </c>
       <c r="F8" t="n">
-        <v>34109700</v>
+        <v>31239500</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -643,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B9" t="n">
-        <v>248.8827362060547</v>
+        <v>252.5930922260568</v>
       </c>
       <c r="C9" t="n">
-        <v>250.9473740826164</v>
+        <v>255.3359589728353</v>
       </c>
       <c r="D9" t="n">
-        <v>245.6411664684413</v>
+        <v>251.1568250217611</v>
       </c>
       <c r="E9" t="n">
-        <v>250.5683549046871</v>
+        <v>254.0592803955078</v>
       </c>
       <c r="F9" t="n">
-        <v>34108000</v>
+        <v>55571400</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -669,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B10" t="n">
-        <v>251.3762512207031</v>
+        <v>253.7700350469374</v>
       </c>
       <c r="C10" t="n">
-        <v>253.3311738191467</v>
+        <v>255.1165394138156</v>
       </c>
       <c r="D10" t="n">
-        <v>249.1520399405299</v>
+        <v>249.6507580677981</v>
       </c>
       <c r="E10" t="n">
-        <v>251.0271530076639</v>
+        <v>251.8749694824219</v>
       </c>
       <c r="F10" t="n">
-        <v>31239500</v>
+        <v>32290500</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -695,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B11" t="n">
-        <v>254.0592803955078</v>
+        <v>252.38362744671</v>
       </c>
       <c r="C11" t="n">
-        <v>255.3359589728353</v>
+        <v>253.7002107757565</v>
       </c>
       <c r="D11" t="n">
-        <v>251.1568250217611</v>
+        <v>249.8302703204236</v>
       </c>
       <c r="E11" t="n">
-        <v>252.5930922260568</v>
+        <v>251.0072174072266</v>
       </c>
       <c r="F11" t="n">
-        <v>55571400</v>
+        <v>26628000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -721,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B12" t="n">
-        <v>251.8749694824219</v>
+        <v>251.0072270537175</v>
       </c>
       <c r="C12" t="n">
-        <v>255.1165394138156</v>
+        <v>251.6954397095125</v>
       </c>
       <c r="D12" t="n">
-        <v>249.6507580677981</v>
+        <v>245.8007659055053</v>
       </c>
       <c r="E12" t="n">
-        <v>253.7700350469374</v>
+        <v>246.4989471435547</v>
       </c>
       <c r="F12" t="n">
-        <v>32290500</v>
+        <v>28201000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -747,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B13" t="n">
-        <v>251.0072174072266</v>
+        <v>243.7660414512771</v>
       </c>
       <c r="C13" t="n">
-        <v>253.7002107757565</v>
+        <v>245.8506317386469</v>
       </c>
       <c r="D13" t="n">
-        <v>249.8302703204236</v>
+        <v>240.1155467413105</v>
       </c>
       <c r="E13" t="n">
-        <v>252.38362744671</v>
+        <v>245.1524353027344</v>
       </c>
       <c r="F13" t="n">
-        <v>26628000</v>
+        <v>31020400</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -773,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B14" t="n">
-        <v>246.4989318847656</v>
+        <v>246.4291213887164</v>
       </c>
       <c r="C14" t="n">
-        <v>251.6954241290499</v>
+        <v>248.7730164871513</v>
       </c>
       <c r="D14" t="n">
-        <v>245.8007506899351</v>
+        <v>245.3319686402006</v>
       </c>
       <c r="E14" t="n">
-        <v>251.0072115158567</v>
+        <v>245.9004821777344</v>
       </c>
       <c r="F14" t="n">
-        <v>28201000</v>
+        <v>18503200</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -799,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B15" t="n">
-        <v>245.1524200439453</v>
+        <v>247.2071078925349</v>
       </c>
       <c r="C15" t="n">
-        <v>245.8506164364007</v>
+        <v>250.4985358461003</v>
       </c>
       <c r="D15" t="n">
-        <v>240.1155317960277</v>
+        <v>242.1402830798725</v>
       </c>
       <c r="E15" t="n">
-        <v>243.76602627878</v>
+        <v>243.4169616699219</v>
       </c>
       <c r="F15" t="n">
-        <v>31020400</v>
+        <v>32505800</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -825,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B16" t="n">
-        <v>245.9004974365234</v>
+        <v>242.180180344627</v>
       </c>
       <c r="C16" t="n">
-        <v>248.7730319241888</v>
+        <v>242.6589310263489</v>
       </c>
       <c r="D16" t="n">
-        <v>245.3319838637119</v>
+        <v>238.6294169517045</v>
       </c>
       <c r="E16" t="n">
-        <v>246.429136680309</v>
+        <v>242.4694366455078</v>
       </c>
       <c r="F16" t="n">
-        <v>18503200</v>
+        <v>34724300</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -851,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B17" t="n">
-        <v>243.4169616699219</v>
+        <v>240.125510895299</v>
       </c>
       <c r="C17" t="n">
-        <v>250.4985358461003</v>
+        <v>245.661117617101</v>
       </c>
       <c r="D17" t="n">
-        <v>242.1402830798725</v>
+        <v>237.9910625183314</v>
       </c>
       <c r="E17" t="n">
-        <v>247.2071078925349</v>
+        <v>244.2647399902344</v>
       </c>
       <c r="F17" t="n">
-        <v>32505800</v>
+        <v>31658200</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -877,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B18" t="n">
-        <v>242.4694213867188</v>
+        <v>244.5141112731399</v>
       </c>
       <c r="C18" t="n">
-        <v>242.6589157556348</v>
+        <v>246.1698091326398</v>
       </c>
       <c r="D18" t="n">
-        <v>238.6294019345709</v>
+        <v>241.6715128807893</v>
       </c>
       <c r="E18" t="n">
-        <v>242.1801651040411</v>
+        <v>245.0527191162109</v>
       </c>
       <c r="F18" t="n">
-        <v>34724300</v>
+        <v>25483300</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -903,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B19" t="n">
-        <v>244.2647247314453</v>
+        <v>243.8558074699024</v>
       </c>
       <c r="C19" t="n">
-        <v>245.6611022710827</v>
+        <v>245.661109961835</v>
       </c>
       <c r="D19" t="n">
-        <v>237.991047651448</v>
+        <v>241.0331465588312</v>
       </c>
       <c r="E19" t="n">
-        <v>240.1254958950803</v>
+        <v>244.7135772705078</v>
       </c>
       <c r="F19" t="n">
-        <v>31658200</v>
+        <v>30249600</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -929,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B20" t="n">
-        <v>245.0526885986328</v>
+        <v>244.145057284137</v>
       </c>
       <c r="C20" t="n">
-        <v>246.1697784759451</v>
+        <v>250.6681015230512</v>
       </c>
       <c r="D20" t="n">
-        <v>241.6714827842888</v>
+        <v>243.9455791134174</v>
       </c>
       <c r="E20" t="n">
-        <v>244.5140808226371</v>
+        <v>249.7803955078125</v>
       </c>
       <c r="F20" t="n">
-        <v>25483300</v>
+        <v>28894700</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -955,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B21" t="n">
-        <v>244.7136077880859</v>
+        <v>247.6260118192477</v>
       </c>
       <c r="C21" t="n">
-        <v>245.6611405975774</v>
+        <v>249.7903811872092</v>
       </c>
       <c r="D21" t="n">
-        <v>241.0331766174326</v>
+        <v>244.8831450984028</v>
       </c>
       <c r="E21" t="n">
-        <v>243.8558378805103</v>
+        <v>245.1225128173828</v>
       </c>
       <c r="F21" t="n">
-        <v>30249600</v>
+        <v>23181300</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -981,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B22" t="n">
-        <v>249.7804107666016</v>
+        <v>244.3246032710778</v>
       </c>
       <c r="C22" t="n">
-        <v>250.6681168360691</v>
+        <v>245.3718674935034</v>
       </c>
       <c r="D22" t="n">
-        <v>243.9455940157645</v>
+        <v>243.187560933671</v>
       </c>
       <c r="E22" t="n">
-        <v>244.1450721986699</v>
+        <v>243.9854736328125</v>
       </c>
       <c r="F22" t="n">
-        <v>28894700</v>
+        <v>21307100</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1007,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B23" t="n">
-        <v>245.1225128173828</v>
+        <v>243.8358644557508</v>
       </c>
       <c r="C23" t="n">
-        <v>249.7903811872092</v>
+        <v>244.1251055211473</v>
       </c>
       <c r="D23" t="n">
-        <v>244.8831450984028</v>
+        <v>238.5296568297252</v>
       </c>
       <c r="E23" t="n">
-        <v>247.6260118192477</v>
+        <v>240.9034881591797</v>
       </c>
       <c r="F23" t="n">
-        <v>23181300</v>
+        <v>27892100</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1033,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B24" t="n">
-        <v>243.9854583740234</v>
+        <v>240.8037387238312</v>
       </c>
       <c r="C24" t="n">
-        <v>245.3718521480096</v>
+        <v>243.4568425066541</v>
       </c>
       <c r="D24" t="n">
-        <v>243.1875457247831</v>
+        <v>235.2282424787384</v>
       </c>
       <c r="E24" t="n">
-        <v>244.3245879910796</v>
+        <v>235.9563598632812</v>
       </c>
       <c r="F24" t="n">
-        <v>21307100</v>
+        <v>33180300</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1059,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B25" t="n">
-        <v>240.9034881591797</v>
+        <v>239.5869408797282</v>
       </c>
       <c r="C25" t="n">
-        <v>244.1251055211473</v>
+        <v>243.865806618421</v>
       </c>
       <c r="D25" t="n">
-        <v>238.5296568297252</v>
+        <v>239.0882377987089</v>
       </c>
       <c r="E25" t="n">
-        <v>243.8358644557508</v>
+        <v>243.5167083740234</v>
       </c>
       <c r="F25" t="n">
-        <v>27892100</v>
+        <v>24995000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1085,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B26" t="n">
-        <v>235.9563598632812</v>
+        <v>240.6042690189676</v>
       </c>
       <c r="C26" t="n">
-        <v>243.4568425066541</v>
+        <v>246.4789903337629</v>
       </c>
       <c r="D26" t="n">
-        <v>235.2282424787384</v>
+        <v>239.8861354100955</v>
       </c>
       <c r="E26" t="n">
-        <v>240.8037387238312</v>
+        <v>244.8133239746094</v>
       </c>
       <c r="F26" t="n">
-        <v>33180300</v>
+        <v>22111600</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1111,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B27" t="n">
-        <v>243.5166931152344</v>
+        <v>246.6086665065597</v>
       </c>
       <c r="C27" t="n">
-        <v>243.8657913377574</v>
+        <v>251.4560609241123</v>
       </c>
       <c r="D27" t="n">
-        <v>239.0882228174084</v>
+        <v>245.3519402572719</v>
       </c>
       <c r="E27" t="n">
-        <v>239.5869258671789</v>
+        <v>250.3788604736328</v>
       </c>
       <c r="F27" t="n">
-        <v>24995000</v>
+        <v>27007700</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1137,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B28" t="n">
-        <v>244.8133239746094</v>
+        <v>251.1169174295502</v>
       </c>
       <c r="C28" t="n">
-        <v>246.4789903337629</v>
+        <v>256.2934418791717</v>
       </c>
       <c r="D28" t="n">
-        <v>239.8861354100955</v>
+        <v>249.451251205687</v>
       </c>
       <c r="E28" t="n">
-        <v>240.6042690189676</v>
+        <v>250.8077239990234</v>
       </c>
       <c r="F28" t="n">
-        <v>22111600</v>
+        <v>27997200</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1163,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B29" t="n">
-        <v>250.3788452148438</v>
+        <v>250.1095396639979</v>
       </c>
       <c r="C29" t="n">
-        <v>251.4560455996756</v>
+        <v>253.5605713492617</v>
       </c>
       <c r="D29" t="n">
-        <v>245.3519253048375</v>
+        <v>247.1671948127543</v>
       </c>
       <c r="E29" t="n">
-        <v>246.6086514775368</v>
+        <v>252.6429595947266</v>
       </c>
       <c r="F29" t="n">
-        <v>27007700</v>
+        <v>29671600</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1189,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B30" t="n">
-        <v>250.8077392578125</v>
+        <v>254.0293607582065</v>
       </c>
       <c r="C30" t="n">
-        <v>256.2934574717041</v>
+        <v>256.6624970209002</v>
       </c>
       <c r="D30" t="n">
-        <v>249.4512663819502</v>
+        <v>253.5705472580769</v>
       </c>
       <c r="E30" t="n">
-        <v>251.1169327071502</v>
+        <v>255.884521484375</v>
       </c>
       <c r="F30" t="n">
-        <v>27997200</v>
+        <v>22350200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1215,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B31" t="n">
-        <v>252.6429595947266</v>
+        <v>254.079230052693</v>
       </c>
       <c r="C31" t="n">
-        <v>253.5605713492617</v>
+        <v>254.2188662949897</v>
       </c>
       <c r="D31" t="n">
-        <v>247.1671948127543</v>
+        <v>243.5166881090968</v>
       </c>
       <c r="E31" t="n">
-        <v>250.1095396639979</v>
+        <v>249.8103332519531</v>
       </c>
       <c r="F31" t="n">
-        <v>29671600</v>
+        <v>47312100</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1241,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B32" t="n">
-        <v>255.8845367431641</v>
+        <v>253.710180894347</v>
       </c>
       <c r="C32" t="n">
-        <v>256.6625123260812</v>
+        <v>255.6950092626011</v>
       </c>
       <c r="D32" t="n">
-        <v>253.5705623788801</v>
+        <v>248.6433561577788</v>
       </c>
       <c r="E32" t="n">
-        <v>254.0293759063695</v>
+        <v>251.0371398925781</v>
       </c>
       <c r="F32" t="n">
-        <v>22350200</v>
+        <v>35029400</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1267,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B33" t="n">
-        <v>249.8103332519531</v>
+        <v>252.3237762573301</v>
       </c>
       <c r="C33" t="n">
-        <v>254.2188662949897</v>
+        <v>254.378430268887</v>
       </c>
       <c r="D33" t="n">
-        <v>243.5166881090968</v>
+        <v>251.1967177788712</v>
       </c>
       <c r="E33" t="n">
-        <v>254.079230052693</v>
+        <v>252.4235229492188</v>
       </c>
       <c r="F33" t="n">
-        <v>47312100</v>
+        <v>19901400</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1293,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B34" t="n">
-        <v>251.0371551513672</v>
+        <v>255.9144557753844</v>
       </c>
       <c r="C34" t="n">
-        <v>255.6950248045094</v>
+        <v>261.0012332121926</v>
       </c>
       <c r="D34" t="n">
-        <v>248.6433712710665</v>
+        <v>254.6577447284323</v>
       </c>
       <c r="E34" t="n">
-        <v>253.7101963156115</v>
+        <v>259.2458190917969</v>
       </c>
       <c r="F34" t="n">
-        <v>35029400</v>
+        <v>28655100</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1319,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B35" t="n">
-        <v>252.4235382080078</v>
+        <v>264.1330642482098</v>
       </c>
       <c r="C35" t="n">
-        <v>254.3784456458486</v>
+        <v>269.4392714738914</v>
       </c>
       <c r="D35" t="n">
-        <v>251.196732963501</v>
+        <v>263.5944564854066</v>
       </c>
       <c r="E35" t="n">
-        <v>252.3237915100895</v>
+        <v>268.5715026855469</v>
       </c>
       <c r="F35" t="n">
-        <v>19901400</v>
+        <v>35235200</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1345,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B36" t="n">
-        <v>259.2458190917969</v>
+        <v>268.9904881616853</v>
       </c>
       <c r="C36" t="n">
-        <v>261.0012332121926</v>
+        <v>270.0277991619387</v>
       </c>
       <c r="D36" t="n">
-        <v>254.6577447284323</v>
+        <v>265.8087598581407</v>
       </c>
       <c r="E36" t="n">
-        <v>255.9144557753844</v>
+        <v>266.7762451171875</v>
       </c>
       <c r="F36" t="n">
-        <v>28655100</v>
+        <v>29738600</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1371,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B37" t="n">
-        <v>268.571533203125</v>
+        <v>267.055471479175</v>
       </c>
       <c r="C37" t="n">
-        <v>269.4393020900735</v>
+        <v>274.6257797911847</v>
       </c>
       <c r="D37" t="n">
-        <v>263.5944864374467</v>
+        <v>266.975692387603</v>
       </c>
       <c r="E37" t="n">
-        <v>264.1330942614516</v>
+        <v>273.8577880859375</v>
       </c>
       <c r="F37" t="n">
-        <v>35235200</v>
+        <v>43580300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1397,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B38" t="n">
-        <v>266.7761840820312</v>
+        <v>290.8336389163956</v>
       </c>
       <c r="C38" t="n">
-        <v>270.0277373828665</v>
+        <v>290.8336389163956</v>
       </c>
       <c r="D38" t="n">
-        <v>265.8086990443333</v>
+        <v>279.3335478851562</v>
       </c>
       <c r="E38" t="n">
-        <v>268.9904266199372</v>
+        <v>280.7498779296875</v>
       </c>
       <c r="F38" t="n">
-        <v>29738600</v>
+        <v>74876000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1423,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B39" t="n">
-        <v>273.8577880859375</v>
+        <v>282.4753817503845</v>
       </c>
       <c r="C39" t="n">
-        <v>274.6257797911847</v>
+        <v>285.2581533777714</v>
       </c>
       <c r="D39" t="n">
-        <v>266.975692387603</v>
+        <v>276.3114191679317</v>
       </c>
       <c r="E39" t="n">
-        <v>267.055471479175</v>
+        <v>280.4606323242188</v>
       </c>
       <c r="F39" t="n">
-        <v>43580300</v>
+        <v>39267900</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1449,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B40" t="n">
-        <v>280.7499084472656</v>
+        <v>281.4480255017143</v>
       </c>
       <c r="C40" t="n">
-        <v>290.8336705300809</v>
+        <v>284.7893417811305</v>
       </c>
       <c r="D40" t="n">
-        <v>279.3335782487789</v>
+        <v>279.0741942863961</v>
       </c>
       <c r="E40" t="n">
-        <v>290.8336705300809</v>
+        <v>282.9840393066406</v>
       </c>
       <c r="F40" t="n">
-        <v>74876000</v>
+        <v>29786000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1475,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B41" t="n">
-        <v>280.4606323242188</v>
+        <v>276.0321395313242</v>
       </c>
       <c r="C41" t="n">
-        <v>285.2581533777714</v>
+        <v>280.5404041676455</v>
       </c>
       <c r="D41" t="n">
-        <v>276.3114191679317</v>
+        <v>275.5434202802167</v>
       </c>
       <c r="E41" t="n">
-        <v>282.4753817503845</v>
+        <v>276.8200988769531</v>
       </c>
       <c r="F41" t="n">
-        <v>39267900</v>
+        <v>30078400</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1501,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B42" t="n">
-        <v>282.9840698242188</v>
+        <v>278.1466483880774</v>
       </c>
       <c r="C42" t="n">
-        <v>284.7893724933962</v>
+        <v>285.6770830892533</v>
       </c>
       <c r="D42" t="n">
-        <v>279.0742243823285</v>
+        <v>276.6206181949745</v>
       </c>
       <c r="E42" t="n">
-        <v>281.4480558536455</v>
+        <v>283.5725402832031</v>
       </c>
       <c r="F42" t="n">
-        <v>29786000</v>
+        <v>31010300</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1527,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B43" t="n">
-        <v>276.8200988769531</v>
+        <v>284.5898651937554</v>
       </c>
       <c r="C43" t="n">
-        <v>280.5404041676455</v>
+        <v>287.6020510547858</v>
       </c>
       <c r="D43" t="n">
-        <v>275.5434202802167</v>
+        <v>280.4107616957575</v>
       </c>
       <c r="E43" t="n">
-        <v>276.0321395313242</v>
+        <v>284.0113830566406</v>
       </c>
       <c r="F43" t="n">
-        <v>30078400</v>
+        <v>37173600</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1553,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B44" t="n">
-        <v>283.572509765625</v>
+        <v>282.4753634096288</v>
       </c>
       <c r="C44" t="n">
-        <v>285.677052345188</v>
+        <v>283.0438921724298</v>
       </c>
       <c r="D44" t="n">
-        <v>276.62058842555</v>
+        <v>274.4761777186906</v>
       </c>
       <c r="E44" t="n">
-        <v>278.1466184544242</v>
+        <v>278.1067199707031</v>
       </c>
       <c r="F44" t="n">
-        <v>31010300</v>
+        <v>34479600</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1579,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B45" t="n">
-        <v>284.0113830566406</v>
+        <v>283.6822445549795</v>
       </c>
       <c r="C45" t="n">
-        <v>287.6020510547858</v>
+        <v>290.0456696400176</v>
       </c>
       <c r="D45" t="n">
-        <v>280.4107616957575</v>
+        <v>282.1262631003564</v>
       </c>
       <c r="E45" t="n">
-        <v>284.5898651937554</v>
+        <v>289.3475036621094</v>
       </c>
       <c r="F45" t="n">
-        <v>37173600</v>
+        <v>29557300</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1605,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B46" t="n">
-        <v>278.1067199707031</v>
+        <v>287.0035887304013</v>
       </c>
       <c r="C46" t="n">
-        <v>283.0438921724298</v>
+        <v>291.1627853205446</v>
       </c>
       <c r="D46" t="n">
-        <v>274.4761777186906</v>
+        <v>286.5747114373448</v>
       </c>
       <c r="E46" t="n">
-        <v>282.4753634096288</v>
+        <v>290.5543518066406</v>
       </c>
       <c r="F46" t="n">
-        <v>34479600</v>
+        <v>19842100</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1631,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B47" t="n">
-        <v>289.3475036621094</v>
+        <v>290.9233873275988</v>
       </c>
       <c r="C47" t="n">
-        <v>290.0456696400176</v>
+        <v>291.2525483673142</v>
       </c>
       <c r="D47" t="n">
-        <v>282.1262631003564</v>
+        <v>282.9541227840324</v>
       </c>
       <c r="E47" t="n">
-        <v>283.6822445549795</v>
+        <v>285.9662780761719</v>
       </c>
       <c r="F47" t="n">
-        <v>29557300</v>
+        <v>24829900</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1657,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B48" t="n">
-        <v>290.5543518066406</v>
+        <v>281.6076219797447</v>
       </c>
       <c r="C48" t="n">
-        <v>291.1627853205446</v>
+        <v>282.1063250073575</v>
       </c>
       <c r="D48" t="n">
-        <v>286.5747114373448</v>
+        <v>276.5208450104115</v>
       </c>
       <c r="E48" t="n">
-        <v>287.0035887304013</v>
+        <v>277.847412109375</v>
       </c>
       <c r="F48" t="n">
-        <v>19842100</v>
+        <v>29494000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1683,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B49" t="n">
-        <v>285.96630859375</v>
+        <v>270.7059931829425</v>
       </c>
       <c r="C49" t="n">
-        <v>291.2525794490294</v>
+        <v>277.8374407083971</v>
       </c>
       <c r="D49" t="n">
-        <v>282.9541529801612</v>
+        <v>269.9978433748846</v>
       </c>
       <c r="E49" t="n">
-        <v>290.9234183741868</v>
+        <v>275.6930236816406</v>
       </c>
       <c r="F49" t="n">
-        <v>24829900</v>
+        <v>31647200</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1709,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B50" t="n">
-        <v>277.8474426269531</v>
+        <v>285.0387085276487</v>
       </c>
       <c r="C50" t="n">
-        <v>282.1063559927165</v>
+        <v>293.1875295999499</v>
       </c>
       <c r="D50" t="n">
-        <v>276.5208753822851</v>
+        <v>282.8344496120375</v>
       </c>
       <c r="E50" t="n">
-        <v>281.6076529103283</v>
+        <v>284.2806701660156</v>
       </c>
       <c r="F50" t="n">
-        <v>29494000</v>
+        <v>52670200</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1735,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B51" t="n">
-        <v>275.6929931640625</v>
+        <v>287.1731444150601</v>
       </c>
       <c r="C51" t="n">
-        <v>277.8374099534448</v>
+        <v>288.0508361130442</v>
       </c>
       <c r="D51" t="n">
-        <v>269.997813487729</v>
+        <v>277.4783570293678</v>
       </c>
       <c r="E51" t="n">
-        <v>270.705963217399</v>
+        <v>283.5425720214844</v>
       </c>
       <c r="F51" t="n">
-        <v>31647200</v>
+        <v>49158700</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1761,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B52" t="n">
-        <v>284.2806701660156</v>
+        <v>286.4151377283875</v>
       </c>
       <c r="C52" t="n">
-        <v>293.1875295999499</v>
+        <v>303.0219431129204</v>
       </c>
       <c r="D52" t="n">
-        <v>282.8344496120375</v>
+        <v>285.8865137158778</v>
       </c>
       <c r="E52" t="n">
-        <v>285.0387085276487</v>
+        <v>292.0504760742188</v>
       </c>
       <c r="F52" t="n">
-        <v>52670200</v>
+        <v>68198900</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1787,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B53" t="n">
-        <v>283.5426025390625</v>
+        <v>303.7500737161881</v>
       </c>
       <c r="C53" t="n">
-        <v>288.0508671158451</v>
+        <v>305.625202125324</v>
       </c>
       <c r="D53" t="n">
-        <v>277.4783868942568</v>
+        <v>287.921243180084</v>
       </c>
       <c r="E53" t="n">
-        <v>287.1731753233953</v>
+        <v>288.69921875</v>
       </c>
       <c r="F53" t="n">
-        <v>49158700</v>
+        <v>62025200</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1813,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B54" t="n">
-        <v>292.0504760742188</v>
+        <v>295.6511046778972</v>
       </c>
       <c r="C54" t="n">
-        <v>303.0219431129204</v>
+        <v>303.1316497984607</v>
       </c>
       <c r="D54" t="n">
-        <v>285.8865137158778</v>
+        <v>293.0877639113642</v>
       </c>
       <c r="E54" t="n">
-        <v>286.4151377283875</v>
+        <v>298.8826904296875</v>
       </c>
       <c r="F54" t="n">
-        <v>68198900</v>
+        <v>74137700</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1839,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B55" t="n">
-        <v>288.6991882324219</v>
+        <v>310.3229443803346</v>
       </c>
       <c r="C55" t="n">
-        <v>305.625169818548</v>
+        <v>318.651290855991</v>
       </c>
       <c r="D55" t="n">
-        <v>287.9212127447435</v>
+        <v>308.796914365105</v>
       </c>
       <c r="E55" t="n">
-        <v>303.7500416076266</v>
+        <v>317.7536010742188</v>
       </c>
       <c r="F55" t="n">
-        <v>62025200</v>
+        <v>85165100</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1865,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B56" t="n">
-        <v>298.8827209472656</v>
+        <v>325.3638169665917</v>
       </c>
       <c r="C56" t="n">
-        <v>303.1316807498811</v>
+        <v>327.9770159307299</v>
       </c>
       <c r="D56" t="n">
-        <v>293.0877938372482</v>
+        <v>316.826023668276</v>
       </c>
       <c r="E56" t="n">
-        <v>295.6511348655125</v>
+        <v>322.6010131835938</v>
       </c>
       <c r="F56" t="n">
-        <v>74137700</v>
+        <v>88632100</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1891,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B57" t="n">
-        <v>317.7536010742188</v>
+        <v>319.8482042131112</v>
       </c>
       <c r="C57" t="n">
-        <v>318.651290855991</v>
+        <v>323.658303098724</v>
       </c>
       <c r="D57" t="n">
-        <v>308.796914365105</v>
+        <v>315.9683100285969</v>
       </c>
       <c r="E57" t="n">
-        <v>310.3229443803346</v>
+        <v>319.1201171875</v>
       </c>
       <c r="F57" t="n">
-        <v>85165100</v>
+        <v>51373400</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1917,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B58" t="n">
-        <v>322.6010131835938</v>
+        <v>322.5312152935296</v>
       </c>
       <c r="C58" t="n">
-        <v>327.9770159307299</v>
+        <v>326.0021995827445</v>
       </c>
       <c r="D58" t="n">
-        <v>316.826023668276</v>
+        <v>315.9682963529555</v>
       </c>
       <c r="E58" t="n">
-        <v>325.3638169665917</v>
+        <v>319.3494873046875</v>
       </c>
       <c r="F58" t="n">
-        <v>88632100</v>
+        <v>26018600</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1943,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B59" t="n">
-        <v>319.1201171875</v>
+        <v>316.8759202886677</v>
       </c>
       <c r="C59" t="n">
-        <v>323.658303098724</v>
+        <v>319.02033724928</v>
       </c>
       <c r="D59" t="n">
-        <v>315.9683100285969</v>
+        <v>313.075805600947</v>
       </c>
       <c r="E59" t="n">
-        <v>319.8482042131112</v>
+        <v>314.0732116699219</v>
       </c>
       <c r="F59" t="n">
-        <v>51373400</v>
+        <v>41183000</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1969,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B60" t="n">
-        <v>319.3494873046875</v>
+        <v>315.9183945655827</v>
       </c>
       <c r="C60" t="n">
-        <v>326.0021995827445</v>
+        <v>317.554155160306</v>
       </c>
       <c r="D60" t="n">
-        <v>315.9682963529555</v>
+        <v>313.0957487295115</v>
       </c>
       <c r="E60" t="n">
-        <v>322.5312152935296</v>
+        <v>314.9908142089844</v>
       </c>
       <c r="F60" t="n">
-        <v>26018600</v>
+        <v>35854700</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -1995,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B61" t="n">
-        <v>314.0732421875</v>
+        <v>315.0706144021458</v>
       </c>
       <c r="C61" t="n">
-        <v>319.020368247556</v>
+        <v>320.7458268711651</v>
       </c>
       <c r="D61" t="n">
-        <v>313.0758360216101</v>
+        <v>313.2852490348319</v>
       </c>
       <c r="E61" t="n">
-        <v>316.8759510785769</v>
+        <v>318.8009033203125</v>
       </c>
       <c r="F61" t="n">
-        <v>41183000</v>
+        <v>41838300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2021,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B62" t="n">
-        <v>314.9908447265625</v>
+        <v>321.3942008459266</v>
       </c>
       <c r="C62" t="n">
-        <v>317.5541859262309</v>
+        <v>321.5238380796439</v>
       </c>
       <c r="D62" t="n">
-        <v>313.095779063488</v>
+        <v>313.8837336096964</v>
       </c>
       <c r="E62" t="n">
-        <v>315.9184251730286</v>
+        <v>316.796142578125</v>
       </c>
       <c r="F62" t="n">
-        <v>35854700</v>
+        <v>31240900</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2047,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B63" t="n">
-        <v>318.8009033203125</v>
+        <v>318.6612335259534</v>
       </c>
       <c r="C63" t="n">
-        <v>320.7458268711651</v>
+        <v>322.3217269426038</v>
       </c>
       <c r="D63" t="n">
-        <v>313.2852490348319</v>
+        <v>318.3420867388224</v>
       </c>
       <c r="E63" t="n">
-        <v>315.0706144021458</v>
+        <v>320.4366149902344</v>
       </c>
       <c r="F63" t="n">
-        <v>41838300</v>
+        <v>28851700</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2073,25 +2081,25 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B64" t="n">
-        <v>316.7961120605469</v>
+        <v>319.428628654094</v>
       </c>
       <c r="C64" t="n">
-        <v>321.5238071066378</v>
+        <v>319.8178861109197</v>
       </c>
       <c r="D64" t="n">
-        <v>313.8837033726762</v>
+        <v>310.6157850065654</v>
       </c>
       <c r="E64" t="n">
-        <v>321.3941698854088</v>
+        <v>313.1109313964844</v>
       </c>
       <c r="F64" t="n">
-        <v>31240900</v>
+        <v>33909400</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2099,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B65" t="n">
-        <v>320.4366455078125</v>
+        <v>311.7635388280278</v>
       </c>
       <c r="C65" t="n">
-        <v>322.3217576397153</v>
+        <v>317.3726229056239</v>
       </c>
       <c r="D65" t="n">
-        <v>318.3421170569229</v>
+        <v>311.2944500995635</v>
       </c>
       <c r="E65" t="n">
-        <v>318.6612638744486</v>
+        <v>316.4643859863281</v>
       </c>
       <c r="F65" t="n">
-        <v>28851700</v>
+        <v>30194000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2125,25 +2133,25 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B66" t="n">
-        <v>313.1109008789062</v>
+        <v>315.2168165746965</v>
       </c>
       <c r="C66" t="n">
-        <v>319.8178549396436</v>
+        <v>320.6861883612462</v>
       </c>
       <c r="D66" t="n">
-        <v>310.6157547321785</v>
+        <v>314.069055340672</v>
       </c>
       <c r="E66" t="n">
-        <v>319.4285975207571</v>
+        <v>319.5883178710938</v>
       </c>
       <c r="F66" t="n">
-        <v>33909400</v>
+        <v>33428900</v>
       </c>
       <c r="G66" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2151,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B67" t="n">
-        <v>316.4643859863281</v>
+        <v>319.4585358397385</v>
       </c>
       <c r="C67" t="n">
-        <v>317.3726229056239</v>
+        <v>320.4965251579071</v>
       </c>
       <c r="D67" t="n">
-        <v>311.2944500995635</v>
+        <v>308.0008443067889</v>
       </c>
       <c r="E67" t="n">
-        <v>311.7635388280278</v>
+        <v>311.8233947753906</v>
       </c>
       <c r="F67" t="n">
-        <v>30194000</v>
+        <v>42353700</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2177,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B68" t="n">
-        <v>319.5883178710938</v>
+        <v>313.0909556884665</v>
       </c>
       <c r="C68" t="n">
-        <v>320.6861883612462</v>
+        <v>314.2586670471713</v>
       </c>
       <c r="D68" t="n">
-        <v>314.069055340672</v>
+        <v>304.9667450846255</v>
       </c>
       <c r="E68" t="n">
-        <v>315.2168165746965</v>
+        <v>308.6895141601562</v>
       </c>
       <c r="F68" t="n">
-        <v>33428900</v>
+        <v>35940200</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2203,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B69" t="n">
-        <v>311.8234252929688</v>
+        <v>310.7155693717638</v>
       </c>
       <c r="C69" t="n">
-        <v>320.4965565243085</v>
+        <v>310.8153813101663</v>
       </c>
       <c r="D69" t="n">
-        <v>308.0008744502611</v>
+        <v>304.288070405232</v>
       </c>
       <c r="E69" t="n">
-        <v>319.4585671045538</v>
+        <v>307.62158203125</v>
       </c>
       <c r="F69" t="n">
-        <v>42353700</v>
+        <v>29151900</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2229,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B70" t="n">
-        <v>308.6895141601562</v>
+        <v>304.3579426322819</v>
       </c>
       <c r="C70" t="n">
-        <v>314.2586670471713</v>
+        <v>310.1666197797816</v>
       </c>
       <c r="D70" t="n">
-        <v>304.9667450846255</v>
+        <v>302.0025088045779</v>
       </c>
       <c r="E70" t="n">
-        <v>313.0909556884665</v>
+        <v>305.9747924804688</v>
       </c>
       <c r="F70" t="n">
-        <v>35940200</v>
+        <v>30585000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2255,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B71" t="n">
-        <v>307.6216125488281</v>
+        <v>307.4120099511304</v>
       </c>
       <c r="C71" t="n">
-        <v>310.8154121445851</v>
+        <v>307.4918412298865</v>
       </c>
       <c r="D71" t="n">
-        <v>304.2881005921093</v>
+        <v>295.5450797036171</v>
       </c>
       <c r="E71" t="n">
-        <v>310.7156001962807</v>
+        <v>296.1439208984375</v>
       </c>
       <c r="F71" t="n">
-        <v>29151900</v>
+        <v>43930400</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2281,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B72" t="n">
-        <v>305.9747924804688</v>
+        <v>301.1342186567393</v>
       </c>
       <c r="C72" t="n">
-        <v>310.1666197797816</v>
+        <v>303.3698600006946</v>
       </c>
       <c r="D72" t="n">
-        <v>302.0025088045779</v>
+        <v>298.6490626821344</v>
       </c>
       <c r="E72" t="n">
-        <v>304.3579426322819</v>
+        <v>301.8727722167969</v>
       </c>
       <c r="F72" t="n">
-        <v>30585000</v>
+        <v>33518000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2307,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B73" t="n">
-        <v>296.1439208984375</v>
+        <v>301.1442091965169</v>
       </c>
       <c r="C73" t="n">
-        <v>307.4918412298865</v>
+        <v>306.6534812800651</v>
       </c>
       <c r="D73" t="n">
-        <v>295.5450797036171</v>
+        <v>300.3856749721532</v>
       </c>
       <c r="E73" t="n">
-        <v>307.4120099511304</v>
+        <v>306.5636596679688</v>
       </c>
       <c r="F73" t="n">
-        <v>43930400</v>
+        <v>59943200</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2333,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B74" t="n">
-        <v>301.8727722167969</v>
+        <v>309.2783702904479</v>
       </c>
       <c r="C74" t="n">
-        <v>303.3698600006946</v>
+        <v>309.5278849133803</v>
       </c>
       <c r="D74" t="n">
-        <v>298.6490626821344</v>
+        <v>304.7072453416635</v>
       </c>
       <c r="E74" t="n">
-        <v>301.1342186567393</v>
+        <v>309.1785583496094</v>
       </c>
       <c r="F74" t="n">
-        <v>33518000</v>
+        <v>26429900</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2359,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B75" t="n">
-        <v>306.5636596679688</v>
+        <v>309.0288478780406</v>
       </c>
       <c r="C75" t="n">
-        <v>306.6534812800651</v>
+        <v>314.328535898872</v>
       </c>
       <c r="D75" t="n">
-        <v>300.3856749721532</v>
+        <v>308.7194521900694</v>
       </c>
       <c r="E75" t="n">
-        <v>301.1442091965169</v>
+        <v>313.7396850585938</v>
       </c>
       <c r="F75" t="n">
-        <v>59943200</v>
+        <v>25478700</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2385,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B76" t="n">
-        <v>309.1785888671875</v>
+        <v>314.1588359856885</v>
       </c>
       <c r="C76" t="n">
-        <v>309.5279154654388</v>
+        <v>314.4682316573388</v>
       </c>
       <c r="D76" t="n">
-        <v>304.707275417899</v>
+        <v>311.3143938726672</v>
       </c>
       <c r="E76" t="n">
-        <v>309.278400817878</v>
+        <v>313.4801635742188</v>
       </c>
       <c r="F76" t="n">
-        <v>26429900</v>
+        <v>10097400</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2411,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B77" t="n">
-        <v>313.7396850585938</v>
+        <v>313.8694546536391</v>
       </c>
       <c r="C77" t="n">
-        <v>314.328535898872</v>
+        <v>314.4782557314601</v>
       </c>
       <c r="D77" t="n">
-        <v>308.7194521900694</v>
+        <v>311.6737137240756</v>
       </c>
       <c r="E77" t="n">
-        <v>309.0288478780406</v>
+        <v>312.9013366699219</v>
       </c>
       <c r="F77" t="n">
-        <v>25478700</v>
+        <v>10899000</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2437,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B78" t="n">
-        <v>313.4801635742188</v>
+        <v>310.7654822740718</v>
       </c>
       <c r="C78" t="n">
-        <v>314.4682316573388</v>
+        <v>313.4103313095557</v>
       </c>
       <c r="D78" t="n">
-        <v>311.3143938726672</v>
+        <v>310.0169383701615</v>
       </c>
       <c r="E78" t="n">
-        <v>314.1588359856885</v>
+        <v>312.9512329101562</v>
       </c>
       <c r="F78" t="n">
-        <v>10097400</v>
+        <v>19621800</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2463,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B79" t="n">
-        <v>312.9013671875</v>
+        <v>311.8932765746258</v>
       </c>
       <c r="C79" t="n">
-        <v>314.4782864028367</v>
+        <v>316.3346490163796</v>
       </c>
       <c r="D79" t="n">
-        <v>311.6737441219225</v>
+        <v>311.8533457068925</v>
       </c>
       <c r="E79" t="n">
-        <v>313.8694852656387</v>
+        <v>313.2406616210938</v>
       </c>
       <c r="F79" t="n">
-        <v>10899000</v>
+        <v>17380900</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2489,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B80" t="n">
-        <v>312.9512634277344</v>
+        <v>312.2426007868329</v>
       </c>
       <c r="C80" t="n">
-        <v>313.410361871903</v>
+        <v>313.9692224596297</v>
       </c>
       <c r="D80" t="n">
-        <v>310.0169686016006</v>
+        <v>310.8353346785167</v>
       </c>
       <c r="E80" t="n">
-        <v>310.7655125785055</v>
+        <v>312.3923034667969</v>
       </c>
       <c r="F80" t="n">
-        <v>19621800</v>
+        <v>16377700</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2515,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B81" t="n">
-        <v>313.2406616210938</v>
+        <v>316.2847494408858</v>
       </c>
       <c r="C81" t="n">
-        <v>316.3346490163796</v>
+        <v>321.8738834308866</v>
       </c>
       <c r="D81" t="n">
-        <v>311.8533457068925</v>
+        <v>309.727497435876</v>
       </c>
       <c r="E81" t="n">
-        <v>311.8932765746258</v>
+        <v>314.5381469726562</v>
       </c>
       <c r="F81" t="n">
-        <v>17380900</v>
+        <v>32009400</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2541,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B82" t="n">
-        <v>312.3923034667969</v>
+        <v>317.0432968268774</v>
       </c>
       <c r="C82" t="n">
-        <v>313.9692224596297</v>
+        <v>318.4006418955826</v>
       </c>
       <c r="D82" t="n">
-        <v>310.8353346785167</v>
+        <v>314.0191805034655</v>
       </c>
       <c r="E82" t="n">
-        <v>312.2426007868329</v>
+        <v>315.9254760742188</v>
       </c>
       <c r="F82" t="n">
-        <v>16377700</v>
+        <v>30195600</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2567,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B83" t="n">
-        <v>314.5381164550781</v>
+        <v>315.7857038876524</v>
       </c>
       <c r="C83" t="n">
-        <v>321.87385220157</v>
+        <v>320.3168980142969</v>
       </c>
       <c r="D83" t="n">
-        <v>309.7274673850438</v>
+        <v>311.1746784825258</v>
       </c>
       <c r="E83" t="n">
-        <v>316.2847187538463</v>
+        <v>313.7297058105469</v>
       </c>
       <c r="F83" t="n">
-        <v>32009400</v>
+        <v>31212100</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2593,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B84" t="n">
-        <v>315.9254455566406</v>
+        <v>313.7496277154789</v>
       </c>
       <c r="C84" t="n">
-        <v>318.4006111389099</v>
+        <v>325.5167449190081</v>
       </c>
       <c r="D84" t="n">
-        <v>314.0191501700305</v>
+        <v>313.5799748421341</v>
       </c>
       <c r="E84" t="n">
-        <v>317.0432662013207</v>
+        <v>321.3548583984375</v>
       </c>
       <c r="F84" t="n">
-        <v>30195600</v>
+        <v>35104400</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2619,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B85" t="n">
-        <v>313.7297058105469</v>
+        <v>328.3313118537803</v>
       </c>
       <c r="C85" t="n">
-        <v>320.3168980142969</v>
+        <v>329.6786969446188</v>
       </c>
       <c r="D85" t="n">
-        <v>311.1746784825258</v>
+        <v>320.8758135066914</v>
       </c>
       <c r="E85" t="n">
-        <v>315.7857038876524</v>
+        <v>324.8081665039062</v>
       </c>
       <c r="F85" t="n">
-        <v>31212100</v>
+        <v>31896100</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2645,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B86" t="n">
-        <v>321.3549194335938</v>
+        <v>326.4549607998293</v>
       </c>
       <c r="C86" t="n">
-        <v>325.5168067446344</v>
+        <v>330.1876899539591</v>
       </c>
       <c r="D86" t="n">
-        <v>313.5800344006012</v>
+        <v>325.1674567682817</v>
       </c>
       <c r="E86" t="n">
-        <v>313.7496873061683</v>
+        <v>327.9320983886719</v>
       </c>
       <c r="F86" t="n">
-        <v>35104400</v>
+        <v>26214200</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2671,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B87" t="n">
-        <v>324.8081665039062</v>
+        <v>325.1674358606418</v>
       </c>
       <c r="C87" t="n">
-        <v>329.6786969446188</v>
+        <v>333.3914583276215</v>
       </c>
       <c r="D87" t="n">
-        <v>320.8758135066914</v>
+        <v>324.3690012716118</v>
       </c>
       <c r="E87" t="n">
-        <v>328.3313118537803</v>
+        <v>331.2156677246094</v>
       </c>
       <c r="F87" t="n">
-        <v>31896100</v>
+        <v>33923900</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2697,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B88" t="n">
-        <v>327.9320983886719</v>
+        <v>334.2997097916206</v>
       </c>
       <c r="C88" t="n">
-        <v>330.1876899539591</v>
+        <v>339.828932001794</v>
       </c>
       <c r="D88" t="n">
-        <v>325.1674567682817</v>
+        <v>332.9722749179122</v>
       </c>
       <c r="E88" t="n">
-        <v>326.4549607998293</v>
+        <v>335.3177185058594</v>
       </c>
       <c r="F88" t="n">
-        <v>26214200</v>
+        <v>33517600</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2723,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B89" t="n">
-        <v>331.2156982421875</v>
+        <v>334.4095038108318</v>
       </c>
       <c r="C89" t="n">
-        <v>333.3914890456728</v>
+        <v>335.8666608024698</v>
       </c>
       <c r="D89" t="n">
-        <v>324.3690311583512</v>
+        <v>329.838408937521</v>
       </c>
       <c r="E89" t="n">
-        <v>325.1674658209474</v>
+        <v>335.18798828125</v>
       </c>
       <c r="F89" t="n">
-        <v>33923900</v>
+        <v>28525600</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2749,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B90" t="n">
-        <v>335.3176879882812</v>
+        <v>336.9944202593897</v>
       </c>
       <c r="C90" t="n">
-        <v>339.8289010736461</v>
+        <v>337.0343511246202</v>
       </c>
       <c r="D90" t="n">
-        <v>332.9722446137951</v>
+        <v>330.0978329050398</v>
       </c>
       <c r="E90" t="n">
-        <v>334.2996793666924</v>
+        <v>332.1338806152344</v>
       </c>
       <c r="F90" t="n">
-        <v>33517600</v>
+        <v>28442400</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2775,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B91" t="n">
-        <v>335.1879577636719</v>
+        <v>333.7607557246461</v>
       </c>
       <c r="C91" t="n">
-        <v>335.8666302231012</v>
+        <v>334.0002800245007</v>
       </c>
       <c r="D91" t="n">
-        <v>329.8383789070015</v>
+        <v>327.0637915356931</v>
       </c>
       <c r="E91" t="n">
-        <v>334.4094733641317</v>
+        <v>329.3593139648438</v>
       </c>
       <c r="F91" t="n">
-        <v>28525600</v>
+        <v>40341600</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2801,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B92" t="n">
-        <v>332.1339111328125</v>
+        <v>320.2470363972373</v>
       </c>
       <c r="C92" t="n">
-        <v>337.03438209247</v>
+        <v>327.0937337673917</v>
       </c>
       <c r="D92" t="n">
-        <v>330.097863235539</v>
+        <v>319.8078882063433</v>
       </c>
       <c r="E92" t="n">
-        <v>336.9944512235705</v>
+        <v>321.3748474121094</v>
       </c>
       <c r="F92" t="n">
-        <v>28442400</v>
+        <v>35361000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2827,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B93" t="n">
-        <v>329.3593139648438</v>
+        <v>320.2969541162656</v>
       </c>
       <c r="C93" t="n">
-        <v>334.0002800245007</v>
+        <v>331.8345081879527</v>
       </c>
       <c r="D93" t="n">
-        <v>327.0637915356931</v>
+        <v>318.729994927537</v>
       </c>
       <c r="E93" t="n">
-        <v>333.7607557246461</v>
+        <v>327.7424621582031</v>
       </c>
       <c r="F93" t="n">
-        <v>40341600</v>
+        <v>35386600</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2853,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B94" t="n">
-        <v>321.3748474121094</v>
+        <v>333.8006666576773</v>
       </c>
       <c r="C94" t="n">
-        <v>327.0937337673917</v>
+        <v>334.4992893099707</v>
       </c>
       <c r="D94" t="n">
-        <v>319.8078882063433</v>
+        <v>328.1117212092731</v>
       </c>
       <c r="E94" t="n">
-        <v>320.2470363972373</v>
+        <v>329.8982543945312</v>
       </c>
       <c r="F94" t="n">
-        <v>35361000</v>
+        <v>26253600</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2879,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B95" t="n">
-        <v>327.7424621582031</v>
+        <v>331.8444485977197</v>
       </c>
       <c r="C95" t="n">
-        <v>331.8345081879527</v>
+        <v>333.0421309365838</v>
       </c>
       <c r="D95" t="n">
-        <v>318.729994927537</v>
+        <v>326.8142558744754</v>
       </c>
       <c r="E95" t="n">
-        <v>320.2969541162656</v>
+        <v>327.2933044433594</v>
       </c>
       <c r="F95" t="n">
-        <v>35386600</v>
+        <v>27280000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2905,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B96" t="n">
-        <v>329.8982543945312</v>
+        <v>327.1735452193246</v>
       </c>
       <c r="C96" t="n">
-        <v>334.4992893099707</v>
+        <v>335.1879535299186</v>
       </c>
       <c r="D96" t="n">
-        <v>328.1117212092731</v>
+        <v>326.3651202937951</v>
       </c>
       <c r="E96" t="n">
-        <v>333.8006666576773</v>
+        <v>332.6129760742188</v>
       </c>
       <c r="F96" t="n">
-        <v>26253600</v>
+        <v>26042100</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2931,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B97" t="n">
-        <v>327.2933044433594</v>
+        <v>334.7188669221849</v>
       </c>
       <c r="C97" t="n">
-        <v>333.0421309365838</v>
+        <v>337.2539439848537</v>
       </c>
       <c r="D97" t="n">
-        <v>326.8142558744754</v>
+        <v>332.8325522369338</v>
       </c>
       <c r="E97" t="n">
-        <v>331.8444485977197</v>
+        <v>333.9004516601562</v>
       </c>
       <c r="F97" t="n">
-        <v>27280000</v>
+        <v>21636200</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2957,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B98" t="n">
-        <v>332.6129760742188</v>
+        <v>335.4075262381039</v>
       </c>
       <c r="C98" t="n">
-        <v>335.1879535299186</v>
+        <v>336.8846637353836</v>
       </c>
       <c r="D98" t="n">
-        <v>326.3651202937951</v>
+        <v>331.2955302242731</v>
       </c>
       <c r="E98" t="n">
-        <v>327.1735452193246</v>
+        <v>335.3576354980469</v>
       </c>
       <c r="F98" t="n">
-        <v>26042100</v>
+        <v>27434400</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2983,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B99" t="n">
-        <v>333.9004516601562</v>
+        <v>339.6393000059441</v>
       </c>
       <c r="C99" t="n">
-        <v>337.2539439848537</v>
+        <v>341.625457159737</v>
       </c>
       <c r="D99" t="n">
-        <v>332.8325522369338</v>
+        <v>325.9060355700189</v>
       </c>
       <c r="E99" t="n">
-        <v>334.7188669221849</v>
+        <v>337.5932922363281</v>
       </c>
       <c r="F99" t="n">
-        <v>21636200</v>
+        <v>39785600</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3009,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B100" t="n">
-        <v>335.3576354980469</v>
+        <v>339.3398975620609</v>
       </c>
       <c r="C100" t="n">
-        <v>336.8846637353836</v>
+        <v>339.3398975620609</v>
       </c>
       <c r="D100" t="n">
-        <v>331.2955302242731</v>
+        <v>331.6448748839121</v>
       </c>
       <c r="E100" t="n">
-        <v>335.4075262381039</v>
+        <v>337.3437805175781</v>
       </c>
       <c r="F100" t="n">
-        <v>27434400</v>
+        <v>31024000</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3035,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B101" t="n">
-        <v>337.5932922363281</v>
+        <v>335.5672372238362</v>
       </c>
       <c r="C101" t="n">
-        <v>341.625457159737</v>
+        <v>344.160506471566</v>
       </c>
       <c r="D101" t="n">
-        <v>325.9060355700189</v>
+        <v>334.9783863513143</v>
       </c>
       <c r="E101" t="n">
-        <v>339.6393000059441</v>
+        <v>343.0227355957031</v>
       </c>
       <c r="F101" t="n">
-        <v>39785600</v>
+        <v>32006100</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3061,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B102" t="n">
-        <v>337.3437805175781</v>
+        <v>346.6656368085559</v>
       </c>
       <c r="C102" t="n">
-        <v>339.3398975620609</v>
+        <v>348.322417578686</v>
       </c>
       <c r="D102" t="n">
-        <v>331.6448748839121</v>
+        <v>336.8148042563823</v>
       </c>
       <c r="E102" t="n">
-        <v>339.3398975620609</v>
+        <v>339.0504455566406</v>
       </c>
       <c r="F102" t="n">
-        <v>31024000</v>
+        <v>36506700</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3087,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B103" t="n">
-        <v>343.022705078125</v>
+        <v>342.2941250868659</v>
       </c>
       <c r="C103" t="n">
-        <v>344.1604758527643</v>
+        <v>342.6434516437907</v>
       </c>
       <c r="D103" t="n">
-        <v>334.9783565494149</v>
+        <v>327.8821583120744</v>
       </c>
       <c r="E103" t="n">
-        <v>335.5672073695487</v>
+        <v>332.3934020996094</v>
       </c>
       <c r="F103" t="n">
-        <v>32006100</v>
+        <v>70618400</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3113,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B104" t="n">
-        <v>339.0504455566406</v>
+        <v>311.6137920773395</v>
       </c>
       <c r="C104" t="n">
-        <v>348.322417578686</v>
+        <v>332.0440485608184</v>
       </c>
       <c r="D104" t="n">
-        <v>336.8148042563823</v>
+        <v>305.8649659981283</v>
       </c>
       <c r="E104" t="n">
-        <v>346.6656368085559</v>
+        <v>330.6068420410156</v>
       </c>
       <c r="F104" t="n">
-        <v>36506700</v>
+        <v>88205800</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3139,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B105" t="n">
-        <v>332.3934326171875</v>
+        <v>326.5447743483745</v>
       </c>
       <c r="C105" t="n">
-        <v>342.6434831024425</v>
+        <v>329.7385737476322</v>
       </c>
       <c r="D105" t="n">
-        <v>327.8821884154679</v>
+        <v>319.2988903139048</v>
       </c>
       <c r="E105" t="n">
-        <v>342.2941565134455</v>
+        <v>322.233154296875</v>
       </c>
       <c r="F105" t="n">
-        <v>70618400</v>
+        <v>56380500</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3165,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B106" t="n">
-        <v>330.6069030761719</v>
+        <v>320.3069052195784</v>
       </c>
       <c r="C106" t="n">
-        <v>332.0441098613053</v>
+        <v>327.0637807183464</v>
       </c>
       <c r="D106" t="n">
-        <v>305.8650224655501</v>
+        <v>316.6440476026885</v>
       </c>
       <c r="E106" t="n">
-        <v>311.6138496060838</v>
+        <v>323.6903381347656</v>
       </c>
       <c r="F106" t="n">
-        <v>88205800</v>
+        <v>39640100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3191,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B107" t="n">
-        <v>322.233154296875</v>
+        <v>320.3468306795893</v>
       </c>
       <c r="C107" t="n">
-        <v>329.7385737476322</v>
+        <v>321.0454837970353</v>
       </c>
       <c r="D107" t="n">
-        <v>319.2988903139048</v>
+        <v>313.9991629255859</v>
       </c>
       <c r="E107" t="n">
-        <v>326.5447743483745</v>
+        <v>317.9614562988281</v>
       </c>
       <c r="F107" t="n">
-        <v>56380500</v>
+        <v>39170000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3217,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B108" t="n">
-        <v>323.6903381347656</v>
+        <v>318.3507205277581</v>
       </c>
       <c r="C108" t="n">
-        <v>327.0637807183464</v>
+        <v>320.4366591349046</v>
       </c>
       <c r="D108" t="n">
-        <v>316.6440476026885</v>
+        <v>309.0587983421378</v>
       </c>
       <c r="E108" t="n">
-        <v>320.3069052195784</v>
+        <v>310.3562622070312</v>
       </c>
       <c r="F108" t="n">
-        <v>39640100</v>
+        <v>45406400</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3243,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B109" t="n">
-        <v>317.9614562988281</v>
+        <v>311.4840518259579</v>
       </c>
       <c r="C109" t="n">
-        <v>321.0454837970353</v>
+        <v>315.6259882196205</v>
       </c>
       <c r="D109" t="n">
-        <v>313.9991629255859</v>
+        <v>306.603561940612</v>
       </c>
       <c r="E109" t="n">
-        <v>320.3468306795893</v>
+        <v>308.4000549316406</v>
       </c>
       <c r="F109" t="n">
-        <v>39170000</v>
+        <v>47761300</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3269,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B110" t="n">
-        <v>310.3562316894531</v>
+        <v>307.1325415821482</v>
       </c>
       <c r="C110" t="n">
-        <v>320.4366276261131</v>
+        <v>308.0307881065925</v>
       </c>
       <c r="D110" t="n">
-        <v>309.0587679521403</v>
+        <v>303.1203270701956</v>
       </c>
       <c r="E110" t="n">
-        <v>318.3506892240785</v>
+        <v>305.1264343261719</v>
       </c>
       <c r="F110" t="n">
-        <v>45406400</v>
+        <v>38499700</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3295,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B111" t="n">
-        <v>308.4000854492188</v>
+        <v>299.4574575670962</v>
       </c>
       <c r="C111" t="n">
-        <v>315.6260194522374</v>
+        <v>303.8489085337251</v>
       </c>
       <c r="D111" t="n">
-        <v>306.603592280419</v>
+        <v>295.674807618098</v>
       </c>
       <c r="E111" t="n">
-        <v>311.4840826487114</v>
+        <v>301.43359375</v>
       </c>
       <c r="F111" t="n">
-        <v>47761300</v>
+        <v>39247600</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3321,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B112" t="n">
-        <v>305.1264343261719</v>
+        <v>301.5035060024616</v>
       </c>
       <c r="C112" t="n">
-        <v>308.0307881065925</v>
+        <v>304.7871271852118</v>
       </c>
       <c r="D112" t="n">
-        <v>303.1203270701956</v>
+        <v>300.6651404690992</v>
       </c>
       <c r="E112" t="n">
-        <v>307.1325415821482</v>
+        <v>302.7410888671875</v>
       </c>
       <c r="F112" t="n">
-        <v>38499700</v>
+        <v>28482100</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3347,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B113" t="n">
-        <v>301.43359375</v>
+        <v>301.2340248853423</v>
       </c>
       <c r="C113" t="n">
-        <v>303.8489085337251</v>
+        <v>304.8769323320439</v>
       </c>
       <c r="D113" t="n">
-        <v>295.674807618098</v>
+        <v>299.4574819671566</v>
       </c>
       <c r="E113" t="n">
-        <v>299.4574575670962</v>
+        <v>302.2620239257812</v>
       </c>
       <c r="F113" t="n">
-        <v>39247600</v>
+        <v>25834400</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3373,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B114" t="n">
-        <v>302.7410888671875</v>
+        <v>303.7291622459488</v>
       </c>
       <c r="C114" t="n">
-        <v>304.7871271852118</v>
+        <v>315.885507154404</v>
       </c>
       <c r="D114" t="n">
-        <v>300.6651404690992</v>
+        <v>303.3099642850277</v>
       </c>
       <c r="E114" t="n">
-        <v>301.5035060024616</v>
+        <v>314.3684692382812</v>
       </c>
       <c r="F114" t="n">
-        <v>28482100</v>
+        <v>53210800</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3399,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B115" t="n">
-        <v>302.2620239257812</v>
+        <v>318.4305429928518</v>
       </c>
       <c r="C115" t="n">
-        <v>304.8769323320439</v>
+        <v>318.8996316925602</v>
       </c>
       <c r="D115" t="n">
-        <v>299.4574819671566</v>
+        <v>309.2683735389658</v>
       </c>
       <c r="E115" t="n">
-        <v>301.2340248853423</v>
+        <v>310.8852233886719</v>
       </c>
       <c r="F115" t="n">
-        <v>25834400</v>
+        <v>31423000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3425,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B116" t="n">
-        <v>314.3684997558594</v>
+        <v>309.9171500893873</v>
       </c>
       <c r="C116" t="n">
-        <v>315.8855378192499</v>
+        <v>311.6637526652123</v>
       </c>
       <c r="D116" t="n">
-        <v>303.3099937290923</v>
+        <v>305.3360647026519</v>
       </c>
       <c r="E116" t="n">
-        <v>303.7291917307074</v>
+        <v>310.2964172363281</v>
       </c>
       <c r="F116" t="n">
-        <v>53210800</v>
+        <v>25615600</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3451,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B117" t="n">
-        <v>310.8852233886719</v>
+        <v>311.4541150323118</v>
       </c>
       <c r="C117" t="n">
-        <v>318.8996316925602</v>
+        <v>313.0310644276307</v>
       </c>
       <c r="D117" t="n">
-        <v>309.2683735389658</v>
+        <v>308.8392067871133</v>
       </c>
       <c r="E117" t="n">
-        <v>318.4305429928518</v>
+        <v>312.29248046875</v>
       </c>
       <c r="F117" t="n">
-        <v>31423000</v>
+        <v>29963600</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3477,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B118" t="n">
-        <v>310.29638671875</v>
+        <v>312.0330622595087</v>
       </c>
       <c r="C118" t="n">
-        <v>311.6637220131571</v>
+        <v>312.5320915706006</v>
       </c>
       <c r="D118" t="n">
-        <v>305.3360346729232</v>
+        <v>301.7630305089056</v>
       </c>
       <c r="E118" t="n">
-        <v>309.91711960911</v>
+        <v>306.7832641601562</v>
       </c>
       <c r="F118" t="n">
-        <v>25615600</v>
+        <v>36431200</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3503,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B119" t="n">
-        <v>312.2925109863281</v>
+        <v>303.5495233120643</v>
       </c>
       <c r="C119" t="n">
-        <v>313.031095017384</v>
+        <v>311.7635251790807</v>
       </c>
       <c r="D119" t="n">
-        <v>308.8392369672335</v>
+        <v>303.2101566226461</v>
       </c>
       <c r="E119" t="n">
-        <v>311.4541454679639</v>
+        <v>311.1547241210938</v>
       </c>
       <c r="F119" t="n">
-        <v>29963600</v>
+        <v>44640600</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3529,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B120" t="n">
-        <v>306.783203125</v>
+        <v>302.6412753457796</v>
       </c>
       <c r="C120" t="n">
-        <v>312.5320293917034</v>
+        <v>307.8910420913047</v>
       </c>
       <c r="D120" t="n">
-        <v>301.762970472535</v>
+        <v>300.7149993852133</v>
       </c>
       <c r="E120" t="n">
-        <v>312.0330001798944</v>
+        <v>305.9248657226562</v>
       </c>
       <c r="F120" t="n">
-        <v>36431200</v>
+        <v>34790200</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3555,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B121" t="n">
-        <v>311.1547241210938</v>
+        <v>298.0102681623609</v>
       </c>
       <c r="C121" t="n">
-        <v>311.7635251790807</v>
+        <v>303.3498869477631</v>
       </c>
       <c r="D121" t="n">
-        <v>303.2101566226461</v>
+        <v>296.1339134078651</v>
       </c>
       <c r="E121" t="n">
-        <v>303.5495233120643</v>
+        <v>302.9905700683594</v>
       </c>
       <c r="F121" t="n">
-        <v>44640600</v>
+        <v>35497000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3581,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B122" t="n">
-        <v>305.9248962402344</v>
+        <v>302.3019795923877</v>
       </c>
       <c r="C122" t="n">
-        <v>307.8910728050191</v>
+        <v>304.8769573413998</v>
       </c>
       <c r="D122" t="n">
-        <v>300.7150293830805</v>
+        <v>300.1661195993462</v>
       </c>
       <c r="E122" t="n">
-        <v>302.6413055358027</v>
+        <v>302.54150390625</v>
       </c>
       <c r="F122" t="n">
-        <v>34790200</v>
+        <v>29536200</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3607,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B123" t="n">
-        <v>302.9905700683594</v>
+        <v>302.4516473530844</v>
       </c>
       <c r="C123" t="n">
-        <v>303.3498869477631</v>
+        <v>302.711121843687</v>
       </c>
       <c r="D123" t="n">
-        <v>296.1339134078651</v>
+        <v>297.4114338033223</v>
       </c>
       <c r="E123" t="n">
-        <v>298.0102681623609</v>
+        <v>300.2958374023438</v>
       </c>
       <c r="F123" t="n">
-        <v>35497000</v>
+        <v>35752300</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3633,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B124" t="n">
-        <v>302.54150390625</v>
+        <v>295.5151547022239</v>
       </c>
       <c r="C124" t="n">
-        <v>304.8769573413998</v>
+        <v>299.9465371351957</v>
       </c>
       <c r="D124" t="n">
-        <v>300.1661195993462</v>
+        <v>294.6069177596933</v>
       </c>
       <c r="E124" t="n">
-        <v>302.3019795923877</v>
+        <v>297.9404296875</v>
       </c>
       <c r="F124" t="n">
-        <v>29536200</v>
+        <v>25576900</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3659,25 +3667,25 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B125" t="n">
-        <v>300.2958679199219</v>
+        <v>293.9952756214191</v>
       </c>
       <c r="C125" t="n">
-        <v>302.7111526067185</v>
+        <v>306.4198649966507</v>
       </c>
       <c r="D125" t="n">
-        <v>297.4114640277728</v>
+        <v>293.7156237584298</v>
       </c>
       <c r="E125" t="n">
-        <v>302.4516780897468</v>
+        <v>305.9804077148438</v>
       </c>
       <c r="F125" t="n">
-        <v>35752300</v>
+        <v>29312100</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -3685,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B126" t="n">
-        <v>297.9404296875</v>
+        <v>305.7906896809686</v>
       </c>
       <c r="C126" t="n">
-        <v>299.9465371351957</v>
+        <v>309.1265479913924</v>
       </c>
       <c r="D126" t="n">
-        <v>294.6069177596933</v>
+        <v>305.1914269440574</v>
       </c>
       <c r="E126" t="n">
-        <v>295.5151547022239</v>
+        <v>306.6596069335938</v>
       </c>
       <c r="F126" t="n">
-        <v>25576900</v>
+        <v>23239700</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3711,25 +3719,25 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B127" t="n">
-        <v>305.9804077148438</v>
+        <v>306.3699695674413</v>
       </c>
       <c r="C127" t="n">
-        <v>306.4198649966507</v>
+        <v>311.0341973481569</v>
       </c>
       <c r="D127" t="n">
-        <v>293.7156237584298</v>
+        <v>305.5410112597431</v>
       </c>
       <c r="E127" t="n">
-        <v>293.9952756214191</v>
+        <v>308.3175659179688</v>
       </c>
       <c r="F127" t="n">
-        <v>29312100</v>
+        <v>24125700</v>
       </c>
       <c r="G127" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -3737,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B128" t="n">
-        <v>306.6596069335938</v>
+        <v>306.4398879814062</v>
       </c>
       <c r="C128" t="n">
-        <v>309.1265479913924</v>
+        <v>308.5572566363961</v>
       </c>
       <c r="D128" t="n">
-        <v>305.1914269440574</v>
+        <v>300.6570526787451</v>
       </c>
       <c r="E128" t="n">
-        <v>305.7906896809686</v>
+        <v>303.1739196777344</v>
       </c>
       <c r="F128" t="n">
-        <v>23239700</v>
+        <v>24928300</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3763,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B129" t="n">
-        <v>308.3175659179688</v>
+        <v>306.6296377698095</v>
       </c>
       <c r="C129" t="n">
-        <v>311.0341973481569</v>
+        <v>307.3087879643589</v>
       </c>
       <c r="D129" t="n">
-        <v>305.5410112597431</v>
+        <v>300.0677703977713</v>
       </c>
       <c r="E129" t="n">
-        <v>306.3699695674413</v>
+        <v>301.9054870605469</v>
       </c>
       <c r="F129" t="n">
-        <v>24125700</v>
+        <v>23693100</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3789,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B130" t="n">
-        <v>303.1738891601562</v>
+        <v>303.9729346538992</v>
       </c>
       <c r="C130" t="n">
-        <v>308.5572255769297</v>
+        <v>306.1102674724465</v>
       </c>
       <c r="D130" t="n">
-        <v>300.6570224145156</v>
+        <v>302.6445653756606</v>
       </c>
       <c r="E130" t="n">
-        <v>306.4398571350748</v>
+        <v>305.1814270019531</v>
       </c>
       <c r="F130" t="n">
-        <v>24928300</v>
+        <v>23519700</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3815,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B131" t="n">
-        <v>301.9054870605469</v>
+        <v>305.481031231764</v>
       </c>
       <c r="C131" t="n">
-        <v>307.3087879643589</v>
+        <v>311.0341705495281</v>
       </c>
       <c r="D131" t="n">
-        <v>300.0677703977713</v>
+        <v>305.1214918945171</v>
       </c>
       <c r="E131" t="n">
-        <v>306.6296377698095</v>
+        <v>310.5347900390625</v>
       </c>
       <c r="F131" t="n">
-        <v>23693100</v>
+        <v>21955200</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3841,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B132" t="n">
-        <v>305.1814270019531</v>
+        <v>308.8868058363209</v>
       </c>
       <c r="C132" t="n">
-        <v>306.1102674724465</v>
+        <v>312.0828532524296</v>
       </c>
       <c r="D132" t="n">
-        <v>302.6445653756606</v>
+        <v>306.5497087361953</v>
       </c>
       <c r="E132" t="n">
-        <v>303.9729346538992</v>
+        <v>307.3087768554688</v>
       </c>
       <c r="F132" t="n">
-        <v>23519700</v>
+        <v>20009800</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3867,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B133" t="n">
-        <v>310.5347900390625</v>
+        <v>303.6333516523425</v>
       </c>
       <c r="C133" t="n">
-        <v>311.0341705495281</v>
+        <v>307.6783216475022</v>
       </c>
       <c r="D133" t="n">
-        <v>305.1214918945171</v>
+        <v>301.9754046785898</v>
       </c>
       <c r="E133" t="n">
-        <v>305.481031231764</v>
+        <v>306.7494812011719</v>
       </c>
       <c r="F133" t="n">
-        <v>21955200</v>
+        <v>25075800</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3893,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B134" t="n">
-        <v>307.3087768554688</v>
+        <v>305.0815409313132</v>
       </c>
       <c r="C134" t="n">
-        <v>312.0828532524296</v>
+        <v>305.620880431115</v>
       </c>
       <c r="D134" t="n">
-        <v>306.5497087361953</v>
+        <v>297.9004465638477</v>
       </c>
       <c r="E134" t="n">
-        <v>308.8868058363209</v>
+        <v>300.6270751953125</v>
       </c>
       <c r="F134" t="n">
-        <v>20009800</v>
+        <v>44364100</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3919,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B135" t="n">
-        <v>306.7494812011719</v>
+        <v>301.7356863586682</v>
       </c>
       <c r="C135" t="n">
-        <v>307.6783216475022</v>
+        <v>305.6009172273957</v>
       </c>
       <c r="D135" t="n">
-        <v>301.9754046785898</v>
+        <v>300.5571556341351</v>
       </c>
       <c r="E135" t="n">
-        <v>303.6333516523425</v>
+        <v>301.6857604980469</v>
       </c>
       <c r="F135" t="n">
-        <v>25075800</v>
+        <v>29326900</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3945,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B136" t="n">
-        <v>300.6270751953125</v>
+        <v>298.8293264668504</v>
       </c>
       <c r="C136" t="n">
-        <v>305.620880431115</v>
+        <v>299.5484356615691</v>
       </c>
       <c r="D136" t="n">
-        <v>297.9004465638477</v>
+        <v>289.9702901097709</v>
       </c>
       <c r="E136" t="n">
-        <v>305.0815409313132</v>
+        <v>290.0801696777344</v>
       </c>
       <c r="F136" t="n">
-        <v>44364100</v>
+        <v>36864300</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3971,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B137" t="n">
-        <v>301.685791015625</v>
+        <v>293.0764495892524</v>
       </c>
       <c r="C137" t="n">
-        <v>305.6009481410186</v>
+        <v>295.6332754793409</v>
       </c>
       <c r="D137" t="n">
-        <v>300.5571860375472</v>
+        <v>288.8816409209488</v>
       </c>
       <c r="E137" t="n">
-        <v>301.7357168812967</v>
+        <v>290.5695495605469</v>
       </c>
       <c r="F137" t="n">
-        <v>29326900</v>
+        <v>29460700</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -3997,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B138" t="n">
-        <v>290.0801696777344</v>
+        <v>287.553321534765</v>
       </c>
       <c r="C138" t="n">
-        <v>299.5484356615691</v>
+        <v>287.5932805144313</v>
       </c>
       <c r="D138" t="n">
-        <v>289.9702901097709</v>
+        <v>278.1549756132059</v>
       </c>
       <c r="E138" t="n">
-        <v>298.8293264668504</v>
+        <v>280.5719909667969</v>
       </c>
       <c r="F138" t="n">
-        <v>36864300</v>
+        <v>39080600</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4023,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B139" t="n">
-        <v>290.5695495605469</v>
+        <v>276.9364513575891</v>
       </c>
       <c r="C139" t="n">
-        <v>295.6332754793409</v>
+        <v>279.0238582088365</v>
       </c>
       <c r="D139" t="n">
-        <v>288.8816409209488</v>
+        <v>273.6105906087015</v>
       </c>
       <c r="E139" t="n">
-        <v>293.0764495892524</v>
+        <v>274.0000915527344</v>
       </c>
       <c r="F139" t="n">
-        <v>29460700</v>
+        <v>35890600</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4049,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B140" t="n">
-        <v>280.5719604492188</v>
+        <v>276.0775591796553</v>
       </c>
       <c r="C140" t="n">
-        <v>287.5932492331535</v>
+        <v>276.7467120540596</v>
       </c>
       <c r="D140" t="n">
-        <v>278.1549453585245</v>
+        <v>271.772870758184</v>
       </c>
       <c r="E140" t="n">
-        <v>287.5532902578335</v>
+        <v>273.1611633300781</v>
       </c>
       <c r="F140" t="n">
-        <v>39080600</v>
+        <v>35141200</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4075,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B141" t="n">
-        <v>274.0001220703125</v>
+        <v>277.6955407888773</v>
       </c>
       <c r="C141" t="n">
-        <v>279.0238892859517</v>
+        <v>287.7230801433843</v>
       </c>
       <c r="D141" t="n">
-        <v>273.6106210828978</v>
+        <v>276.7467055656006</v>
       </c>
       <c r="E141" t="n">
-        <v>276.9364822022131</v>
+        <v>287.2037353515625</v>
       </c>
       <c r="F141" t="n">
-        <v>35890600</v>
+        <v>43875400</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4101,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B142" t="n">
-        <v>273.1611633300781</v>
+        <v>290.4796724840224</v>
       </c>
       <c r="C142" t="n">
-        <v>276.7467120540596</v>
+        <v>300.1476725442409</v>
       </c>
       <c r="D142" t="n">
-        <v>271.772870758184</v>
+        <v>290.0502125293938</v>
       </c>
       <c r="E142" t="n">
-        <v>276.0775591796553</v>
+        <v>297.0215759277344</v>
       </c>
       <c r="F142" t="n">
-        <v>35141200</v>
+        <v>37684500</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4127,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B143" t="n">
-        <v>287.2037353515625</v>
+        <v>290.3298413990028</v>
       </c>
       <c r="C143" t="n">
-        <v>287.7230801433843</v>
+        <v>297.7106694379238</v>
       </c>
       <c r="D143" t="n">
-        <v>276.7467055656006</v>
+        <v>289.0913874960174</v>
       </c>
       <c r="E143" t="n">
-        <v>277.6955407888773</v>
+        <v>295.4035339355469</v>
       </c>
       <c r="F143" t="n">
-        <v>43875400</v>
+        <v>21666500</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4153,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B144" t="n">
-        <v>297.0215759277344</v>
+        <v>295.5034561131459</v>
       </c>
       <c r="C144" t="n">
-        <v>300.1476725442409</v>
+        <v>300.2475715682514</v>
       </c>
       <c r="D144" t="n">
-        <v>290.0502125293938</v>
+        <v>294.8143084823383</v>
       </c>
       <c r="E144" t="n">
-        <v>290.4796724840224</v>
+        <v>299.6183471679688</v>
       </c>
       <c r="F144" t="n">
-        <v>37684500</v>
+        <v>16945500</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4179,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B145" t="n">
-        <v>295.403564453125</v>
+        <v>302.3549447988444</v>
       </c>
       <c r="C145" t="n">
-        <v>297.7107001938477</v>
+        <v>305.2513457589993</v>
       </c>
       <c r="D145" t="n">
-        <v>289.0914173614996</v>
+        <v>297.3511421656273</v>
       </c>
       <c r="E145" t="n">
-        <v>290.3298713924274</v>
+        <v>305.08154296875</v>
       </c>
       <c r="F145" t="n">
-        <v>21666500</v>
+        <v>23205400</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4205,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B146" t="n">
-        <v>299.6183166503906</v>
+        <v>320.0530070056894</v>
       </c>
       <c r="C146" t="n">
-        <v>300.2475409865838</v>
+        <v>321.6809619973042</v>
       </c>
       <c r="D146" t="n">
-        <v>294.8142784540748</v>
+        <v>314.6297110626625</v>
       </c>
       <c r="E146" t="n">
-        <v>295.5034260146894</v>
+        <v>316.9268798828125</v>
       </c>
       <c r="F146" t="n">
-        <v>16945500</v>
+        <v>33547100</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4231,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B147" t="n">
-        <v>305.08154296875</v>
+        <v>315.5186078441214</v>
       </c>
       <c r="C147" t="n">
-        <v>305.2513457589993</v>
+        <v>319.1441153425082</v>
       </c>
       <c r="D147" t="n">
-        <v>297.3511421656273</v>
+        <v>310.6746106421415</v>
       </c>
       <c r="E147" t="n">
-        <v>302.3549447988444</v>
+        <v>318.0953979492188</v>
       </c>
       <c r="F147" t="n">
-        <v>23205400</v>
+        <v>23739200</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4257,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B148" t="n">
-        <v>316.9268798828125</v>
+        <v>319.6235089208506</v>
       </c>
       <c r="C148" t="n">
-        <v>321.6809619973042</v>
+        <v>321.4312640320202</v>
       </c>
       <c r="D148" t="n">
-        <v>314.6297110626625</v>
+        <v>315.9281112234418</v>
       </c>
       <c r="E148" t="n">
-        <v>320.0530070056894</v>
+        <v>316.8469543457031</v>
       </c>
       <c r="F148" t="n">
-        <v>33547100</v>
+        <v>19152600</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4283,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B149" t="n">
-        <v>318.0953979492188</v>
+        <v>316.7471095555252</v>
       </c>
       <c r="C149" t="n">
-        <v>319.1441153425082</v>
+        <v>321.2315371363443</v>
       </c>
       <c r="D149" t="n">
-        <v>310.6746106421415</v>
+        <v>315.0791651091577</v>
       </c>
       <c r="E149" t="n">
-        <v>315.5186078441214</v>
+        <v>320.9119262695312</v>
       </c>
       <c r="F149" t="n">
-        <v>23739200</v>
+        <v>18866400</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4309,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B150" t="n">
-        <v>316.8469543457031</v>
+        <v>324.3876234083889</v>
       </c>
       <c r="C150" t="n">
-        <v>321.4312640320202</v>
+        <v>332.8770926852431</v>
       </c>
       <c r="D150" t="n">
-        <v>315.9281112234418</v>
+        <v>323.3489033390031</v>
       </c>
       <c r="E150" t="n">
-        <v>319.6235089208506</v>
+        <v>332.49755859375</v>
       </c>
       <c r="F150" t="n">
-        <v>19152600</v>
+        <v>27721400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4335,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B151" t="n">
-        <v>320.9119262695312</v>
+        <v>332.4775916674409</v>
       </c>
       <c r="C151" t="n">
-        <v>321.2315371363443</v>
+        <v>337.0619013824557</v>
       </c>
       <c r="D151" t="n">
-        <v>315.0791651091577</v>
+        <v>330.4900363853266</v>
       </c>
       <c r="E151" t="n">
-        <v>316.7471095555252</v>
+        <v>336.7023315429688</v>
       </c>
       <c r="F151" t="n">
-        <v>18866400</v>
+        <v>24918800</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4361,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B152" t="n">
-        <v>332.49755859375</v>
+        <v>338.3302967803236</v>
       </c>
       <c r="C152" t="n">
-        <v>332.8770926852431</v>
+        <v>339.458901613874</v>
       </c>
       <c r="D152" t="n">
-        <v>323.3489033390031</v>
+        <v>334.105526677332</v>
       </c>
       <c r="E152" t="n">
-        <v>324.3876234083889</v>
+        <v>335.6036682128906</v>
       </c>
       <c r="F152" t="n">
-        <v>27721400</v>
+        <v>20541500</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4387,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B153" t="n">
-        <v>336.7023315429688</v>
+        <v>337.2316773591919</v>
       </c>
       <c r="C153" t="n">
-        <v>337.0619013824557</v>
+        <v>341.895905080184</v>
       </c>
       <c r="D153" t="n">
-        <v>330.4900363853266</v>
+        <v>335.8234205588037</v>
       </c>
       <c r="E153" t="n">
-        <v>332.4775916674409</v>
+        <v>341.2566833496094</v>
       </c>
       <c r="F153" t="n">
-        <v>24918800</v>
+        <v>25581900</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4413,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B154" t="n">
-        <v>335.6036682128906</v>
+        <v>340.3378420577138</v>
       </c>
       <c r="C154" t="n">
-        <v>339.458901613874</v>
+        <v>340.9770333119858</v>
       </c>
       <c r="D154" t="n">
-        <v>334.105526677332</v>
+        <v>336.1929591105031</v>
       </c>
       <c r="E154" t="n">
-        <v>338.3302967803236</v>
+        <v>337.0019836425781</v>
       </c>
       <c r="F154" t="n">
-        <v>20541500</v>
+        <v>18784200</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4439,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B155" t="n">
-        <v>341.2566833496094</v>
+        <v>337.2716301294484</v>
       </c>
       <c r="C155" t="n">
-        <v>341.895905080184</v>
+        <v>338.9195798085849</v>
       </c>
       <c r="D155" t="n">
-        <v>335.8234205588037</v>
+        <v>330.9394885663705</v>
       </c>
       <c r="E155" t="n">
-        <v>337.2316773591919</v>
+        <v>331.8783264160156</v>
       </c>
       <c r="F155" t="n">
-        <v>25581900</v>
+        <v>23123800</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4465,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B156" t="n">
-        <v>337.0019836425781</v>
+        <v>336.6024588411248</v>
       </c>
       <c r="C156" t="n">
-        <v>340.9770333119858</v>
+        <v>339.3990082413208</v>
       </c>
       <c r="D156" t="n">
-        <v>336.1929591105031</v>
+        <v>334.7547751685775</v>
       </c>
       <c r="E156" t="n">
-        <v>340.3378420577138</v>
+        <v>338.8996276855469</v>
       </c>
       <c r="F156" t="n">
-        <v>18784200</v>
+        <v>20293000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4491,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B157" t="n">
-        <v>331.8783264160156</v>
+        <v>340.7572947145818</v>
       </c>
       <c r="C157" t="n">
-        <v>338.9195798085849</v>
+        <v>341.5363271303731</v>
       </c>
       <c r="D157" t="n">
-        <v>330.9394885663705</v>
+        <v>335.7634893621326</v>
       </c>
       <c r="E157" t="n">
-        <v>337.2716301294484</v>
+        <v>338.4701538085938</v>
       </c>
       <c r="F157" t="n">
-        <v>23123800</v>
+        <v>18650300</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4517,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B158" t="n">
-        <v>338.8996276855469</v>
+        <v>338.3103690890599</v>
       </c>
       <c r="C158" t="n">
-        <v>339.3990082413208</v>
+        <v>344.8422449444718</v>
       </c>
       <c r="D158" t="n">
-        <v>334.7547751685775</v>
+        <v>334.9745105669949</v>
       </c>
       <c r="E158" t="n">
-        <v>336.6024588411248</v>
+        <v>343.9733276367188</v>
       </c>
       <c r="F158" t="n">
-        <v>20293000</v>
+        <v>26426100</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4543,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B159" t="n">
-        <v>338.4701538085938</v>
+        <v>345.5513913866066</v>
       </c>
       <c r="C159" t="n">
-        <v>341.5363271303731</v>
+        <v>352.7424533316474</v>
       </c>
       <c r="D159" t="n">
-        <v>335.7634893621326</v>
+        <v>342.3054176703653</v>
       </c>
       <c r="E159" t="n">
-        <v>340.7572947145818</v>
+        <v>349.9059753417969</v>
       </c>
       <c r="F159" t="n">
-        <v>18650300</v>
+        <v>28576900</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4569,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B160" t="n">
-        <v>343.9732971191406</v>
+        <v>348.1181924796765</v>
       </c>
       <c r="C160" t="n">
-        <v>344.8422143498026</v>
+        <v>351.9834237980171</v>
       </c>
       <c r="D160" t="n">
-        <v>334.9744808477988</v>
+        <v>345.6912101596132</v>
       </c>
       <c r="E160" t="n">
-        <v>338.3103390739037</v>
+        <v>349.3466796875</v>
       </c>
       <c r="F160" t="n">
-        <v>26426100</v>
+        <v>27824100</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4595,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B161" t="n">
-        <v>349.9059448242188</v>
+        <v>347.1393804315599</v>
       </c>
       <c r="C161" t="n">
-        <v>352.7424225666816</v>
+        <v>355.3491973627422</v>
       </c>
       <c r="D161" t="n">
-        <v>342.3053878156813</v>
+        <v>343.7835275027263</v>
       </c>
       <c r="E161" t="n">
-        <v>345.55136124882</v>
+        <v>349.5064392089844</v>
       </c>
       <c r="F161" t="n">
-        <v>28576900</v>
+        <v>35376300</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4621,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B162" t="n">
-        <v>349.3466491699219</v>
+        <v>373.6065555628184</v>
       </c>
       <c r="C162" t="n">
-        <v>351.9833930501032</v>
+        <v>385.3619622201579</v>
       </c>
       <c r="D162" t="n">
-        <v>345.6911799613628</v>
+        <v>365.3667768501622</v>
       </c>
       <c r="E162" t="n">
-        <v>348.1181620694143</v>
+        <v>384.3232421875</v>
       </c>
       <c r="F162" t="n">
-        <v>27824100</v>
+        <v>72040000</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4647,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B163" t="n">
-        <v>349.5064697265625</v>
+        <v>381.1572209075714</v>
       </c>
       <c r="C163" t="n">
-        <v>355.3492283904879</v>
+        <v>386.2808704617397</v>
       </c>
       <c r="D163" t="n">
-        <v>343.7835575206014</v>
+        <v>378.5804000830116</v>
       </c>
       <c r="E163" t="n">
-        <v>347.1394107424554</v>
+        <v>385.2121887207031</v>
       </c>
       <c r="F163" t="n">
-        <v>35376300</v>
+        <v>30105200</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4673,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B164" t="n">
-        <v>384.3232421875</v>
+        <v>385.1522332062169</v>
       </c>
       <c r="C164" t="n">
-        <v>385.3619622201579</v>
+        <v>386.9000650646732</v>
       </c>
       <c r="D164" t="n">
-        <v>365.3667768501622</v>
+        <v>379.3194722618546</v>
       </c>
       <c r="E164" t="n">
-        <v>373.6065555628184</v>
+        <v>382.7751770019531</v>
       </c>
       <c r="F164" t="n">
-        <v>72040000</v>
+        <v>26298600</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4699,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B165" t="n">
-        <v>385.2121887207031</v>
+        <v>385.7515048868787</v>
       </c>
       <c r="C165" t="n">
-        <v>386.2808704617397</v>
+        <v>392.3333367803882</v>
       </c>
       <c r="D165" t="n">
-        <v>378.5804000830116</v>
+        <v>383.5442209432822</v>
       </c>
       <c r="E165" t="n">
-        <v>381.1572209075714</v>
+        <v>387.9487609863281</v>
       </c>
       <c r="F165" t="n">
-        <v>30105200</v>
+        <v>23878600</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4725,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B166" t="n">
-        <v>382.7751770019531</v>
+        <v>393.7615619135972</v>
       </c>
       <c r="C166" t="n">
-        <v>386.9000650646732</v>
+        <v>399.3546301445318</v>
       </c>
       <c r="D166" t="n">
-        <v>379.3194722618546</v>
+        <v>392.2734176347804</v>
       </c>
       <c r="E166" t="n">
-        <v>385.1522332062169</v>
+        <v>397.546875</v>
       </c>
       <c r="F166" t="n">
-        <v>26298600</v>
+        <v>31308500</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4751,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B167" t="n">
-        <v>387.9487609863281</v>
+        <v>399.4245497990884</v>
       </c>
       <c r="C167" t="n">
-        <v>392.3333367803882</v>
+        <v>399.6043194807176</v>
       </c>
       <c r="D167" t="n">
-        <v>383.5442209432822</v>
+        <v>392.1934987581594</v>
       </c>
       <c r="E167" t="n">
-        <v>385.7515048868787</v>
+        <v>397.4969177246094</v>
       </c>
       <c r="F167" t="n">
-        <v>23878600</v>
+        <v>24433500</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4777,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B168" t="n">
-        <v>397.546875</v>
+        <v>396.5081562950806</v>
       </c>
       <c r="C168" t="n">
-        <v>399.3546301445318</v>
+        <v>401.5019617899809</v>
       </c>
       <c r="D168" t="n">
-        <v>392.2734176347804</v>
+        <v>395.8689345614438</v>
       </c>
       <c r="E168" t="n">
-        <v>393.7615619135972</v>
+        <v>400.3034362792969</v>
       </c>
       <c r="F168" t="n">
-        <v>31308500</v>
+        <v>21461800</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4803,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B169" t="n">
-        <v>397.4969177246094</v>
+        <v>393.1623113356883</v>
       </c>
       <c r="C169" t="n">
-        <v>399.6043194807176</v>
+        <v>396.9476245393139</v>
       </c>
       <c r="D169" t="n">
-        <v>392.1934987581594</v>
+        <v>387.9887360157618</v>
       </c>
       <c r="E169" t="n">
-        <v>399.4245497990884</v>
+        <v>388.1585388183594</v>
       </c>
       <c r="F169" t="n">
-        <v>24433500</v>
+        <v>30753700</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4829,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B170" t="n">
-        <v>400.3034362792969</v>
+        <v>386.8601198229993</v>
       </c>
       <c r="C170" t="n">
-        <v>401.5019617899809</v>
+        <v>388.0386506028281</v>
       </c>
       <c r="D170" t="n">
-        <v>395.8689345614438</v>
+        <v>382.2957742925754</v>
       </c>
       <c r="E170" t="n">
-        <v>396.5081562950806</v>
+        <v>386.8701171875</v>
       </c>
       <c r="F170" t="n">
-        <v>21461800</v>
+        <v>26017500</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4855,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B171" t="n">
-        <v>388.1585083007812</v>
+        <v>385.1222825184223</v>
       </c>
       <c r="C171" t="n">
-        <v>396.9475933307253</v>
+        <v>403.1998643489371</v>
       </c>
       <c r="D171" t="n">
-        <v>387.9887055115338</v>
+        <v>384.5230197682841</v>
       </c>
       <c r="E171" t="n">
-        <v>393.1622804247065</v>
+        <v>402.1211853027344</v>
       </c>
       <c r="F171" t="n">
-        <v>30753700</v>
+        <v>28144600</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4881,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B172" t="n">
-        <v>386.8701171875</v>
+        <v>396.7878070287349</v>
       </c>
       <c r="C172" t="n">
-        <v>388.0386506028281</v>
+        <v>402.430801125594</v>
       </c>
       <c r="D172" t="n">
-        <v>382.2957742925754</v>
+        <v>395.349588612008</v>
       </c>
       <c r="E172" t="n">
-        <v>386.8601198229993</v>
+        <v>400.5731201171875</v>
       </c>
       <c r="F172" t="n">
-        <v>26017500</v>
+        <v>21136700</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4907,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B173" t="n">
-        <v>402.1211853027344</v>
+        <v>395.8290000666237</v>
       </c>
       <c r="C173" t="n">
-        <v>403.1998643489371</v>
+        <v>399.0450119758119</v>
       </c>
       <c r="D173" t="n">
-        <v>384.5230197682841</v>
+        <v>392.692875633045</v>
       </c>
       <c r="E173" t="n">
-        <v>385.1222825184223</v>
+        <v>396.2884216308594</v>
       </c>
       <c r="F173" t="n">
-        <v>28144600</v>
+        <v>20309700</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4933,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B174" t="n">
-        <v>400.5731201171875</v>
+        <v>395.1997907850553</v>
       </c>
       <c r="C174" t="n">
-        <v>402.430801125594</v>
+        <v>408.1037674120522</v>
       </c>
       <c r="D174" t="n">
-        <v>395.349588612008</v>
+        <v>394.0412242260142</v>
       </c>
       <c r="E174" t="n">
-        <v>396.7878070287349</v>
+        <v>396.4482421875</v>
       </c>
       <c r="F174" t="n">
-        <v>21136700</v>
+        <v>26837200</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4959,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B175" t="n">
-        <v>396.2884216308594</v>
+        <v>396.4681837278221</v>
       </c>
       <c r="C175" t="n">
-        <v>399.0450119758119</v>
+        <v>396.6579507685057</v>
       </c>
       <c r="D175" t="n">
-        <v>392.692875633045</v>
+        <v>385.6316200793582</v>
       </c>
       <c r="E175" t="n">
-        <v>395.8290000666237</v>
+        <v>387.1797180175781</v>
       </c>
       <c r="F175" t="n">
-        <v>20309700</v>
+        <v>39545700</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4985,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B176" t="n">
-        <v>396.4482421875</v>
+        <v>387.2196997137571</v>
       </c>
       <c r="C176" t="n">
-        <v>408.1037674120522</v>
+        <v>393.3720414113799</v>
       </c>
       <c r="D176" t="n">
-        <v>394.0412242260142</v>
+        <v>382.4256280338265</v>
       </c>
       <c r="E176" t="n">
-        <v>395.1997907850553</v>
+        <v>388.4281921386719</v>
       </c>
       <c r="F176" t="n">
-        <v>26837200</v>
+        <v>31744400</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5011,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B177" t="n">
+        <v>385.2221548650083</v>
+      </c>
+      <c r="C177" t="n">
+        <v>392.0137179133836</v>
+      </c>
+      <c r="D177" t="n">
+        <v>382.5454520468608</v>
+      </c>
+      <c r="E177" t="n">
         <v>387.1797180175781</v>
       </c>
-      <c r="C177" t="n">
-        <v>396.6579507685057</v>
-      </c>
-      <c r="D177" t="n">
-        <v>385.6316200793582</v>
-      </c>
-      <c r="E177" t="n">
-        <v>396.4681837278221</v>
-      </c>
       <c r="F177" t="n">
-        <v>39545700</v>
+        <v>24852800</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5037,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B178" t="n">
-        <v>388.4281921386719</v>
+        <v>386.8701229826527</v>
       </c>
       <c r="C178" t="n">
-        <v>393.3720414113799</v>
+        <v>388.258385079403</v>
       </c>
       <c r="D178" t="n">
-        <v>382.4256280338265</v>
+        <v>381.2970189068101</v>
       </c>
       <c r="E178" t="n">
-        <v>387.2196997137571</v>
+        <v>382.4955444335938</v>
       </c>
       <c r="F178" t="n">
-        <v>31744400</v>
+        <v>20442100</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5063,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B179" t="n">
-        <v>387.1797180175781</v>
+        <v>384.0336427193848</v>
       </c>
       <c r="C179" t="n">
-        <v>392.0137179133836</v>
+        <v>388.777757974093</v>
       </c>
       <c r="D179" t="n">
-        <v>382.5454520468608</v>
+        <v>382.1260053488666</v>
       </c>
       <c r="E179" t="n">
-        <v>385.2221548650083</v>
+        <v>388.3982238769531</v>
       </c>
       <c r="F179" t="n">
-        <v>24852800</v>
+        <v>27747400</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5089,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B180" t="n">
-        <v>382.4955444335938</v>
+        <v>386.1909694394293</v>
       </c>
       <c r="C180" t="n">
-        <v>388.258385079403</v>
+        <v>393.3920284639016</v>
       </c>
       <c r="D180" t="n">
-        <v>381.2970189068101</v>
+        <v>385.4219038824068</v>
       </c>
       <c r="E180" t="n">
-        <v>386.8701229826527</v>
+        <v>388.3482666015625</v>
       </c>
       <c r="F180" t="n">
-        <v>20442100</v>
+        <v>23087300</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5115,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B181" t="n">
-        <v>388.398193359375</v>
+        <v>387.5193014898567</v>
       </c>
       <c r="C181" t="n">
-        <v>388.7777274266938</v>
+        <v>391.384502017129</v>
       </c>
       <c r="D181" t="n">
-        <v>382.125975324115</v>
+        <v>384.682823662297</v>
       </c>
       <c r="E181" t="n">
-        <v>384.0336125447445</v>
+        <v>389.6466674804688</v>
       </c>
       <c r="F181" t="n">
-        <v>27747400</v>
+        <v>24357500</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5141,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B182" t="n">
-        <v>388.3482360839844</v>
+        <v>384.7626974671623</v>
       </c>
       <c r="C182" t="n">
-        <v>393.3919975499695</v>
+        <v>384.7626974671623</v>
       </c>
       <c r="D182" t="n">
-        <v>385.421873594791</v>
+        <v>377.9910987617443</v>
       </c>
       <c r="E182" t="n">
-        <v>386.1909390913781</v>
+        <v>379.8687744140625</v>
       </c>
       <c r="F182" t="n">
-        <v>23087300</v>
+        <v>44415800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5167,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B183" t="n">
-        <v>389.6466674804688</v>
+        <v>376.0535251127361</v>
       </c>
       <c r="C183" t="n">
-        <v>391.384502017129</v>
+        <v>378.0910063274455</v>
       </c>
       <c r="D183" t="n">
-        <v>384.682823662297</v>
+        <v>373.0572417592452</v>
       </c>
       <c r="E183" t="n">
-        <v>387.5193014898567</v>
+        <v>375.9037170410156</v>
       </c>
       <c r="F183" t="n">
-        <v>24357500</v>
+        <v>28672100</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5193,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B184" t="n">
-        <v>379.8687744140625</v>
+        <v>366.1358206463617</v>
       </c>
       <c r="C184" t="n">
-        <v>384.7626974671623</v>
+        <v>373.0772223440179</v>
       </c>
       <c r="D184" t="n">
-        <v>377.9910987617443</v>
+        <v>357.9959239406105</v>
       </c>
       <c r="E184" t="n">
-        <v>384.7626974671623</v>
+        <v>361.4017028808594</v>
       </c>
       <c r="F184" t="n">
-        <v>44415800</v>
+        <v>50412300</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5219,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B185" t="n">
-        <v>375.9037170410156</v>
+        <v>361.5814692403301</v>
       </c>
       <c r="C185" t="n">
-        <v>378.0910063274455</v>
+        <v>365.9960065843375</v>
       </c>
       <c r="D185" t="n">
-        <v>373.0572417592452</v>
+        <v>357.6363508187865</v>
       </c>
       <c r="E185" t="n">
-        <v>376.0535251127361</v>
+        <v>358.5452270507812</v>
       </c>
       <c r="F185" t="n">
-        <v>28672100</v>
+        <v>55441600</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5245,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B186" t="n">
-        <v>361.4017028808594</v>
+        <v>358.4553387971999</v>
       </c>
       <c r="C186" t="n">
-        <v>373.0772223440179</v>
+        <v>372.7875661225121</v>
       </c>
       <c r="D186" t="n">
-        <v>357.9959239406105</v>
+        <v>357.7661912265356</v>
       </c>
       <c r="E186" t="n">
-        <v>366.1358206463617</v>
+        <v>371.7288818359375</v>
       </c>
       <c r="F186" t="n">
-        <v>50412300</v>
+        <v>44055500</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5271,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B187" t="n">
-        <v>358.5452270507812</v>
+        <v>365.8861360555161</v>
       </c>
       <c r="C187" t="n">
-        <v>365.9960065843375</v>
+        <v>371.6190149899659</v>
       </c>
       <c r="D187" t="n">
-        <v>357.6363508187865</v>
+        <v>363.6688852043904</v>
       </c>
       <c r="E187" t="n">
-        <v>361.5814692403301</v>
+        <v>368.0734252929688</v>
       </c>
       <c r="F187" t="n">
-        <v>55441600</v>
+        <v>37471200</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5297,25 +5305,25 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B188" t="n">
-        <v>371.7289123535156</v>
+        <v>364.9454235864071</v>
       </c>
       <c r="C188" t="n">
-        <v>372.7875967270043</v>
+        <v>365.9647879200631</v>
       </c>
       <c r="D188" t="n">
-        <v>357.7662205978281</v>
+        <v>360.2984165590168</v>
       </c>
       <c r="E188" t="n">
-        <v>358.4553682250688</v>
+        <v>363.0766296386719</v>
       </c>
       <c r="F188" t="n">
-        <v>44055500</v>
+        <v>27942500</v>
       </c>
       <c r="G188" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5323,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B189" t="n">
-        <v>368.0734252929688</v>
+        <v>366.8542002567407</v>
       </c>
       <c r="C189" t="n">
-        <v>371.6190149899659</v>
+        <v>371.8409852276818</v>
       </c>
       <c r="D189" t="n">
-        <v>363.6688852043904</v>
+        <v>357.0704802123837</v>
       </c>
       <c r="E189" t="n">
-        <v>365.8861360555161</v>
+        <v>364.0260314941406</v>
       </c>
       <c r="F189" t="n">
-        <v>37471200</v>
+        <v>29535100</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5349,25 +5357,25 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B190" t="n">
-        <v>363.0766296386719</v>
+        <v>362.9567158453764</v>
       </c>
       <c r="C190" t="n">
-        <v>365.9647879200631</v>
+        <v>368.3232616719084</v>
       </c>
       <c r="D190" t="n">
-        <v>360.2984165590168</v>
+        <v>354.9718577941881</v>
       </c>
       <c r="E190" t="n">
-        <v>364.9454235864071</v>
+        <v>356.1510925292969</v>
       </c>
       <c r="F190" t="n">
-        <v>27942500</v>
+        <v>32357100</v>
       </c>
       <c r="G190" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5375,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B191" t="n">
-        <v>364.0260314941406</v>
+        <v>355.7013467902599</v>
       </c>
       <c r="C191" t="n">
-        <v>371.8409852276818</v>
+        <v>358.5694982511428</v>
       </c>
       <c r="D191" t="n">
-        <v>357.0704802123837</v>
+        <v>346.1374871435174</v>
       </c>
       <c r="E191" t="n">
-        <v>366.8542002567407</v>
+        <v>357.5401611328125</v>
       </c>
       <c r="F191" t="n">
-        <v>29535100</v>
+        <v>35538200</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5401,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B192" t="n">
-        <v>356.1510925292969</v>
+        <v>362.3870579560934</v>
       </c>
       <c r="C192" t="n">
-        <v>368.3232616719084</v>
+        <v>366.3345327833823</v>
       </c>
       <c r="D192" t="n">
-        <v>354.9718577941881</v>
+        <v>354.7119986974298</v>
       </c>
       <c r="E192" t="n">
-        <v>362.9567158453764</v>
+        <v>359.4489440917969</v>
       </c>
       <c r="F192" t="n">
-        <v>32357100</v>
+        <v>24704600</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5427,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B193" t="n">
-        <v>357.5401611328125</v>
+        <v>367.6936611370598</v>
       </c>
       <c r="C193" t="n">
-        <v>358.5694982511428</v>
+        <v>372.7504085202595</v>
       </c>
       <c r="D193" t="n">
-        <v>346.1374871435174</v>
+        <v>366.3145426692825</v>
       </c>
       <c r="E193" t="n">
-        <v>355.7013467902599</v>
+        <v>369.1127624511719</v>
       </c>
       <c r="F193" t="n">
-        <v>35538200</v>
+        <v>27727500</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5453,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B194" t="n">
-        <v>359.4489440917969</v>
+        <v>369.3626044753487</v>
       </c>
       <c r="C194" t="n">
-        <v>366.3345327833823</v>
+        <v>375.7584875251172</v>
       </c>
       <c r="D194" t="n">
-        <v>354.7119986974298</v>
+        <v>366.8242274297617</v>
       </c>
       <c r="E194" t="n">
-        <v>362.3870579560934</v>
+        <v>373.01025390625</v>
       </c>
       <c r="F194" t="n">
-        <v>24704600</v>
+        <v>24876100</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5479,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B195" t="n">
-        <v>369.1127624511719</v>
+        <v>368.8929017493238</v>
       </c>
       <c r="C195" t="n">
-        <v>372.7504085202595</v>
+        <v>372.0908279957741</v>
       </c>
       <c r="D195" t="n">
-        <v>366.3145426692825</v>
+        <v>361.7874528539307</v>
       </c>
       <c r="E195" t="n">
-        <v>367.6936611370598</v>
+        <v>363.5563354492188</v>
       </c>
       <c r="F195" t="n">
-        <v>27727500</v>
+        <v>24543600</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5505,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B196" t="n">
-        <v>373.01025390625</v>
+        <v>365.5150449761754</v>
       </c>
       <c r="C196" t="n">
-        <v>375.7584875251172</v>
+        <v>369.2426598317581</v>
       </c>
       <c r="D196" t="n">
-        <v>366.8242274297617</v>
+        <v>358.4396065335441</v>
       </c>
       <c r="E196" t="n">
-        <v>369.3626044753487</v>
+        <v>367.7935791015625</v>
       </c>
       <c r="F196" t="n">
-        <v>24876100</v>
+        <v>44470100</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5531,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B197" t="n">
-        <v>363.5563354492188</v>
+        <v>357.7200907639775</v>
       </c>
       <c r="C197" t="n">
-        <v>372.0908279957741</v>
+        <v>358.6894689253907</v>
       </c>
       <c r="D197" t="n">
-        <v>361.7874528539307</v>
+        <v>341.5005047739323</v>
       </c>
       <c r="E197" t="n">
-        <v>368.8929017493238</v>
+        <v>349.4553833007812</v>
       </c>
       <c r="F197" t="n">
-        <v>24543600</v>
+        <v>52814800</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5557,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B198" t="n">
-        <v>367.7935791015625</v>
+        <v>340.4711459801061</v>
       </c>
       <c r="C198" t="n">
-        <v>369.2426598317581</v>
+        <v>349.0656275102868</v>
       </c>
       <c r="D198" t="n">
-        <v>358.4396065335441</v>
+        <v>339.981470511436</v>
       </c>
       <c r="E198" t="n">
-        <v>365.5150449761754</v>
+        <v>345.9076538085938</v>
       </c>
       <c r="F198" t="n">
-        <v>44470100</v>
+        <v>34007700</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5583,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B199" t="n">
-        <v>349.4553833007812</v>
+        <v>348.8157979233392</v>
       </c>
       <c r="C199" t="n">
-        <v>358.6894689253907</v>
+        <v>353.2529482684732</v>
       </c>
       <c r="D199" t="n">
-        <v>341.5005047739323</v>
+        <v>341.7103492701006</v>
       </c>
       <c r="E199" t="n">
-        <v>357.7200907639775</v>
+        <v>345.0682067871094</v>
       </c>
       <c r="F199" t="n">
-        <v>52814800</v>
+        <v>44997300</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5609,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B200" t="n">
-        <v>345.9076538085938</v>
+        <v>336.5137001542092</v>
       </c>
       <c r="C200" t="n">
-        <v>349.0656275102868</v>
+        <v>345.3480177972958</v>
       </c>
       <c r="D200" t="n">
-        <v>339.981470511436</v>
+        <v>335.6242572392167</v>
       </c>
       <c r="E200" t="n">
-        <v>340.4711459801061</v>
+        <v>343.4891967773438</v>
       </c>
       <c r="F200" t="n">
-        <v>34007700</v>
+        <v>44491400</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5635,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B201" t="n">
-        <v>345.0682067871094</v>
+        <v>342.3299372399903</v>
       </c>
       <c r="C201" t="n">
-        <v>353.2529482684732</v>
+        <v>346.1374872957393</v>
       </c>
       <c r="D201" t="n">
-        <v>341.7103492701006</v>
+        <v>329.98789515005</v>
       </c>
       <c r="E201" t="n">
-        <v>348.8157979233392</v>
+        <v>337.1732788085938</v>
       </c>
       <c r="F201" t="n">
-        <v>44997300</v>
+        <v>114706300</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5661,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B202" t="n">
-        <v>343.4891967773438</v>
+        <v>341.6104064955248</v>
       </c>
       <c r="C202" t="n">
-        <v>345.3480177972958</v>
+        <v>354.122383587675</v>
       </c>
       <c r="D202" t="n">
-        <v>335.6242572392167</v>
+        <v>340.4511784786947</v>
       </c>
       <c r="E202" t="n">
-        <v>336.5137001542092</v>
+        <v>353.4228210449219</v>
       </c>
       <c r="F202" t="n">
-        <v>44491400</v>
+        <v>34213900</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5687,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B203" t="n">
-        <v>337.1732788085938</v>
+        <v>353.6426900862941</v>
       </c>
       <c r="C203" t="n">
-        <v>346.1374872957393</v>
+        <v>358.3896389689017</v>
       </c>
       <c r="D203" t="n">
-        <v>329.98789515005</v>
+        <v>350.1749177879227</v>
       </c>
       <c r="E203" t="n">
-        <v>342.3299372399903</v>
+        <v>357.1404418945312</v>
       </c>
       <c r="F203" t="n">
-        <v>114706300</v>
+        <v>35237200</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5713,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B204" t="n">
-        <v>353.4228210449219</v>
+        <v>358.1397942573561</v>
       </c>
       <c r="C204" t="n">
-        <v>354.122383587675</v>
+        <v>362.7368455226467</v>
       </c>
       <c r="D204" t="n">
-        <v>340.4511784786947</v>
+        <v>356.2010379867681</v>
       </c>
       <c r="E204" t="n">
-        <v>341.6104064955248</v>
+        <v>360.9779663085938</v>
       </c>
       <c r="F204" t="n">
-        <v>34213900</v>
+        <v>26736400</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5739,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B205" t="n">
-        <v>357.1404418945312</v>
+        <v>359.2490860357571</v>
       </c>
       <c r="C205" t="n">
-        <v>358.3896389689017</v>
+        <v>363.9760280309549</v>
       </c>
       <c r="D205" t="n">
-        <v>350.1749177879227</v>
+        <v>353.1929813351636</v>
       </c>
       <c r="E205" t="n">
-        <v>353.6426900862941</v>
+        <v>359.6788024902344</v>
       </c>
       <c r="F205" t="n">
-        <v>35237200</v>
+        <v>25974800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5765,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B206" t="n">
-        <v>360.9779663085938</v>
+        <v>361.3177293642356</v>
       </c>
       <c r="C206" t="n">
-        <v>362.7368455226467</v>
+        <v>367.693635754559</v>
       </c>
       <c r="D206" t="n">
-        <v>356.2010379867681</v>
+        <v>357.1504252362982</v>
       </c>
       <c r="E206" t="n">
-        <v>358.1397942573561</v>
+        <v>366.2245788574219</v>
       </c>
       <c r="F206" t="n">
-        <v>26736400</v>
+        <v>26915800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5791,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B207" t="n">
-        <v>359.6788024902344</v>
+        <v>368.8329180211536</v>
       </c>
       <c r="C207" t="n">
-        <v>363.9760280309549</v>
+        <v>372.9202869594668</v>
       </c>
       <c r="D207" t="n">
-        <v>353.1929813351636</v>
+        <v>365.2652040573587</v>
       </c>
       <c r="E207" t="n">
-        <v>359.2490860357571</v>
+        <v>366.7942199707031</v>
       </c>
       <c r="F207" t="n">
-        <v>25974800</v>
+        <v>24045600</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5817,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B208" t="n">
-        <v>366.2245788574219</v>
+        <v>364.525702555654</v>
       </c>
       <c r="C208" t="n">
-        <v>367.693635754559</v>
+        <v>367.6037106679975</v>
       </c>
       <c r="D208" t="n">
-        <v>357.1504252362982</v>
+        <v>357.7900113228786</v>
       </c>
       <c r="E208" t="n">
-        <v>361.3177293642356</v>
+        <v>361.6875305175781</v>
       </c>
       <c r="F208" t="n">
-        <v>26915800</v>
+        <v>22094800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5843,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B209" t="n">
-        <v>366.7942199707031</v>
+        <v>354.0824097063769</v>
       </c>
       <c r="C209" t="n">
-        <v>372.9202869594668</v>
+        <v>359.4189759454678</v>
       </c>
       <c r="D209" t="n">
-        <v>365.2652040573587</v>
+        <v>350.8544734886641</v>
       </c>
       <c r="E209" t="n">
-        <v>368.8329180211536</v>
+        <v>358.6594848632812</v>
       </c>
       <c r="F209" t="n">
-        <v>24045600</v>
+        <v>24729100</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5869,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B210" t="n">
-        <v>361.6875305175781</v>
+        <v>357.3003428038799</v>
       </c>
       <c r="C210" t="n">
-        <v>367.6037106679975</v>
+        <v>357.5901650645865</v>
       </c>
       <c r="D210" t="n">
-        <v>357.7900113228786</v>
+        <v>352.5234144110846</v>
       </c>
       <c r="E210" t="n">
-        <v>364.525702555654</v>
+        <v>356.9505615234375</v>
       </c>
       <c r="F210" t="n">
-        <v>22094800</v>
+        <v>18146100</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5895,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B211" t="n">
-        <v>358.6594848632812</v>
+        <v>355.9611981097028</v>
       </c>
       <c r="C211" t="n">
-        <v>359.4189759454678</v>
+        <v>357.8999543595846</v>
       </c>
       <c r="D211" t="n">
-        <v>350.8544734886641</v>
+        <v>351.5240477747128</v>
       </c>
       <c r="E211" t="n">
-        <v>354.0824097063769</v>
+        <v>352.2835693359375</v>
       </c>
       <c r="F211" t="n">
-        <v>24729100</v>
+        <v>15901700</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5921,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B212" t="n">
-        <v>356.9505615234375</v>
+        <v>350.9744235107016</v>
       </c>
       <c r="C212" t="n">
-        <v>357.5901650645865</v>
+        <v>359.92865963343</v>
       </c>
       <c r="D212" t="n">
-        <v>352.5234144110846</v>
+        <v>350.8644783088037</v>
       </c>
       <c r="E212" t="n">
-        <v>357.3003428038799</v>
+        <v>359.2790832519531</v>
       </c>
       <c r="F212" t="n">
-        <v>18146100</v>
+        <v>18259400</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5947,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B213" t="n">
-        <v>352.2835693359375</v>
+        <v>357.7400685886304</v>
       </c>
       <c r="C213" t="n">
-        <v>357.8999543595846</v>
+        <v>373.4099896327818</v>
       </c>
       <c r="D213" t="n">
-        <v>351.5240477747128</v>
+        <v>357.5302120160503</v>
       </c>
       <c r="E213" t="n">
-        <v>355.9611981097028</v>
+        <v>370.6817626953125</v>
       </c>
       <c r="F213" t="n">
-        <v>15901700</v>
+        <v>28284600</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5973,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B214" t="n">
-        <v>359.2790832519531</v>
+        <v>372.8203579699616</v>
       </c>
       <c r="C214" t="n">
-        <v>359.92865963343</v>
+        <v>375.0289298103755</v>
       </c>
       <c r="D214" t="n">
-        <v>350.8644783088037</v>
+        <v>352.0736836469807</v>
       </c>
       <c r="E214" t="n">
-        <v>350.9744235107016</v>
+        <v>354.2322998046875</v>
       </c>
       <c r="F214" t="n">
-        <v>18259400</v>
+        <v>41158500</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -5999,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B215" t="n">
-        <v>370.6817626953125</v>
+        <v>345.7777467999313</v>
       </c>
       <c r="C215" t="n">
-        <v>373.4099896327818</v>
+        <v>348.2961170979314</v>
       </c>
       <c r="D215" t="n">
-        <v>357.5302120160503</v>
+        <v>341.1407126662452</v>
       </c>
       <c r="E215" t="n">
-        <v>357.7400685886304</v>
+        <v>346.5472412109375</v>
       </c>
       <c r="F215" t="n">
-        <v>28284600</v>
+        <v>29959300</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6025,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B216" t="n">
-        <v>354.2322998046875</v>
+        <v>350.6546131580819</v>
       </c>
       <c r="C216" t="n">
-        <v>375.0289298103755</v>
+        <v>359.4489481797366</v>
       </c>
       <c r="D216" t="n">
-        <v>352.0736836469807</v>
+        <v>350.2948285491913</v>
       </c>
       <c r="E216" t="n">
-        <v>372.8203579699616</v>
+        <v>351.7638854980469</v>
       </c>
       <c r="F216" t="n">
-        <v>41158500</v>
+        <v>24736600</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6051,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B217" t="n">
-        <v>346.5472412109375</v>
+        <v>351.094336770995</v>
       </c>
       <c r="C217" t="n">
-        <v>348.2961170979314</v>
+        <v>351.094336770995</v>
       </c>
       <c r="D217" t="n">
-        <v>341.1407126662452</v>
+        <v>346.7771044052826</v>
       </c>
       <c r="E217" t="n">
-        <v>345.7777467999313</v>
+        <v>346.927001953125</v>
       </c>
       <c r="F217" t="n">
-        <v>29959300</v>
+        <v>23369800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6077,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B218" t="n">
-        <v>351.7638854980469</v>
+        <v>347.9363472365376</v>
       </c>
       <c r="C218" t="n">
-        <v>359.4489481797366</v>
+        <v>349.7152025525983</v>
       </c>
       <c r="D218" t="n">
-        <v>350.2948285491913</v>
+        <v>341.5104851592261</v>
       </c>
       <c r="E218" t="n">
-        <v>350.6546131580819</v>
+        <v>341.8702392578125</v>
       </c>
       <c r="F218" t="n">
-        <v>24736600</v>
+        <v>39334100</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6103,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B219" t="n">
-        <v>346.927001953125</v>
+        <v>320.9237241212255</v>
       </c>
       <c r="C219" t="n">
-        <v>351.094336770995</v>
+        <v>324.2815511558238</v>
       </c>
       <c r="D219" t="n">
-        <v>346.7771044052826</v>
+        <v>314.6977150387725</v>
       </c>
       <c r="E219" t="n">
-        <v>351.094336770995</v>
+        <v>317.4859313964844</v>
       </c>
       <c r="F219" t="n">
-        <v>23369800</v>
+        <v>69419700</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6129,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B220" t="n">
-        <v>341.8702392578125</v>
+        <v>318.2154780071113</v>
       </c>
       <c r="C220" t="n">
-        <v>349.7152025525983</v>
+        <v>323.9717573627877</v>
       </c>
       <c r="D220" t="n">
-        <v>341.5104851592261</v>
+        <v>317.1161784867298</v>
       </c>
       <c r="E220" t="n">
-        <v>347.9363472365376</v>
+        <v>319.5346069335938</v>
       </c>
       <c r="F220" t="n">
-        <v>39334100</v>
+        <v>31806600</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6155,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B221" t="n">
-        <v>317.4859313964844</v>
+        <v>324.83120713377</v>
       </c>
       <c r="C221" t="n">
-        <v>324.2815511558238</v>
+        <v>330.2077559724587</v>
       </c>
       <c r="D221" t="n">
-        <v>314.6977150387725</v>
+        <v>324.2415898017393</v>
       </c>
       <c r="E221" t="n">
-        <v>320.9237241212255</v>
+        <v>326.3502197265625</v>
       </c>
       <c r="F221" t="n">
-        <v>69419700</v>
+        <v>28471600</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6181,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B222" t="n">
-        <v>319.5346069335938</v>
+        <v>327.6893704249235</v>
       </c>
       <c r="C222" t="n">
-        <v>323.9717573627877</v>
+        <v>335.6642555263833</v>
       </c>
       <c r="D222" t="n">
-        <v>317.1161784867298</v>
+        <v>324.2316014627561</v>
       </c>
       <c r="E222" t="n">
-        <v>318.2154780071113</v>
+        <v>333.4956359863281</v>
       </c>
       <c r="F222" t="n">
-        <v>31806600</v>
+        <v>29511900</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6207,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B223" t="n">
-        <v>326.3502197265625</v>
+        <v>334.455045685483</v>
       </c>
       <c r="C223" t="n">
-        <v>330.2077559724587</v>
+        <v>342.2800028423013</v>
       </c>
       <c r="D223" t="n">
-        <v>324.2415898017393</v>
+        <v>331.4069864854741</v>
       </c>
       <c r="E223" t="n">
-        <v>324.83120713377</v>
+        <v>336.4937133789062</v>
       </c>
       <c r="F223" t="n">
-        <v>28471600</v>
+        <v>27501600</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6233,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B224" t="n">
-        <v>333.4956359863281</v>
+        <v>333.9853403838827</v>
       </c>
       <c r="C224" t="n">
-        <v>335.6642555263833</v>
+        <v>336.2938541262907</v>
       </c>
       <c r="D224" t="n">
-        <v>324.2316014627561</v>
+        <v>330.1278039779788</v>
       </c>
       <c r="E224" t="n">
-        <v>327.6893704249235</v>
+        <v>333.4456787109375</v>
       </c>
       <c r="F224" t="n">
-        <v>29511900</v>
+        <v>30168000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6259,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B225" t="n">
-        <v>336.4937133789062</v>
+        <v>340.611054758666</v>
       </c>
       <c r="C225" t="n">
-        <v>342.2800028423013</v>
+        <v>358.3496530632621</v>
       </c>
       <c r="D225" t="n">
-        <v>331.4069864854741</v>
+        <v>339.7816013274756</v>
       </c>
       <c r="E225" t="n">
-        <v>334.455045685483</v>
+        <v>355.9012451171875</v>
       </c>
       <c r="F225" t="n">
-        <v>27501600</v>
+        <v>46498000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6285,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B226" t="n">
-        <v>333.4456787109375</v>
+        <v>365.2152604560987</v>
       </c>
       <c r="C226" t="n">
-        <v>336.2938541262907</v>
+        <v>376.4480305309448</v>
       </c>
       <c r="D226" t="n">
-        <v>330.1278039779788</v>
+        <v>363.1166033198653</v>
       </c>
       <c r="E226" t="n">
-        <v>333.9853403838827</v>
+        <v>373.2700805664062</v>
       </c>
       <c r="F226" t="n">
-        <v>30168000</v>
+        <v>38669700</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6311,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B227" t="n">
-        <v>355.9012451171875</v>
+        <v>367.9834743668337</v>
       </c>
       <c r="C227" t="n">
-        <v>358.3496530632621</v>
+        <v>380.2755612380555</v>
       </c>
       <c r="D227" t="n">
-        <v>339.7816013274756</v>
+        <v>367.263935640354</v>
       </c>
       <c r="E227" t="n">
-        <v>340.611054758666</v>
+        <v>377.4074096679688</v>
       </c>
       <c r="F227" t="n">
-        <v>46498000</v>
+        <v>35705700</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6337,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B228" t="n">
-        <v>373.2700805664062</v>
+        <v>383.0937455186354</v>
       </c>
       <c r="C228" t="n">
-        <v>376.4480305309448</v>
+        <v>384.2330278418686</v>
       </c>
       <c r="D228" t="n">
-        <v>363.1166033198653</v>
+        <v>356.5408062961898</v>
       </c>
       <c r="E228" t="n">
-        <v>365.2152604560987</v>
+        <v>362.1971740722656</v>
       </c>
       <c r="F228" t="n">
-        <v>38669700</v>
+        <v>46926300</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6363,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B229" t="n">
-        <v>377.4074096679688</v>
+        <v>360.5382517887205</v>
       </c>
       <c r="C229" t="n">
-        <v>380.2755612380555</v>
+        <v>363.8961093831237</v>
       </c>
       <c r="D229" t="n">
-        <v>367.263935640354</v>
+        <v>356.6507663527499</v>
       </c>
       <c r="E229" t="n">
-        <v>367.9834743668337</v>
+        <v>357.5202026367188</v>
       </c>
       <c r="F229" t="n">
-        <v>35705700</v>
+        <v>25235900</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6389,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B230" t="n">
-        <v>362.1971740722656</v>
+        <v>356.4908465215469</v>
       </c>
       <c r="C230" t="n">
-        <v>384.2330278418686</v>
+        <v>358.6694387836589</v>
       </c>
       <c r="D230" t="n">
-        <v>356.5408062961898</v>
+        <v>353.5527327193329</v>
       </c>
       <c r="E230" t="n">
-        <v>383.0937455186354</v>
+        <v>354.0723876953125</v>
       </c>
       <c r="F230" t="n">
-        <v>46926300</v>
+        <v>19859900</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6415,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B231" t="n">
-        <v>357.5202026367188</v>
+        <v>354.951850943437</v>
       </c>
       <c r="C231" t="n">
-        <v>363.8961093831237</v>
+        <v>357.3802827690857</v>
       </c>
       <c r="D231" t="n">
-        <v>356.6507663527499</v>
+        <v>352.4834362714388</v>
       </c>
       <c r="E231" t="n">
-        <v>360.5382517887205</v>
+        <v>357.2903442382812</v>
       </c>
       <c r="F231" t="n">
-        <v>25235900</v>
+        <v>18991400</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6441,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B232" t="n">
-        <v>354.0723876953125</v>
+        <v>355.6613923515014</v>
       </c>
       <c r="C232" t="n">
-        <v>358.6694387836589</v>
+        <v>356.5807842683805</v>
       </c>
       <c r="D232" t="n">
-        <v>353.5527327193329</v>
+        <v>343.1694223006263</v>
       </c>
       <c r="E232" t="n">
-        <v>356.4908465215469</v>
+        <v>343.5791320800781</v>
       </c>
       <c r="F232" t="n">
-        <v>19859900</v>
+        <v>29081800</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6467,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B233" t="n">
-        <v>357.2903442382812</v>
+        <v>346.0875456512855</v>
       </c>
       <c r="C233" t="n">
-        <v>357.3802827690857</v>
+        <v>346.2574498710514</v>
       </c>
       <c r="D233" t="n">
-        <v>352.4834362714388</v>
+        <v>340.661040926288</v>
       </c>
       <c r="E233" t="n">
-        <v>354.951850943437</v>
+        <v>343.3193359375</v>
       </c>
       <c r="F233" t="n">
-        <v>18991400</v>
+        <v>25012000</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6493,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B234" t="n">
-        <v>343.5791320800781</v>
+        <v>345.5478948342235</v>
       </c>
       <c r="C234" t="n">
-        <v>356.5807842683805</v>
+        <v>347.7065110877775</v>
       </c>
       <c r="D234" t="n">
-        <v>343.1694223006263</v>
+        <v>343.5392066313974</v>
       </c>
       <c r="E234" t="n">
-        <v>355.6613923515014</v>
+        <v>346.1375122070312</v>
       </c>
       <c r="F234" t="n">
-        <v>29081800</v>
+        <v>17866100</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6519,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B235" t="n">
-        <v>343.3193359375</v>
+        <v>346.5772111705174</v>
       </c>
       <c r="C235" t="n">
-        <v>346.2574498710514</v>
+        <v>350.2248908898295</v>
       </c>
       <c r="D235" t="n">
-        <v>340.661040926288</v>
+        <v>344.2787008387085</v>
       </c>
       <c r="E235" t="n">
-        <v>346.0875456512855</v>
+        <v>345.6777954101562</v>
       </c>
       <c r="F235" t="n">
-        <v>25012000</v>
+        <v>17808600</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6545,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B236" t="n">
-        <v>346.1375122070312</v>
+        <v>346.0475530411078</v>
       </c>
       <c r="C236" t="n">
-        <v>347.7065110877775</v>
+        <v>347.0269344906474</v>
       </c>
       <c r="D236" t="n">
-        <v>343.5392066313974</v>
+        <v>341.7103446182459</v>
       </c>
       <c r="E236" t="n">
-        <v>345.5478948342235</v>
+        <v>343.7790222167969</v>
       </c>
       <c r="F236" t="n">
-        <v>17866100</v>
+        <v>18291300</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6571,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B237" t="n">
-        <v>345.6777954101562</v>
+        <v>342.1900536360575</v>
       </c>
       <c r="C237" t="n">
-        <v>350.2248908898295</v>
+        <v>344.6484648943574</v>
       </c>
       <c r="D237" t="n">
-        <v>344.2787008387085</v>
+        <v>339.9714784523309</v>
       </c>
       <c r="E237" t="n">
-        <v>346.5772111705174</v>
+        <v>343.9789123535156</v>
       </c>
       <c r="F237" t="n">
-        <v>17808600</v>
+        <v>19248800</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6597,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B238" t="n">
-        <v>343.7790222167969</v>
+        <v>342.2400076559886</v>
       </c>
       <c r="C238" t="n">
-        <v>347.0269344906474</v>
+        <v>346.5072842825429</v>
       </c>
       <c r="D238" t="n">
-        <v>341.7103446182459</v>
+        <v>340.4411761094805</v>
       </c>
       <c r="E238" t="n">
-        <v>346.0475530411078</v>
+        <v>344.4985656738281</v>
       </c>
       <c r="F238" t="n">
-        <v>18291300</v>
+        <v>19733800</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6623,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B239" t="n">
-        <v>343.9789123535156</v>
+        <v>342.8396207141765</v>
       </c>
       <c r="C239" t="n">
-        <v>344.6484648943574</v>
+        <v>343.6790774504127</v>
       </c>
       <c r="D239" t="n">
-        <v>339.9714784523309</v>
+        <v>338.3525147854226</v>
       </c>
       <c r="E239" t="n">
-        <v>342.1900536360575</v>
+        <v>340.451171875</v>
       </c>
       <c r="F239" t="n">
-        <v>19248800</v>
+        <v>18570400</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6649,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B240" t="n">
-        <v>344.4985656738281</v>
+        <v>342.359928876986</v>
       </c>
       <c r="C240" t="n">
-        <v>346.5072842825429</v>
+        <v>345.9776291730591</v>
       </c>
       <c r="D240" t="n">
-        <v>340.4411761094805</v>
+        <v>340.1813365286692</v>
       </c>
       <c r="E240" t="n">
-        <v>342.2400076559886</v>
+        <v>344.5985107421875</v>
       </c>
       <c r="F240" t="n">
-        <v>19733800</v>
+        <v>20849800</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6675,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B241" t="n">
-        <v>340.451171875</v>
+        <v>343.3992753172161</v>
       </c>
       <c r="C241" t="n">
-        <v>343.6790774504127</v>
+        <v>351.3741604480826</v>
       </c>
       <c r="D241" t="n">
-        <v>338.3525147854226</v>
+        <v>342.2699962782288</v>
       </c>
       <c r="E241" t="n">
-        <v>342.8396207141765</v>
+        <v>347.83642578125</v>
       </c>
       <c r="F241" t="n">
-        <v>18570400</v>
+        <v>26338200</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6701,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B242" t="n">
-        <v>344.5985107421875</v>
+        <v>349.4154232615459</v>
       </c>
       <c r="C242" t="n">
-        <v>345.9776291730591</v>
+        <v>349.9350782600912</v>
       </c>
       <c r="D242" t="n">
-        <v>340.1813365286692</v>
+        <v>345.3780098175396</v>
       </c>
       <c r="E242" t="n">
-        <v>342.359928876986</v>
+        <v>346.7371215820312</v>
       </c>
       <c r="F242" t="n">
-        <v>20849800</v>
+        <v>20649700</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6727,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B243" t="n">
-        <v>347.83642578125</v>
+        <v>346.3973312516375</v>
       </c>
       <c r="C243" t="n">
-        <v>351.3741604480826</v>
+        <v>346.6571739906042</v>
       </c>
       <c r="D243" t="n">
-        <v>342.2699962782288</v>
+        <v>339.9614657782595</v>
       </c>
       <c r="E243" t="n">
-        <v>343.3992753172161</v>
+        <v>341.7803039550781</v>
       </c>
       <c r="F243" t="n">
-        <v>26338200</v>
+        <v>20420300</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6753,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B244" t="n">
-        <v>346.7371215820312</v>
+        <v>339.4518318672431</v>
       </c>
       <c r="C244" t="n">
-        <v>349.9350782600912</v>
+        <v>341.4705233735174</v>
       </c>
       <c r="D244" t="n">
-        <v>345.3780098175396</v>
+        <v>338.3025461528343</v>
       </c>
       <c r="E244" t="n">
-        <v>349.4154232615459</v>
+        <v>340.4311828613281</v>
       </c>
       <c r="F244" t="n">
-        <v>20649700</v>
+        <v>23391400</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6779,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B245" t="n">
-        <v>341.7803039550781</v>
+        <v>340.4911426360338</v>
       </c>
       <c r="C245" t="n">
-        <v>346.6571739906042</v>
+        <v>348.9157509584863</v>
       </c>
       <c r="D245" t="n">
-        <v>339.9614657782595</v>
+        <v>340.0514228221321</v>
       </c>
       <c r="E245" t="n">
-        <v>346.3973312516375</v>
+        <v>346.3673706054688</v>
       </c>
       <c r="F245" t="n">
-        <v>20420300</v>
+        <v>25347200</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6805,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B246" t="n">
-        <v>340.4311828613281</v>
+        <v>343.609121722545</v>
       </c>
       <c r="C246" t="n">
-        <v>341.4705233735174</v>
+        <v>344.3686432833908</v>
       </c>
       <c r="D246" t="n">
-        <v>338.3025461528343</v>
+        <v>336.943423385668</v>
       </c>
       <c r="E246" t="n">
-        <v>339.4518318672431</v>
+        <v>339.1320190429688</v>
       </c>
       <c r="F246" t="n">
-        <v>23391400</v>
+        <v>33493600</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6831,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B247" t="n">
-        <v>346.3673706054688</v>
+        <v>335.7841605001305</v>
       </c>
       <c r="C247" t="n">
-        <v>348.9157509584863</v>
+        <v>336.9834018439635</v>
       </c>
       <c r="D247" t="n">
-        <v>340.0514228221321</v>
+        <v>332.8360433203593</v>
       </c>
       <c r="E247" t="n">
-        <v>340.4911426360338</v>
+        <v>334.8047790527344</v>
       </c>
       <c r="F247" t="n">
-        <v>25347200</v>
+        <v>23342700</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6857,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B248" t="n">
-        <v>339.1320190429688</v>
+        <v>333.845410447285</v>
       </c>
       <c r="C248" t="n">
-        <v>344.3686432833908</v>
+        <v>339.7815972628325</v>
       </c>
       <c r="D248" t="n">
-        <v>336.943423385668</v>
+        <v>332.6062167342666</v>
       </c>
       <c r="E248" t="n">
-        <v>343.609121722545</v>
+        <v>336.9034423828125</v>
       </c>
       <c r="F248" t="n">
-        <v>33493600</v>
+        <v>22582300</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6883,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B249" t="n">
-        <v>334.8047790527344</v>
+        <v>340.3412297100126</v>
       </c>
       <c r="C249" t="n">
-        <v>336.9834018439635</v>
+        <v>344.4585782378343</v>
       </c>
       <c r="D249" t="n">
-        <v>332.8360433203593</v>
+        <v>339.841550898423</v>
       </c>
       <c r="E249" t="n">
-        <v>335.7841605001305</v>
+        <v>342.260009765625</v>
       </c>
       <c r="F249" t="n">
-        <v>23342700</v>
+        <v>20726900</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6909,25 +6917,25 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B250" t="n">
-        <v>336.9034423828125</v>
+        <v>342.4700012207031</v>
       </c>
       <c r="C250" t="n">
-        <v>339.7815972628325</v>
+        <v>343.5299987792969</v>
       </c>
       <c r="D250" t="n">
-        <v>332.6062167342666</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="E250" t="n">
-        <v>333.845410447285</v>
+        <v>338.4599914550781</v>
       </c>
       <c r="F250" t="n">
-        <v>22582300</v>
+        <v>23189300</v>
       </c>
       <c r="G250" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -6935,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B251" t="n">
-        <v>342.260009765625</v>
+        <v>335.4200134277344</v>
       </c>
       <c r="C251" t="n">
-        <v>344.4585782378343</v>
+        <v>339.6799926757812</v>
       </c>
       <c r="D251" t="n">
-        <v>339.841550898423</v>
+        <v>333.2200012207031</v>
       </c>
       <c r="E251" t="n">
-        <v>340.3412297100126</v>
+        <v>338.3599853515625</v>
       </c>
       <c r="F251" t="n">
-        <v>20726900</v>
+        <v>22915800</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6961,45 +6969,27 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B252" t="n">
-        <v>338.4599914550781</v>
+        <v>331.6499938964844</v>
       </c>
       <c r="C252" t="n">
-        <v>343.5299987792969</v>
+        <v>331.8500061035156</v>
       </c>
       <c r="D252" t="n">
-        <v>337.0899963378906</v>
+        <v>327.8999938964844</v>
       </c>
       <c r="E252" t="n">
-        <v>342.4700012207031</v>
+        <v>330.6499938964844</v>
       </c>
       <c r="F252" t="n">
-        <v>23157700</v>
+        <v>33081300</v>
       </c>
       <c r="G252" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B253" t="inlineStr"/>
-      <c r="C253" t="inlineStr"/>
-      <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr"/>
-      <c r="F253" t="n">
-        <v>22262778</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10782,49 +10772,49 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>330.65</v>
+      </c>
+      <c r="D2" t="n">
         <v>338.36</v>
       </c>
-      <c r="D2" t="n">
-        <v>338.46</v>
-      </c>
       <c r="E2" t="n">
-        <v>335.38</v>
+        <v>331.69</v>
       </c>
       <c r="F2" t="n">
-        <v>339.665</v>
+        <v>331.85</v>
       </c>
       <c r="G2" t="n">
-        <v>333.22</v>
+        <v>327.9</v>
       </c>
       <c r="H2" t="n">
-        <v>22262778</v>
+        <v>32730889</v>
       </c>
       <c r="I2" t="n">
-        <v>30137845</v>
+        <v>30031591</v>
       </c>
       <c r="J2" t="n">
-        <v>4138120773632</v>
+        <v>4043827838976</v>
       </c>
       <c r="K2" t="n">
-        <v>16.968906</v>
+        <v>16.97382</v>
       </c>
       <c r="L2" t="n">
-        <v>22.779003</v>
+        <v>22.259953</v>
       </c>
       <c r="M2" t="n">
-        <v>19.94</v>
+        <v>19.48</v>
       </c>
       <c r="N2" t="n">
         <v>408.61</v>
       </c>
       <c r="O2" t="n">
-        <v>233.23</v>
+        <v>235.84</v>
       </c>
       <c r="P2" t="n">
         <v>1.225</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="R2" t="n">
         <v>0.54771</v>
@@ -10848,7 +10838,7 @@
         <v>50.896</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.6480665</v>
+        <v>6.496581</v>
       </c>
       <c r="Z2" t="n">
         <v>2.94</v>
@@ -10860,7 +10850,7 @@
         <v>445865984000</v>
       </c>
       <c r="AC2" t="n">
-        <v>4034482929664</v>
+        <v>3940189470720</v>
       </c>
       <c r="AD2" t="n">
         <v>173164003328</v>
@@ -10887,7 +10877,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-09 09:14:51</t>
+          <t>2026-09-10 18:59:07</t>
         </is>
       </c>
     </row>

--- a/data/GOOGL_data.xlsx
+++ b/data/GOOGL_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B2" t="n">
-        <v>238.2803024247839</v>
+        <v>239.2577712479691</v>
       </c>
       <c r="C2" t="n">
-        <v>241.0331528996711</v>
+        <v>241.6216187469878</v>
       </c>
       <c r="D2" t="n">
-        <v>237.2330382337294</v>
+        <v>235.6371823693535</v>
       </c>
       <c r="E2" t="n">
-        <v>238.5496063232422</v>
+        <v>239.7464904785156</v>
       </c>
       <c r="F2" t="n">
-        <v>35141100</v>
+        <v>30599300</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B3" t="n">
-        <v>239.2577864756533</v>
+        <v>239.746507229255</v>
       </c>
       <c r="C3" t="n">
-        <v>241.6216341251204</v>
+        <v>241.4520784124984</v>
       </c>
       <c r="D3" t="n">
-        <v>235.6371973666035</v>
+        <v>237.3826595650776</v>
       </c>
       <c r="E3" t="n">
-        <v>239.7465057373047</v>
+        <v>240.1753997802734</v>
       </c>
       <c r="F3" t="n">
-        <v>30599300</v>
+        <v>26771600</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B4" t="n">
-        <v>239.7464919977143</v>
+        <v>244.0253674338205</v>
       </c>
       <c r="C4" t="n">
-        <v>241.4520630725996</v>
+        <v>251.7552643082765</v>
       </c>
       <c r="D4" t="n">
-        <v>237.3826444837165</v>
+        <v>244.0253674338205</v>
       </c>
       <c r="E4" t="n">
-        <v>240.1753845214844</v>
+        <v>250.9573364257812</v>
       </c>
       <c r="F4" t="n">
-        <v>26771600</v>
+        <v>58383800</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B5" t="n">
-        <v>244.0253674338205</v>
+        <v>251.4261108558069</v>
       </c>
       <c r="C5" t="n">
-        <v>251.7552643082765</v>
+        <v>252.3836121103763</v>
       </c>
       <c r="D5" t="n">
-        <v>244.0253674338205</v>
+        <v>248.8228805399337</v>
       </c>
       <c r="E5" t="n">
-        <v>250.9573364257812</v>
+        <v>250.5084991455078</v>
       </c>
       <c r="F5" t="n">
-        <v>58383800</v>
+        <v>34109700</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B6" t="n">
-        <v>251.4261261704888</v>
+        <v>250.5683549046871</v>
       </c>
       <c r="C6" t="n">
-        <v>252.3836274833809</v>
+        <v>250.9473740826164</v>
       </c>
       <c r="D6" t="n">
-        <v>248.8228956960496</v>
+        <v>245.6411664684413</v>
       </c>
       <c r="E6" t="n">
-        <v>250.5085144042969</v>
+        <v>248.8827362060547</v>
       </c>
       <c r="F6" t="n">
-        <v>34109700</v>
+        <v>34108000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B7" t="n">
-        <v>250.56837026682</v>
+        <v>251.0271530076639</v>
       </c>
       <c r="C7" t="n">
-        <v>250.9473894679867</v>
+        <v>253.3311738191467</v>
       </c>
       <c r="D7" t="n">
-        <v>245.6411815284925</v>
+        <v>249.1520399405299</v>
       </c>
       <c r="E7" t="n">
-        <v>248.8827514648438</v>
+        <v>251.3762512207031</v>
       </c>
       <c r="F7" t="n">
-        <v>34108000</v>
+        <v>31239500</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B8" t="n">
-        <v>251.0271682452624</v>
+        <v>252.5930922260568</v>
       </c>
       <c r="C8" t="n">
-        <v>253.3311891966015</v>
+        <v>255.3359589728353</v>
       </c>
       <c r="D8" t="n">
-        <v>249.1520550643071</v>
+        <v>251.1568250217611</v>
       </c>
       <c r="E8" t="n">
-        <v>251.3762664794922</v>
+        <v>254.0592803955078</v>
       </c>
       <c r="F8" t="n">
-        <v>31239500</v>
+        <v>55571400</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B9" t="n">
-        <v>252.5930922260568</v>
+        <v>253.7700350469374</v>
       </c>
       <c r="C9" t="n">
-        <v>255.3359589728353</v>
+        <v>255.1165394138156</v>
       </c>
       <c r="D9" t="n">
-        <v>251.1568250217611</v>
+        <v>249.6507580677981</v>
       </c>
       <c r="E9" t="n">
-        <v>254.0592803955078</v>
+        <v>251.8749694824219</v>
       </c>
       <c r="F9" t="n">
-        <v>55571400</v>
+        <v>32290500</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B10" t="n">
-        <v>253.7700350469374</v>
+        <v>252.38362744671</v>
       </c>
       <c r="C10" t="n">
-        <v>255.1165394138156</v>
+        <v>253.7002107757565</v>
       </c>
       <c r="D10" t="n">
-        <v>249.6507580677981</v>
+        <v>249.8302703204236</v>
       </c>
       <c r="E10" t="n">
-        <v>251.8749694824219</v>
+        <v>251.0072174072266</v>
       </c>
       <c r="F10" t="n">
-        <v>32290500</v>
+        <v>26628000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B11" t="n">
-        <v>252.38362744671</v>
+        <v>251.0072115158567</v>
       </c>
       <c r="C11" t="n">
-        <v>253.7002107757565</v>
+        <v>251.6954241290499</v>
       </c>
       <c r="D11" t="n">
-        <v>249.8302703204236</v>
+        <v>245.8007506899351</v>
       </c>
       <c r="E11" t="n">
-        <v>251.0072174072266</v>
+        <v>246.4989318847656</v>
       </c>
       <c r="F11" t="n">
-        <v>26628000</v>
+        <v>28201000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B12" t="n">
-        <v>251.0072270537175</v>
+        <v>243.76602627878</v>
       </c>
       <c r="C12" t="n">
-        <v>251.6954397095125</v>
+        <v>245.8506164364007</v>
       </c>
       <c r="D12" t="n">
-        <v>245.8007659055053</v>
+        <v>240.1155317960277</v>
       </c>
       <c r="E12" t="n">
-        <v>246.4989471435547</v>
+        <v>245.1524200439453</v>
       </c>
       <c r="F12" t="n">
-        <v>28201000</v>
+        <v>31020400</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B13" t="n">
-        <v>243.7660414512771</v>
+        <v>246.429136680309</v>
       </c>
       <c r="C13" t="n">
-        <v>245.8506317386469</v>
+        <v>248.7730319241888</v>
       </c>
       <c r="D13" t="n">
-        <v>240.1155467413105</v>
+        <v>245.3319838637119</v>
       </c>
       <c r="E13" t="n">
-        <v>245.1524353027344</v>
+        <v>245.9004974365234</v>
       </c>
       <c r="F13" t="n">
-        <v>31020400</v>
+        <v>18503200</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B14" t="n">
-        <v>246.4291213887164</v>
+        <v>247.2071078925349</v>
       </c>
       <c r="C14" t="n">
-        <v>248.7730164871513</v>
+        <v>250.4985358461003</v>
       </c>
       <c r="D14" t="n">
-        <v>245.3319686402006</v>
+        <v>242.1402830798725</v>
       </c>
       <c r="E14" t="n">
-        <v>245.9004821777344</v>
+        <v>243.4169616699219</v>
       </c>
       <c r="F14" t="n">
-        <v>18503200</v>
+        <v>32505800</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B15" t="n">
-        <v>247.2071078925349</v>
+        <v>242.1801651040411</v>
       </c>
       <c r="C15" t="n">
-        <v>250.4985358461003</v>
+        <v>242.6589157556348</v>
       </c>
       <c r="D15" t="n">
-        <v>242.1402830798725</v>
+        <v>238.6294019345709</v>
       </c>
       <c r="E15" t="n">
-        <v>243.4169616699219</v>
+        <v>242.4694213867188</v>
       </c>
       <c r="F15" t="n">
-        <v>32505800</v>
+        <v>34724300</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B16" t="n">
-        <v>242.180180344627</v>
+        <v>240.1254958950803</v>
       </c>
       <c r="C16" t="n">
-        <v>242.6589310263489</v>
+        <v>245.6611022710827</v>
       </c>
       <c r="D16" t="n">
-        <v>238.6294169517045</v>
+        <v>237.991047651448</v>
       </c>
       <c r="E16" t="n">
-        <v>242.4694366455078</v>
+        <v>244.2647247314453</v>
       </c>
       <c r="F16" t="n">
-        <v>34724300</v>
+        <v>31658200</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B17" t="n">
-        <v>240.125510895299</v>
+        <v>244.5140808226371</v>
       </c>
       <c r="C17" t="n">
-        <v>245.661117617101</v>
+        <v>246.1697784759451</v>
       </c>
       <c r="D17" t="n">
-        <v>237.9910625183314</v>
+        <v>241.6714827842888</v>
       </c>
       <c r="E17" t="n">
-        <v>244.2647399902344</v>
+        <v>245.0526885986328</v>
       </c>
       <c r="F17" t="n">
-        <v>31658200</v>
+        <v>25483300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B18" t="n">
-        <v>244.5141112731399</v>
+        <v>243.8558378805103</v>
       </c>
       <c r="C18" t="n">
-        <v>246.1698091326398</v>
+        <v>245.6611405975774</v>
       </c>
       <c r="D18" t="n">
-        <v>241.6715128807893</v>
+        <v>241.0331766174326</v>
       </c>
       <c r="E18" t="n">
-        <v>245.0527191162109</v>
+        <v>244.7136077880859</v>
       </c>
       <c r="F18" t="n">
-        <v>25483300</v>
+        <v>30249600</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B19" t="n">
-        <v>243.8558074699024</v>
+        <v>244.1450721986699</v>
       </c>
       <c r="C19" t="n">
-        <v>245.661109961835</v>
+        <v>250.6681168360691</v>
       </c>
       <c r="D19" t="n">
-        <v>241.0331465588312</v>
+        <v>243.9455940157645</v>
       </c>
       <c r="E19" t="n">
-        <v>244.7135772705078</v>
+        <v>249.7804107666016</v>
       </c>
       <c r="F19" t="n">
-        <v>30249600</v>
+        <v>28894700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B20" t="n">
-        <v>244.145057284137</v>
+        <v>247.6260118192477</v>
       </c>
       <c r="C20" t="n">
-        <v>250.6681015230512</v>
+        <v>249.7903811872092</v>
       </c>
       <c r="D20" t="n">
-        <v>243.9455791134174</v>
+        <v>244.8831450984028</v>
       </c>
       <c r="E20" t="n">
-        <v>249.7803955078125</v>
+        <v>245.1225128173828</v>
       </c>
       <c r="F20" t="n">
-        <v>28894700</v>
+        <v>23181300</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B21" t="n">
-        <v>247.6260118192477</v>
+        <v>244.3245879910796</v>
       </c>
       <c r="C21" t="n">
-        <v>249.7903811872092</v>
+        <v>245.3718521480096</v>
       </c>
       <c r="D21" t="n">
-        <v>244.8831450984028</v>
+        <v>243.1875457247831</v>
       </c>
       <c r="E21" t="n">
-        <v>245.1225128173828</v>
+        <v>243.9854583740234</v>
       </c>
       <c r="F21" t="n">
-        <v>23181300</v>
+        <v>21307100</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B22" t="n">
-        <v>244.3246032710778</v>
+        <v>243.8358644557508</v>
       </c>
       <c r="C22" t="n">
-        <v>245.3718674935034</v>
+        <v>244.1251055211473</v>
       </c>
       <c r="D22" t="n">
-        <v>243.187560933671</v>
+        <v>238.5296568297252</v>
       </c>
       <c r="E22" t="n">
-        <v>243.9854736328125</v>
+        <v>240.9034881591797</v>
       </c>
       <c r="F22" t="n">
-        <v>21307100</v>
+        <v>27892100</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B23" t="n">
-        <v>243.8358644557508</v>
+        <v>240.8037387238312</v>
       </c>
       <c r="C23" t="n">
-        <v>244.1251055211473</v>
+        <v>243.4568425066541</v>
       </c>
       <c r="D23" t="n">
-        <v>238.5296568297252</v>
+        <v>235.2282424787384</v>
       </c>
       <c r="E23" t="n">
-        <v>240.9034881591797</v>
+        <v>235.9563598632812</v>
       </c>
       <c r="F23" t="n">
-        <v>27892100</v>
+        <v>33180300</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B24" t="n">
-        <v>240.8037387238312</v>
+        <v>239.5869258671789</v>
       </c>
       <c r="C24" t="n">
-        <v>243.4568425066541</v>
+        <v>243.8657913377574</v>
       </c>
       <c r="D24" t="n">
-        <v>235.2282424787384</v>
+        <v>239.0882228174084</v>
       </c>
       <c r="E24" t="n">
-        <v>235.9563598632812</v>
+        <v>243.5166931152344</v>
       </c>
       <c r="F24" t="n">
-        <v>33180300</v>
+        <v>24995000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B25" t="n">
-        <v>239.5869408797282</v>
+        <v>240.6042690189676</v>
       </c>
       <c r="C25" t="n">
-        <v>243.865806618421</v>
+        <v>246.4789903337629</v>
       </c>
       <c r="D25" t="n">
-        <v>239.0882377987089</v>
+        <v>239.8861354100955</v>
       </c>
       <c r="E25" t="n">
-        <v>243.5167083740234</v>
+        <v>244.8133239746094</v>
       </c>
       <c r="F25" t="n">
-        <v>24995000</v>
+        <v>22111600</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B26" t="n">
-        <v>240.6042690189676</v>
+        <v>246.6086514775368</v>
       </c>
       <c r="C26" t="n">
-        <v>246.4789903337629</v>
+        <v>251.4560455996756</v>
       </c>
       <c r="D26" t="n">
-        <v>239.8861354100955</v>
+        <v>245.3519253048375</v>
       </c>
       <c r="E26" t="n">
-        <v>244.8133239746094</v>
+        <v>250.3788452148438</v>
       </c>
       <c r="F26" t="n">
-        <v>22111600</v>
+        <v>27007700</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B27" t="n">
-        <v>246.6086665065597</v>
+        <v>251.1169327071502</v>
       </c>
       <c r="C27" t="n">
-        <v>251.4560609241123</v>
+        <v>256.2934574717041</v>
       </c>
       <c r="D27" t="n">
-        <v>245.3519402572719</v>
+        <v>249.4512663819502</v>
       </c>
       <c r="E27" t="n">
-        <v>250.3788604736328</v>
+        <v>250.8077392578125</v>
       </c>
       <c r="F27" t="n">
-        <v>27007700</v>
+        <v>27997200</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B28" t="n">
-        <v>251.1169174295502</v>
+        <v>250.1095396639979</v>
       </c>
       <c r="C28" t="n">
-        <v>256.2934418791717</v>
+        <v>253.5605713492617</v>
       </c>
       <c r="D28" t="n">
-        <v>249.451251205687</v>
+        <v>247.1671948127543</v>
       </c>
       <c r="E28" t="n">
-        <v>250.8077239990234</v>
+        <v>252.6429595947266</v>
       </c>
       <c r="F28" t="n">
-        <v>27997200</v>
+        <v>29671600</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B29" t="n">
-        <v>250.1095396639979</v>
+        <v>254.0293759063695</v>
       </c>
       <c r="C29" t="n">
-        <v>253.5605713492617</v>
+        <v>256.6625123260812</v>
       </c>
       <c r="D29" t="n">
-        <v>247.1671948127543</v>
+        <v>253.5705623788801</v>
       </c>
       <c r="E29" t="n">
-        <v>252.6429595947266</v>
+        <v>255.8845367431641</v>
       </c>
       <c r="F29" t="n">
-        <v>29671600</v>
+        <v>22350200</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B30" t="n">
-        <v>254.0293607582065</v>
+        <v>254.079230052693</v>
       </c>
       <c r="C30" t="n">
-        <v>256.6624970209002</v>
+        <v>254.2188662949897</v>
       </c>
       <c r="D30" t="n">
-        <v>253.5705472580769</v>
+        <v>243.5166881090968</v>
       </c>
       <c r="E30" t="n">
-        <v>255.884521484375</v>
+        <v>249.8103332519531</v>
       </c>
       <c r="F30" t="n">
-        <v>22350200</v>
+        <v>47312100</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B31" t="n">
-        <v>254.079230052693</v>
+        <v>253.7101963156115</v>
       </c>
       <c r="C31" t="n">
-        <v>254.2188662949897</v>
+        <v>255.6950248045094</v>
       </c>
       <c r="D31" t="n">
-        <v>243.5166881090968</v>
+        <v>248.6433712710665</v>
       </c>
       <c r="E31" t="n">
-        <v>249.8103332519531</v>
+        <v>251.0371551513672</v>
       </c>
       <c r="F31" t="n">
-        <v>47312100</v>
+        <v>35029400</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B32" t="n">
-        <v>253.710180894347</v>
+        <v>252.3237915100895</v>
       </c>
       <c r="C32" t="n">
-        <v>255.6950092626011</v>
+        <v>254.3784456458486</v>
       </c>
       <c r="D32" t="n">
-        <v>248.6433561577788</v>
+        <v>251.196732963501</v>
       </c>
       <c r="E32" t="n">
-        <v>251.0371398925781</v>
+        <v>252.4235382080078</v>
       </c>
       <c r="F32" t="n">
-        <v>35029400</v>
+        <v>19901400</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B33" t="n">
-        <v>252.3237762573301</v>
+        <v>255.9144557753844</v>
       </c>
       <c r="C33" t="n">
-        <v>254.378430268887</v>
+        <v>261.0012332121926</v>
       </c>
       <c r="D33" t="n">
-        <v>251.1967177788712</v>
+        <v>254.6577447284323</v>
       </c>
       <c r="E33" t="n">
-        <v>252.4235229492188</v>
+        <v>259.2458190917969</v>
       </c>
       <c r="F33" t="n">
-        <v>19901400</v>
+        <v>28655100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B34" t="n">
-        <v>255.9144557753844</v>
+        <v>264.1330942614516</v>
       </c>
       <c r="C34" t="n">
-        <v>261.0012332121926</v>
+        <v>269.4393020900735</v>
       </c>
       <c r="D34" t="n">
-        <v>254.6577447284323</v>
+        <v>263.5944864374467</v>
       </c>
       <c r="E34" t="n">
-        <v>259.2458190917969</v>
+        <v>268.571533203125</v>
       </c>
       <c r="F34" t="n">
-        <v>28655100</v>
+        <v>35235200</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B35" t="n">
-        <v>264.1330642482098</v>
+        <v>268.9904266199372</v>
       </c>
       <c r="C35" t="n">
-        <v>269.4392714738914</v>
+        <v>270.0277373828665</v>
       </c>
       <c r="D35" t="n">
-        <v>263.5944564854066</v>
+        <v>265.8086990443333</v>
       </c>
       <c r="E35" t="n">
-        <v>268.5715026855469</v>
+        <v>266.7761840820312</v>
       </c>
       <c r="F35" t="n">
-        <v>35235200</v>
+        <v>29738600</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B36" t="n">
-        <v>268.9904881616853</v>
+        <v>267.055471479175</v>
       </c>
       <c r="C36" t="n">
-        <v>270.0277991619387</v>
+        <v>274.6257797911847</v>
       </c>
       <c r="D36" t="n">
-        <v>265.8087598581407</v>
+        <v>266.975692387603</v>
       </c>
       <c r="E36" t="n">
-        <v>266.7762451171875</v>
+        <v>273.8577880859375</v>
       </c>
       <c r="F36" t="n">
-        <v>29738600</v>
+        <v>43580300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B37" t="n">
-        <v>267.055471479175</v>
+        <v>290.8336705300809</v>
       </c>
       <c r="C37" t="n">
-        <v>274.6257797911847</v>
+        <v>290.8336705300809</v>
       </c>
       <c r="D37" t="n">
-        <v>266.975692387603</v>
+        <v>279.3335782487789</v>
       </c>
       <c r="E37" t="n">
-        <v>273.8577880859375</v>
+        <v>280.7499084472656</v>
       </c>
       <c r="F37" t="n">
-        <v>43580300</v>
+        <v>74876000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B38" t="n">
-        <v>290.8336389163956</v>
+        <v>282.4753817503845</v>
       </c>
       <c r="C38" t="n">
-        <v>290.8336389163956</v>
+        <v>285.2581533777714</v>
       </c>
       <c r="D38" t="n">
-        <v>279.3335478851562</v>
+        <v>276.3114191679317</v>
       </c>
       <c r="E38" t="n">
-        <v>280.7498779296875</v>
+        <v>280.4606323242188</v>
       </c>
       <c r="F38" t="n">
-        <v>74876000</v>
+        <v>39267900</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B39" t="n">
-        <v>282.4753817503845</v>
+        <v>281.4480558536455</v>
       </c>
       <c r="C39" t="n">
-        <v>285.2581533777714</v>
+        <v>284.7893724933962</v>
       </c>
       <c r="D39" t="n">
-        <v>276.3114191679317</v>
+        <v>279.0742243823285</v>
       </c>
       <c r="E39" t="n">
-        <v>280.4606323242188</v>
+        <v>282.9840698242188</v>
       </c>
       <c r="F39" t="n">
-        <v>39267900</v>
+        <v>29786000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B40" t="n">
-        <v>281.4480255017143</v>
+        <v>276.0321395313242</v>
       </c>
       <c r="C40" t="n">
-        <v>284.7893417811305</v>
+        <v>280.5404041676455</v>
       </c>
       <c r="D40" t="n">
-        <v>279.0741942863961</v>
+        <v>275.5434202802167</v>
       </c>
       <c r="E40" t="n">
-        <v>282.9840393066406</v>
+        <v>276.8200988769531</v>
       </c>
       <c r="F40" t="n">
-        <v>29786000</v>
+        <v>30078400</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B41" t="n">
-        <v>276.0321395313242</v>
+        <v>278.1466184544242</v>
       </c>
       <c r="C41" t="n">
-        <v>280.5404041676455</v>
+        <v>285.677052345188</v>
       </c>
       <c r="D41" t="n">
-        <v>275.5434202802167</v>
+        <v>276.62058842555</v>
       </c>
       <c r="E41" t="n">
-        <v>276.8200988769531</v>
+        <v>283.572509765625</v>
       </c>
       <c r="F41" t="n">
-        <v>30078400</v>
+        <v>31010300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B42" t="n">
-        <v>278.1466483880774</v>
+        <v>284.5898651937554</v>
       </c>
       <c r="C42" t="n">
-        <v>285.6770830892533</v>
+        <v>287.6020510547858</v>
       </c>
       <c r="D42" t="n">
-        <v>276.6206181949745</v>
+        <v>280.4107616957575</v>
       </c>
       <c r="E42" t="n">
-        <v>283.5725402832031</v>
+        <v>284.0113830566406</v>
       </c>
       <c r="F42" t="n">
-        <v>31010300</v>
+        <v>37173600</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B43" t="n">
-        <v>284.5898651937554</v>
+        <v>282.4753634096288</v>
       </c>
       <c r="C43" t="n">
-        <v>287.6020510547858</v>
+        <v>283.0438921724298</v>
       </c>
       <c r="D43" t="n">
-        <v>280.4107616957575</v>
+        <v>274.4761777186906</v>
       </c>
       <c r="E43" t="n">
-        <v>284.0113830566406</v>
+        <v>278.1067199707031</v>
       </c>
       <c r="F43" t="n">
-        <v>37173600</v>
+        <v>34479600</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B44" t="n">
-        <v>282.4753634096288</v>
+        <v>283.6822445549795</v>
       </c>
       <c r="C44" t="n">
-        <v>283.0438921724298</v>
+        <v>290.0456696400176</v>
       </c>
       <c r="D44" t="n">
-        <v>274.4761777186906</v>
+        <v>282.1262631003564</v>
       </c>
       <c r="E44" t="n">
-        <v>278.1067199707031</v>
+        <v>289.3475036621094</v>
       </c>
       <c r="F44" t="n">
-        <v>34479600</v>
+        <v>29557300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B45" t="n">
-        <v>283.6822445549795</v>
+        <v>287.0035887304013</v>
       </c>
       <c r="C45" t="n">
-        <v>290.0456696400176</v>
+        <v>291.1627853205446</v>
       </c>
       <c r="D45" t="n">
-        <v>282.1262631003564</v>
+        <v>286.5747114373448</v>
       </c>
       <c r="E45" t="n">
-        <v>289.3475036621094</v>
+        <v>290.5543518066406</v>
       </c>
       <c r="F45" t="n">
-        <v>29557300</v>
+        <v>19842100</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B46" t="n">
-        <v>287.0035887304013</v>
+        <v>290.9234183741868</v>
       </c>
       <c r="C46" t="n">
-        <v>291.1627853205446</v>
+        <v>291.2525794490294</v>
       </c>
       <c r="D46" t="n">
-        <v>286.5747114373448</v>
+        <v>282.9541529801612</v>
       </c>
       <c r="E46" t="n">
-        <v>290.5543518066406</v>
+        <v>285.96630859375</v>
       </c>
       <c r="F46" t="n">
-        <v>19842100</v>
+        <v>24829900</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B47" t="n">
-        <v>290.9233873275988</v>
+        <v>281.6076529103283</v>
       </c>
       <c r="C47" t="n">
-        <v>291.2525483673142</v>
+        <v>282.1063559927165</v>
       </c>
       <c r="D47" t="n">
-        <v>282.9541227840324</v>
+        <v>276.5208753822851</v>
       </c>
       <c r="E47" t="n">
-        <v>285.9662780761719</v>
+        <v>277.8474426269531</v>
       </c>
       <c r="F47" t="n">
-        <v>24829900</v>
+        <v>29494000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B48" t="n">
-        <v>281.6076219797447</v>
+        <v>270.705963217399</v>
       </c>
       <c r="C48" t="n">
-        <v>282.1063250073575</v>
+        <v>277.8374099534448</v>
       </c>
       <c r="D48" t="n">
-        <v>276.5208450104115</v>
+        <v>269.997813487729</v>
       </c>
       <c r="E48" t="n">
-        <v>277.847412109375</v>
+        <v>275.6929931640625</v>
       </c>
       <c r="F48" t="n">
-        <v>29494000</v>
+        <v>31647200</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B49" t="n">
-        <v>270.7059931829425</v>
+        <v>285.0387085276487</v>
       </c>
       <c r="C49" t="n">
-        <v>277.8374407083971</v>
+        <v>293.1875295999499</v>
       </c>
       <c r="D49" t="n">
-        <v>269.9978433748846</v>
+        <v>282.8344496120375</v>
       </c>
       <c r="E49" t="n">
-        <v>275.6930236816406</v>
+        <v>284.2806701660156</v>
       </c>
       <c r="F49" t="n">
-        <v>31647200</v>
+        <v>52670200</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B50" t="n">
-        <v>285.0387085276487</v>
+        <v>287.1731753233953</v>
       </c>
       <c r="C50" t="n">
-        <v>293.1875295999499</v>
+        <v>288.0508671158451</v>
       </c>
       <c r="D50" t="n">
-        <v>282.8344496120375</v>
+        <v>277.4783868942568</v>
       </c>
       <c r="E50" t="n">
-        <v>284.2806701660156</v>
+        <v>283.5426025390625</v>
       </c>
       <c r="F50" t="n">
-        <v>52670200</v>
+        <v>49158700</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B51" t="n">
-        <v>287.1731444150601</v>
+        <v>286.4151377283875</v>
       </c>
       <c r="C51" t="n">
-        <v>288.0508361130442</v>
+        <v>303.0219431129204</v>
       </c>
       <c r="D51" t="n">
-        <v>277.4783570293678</v>
+        <v>285.8865137158778</v>
       </c>
       <c r="E51" t="n">
-        <v>283.5425720214844</v>
+        <v>292.0504760742188</v>
       </c>
       <c r="F51" t="n">
-        <v>49158700</v>
+        <v>68198900</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B52" t="n">
-        <v>286.4151377283875</v>
+        <v>303.7500416076266</v>
       </c>
       <c r="C52" t="n">
-        <v>303.0219431129204</v>
+        <v>305.625169818548</v>
       </c>
       <c r="D52" t="n">
-        <v>285.8865137158778</v>
+        <v>287.9212127447435</v>
       </c>
       <c r="E52" t="n">
-        <v>292.0504760742188</v>
+        <v>288.6991882324219</v>
       </c>
       <c r="F52" t="n">
-        <v>68198900</v>
+        <v>62025200</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B53" t="n">
-        <v>303.7500737161881</v>
+        <v>295.6511348655125</v>
       </c>
       <c r="C53" t="n">
-        <v>305.625202125324</v>
+        <v>303.1316807498811</v>
       </c>
       <c r="D53" t="n">
-        <v>287.921243180084</v>
+        <v>293.0877938372482</v>
       </c>
       <c r="E53" t="n">
-        <v>288.69921875</v>
+        <v>298.8827209472656</v>
       </c>
       <c r="F53" t="n">
-        <v>62025200</v>
+        <v>74137700</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B54" t="n">
-        <v>295.6511046778972</v>
+        <v>310.3229443803346</v>
       </c>
       <c r="C54" t="n">
-        <v>303.1316497984607</v>
+        <v>318.651290855991</v>
       </c>
       <c r="D54" t="n">
-        <v>293.0877639113642</v>
+        <v>308.796914365105</v>
       </c>
       <c r="E54" t="n">
-        <v>298.8826904296875</v>
+        <v>317.7536010742188</v>
       </c>
       <c r="F54" t="n">
-        <v>74137700</v>
+        <v>85165100</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B55" t="n">
-        <v>310.3229443803346</v>
+        <v>325.3638169665917</v>
       </c>
       <c r="C55" t="n">
-        <v>318.651290855991</v>
+        <v>327.9770159307299</v>
       </c>
       <c r="D55" t="n">
-        <v>308.796914365105</v>
+        <v>316.826023668276</v>
       </c>
       <c r="E55" t="n">
-        <v>317.7536010742188</v>
+        <v>322.6010131835938</v>
       </c>
       <c r="F55" t="n">
-        <v>85165100</v>
+        <v>88632100</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B56" t="n">
-        <v>325.3638169665917</v>
+        <v>319.8482042131112</v>
       </c>
       <c r="C56" t="n">
-        <v>327.9770159307299</v>
+        <v>323.658303098724</v>
       </c>
       <c r="D56" t="n">
-        <v>316.826023668276</v>
+        <v>315.9683100285969</v>
       </c>
       <c r="E56" t="n">
-        <v>322.6010131835938</v>
+        <v>319.1201171875</v>
       </c>
       <c r="F56" t="n">
-        <v>88632100</v>
+        <v>51373400</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B57" t="n">
-        <v>319.8482042131112</v>
+        <v>322.5312152935296</v>
       </c>
       <c r="C57" t="n">
-        <v>323.658303098724</v>
+        <v>326.0021995827445</v>
       </c>
       <c r="D57" t="n">
-        <v>315.9683100285969</v>
+        <v>315.9682963529555</v>
       </c>
       <c r="E57" t="n">
-        <v>319.1201171875</v>
+        <v>319.3494873046875</v>
       </c>
       <c r="F57" t="n">
-        <v>51373400</v>
+        <v>26018600</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B58" t="n">
-        <v>322.5312152935296</v>
+        <v>316.8759510785769</v>
       </c>
       <c r="C58" t="n">
-        <v>326.0021995827445</v>
+        <v>319.020368247556</v>
       </c>
       <c r="D58" t="n">
-        <v>315.9682963529555</v>
+        <v>313.0758360216101</v>
       </c>
       <c r="E58" t="n">
-        <v>319.3494873046875</v>
+        <v>314.0732421875</v>
       </c>
       <c r="F58" t="n">
-        <v>26018600</v>
+        <v>41183000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B59" t="n">
-        <v>316.8759202886677</v>
+        <v>315.9184251730286</v>
       </c>
       <c r="C59" t="n">
-        <v>319.02033724928</v>
+        <v>317.5541859262309</v>
       </c>
       <c r="D59" t="n">
-        <v>313.075805600947</v>
+        <v>313.095779063488</v>
       </c>
       <c r="E59" t="n">
-        <v>314.0732116699219</v>
+        <v>314.9908447265625</v>
       </c>
       <c r="F59" t="n">
-        <v>41183000</v>
+        <v>35854700</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B60" t="n">
-        <v>315.9183945655827</v>
+        <v>315.0706144021458</v>
       </c>
       <c r="C60" t="n">
-        <v>317.554155160306</v>
+        <v>320.7458268711651</v>
       </c>
       <c r="D60" t="n">
-        <v>313.0957487295115</v>
+        <v>313.2852490348319</v>
       </c>
       <c r="E60" t="n">
-        <v>314.9908142089844</v>
+        <v>318.8009033203125</v>
       </c>
       <c r="F60" t="n">
-        <v>35854700</v>
+        <v>41838300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B61" t="n">
-        <v>315.0706144021458</v>
+        <v>321.3941698854088</v>
       </c>
       <c r="C61" t="n">
-        <v>320.7458268711651</v>
+        <v>321.5238071066378</v>
       </c>
       <c r="D61" t="n">
-        <v>313.2852490348319</v>
+        <v>313.8837033726762</v>
       </c>
       <c r="E61" t="n">
-        <v>318.8009033203125</v>
+        <v>316.7961120605469</v>
       </c>
       <c r="F61" t="n">
-        <v>41838300</v>
+        <v>31240900</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B62" t="n">
-        <v>321.3942008459266</v>
+        <v>318.6612638744486</v>
       </c>
       <c r="C62" t="n">
-        <v>321.5238380796439</v>
+        <v>322.3217576397153</v>
       </c>
       <c r="D62" t="n">
-        <v>313.8837336096964</v>
+        <v>318.3421170569229</v>
       </c>
       <c r="E62" t="n">
-        <v>316.796142578125</v>
+        <v>320.4366455078125</v>
       </c>
       <c r="F62" t="n">
-        <v>31240900</v>
+        <v>28851700</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,25 +2055,25 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B63" t="n">
-        <v>318.6612335259534</v>
+        <v>319.4285975207571</v>
       </c>
       <c r="C63" t="n">
-        <v>322.3217269426038</v>
+        <v>319.8178549396436</v>
       </c>
       <c r="D63" t="n">
-        <v>318.3420867388224</v>
+        <v>310.6157547321785</v>
       </c>
       <c r="E63" t="n">
-        <v>320.4366149902344</v>
+        <v>313.1109008789062</v>
       </c>
       <c r="F63" t="n">
-        <v>28851700</v>
+        <v>33909400</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2081,25 +2081,25 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B64" t="n">
-        <v>319.428628654094</v>
+        <v>311.7635388280278</v>
       </c>
       <c r="C64" t="n">
-        <v>319.8178861109197</v>
+        <v>317.3726229056239</v>
       </c>
       <c r="D64" t="n">
-        <v>310.6157850065654</v>
+        <v>311.2944500995635</v>
       </c>
       <c r="E64" t="n">
-        <v>313.1109313964844</v>
+        <v>316.4643859863281</v>
       </c>
       <c r="F64" t="n">
-        <v>33909400</v>
+        <v>30194000</v>
       </c>
       <c r="G64" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B65" t="n">
-        <v>311.7635388280278</v>
+        <v>315.2168165746965</v>
       </c>
       <c r="C65" t="n">
-        <v>317.3726229056239</v>
+        <v>320.6861883612462</v>
       </c>
       <c r="D65" t="n">
-        <v>311.2944500995635</v>
+        <v>314.069055340672</v>
       </c>
       <c r="E65" t="n">
-        <v>316.4643859863281</v>
+        <v>319.5883178710938</v>
       </c>
       <c r="F65" t="n">
-        <v>30194000</v>
+        <v>33428900</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B66" t="n">
-        <v>315.2168165746965</v>
+        <v>319.4585671045538</v>
       </c>
       <c r="C66" t="n">
-        <v>320.6861883612462</v>
+        <v>320.4965565243085</v>
       </c>
       <c r="D66" t="n">
-        <v>314.069055340672</v>
+        <v>308.0008744502611</v>
       </c>
       <c r="E66" t="n">
-        <v>319.5883178710938</v>
+        <v>311.8234252929688</v>
       </c>
       <c r="F66" t="n">
-        <v>33428900</v>
+        <v>42353700</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B67" t="n">
-        <v>319.4585358397385</v>
+        <v>313.0909556884665</v>
       </c>
       <c r="C67" t="n">
-        <v>320.4965251579071</v>
+        <v>314.2586670471713</v>
       </c>
       <c r="D67" t="n">
-        <v>308.0008443067889</v>
+        <v>304.9667450846255</v>
       </c>
       <c r="E67" t="n">
-        <v>311.8233947753906</v>
+        <v>308.6895141601562</v>
       </c>
       <c r="F67" t="n">
-        <v>42353700</v>
+        <v>35940200</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B68" t="n">
-        <v>313.0909556884665</v>
+        <v>310.7156001962807</v>
       </c>
       <c r="C68" t="n">
-        <v>314.2586670471713</v>
+        <v>310.8154121445851</v>
       </c>
       <c r="D68" t="n">
-        <v>304.9667450846255</v>
+        <v>304.2881005921093</v>
       </c>
       <c r="E68" t="n">
-        <v>308.6895141601562</v>
+        <v>307.6216125488281</v>
       </c>
       <c r="F68" t="n">
-        <v>35940200</v>
+        <v>29151900</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B69" t="n">
-        <v>310.7155693717638</v>
+        <v>304.3579426322819</v>
       </c>
       <c r="C69" t="n">
-        <v>310.8153813101663</v>
+        <v>310.1666197797816</v>
       </c>
       <c r="D69" t="n">
-        <v>304.288070405232</v>
+        <v>302.0025088045779</v>
       </c>
       <c r="E69" t="n">
-        <v>307.62158203125</v>
+        <v>305.9747924804688</v>
       </c>
       <c r="F69" t="n">
-        <v>29151900</v>
+        <v>30585000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B70" t="n">
-        <v>304.3579426322819</v>
+        <v>307.4120099511304</v>
       </c>
       <c r="C70" t="n">
-        <v>310.1666197797816</v>
+        <v>307.4918412298865</v>
       </c>
       <c r="D70" t="n">
-        <v>302.0025088045779</v>
+        <v>295.5450797036171</v>
       </c>
       <c r="E70" t="n">
-        <v>305.9747924804688</v>
+        <v>296.1439208984375</v>
       </c>
       <c r="F70" t="n">
-        <v>30585000</v>
+        <v>43930400</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B71" t="n">
-        <v>307.4120099511304</v>
+        <v>301.1342186567393</v>
       </c>
       <c r="C71" t="n">
-        <v>307.4918412298865</v>
+        <v>303.3698600006946</v>
       </c>
       <c r="D71" t="n">
-        <v>295.5450797036171</v>
+        <v>298.6490626821344</v>
       </c>
       <c r="E71" t="n">
-        <v>296.1439208984375</v>
+        <v>301.8727722167969</v>
       </c>
       <c r="F71" t="n">
-        <v>43930400</v>
+        <v>33518000</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B72" t="n">
-        <v>301.1342186567393</v>
+        <v>301.1442091965169</v>
       </c>
       <c r="C72" t="n">
-        <v>303.3698600006946</v>
+        <v>306.6534812800651</v>
       </c>
       <c r="D72" t="n">
-        <v>298.6490626821344</v>
+        <v>300.3856749721532</v>
       </c>
       <c r="E72" t="n">
-        <v>301.8727722167969</v>
+        <v>306.5636596679688</v>
       </c>
       <c r="F72" t="n">
-        <v>33518000</v>
+        <v>59943200</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B73" t="n">
-        <v>301.1442091965169</v>
+        <v>309.278400817878</v>
       </c>
       <c r="C73" t="n">
-        <v>306.6534812800651</v>
+        <v>309.5279154654388</v>
       </c>
       <c r="D73" t="n">
-        <v>300.3856749721532</v>
+        <v>304.707275417899</v>
       </c>
       <c r="E73" t="n">
-        <v>306.5636596679688</v>
+        <v>309.1785888671875</v>
       </c>
       <c r="F73" t="n">
-        <v>59943200</v>
+        <v>26429900</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B74" t="n">
-        <v>309.2783702904479</v>
+        <v>309.0288478780406</v>
       </c>
       <c r="C74" t="n">
-        <v>309.5278849133803</v>
+        <v>314.328535898872</v>
       </c>
       <c r="D74" t="n">
-        <v>304.7072453416635</v>
+        <v>308.7194521900694</v>
       </c>
       <c r="E74" t="n">
-        <v>309.1785583496094</v>
+        <v>313.7396850585938</v>
       </c>
       <c r="F74" t="n">
-        <v>26429900</v>
+        <v>25478700</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B75" t="n">
-        <v>309.0288478780406</v>
+        <v>314.1588359856885</v>
       </c>
       <c r="C75" t="n">
-        <v>314.328535898872</v>
+        <v>314.4682316573388</v>
       </c>
       <c r="D75" t="n">
-        <v>308.7194521900694</v>
+        <v>311.3143938726672</v>
       </c>
       <c r="E75" t="n">
-        <v>313.7396850585938</v>
+        <v>313.4801635742188</v>
       </c>
       <c r="F75" t="n">
-        <v>25478700</v>
+        <v>10097400</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B76" t="n">
-        <v>314.1588359856885</v>
+        <v>313.8694852656387</v>
       </c>
       <c r="C76" t="n">
-        <v>314.4682316573388</v>
+        <v>314.4782864028367</v>
       </c>
       <c r="D76" t="n">
-        <v>311.3143938726672</v>
+        <v>311.6737441219225</v>
       </c>
       <c r="E76" t="n">
-        <v>313.4801635742188</v>
+        <v>312.9013671875</v>
       </c>
       <c r="F76" t="n">
-        <v>10097400</v>
+        <v>10899000</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B77" t="n">
-        <v>313.8694546536391</v>
+        <v>310.7655125785055</v>
       </c>
       <c r="C77" t="n">
-        <v>314.4782557314601</v>
+        <v>313.410361871903</v>
       </c>
       <c r="D77" t="n">
-        <v>311.6737137240756</v>
+        <v>310.0169686016006</v>
       </c>
       <c r="E77" t="n">
-        <v>312.9013366699219</v>
+        <v>312.9512634277344</v>
       </c>
       <c r="F77" t="n">
-        <v>10899000</v>
+        <v>19621800</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B78" t="n">
-        <v>310.7654822740718</v>
+        <v>311.8932765746258</v>
       </c>
       <c r="C78" t="n">
-        <v>313.4103313095557</v>
+        <v>316.3346490163796</v>
       </c>
       <c r="D78" t="n">
-        <v>310.0169383701615</v>
+        <v>311.8533457068925</v>
       </c>
       <c r="E78" t="n">
-        <v>312.9512329101562</v>
+        <v>313.2406616210938</v>
       </c>
       <c r="F78" t="n">
-        <v>19621800</v>
+        <v>17380900</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B79" t="n">
-        <v>311.8932765746258</v>
+        <v>312.2426007868329</v>
       </c>
       <c r="C79" t="n">
-        <v>316.3346490163796</v>
+        <v>313.9692224596297</v>
       </c>
       <c r="D79" t="n">
-        <v>311.8533457068925</v>
+        <v>310.8353346785167</v>
       </c>
       <c r="E79" t="n">
-        <v>313.2406616210938</v>
+        <v>312.3923034667969</v>
       </c>
       <c r="F79" t="n">
-        <v>17380900</v>
+        <v>16377700</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B80" t="n">
-        <v>312.2426007868329</v>
+        <v>316.2847187538463</v>
       </c>
       <c r="C80" t="n">
-        <v>313.9692224596297</v>
+        <v>321.87385220157</v>
       </c>
       <c r="D80" t="n">
-        <v>310.8353346785167</v>
+        <v>309.7274673850438</v>
       </c>
       <c r="E80" t="n">
-        <v>312.3923034667969</v>
+        <v>314.5381164550781</v>
       </c>
       <c r="F80" t="n">
-        <v>16377700</v>
+        <v>32009400</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B81" t="n">
-        <v>316.2847494408858</v>
+        <v>317.0432662013207</v>
       </c>
       <c r="C81" t="n">
-        <v>321.8738834308866</v>
+        <v>318.4006111389099</v>
       </c>
       <c r="D81" t="n">
-        <v>309.727497435876</v>
+        <v>314.0191501700305</v>
       </c>
       <c r="E81" t="n">
-        <v>314.5381469726562</v>
+        <v>315.9254455566406</v>
       </c>
       <c r="F81" t="n">
-        <v>32009400</v>
+        <v>30195600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B82" t="n">
-        <v>317.0432968268774</v>
+        <v>315.7857038876524</v>
       </c>
       <c r="C82" t="n">
-        <v>318.4006418955826</v>
+        <v>320.3168980142969</v>
       </c>
       <c r="D82" t="n">
-        <v>314.0191805034655</v>
+        <v>311.1746784825258</v>
       </c>
       <c r="E82" t="n">
-        <v>315.9254760742188</v>
+        <v>313.7297058105469</v>
       </c>
       <c r="F82" t="n">
-        <v>30195600</v>
+        <v>31212100</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B83" t="n">
-        <v>315.7857038876524</v>
+        <v>313.7496873061683</v>
       </c>
       <c r="C83" t="n">
-        <v>320.3168980142969</v>
+        <v>325.5168067446344</v>
       </c>
       <c r="D83" t="n">
-        <v>311.1746784825258</v>
+        <v>313.5800344006012</v>
       </c>
       <c r="E83" t="n">
-        <v>313.7297058105469</v>
+        <v>321.3549194335938</v>
       </c>
       <c r="F83" t="n">
-        <v>31212100</v>
+        <v>35104400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B84" t="n">
-        <v>313.7496277154789</v>
+        <v>328.3313118537803</v>
       </c>
       <c r="C84" t="n">
-        <v>325.5167449190081</v>
+        <v>329.6786969446188</v>
       </c>
       <c r="D84" t="n">
-        <v>313.5799748421341</v>
+        <v>320.8758135066914</v>
       </c>
       <c r="E84" t="n">
-        <v>321.3548583984375</v>
+        <v>324.8081665039062</v>
       </c>
       <c r="F84" t="n">
-        <v>35104400</v>
+        <v>31896100</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B85" t="n">
-        <v>328.3313118537803</v>
+        <v>326.4549607998293</v>
       </c>
       <c r="C85" t="n">
-        <v>329.6786969446188</v>
+        <v>330.1876899539591</v>
       </c>
       <c r="D85" t="n">
-        <v>320.8758135066914</v>
+        <v>325.1674567682817</v>
       </c>
       <c r="E85" t="n">
-        <v>324.8081665039062</v>
+        <v>327.9320983886719</v>
       </c>
       <c r="F85" t="n">
-        <v>31896100</v>
+        <v>26214200</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B86" t="n">
-        <v>326.4549607998293</v>
+        <v>325.1674658209474</v>
       </c>
       <c r="C86" t="n">
-        <v>330.1876899539591</v>
+        <v>333.3914890456728</v>
       </c>
       <c r="D86" t="n">
-        <v>325.1674567682817</v>
+        <v>324.3690311583512</v>
       </c>
       <c r="E86" t="n">
-        <v>327.9320983886719</v>
+        <v>331.2156982421875</v>
       </c>
       <c r="F86" t="n">
-        <v>26214200</v>
+        <v>33923900</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B87" t="n">
-        <v>325.1674358606418</v>
+        <v>334.2996793666924</v>
       </c>
       <c r="C87" t="n">
-        <v>333.3914583276215</v>
+        <v>339.8289010736461</v>
       </c>
       <c r="D87" t="n">
-        <v>324.3690012716118</v>
+        <v>332.9722446137951</v>
       </c>
       <c r="E87" t="n">
-        <v>331.2156677246094</v>
+        <v>335.3176879882812</v>
       </c>
       <c r="F87" t="n">
-        <v>33923900</v>
+        <v>33517600</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B88" t="n">
-        <v>334.2997097916206</v>
+        <v>334.4094733641317</v>
       </c>
       <c r="C88" t="n">
-        <v>339.828932001794</v>
+        <v>335.8666302231012</v>
       </c>
       <c r="D88" t="n">
-        <v>332.9722749179122</v>
+        <v>329.8383789070015</v>
       </c>
       <c r="E88" t="n">
-        <v>335.3177185058594</v>
+        <v>335.1879577636719</v>
       </c>
       <c r="F88" t="n">
-        <v>33517600</v>
+        <v>28525600</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B89" t="n">
-        <v>334.4095038108318</v>
+        <v>336.9944512235705</v>
       </c>
       <c r="C89" t="n">
-        <v>335.8666608024698</v>
+        <v>337.03438209247</v>
       </c>
       <c r="D89" t="n">
-        <v>329.838408937521</v>
+        <v>330.097863235539</v>
       </c>
       <c r="E89" t="n">
-        <v>335.18798828125</v>
+        <v>332.1339111328125</v>
       </c>
       <c r="F89" t="n">
-        <v>28525600</v>
+        <v>28442400</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B90" t="n">
-        <v>336.9944202593897</v>
+        <v>333.7607557246461</v>
       </c>
       <c r="C90" t="n">
-        <v>337.0343511246202</v>
+        <v>334.0002800245007</v>
       </c>
       <c r="D90" t="n">
-        <v>330.0978329050398</v>
+        <v>327.0637915356931</v>
       </c>
       <c r="E90" t="n">
-        <v>332.1338806152344</v>
+        <v>329.3593139648438</v>
       </c>
       <c r="F90" t="n">
-        <v>28442400</v>
+        <v>40341600</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B91" t="n">
-        <v>333.7607557246461</v>
+        <v>320.2470363972373</v>
       </c>
       <c r="C91" t="n">
-        <v>334.0002800245007</v>
+        <v>327.0937337673917</v>
       </c>
       <c r="D91" t="n">
-        <v>327.0637915356931</v>
+        <v>319.8078882063433</v>
       </c>
       <c r="E91" t="n">
-        <v>329.3593139648438</v>
+        <v>321.3748474121094</v>
       </c>
       <c r="F91" t="n">
-        <v>40341600</v>
+        <v>35361000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B92" t="n">
-        <v>320.2470363972373</v>
+        <v>320.2969541162656</v>
       </c>
       <c r="C92" t="n">
-        <v>327.0937337673917</v>
+        <v>331.8345081879527</v>
       </c>
       <c r="D92" t="n">
-        <v>319.8078882063433</v>
+        <v>318.729994927537</v>
       </c>
       <c r="E92" t="n">
-        <v>321.3748474121094</v>
+        <v>327.7424621582031</v>
       </c>
       <c r="F92" t="n">
-        <v>35361000</v>
+        <v>35386600</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B93" t="n">
-        <v>320.2969541162656</v>
+        <v>333.8006666576773</v>
       </c>
       <c r="C93" t="n">
-        <v>331.8345081879527</v>
+        <v>334.4992893099707</v>
       </c>
       <c r="D93" t="n">
-        <v>318.729994927537</v>
+        <v>328.1117212092731</v>
       </c>
       <c r="E93" t="n">
-        <v>327.7424621582031</v>
+        <v>329.8982543945312</v>
       </c>
       <c r="F93" t="n">
-        <v>35386600</v>
+        <v>26253600</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B94" t="n">
-        <v>333.8006666576773</v>
+        <v>331.8444485977197</v>
       </c>
       <c r="C94" t="n">
-        <v>334.4992893099707</v>
+        <v>333.0421309365838</v>
       </c>
       <c r="D94" t="n">
-        <v>328.1117212092731</v>
+        <v>326.8142558744754</v>
       </c>
       <c r="E94" t="n">
-        <v>329.8982543945312</v>
+        <v>327.2933044433594</v>
       </c>
       <c r="F94" t="n">
-        <v>26253600</v>
+        <v>27280000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B95" t="n">
-        <v>331.8444485977197</v>
+        <v>327.1735452193246</v>
       </c>
       <c r="C95" t="n">
-        <v>333.0421309365838</v>
+        <v>335.1879535299186</v>
       </c>
       <c r="D95" t="n">
-        <v>326.8142558744754</v>
+        <v>326.3651202937951</v>
       </c>
       <c r="E95" t="n">
-        <v>327.2933044433594</v>
+        <v>332.6129760742188</v>
       </c>
       <c r="F95" t="n">
-        <v>27280000</v>
+        <v>26042100</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B96" t="n">
-        <v>327.1735452193246</v>
+        <v>334.7188669221849</v>
       </c>
       <c r="C96" t="n">
-        <v>335.1879535299186</v>
+        <v>337.2539439848537</v>
       </c>
       <c r="D96" t="n">
-        <v>326.3651202937951</v>
+        <v>332.8325522369338</v>
       </c>
       <c r="E96" t="n">
-        <v>332.6129760742188</v>
+        <v>333.9004516601562</v>
       </c>
       <c r="F96" t="n">
-        <v>26042100</v>
+        <v>21636200</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B97" t="n">
-        <v>334.7188669221849</v>
+        <v>335.4075262381039</v>
       </c>
       <c r="C97" t="n">
-        <v>337.2539439848537</v>
+        <v>336.8846637353836</v>
       </c>
       <c r="D97" t="n">
-        <v>332.8325522369338</v>
+        <v>331.2955302242731</v>
       </c>
       <c r="E97" t="n">
-        <v>333.9004516601562</v>
+        <v>335.3576354980469</v>
       </c>
       <c r="F97" t="n">
-        <v>21636200</v>
+        <v>27434400</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B98" t="n">
-        <v>335.4075262381039</v>
+        <v>339.6393000059441</v>
       </c>
       <c r="C98" t="n">
-        <v>336.8846637353836</v>
+        <v>341.625457159737</v>
       </c>
       <c r="D98" t="n">
-        <v>331.2955302242731</v>
+        <v>325.9060355700189</v>
       </c>
       <c r="E98" t="n">
-        <v>335.3576354980469</v>
+        <v>337.5932922363281</v>
       </c>
       <c r="F98" t="n">
-        <v>27434400</v>
+        <v>39785600</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B99" t="n">
-        <v>339.6393000059441</v>
+        <v>339.3398975620609</v>
       </c>
       <c r="C99" t="n">
-        <v>341.625457159737</v>
+        <v>339.3398975620609</v>
       </c>
       <c r="D99" t="n">
-        <v>325.9060355700189</v>
+        <v>331.6448748839121</v>
       </c>
       <c r="E99" t="n">
-        <v>337.5932922363281</v>
+        <v>337.3437805175781</v>
       </c>
       <c r="F99" t="n">
-        <v>39785600</v>
+        <v>31024000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B100" t="n">
-        <v>339.3398975620609</v>
+        <v>335.5672073695487</v>
       </c>
       <c r="C100" t="n">
-        <v>339.3398975620609</v>
+        <v>344.1604758527643</v>
       </c>
       <c r="D100" t="n">
-        <v>331.6448748839121</v>
+        <v>334.9783565494149</v>
       </c>
       <c r="E100" t="n">
-        <v>337.3437805175781</v>
+        <v>343.022705078125</v>
       </c>
       <c r="F100" t="n">
-        <v>31024000</v>
+        <v>32006100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B101" t="n">
-        <v>335.5672372238362</v>
+        <v>346.6656368085559</v>
       </c>
       <c r="C101" t="n">
-        <v>344.160506471566</v>
+        <v>348.322417578686</v>
       </c>
       <c r="D101" t="n">
-        <v>334.9783863513143</v>
+        <v>336.8148042563823</v>
       </c>
       <c r="E101" t="n">
-        <v>343.0227355957031</v>
+        <v>339.0504455566406</v>
       </c>
       <c r="F101" t="n">
-        <v>32006100</v>
+        <v>36506700</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B102" t="n">
-        <v>346.6656368085559</v>
+        <v>342.2941565134455</v>
       </c>
       <c r="C102" t="n">
-        <v>348.322417578686</v>
+        <v>342.6434831024425</v>
       </c>
       <c r="D102" t="n">
-        <v>336.8148042563823</v>
+        <v>327.8821884154679</v>
       </c>
       <c r="E102" t="n">
-        <v>339.0504455566406</v>
+        <v>332.3934326171875</v>
       </c>
       <c r="F102" t="n">
-        <v>36506700</v>
+        <v>70618400</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B103" t="n">
-        <v>342.2941250868659</v>
+        <v>311.6138496060838</v>
       </c>
       <c r="C103" t="n">
-        <v>342.6434516437907</v>
+        <v>332.0441098613053</v>
       </c>
       <c r="D103" t="n">
-        <v>327.8821583120744</v>
+        <v>305.8650224655501</v>
       </c>
       <c r="E103" t="n">
-        <v>332.3934020996094</v>
+        <v>330.6069030761719</v>
       </c>
       <c r="F103" t="n">
-        <v>70618400</v>
+        <v>88205800</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B104" t="n">
-        <v>311.6137920773395</v>
+        <v>326.5447743483745</v>
       </c>
       <c r="C104" t="n">
-        <v>332.0440485608184</v>
+        <v>329.7385737476322</v>
       </c>
       <c r="D104" t="n">
-        <v>305.8649659981283</v>
+        <v>319.2988903139048</v>
       </c>
       <c r="E104" t="n">
-        <v>330.6068420410156</v>
+        <v>322.233154296875</v>
       </c>
       <c r="F104" t="n">
-        <v>88205800</v>
+        <v>56380500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B105" t="n">
-        <v>326.5447743483745</v>
+        <v>320.3069052195784</v>
       </c>
       <c r="C105" t="n">
-        <v>329.7385737476322</v>
+        <v>327.0637807183464</v>
       </c>
       <c r="D105" t="n">
-        <v>319.2988903139048</v>
+        <v>316.6440476026885</v>
       </c>
       <c r="E105" t="n">
-        <v>322.233154296875</v>
+        <v>323.6903381347656</v>
       </c>
       <c r="F105" t="n">
-        <v>56380500</v>
+        <v>39640100</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B106" t="n">
-        <v>320.3069052195784</v>
+        <v>320.3468306795893</v>
       </c>
       <c r="C106" t="n">
-        <v>327.0637807183464</v>
+        <v>321.0454837970353</v>
       </c>
       <c r="D106" t="n">
-        <v>316.6440476026885</v>
+        <v>313.9991629255859</v>
       </c>
       <c r="E106" t="n">
-        <v>323.6903381347656</v>
+        <v>317.9614562988281</v>
       </c>
       <c r="F106" t="n">
-        <v>39640100</v>
+        <v>39170000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B107" t="n">
-        <v>320.3468306795893</v>
+        <v>318.3506892240785</v>
       </c>
       <c r="C107" t="n">
-        <v>321.0454837970353</v>
+        <v>320.4366276261131</v>
       </c>
       <c r="D107" t="n">
-        <v>313.9991629255859</v>
+        <v>309.0587679521403</v>
       </c>
       <c r="E107" t="n">
-        <v>317.9614562988281</v>
+        <v>310.3562316894531</v>
       </c>
       <c r="F107" t="n">
-        <v>39170000</v>
+        <v>45406400</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B108" t="n">
-        <v>318.3507205277581</v>
+        <v>311.4840826487114</v>
       </c>
       <c r="C108" t="n">
-        <v>320.4366591349046</v>
+        <v>315.6260194522374</v>
       </c>
       <c r="D108" t="n">
-        <v>309.0587983421378</v>
+        <v>306.603592280419</v>
       </c>
       <c r="E108" t="n">
-        <v>310.3562622070312</v>
+        <v>308.4000854492188</v>
       </c>
       <c r="F108" t="n">
-        <v>45406400</v>
+        <v>47761300</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B109" t="n">
-        <v>311.4840518259579</v>
+        <v>307.1325415821482</v>
       </c>
       <c r="C109" t="n">
-        <v>315.6259882196205</v>
+        <v>308.0307881065925</v>
       </c>
       <c r="D109" t="n">
-        <v>306.603561940612</v>
+        <v>303.1203270701956</v>
       </c>
       <c r="E109" t="n">
-        <v>308.4000549316406</v>
+        <v>305.1264343261719</v>
       </c>
       <c r="F109" t="n">
-        <v>47761300</v>
+        <v>38499700</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B110" t="n">
-        <v>307.1325415821482</v>
+        <v>299.4574575670962</v>
       </c>
       <c r="C110" t="n">
-        <v>308.0307881065925</v>
+        <v>303.8489085337251</v>
       </c>
       <c r="D110" t="n">
-        <v>303.1203270701956</v>
+        <v>295.674807618098</v>
       </c>
       <c r="E110" t="n">
-        <v>305.1264343261719</v>
+        <v>301.43359375</v>
       </c>
       <c r="F110" t="n">
-        <v>38499700</v>
+        <v>39247600</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B111" t="n">
-        <v>299.4574575670962</v>
+        <v>301.5035060024616</v>
       </c>
       <c r="C111" t="n">
-        <v>303.8489085337251</v>
+        <v>304.7871271852118</v>
       </c>
       <c r="D111" t="n">
-        <v>295.674807618098</v>
+        <v>300.6651404690992</v>
       </c>
       <c r="E111" t="n">
-        <v>301.43359375</v>
+        <v>302.7410888671875</v>
       </c>
       <c r="F111" t="n">
-        <v>39247600</v>
+        <v>28482100</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B112" t="n">
-        <v>301.5035060024616</v>
+        <v>301.2340248853423</v>
       </c>
       <c r="C112" t="n">
-        <v>304.7871271852118</v>
+        <v>304.8769323320439</v>
       </c>
       <c r="D112" t="n">
-        <v>300.6651404690992</v>
+        <v>299.4574819671566</v>
       </c>
       <c r="E112" t="n">
-        <v>302.7410888671875</v>
+        <v>302.2620239257812</v>
       </c>
       <c r="F112" t="n">
-        <v>28482100</v>
+        <v>25834400</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B113" t="n">
-        <v>301.2340248853423</v>
+        <v>303.7291917307074</v>
       </c>
       <c r="C113" t="n">
-        <v>304.8769323320439</v>
+        <v>315.8855378192499</v>
       </c>
       <c r="D113" t="n">
-        <v>299.4574819671566</v>
+        <v>303.3099937290923</v>
       </c>
       <c r="E113" t="n">
-        <v>302.2620239257812</v>
+        <v>314.3684997558594</v>
       </c>
       <c r="F113" t="n">
-        <v>25834400</v>
+        <v>53210800</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B114" t="n">
-        <v>303.7291622459488</v>
+        <v>318.4305429928518</v>
       </c>
       <c r="C114" t="n">
-        <v>315.885507154404</v>
+        <v>318.8996316925602</v>
       </c>
       <c r="D114" t="n">
-        <v>303.3099642850277</v>
+        <v>309.2683735389658</v>
       </c>
       <c r="E114" t="n">
-        <v>314.3684692382812</v>
+        <v>310.8852233886719</v>
       </c>
       <c r="F114" t="n">
-        <v>53210800</v>
+        <v>31423000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B115" t="n">
-        <v>318.4305429928518</v>
+        <v>309.91711960911</v>
       </c>
       <c r="C115" t="n">
-        <v>318.8996316925602</v>
+        <v>311.6637220131571</v>
       </c>
       <c r="D115" t="n">
-        <v>309.2683735389658</v>
+        <v>305.3360346729232</v>
       </c>
       <c r="E115" t="n">
-        <v>310.8852233886719</v>
+        <v>310.29638671875</v>
       </c>
       <c r="F115" t="n">
-        <v>31423000</v>
+        <v>25615600</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B116" t="n">
-        <v>309.9171500893873</v>
+        <v>311.4541454679639</v>
       </c>
       <c r="C116" t="n">
-        <v>311.6637526652123</v>
+        <v>313.031095017384</v>
       </c>
       <c r="D116" t="n">
-        <v>305.3360647026519</v>
+        <v>308.8392369672335</v>
       </c>
       <c r="E116" t="n">
-        <v>310.2964172363281</v>
+        <v>312.2925109863281</v>
       </c>
       <c r="F116" t="n">
-        <v>25615600</v>
+        <v>29963600</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B117" t="n">
-        <v>311.4541150323118</v>
+        <v>312.0330001798944</v>
       </c>
       <c r="C117" t="n">
-        <v>313.0310644276307</v>
+        <v>312.5320293917034</v>
       </c>
       <c r="D117" t="n">
-        <v>308.8392067871133</v>
+        <v>301.762970472535</v>
       </c>
       <c r="E117" t="n">
-        <v>312.29248046875</v>
+        <v>306.783203125</v>
       </c>
       <c r="F117" t="n">
-        <v>29963600</v>
+        <v>36431200</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B118" t="n">
-        <v>312.0330622595087</v>
+        <v>303.5495233120643</v>
       </c>
       <c r="C118" t="n">
-        <v>312.5320915706006</v>
+        <v>311.7635251790807</v>
       </c>
       <c r="D118" t="n">
-        <v>301.7630305089056</v>
+        <v>303.2101566226461</v>
       </c>
       <c r="E118" t="n">
-        <v>306.7832641601562</v>
+        <v>311.1547241210938</v>
       </c>
       <c r="F118" t="n">
-        <v>36431200</v>
+        <v>44640600</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B119" t="n">
-        <v>303.5495233120643</v>
+        <v>302.6413055358027</v>
       </c>
       <c r="C119" t="n">
-        <v>311.7635251790807</v>
+        <v>307.8910728050191</v>
       </c>
       <c r="D119" t="n">
-        <v>303.2101566226461</v>
+        <v>300.7150293830805</v>
       </c>
       <c r="E119" t="n">
-        <v>311.1547241210938</v>
+        <v>305.9248962402344</v>
       </c>
       <c r="F119" t="n">
-        <v>44640600</v>
+        <v>34790200</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B120" t="n">
-        <v>302.6412753457796</v>
+        <v>298.0102681623609</v>
       </c>
       <c r="C120" t="n">
-        <v>307.8910420913047</v>
+        <v>303.3498869477631</v>
       </c>
       <c r="D120" t="n">
-        <v>300.7149993852133</v>
+        <v>296.1339134078651</v>
       </c>
       <c r="E120" t="n">
-        <v>305.9248657226562</v>
+        <v>302.9905700683594</v>
       </c>
       <c r="F120" t="n">
-        <v>34790200</v>
+        <v>35497000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B121" t="n">
-        <v>298.0102681623609</v>
+        <v>302.3019795923877</v>
       </c>
       <c r="C121" t="n">
-        <v>303.3498869477631</v>
+        <v>304.8769573413998</v>
       </c>
       <c r="D121" t="n">
-        <v>296.1339134078651</v>
+        <v>300.1661195993462</v>
       </c>
       <c r="E121" t="n">
-        <v>302.9905700683594</v>
+        <v>302.54150390625</v>
       </c>
       <c r="F121" t="n">
-        <v>35497000</v>
+        <v>29536200</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B122" t="n">
-        <v>302.3019795923877</v>
+        <v>302.4516780897468</v>
       </c>
       <c r="C122" t="n">
-        <v>304.8769573413998</v>
+        <v>302.7111526067185</v>
       </c>
       <c r="D122" t="n">
-        <v>300.1661195993462</v>
+        <v>297.4114640277728</v>
       </c>
       <c r="E122" t="n">
-        <v>302.54150390625</v>
+        <v>300.2958679199219</v>
       </c>
       <c r="F122" t="n">
-        <v>29536200</v>
+        <v>35752300</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B123" t="n">
-        <v>302.4516473530844</v>
+        <v>295.5151547022239</v>
       </c>
       <c r="C123" t="n">
-        <v>302.711121843687</v>
+        <v>299.9465371351957</v>
       </c>
       <c r="D123" t="n">
-        <v>297.4114338033223</v>
+        <v>294.6069177596933</v>
       </c>
       <c r="E123" t="n">
-        <v>300.2958374023438</v>
+        <v>297.9404296875</v>
       </c>
       <c r="F123" t="n">
-        <v>35752300</v>
+        <v>25576900</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,25 +3641,25 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B124" t="n">
-        <v>295.5151547022239</v>
+        <v>293.9952756214191</v>
       </c>
       <c r="C124" t="n">
-        <v>299.9465371351957</v>
+        <v>306.4198649966507</v>
       </c>
       <c r="D124" t="n">
-        <v>294.6069177596933</v>
+        <v>293.7156237584298</v>
       </c>
       <c r="E124" t="n">
-        <v>297.9404296875</v>
+        <v>305.9804077148438</v>
       </c>
       <c r="F124" t="n">
-        <v>25576900</v>
+        <v>29312100</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3667,25 +3667,25 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B125" t="n">
-        <v>293.9952756214191</v>
+        <v>305.7906896809686</v>
       </c>
       <c r="C125" t="n">
-        <v>306.4198649966507</v>
+        <v>309.1265479913924</v>
       </c>
       <c r="D125" t="n">
-        <v>293.7156237584298</v>
+        <v>305.1914269440574</v>
       </c>
       <c r="E125" t="n">
-        <v>305.9804077148438</v>
+        <v>306.6596069335938</v>
       </c>
       <c r="F125" t="n">
-        <v>29312100</v>
+        <v>23239700</v>
       </c>
       <c r="G125" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B126" t="n">
-        <v>305.7906896809686</v>
+        <v>306.3699695674413</v>
       </c>
       <c r="C126" t="n">
-        <v>309.1265479913924</v>
+        <v>311.0341973481569</v>
       </c>
       <c r="D126" t="n">
-        <v>305.1914269440574</v>
+        <v>305.5410112597431</v>
       </c>
       <c r="E126" t="n">
-        <v>306.6596069335938</v>
+        <v>308.3175659179688</v>
       </c>
       <c r="F126" t="n">
-        <v>23239700</v>
+        <v>24125700</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B127" t="n">
-        <v>306.3699695674413</v>
+        <v>306.4398571350748</v>
       </c>
       <c r="C127" t="n">
-        <v>311.0341973481569</v>
+        <v>308.5572255769297</v>
       </c>
       <c r="D127" t="n">
-        <v>305.5410112597431</v>
+        <v>300.6570224145156</v>
       </c>
       <c r="E127" t="n">
-        <v>308.3175659179688</v>
+        <v>303.1738891601562</v>
       </c>
       <c r="F127" t="n">
-        <v>24125700</v>
+        <v>24928300</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B128" t="n">
-        <v>306.4398879814062</v>
+        <v>306.6296377698095</v>
       </c>
       <c r="C128" t="n">
-        <v>308.5572566363961</v>
+        <v>307.3087879643589</v>
       </c>
       <c r="D128" t="n">
-        <v>300.6570526787451</v>
+        <v>300.0677703977713</v>
       </c>
       <c r="E128" t="n">
-        <v>303.1739196777344</v>
+        <v>301.9054870605469</v>
       </c>
       <c r="F128" t="n">
-        <v>24928300</v>
+        <v>23693100</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B129" t="n">
-        <v>306.6296377698095</v>
+        <v>303.9729346538992</v>
       </c>
       <c r="C129" t="n">
-        <v>307.3087879643589</v>
+        <v>306.1102674724465</v>
       </c>
       <c r="D129" t="n">
-        <v>300.0677703977713</v>
+        <v>302.6445653756606</v>
       </c>
       <c r="E129" t="n">
-        <v>301.9054870605469</v>
+        <v>305.1814270019531</v>
       </c>
       <c r="F129" t="n">
-        <v>23693100</v>
+        <v>23519700</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B130" t="n">
-        <v>303.9729346538992</v>
+        <v>305.481031231764</v>
       </c>
       <c r="C130" t="n">
-        <v>306.1102674724465</v>
+        <v>311.0341705495281</v>
       </c>
       <c r="D130" t="n">
-        <v>302.6445653756606</v>
+        <v>305.1214918945171</v>
       </c>
       <c r="E130" t="n">
-        <v>305.1814270019531</v>
+        <v>310.5347900390625</v>
       </c>
       <c r="F130" t="n">
-        <v>23519700</v>
+        <v>21955200</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B131" t="n">
-        <v>305.481031231764</v>
+        <v>308.8868058363209</v>
       </c>
       <c r="C131" t="n">
-        <v>311.0341705495281</v>
+        <v>312.0828532524296</v>
       </c>
       <c r="D131" t="n">
-        <v>305.1214918945171</v>
+        <v>306.5497087361953</v>
       </c>
       <c r="E131" t="n">
-        <v>310.5347900390625</v>
+        <v>307.3087768554688</v>
       </c>
       <c r="F131" t="n">
-        <v>21955200</v>
+        <v>20009800</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B132" t="n">
-        <v>308.8868058363209</v>
+        <v>303.6333516523425</v>
       </c>
       <c r="C132" t="n">
-        <v>312.0828532524296</v>
+        <v>307.6783216475022</v>
       </c>
       <c r="D132" t="n">
-        <v>306.5497087361953</v>
+        <v>301.9754046785898</v>
       </c>
       <c r="E132" t="n">
-        <v>307.3087768554688</v>
+        <v>306.7494812011719</v>
       </c>
       <c r="F132" t="n">
-        <v>20009800</v>
+        <v>25075800</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B133" t="n">
-        <v>303.6333516523425</v>
+        <v>305.0815409313132</v>
       </c>
       <c r="C133" t="n">
-        <v>307.6783216475022</v>
+        <v>305.620880431115</v>
       </c>
       <c r="D133" t="n">
-        <v>301.9754046785898</v>
+        <v>297.9004465638477</v>
       </c>
       <c r="E133" t="n">
-        <v>306.7494812011719</v>
+        <v>300.6270751953125</v>
       </c>
       <c r="F133" t="n">
-        <v>25075800</v>
+        <v>44364100</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B134" t="n">
-        <v>305.0815409313132</v>
+        <v>301.7357168812967</v>
       </c>
       <c r="C134" t="n">
-        <v>305.620880431115</v>
+        <v>305.6009481410186</v>
       </c>
       <c r="D134" t="n">
-        <v>297.9004465638477</v>
+        <v>300.5571860375472</v>
       </c>
       <c r="E134" t="n">
-        <v>300.6270751953125</v>
+        <v>301.685791015625</v>
       </c>
       <c r="F134" t="n">
-        <v>44364100</v>
+        <v>29326900</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B135" t="n">
-        <v>301.7356863586682</v>
+        <v>298.8293264668504</v>
       </c>
       <c r="C135" t="n">
-        <v>305.6009172273957</v>
+        <v>299.5484356615691</v>
       </c>
       <c r="D135" t="n">
-        <v>300.5571556341351</v>
+        <v>289.9702901097709</v>
       </c>
       <c r="E135" t="n">
-        <v>301.6857604980469</v>
+        <v>290.0801696777344</v>
       </c>
       <c r="F135" t="n">
-        <v>29326900</v>
+        <v>36864300</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B136" t="n">
-        <v>298.8293264668504</v>
+        <v>293.0764495892524</v>
       </c>
       <c r="C136" t="n">
-        <v>299.5484356615691</v>
+        <v>295.6332754793409</v>
       </c>
       <c r="D136" t="n">
-        <v>289.9702901097709</v>
+        <v>288.8816409209488</v>
       </c>
       <c r="E136" t="n">
-        <v>290.0801696777344</v>
+        <v>290.5695495605469</v>
       </c>
       <c r="F136" t="n">
-        <v>36864300</v>
+        <v>29460700</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B137" t="n">
-        <v>293.0764495892524</v>
+        <v>287.5532902578335</v>
       </c>
       <c r="C137" t="n">
-        <v>295.6332754793409</v>
+        <v>287.5932492331535</v>
       </c>
       <c r="D137" t="n">
-        <v>288.8816409209488</v>
+        <v>278.1549453585245</v>
       </c>
       <c r="E137" t="n">
-        <v>290.5695495605469</v>
+        <v>280.5719604492188</v>
       </c>
       <c r="F137" t="n">
-        <v>29460700</v>
+        <v>39080600</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B138" t="n">
-        <v>287.553321534765</v>
+        <v>276.9364822022131</v>
       </c>
       <c r="C138" t="n">
-        <v>287.5932805144313</v>
+        <v>279.0238892859517</v>
       </c>
       <c r="D138" t="n">
-        <v>278.1549756132059</v>
+        <v>273.6106210828978</v>
       </c>
       <c r="E138" t="n">
-        <v>280.5719909667969</v>
+        <v>274.0001220703125</v>
       </c>
       <c r="F138" t="n">
-        <v>39080600</v>
+        <v>35890600</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B139" t="n">
-        <v>276.9364513575891</v>
+        <v>276.0775591796553</v>
       </c>
       <c r="C139" t="n">
-        <v>279.0238582088365</v>
+        <v>276.7467120540596</v>
       </c>
       <c r="D139" t="n">
-        <v>273.6105906087015</v>
+        <v>271.772870758184</v>
       </c>
       <c r="E139" t="n">
-        <v>274.0000915527344</v>
+        <v>273.1611633300781</v>
       </c>
       <c r="F139" t="n">
-        <v>35890600</v>
+        <v>35141200</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B140" t="n">
-        <v>276.0775591796553</v>
+        <v>277.6955407888773</v>
       </c>
       <c r="C140" t="n">
-        <v>276.7467120540596</v>
+        <v>287.7230801433843</v>
       </c>
       <c r="D140" t="n">
-        <v>271.772870758184</v>
+        <v>276.7467055656006</v>
       </c>
       <c r="E140" t="n">
-        <v>273.1611633300781</v>
+        <v>287.2037353515625</v>
       </c>
       <c r="F140" t="n">
-        <v>35141200</v>
+        <v>43875400</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B141" t="n">
-        <v>277.6955407888773</v>
+        <v>290.4796724840224</v>
       </c>
       <c r="C141" t="n">
-        <v>287.7230801433843</v>
+        <v>300.1476725442409</v>
       </c>
       <c r="D141" t="n">
-        <v>276.7467055656006</v>
+        <v>290.0502125293938</v>
       </c>
       <c r="E141" t="n">
-        <v>287.2037353515625</v>
+        <v>297.0215759277344</v>
       </c>
       <c r="F141" t="n">
-        <v>43875400</v>
+        <v>37684500</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B142" t="n">
-        <v>290.4796724840224</v>
+        <v>290.3298713924274</v>
       </c>
       <c r="C142" t="n">
-        <v>300.1476725442409</v>
+        <v>297.7107001938477</v>
       </c>
       <c r="D142" t="n">
-        <v>290.0502125293938</v>
+        <v>289.0914173614996</v>
       </c>
       <c r="E142" t="n">
-        <v>297.0215759277344</v>
+        <v>295.403564453125</v>
       </c>
       <c r="F142" t="n">
-        <v>37684500</v>
+        <v>21666500</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B143" t="n">
-        <v>290.3298413990028</v>
+        <v>295.5034260146894</v>
       </c>
       <c r="C143" t="n">
-        <v>297.7106694379238</v>
+        <v>300.2475409865838</v>
       </c>
       <c r="D143" t="n">
-        <v>289.0913874960174</v>
+        <v>294.8142784540748</v>
       </c>
       <c r="E143" t="n">
-        <v>295.4035339355469</v>
+        <v>299.6183166503906</v>
       </c>
       <c r="F143" t="n">
-        <v>21666500</v>
+        <v>16945500</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B144" t="n">
-        <v>295.5034561131459</v>
+        <v>302.3549447988444</v>
       </c>
       <c r="C144" t="n">
-        <v>300.2475715682514</v>
+        <v>305.2513457589993</v>
       </c>
       <c r="D144" t="n">
-        <v>294.8143084823383</v>
+        <v>297.3511421656273</v>
       </c>
       <c r="E144" t="n">
-        <v>299.6183471679688</v>
+        <v>305.08154296875</v>
       </c>
       <c r="F144" t="n">
-        <v>16945500</v>
+        <v>23205400</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B145" t="n">
-        <v>302.3549447988444</v>
+        <v>320.0530070056894</v>
       </c>
       <c r="C145" t="n">
-        <v>305.2513457589993</v>
+        <v>321.6809619973042</v>
       </c>
       <c r="D145" t="n">
-        <v>297.3511421656273</v>
+        <v>314.6297110626625</v>
       </c>
       <c r="E145" t="n">
-        <v>305.08154296875</v>
+        <v>316.9268798828125</v>
       </c>
       <c r="F145" t="n">
-        <v>23205400</v>
+        <v>33547100</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B146" t="n">
-        <v>320.0530070056894</v>
+        <v>315.5186078441214</v>
       </c>
       <c r="C146" t="n">
-        <v>321.6809619973042</v>
+        <v>319.1441153425082</v>
       </c>
       <c r="D146" t="n">
-        <v>314.6297110626625</v>
+        <v>310.6746106421415</v>
       </c>
       <c r="E146" t="n">
-        <v>316.9268798828125</v>
+        <v>318.0953979492188</v>
       </c>
       <c r="F146" t="n">
-        <v>33547100</v>
+        <v>23739200</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B147" t="n">
-        <v>315.5186078441214</v>
+        <v>319.6235089208506</v>
       </c>
       <c r="C147" t="n">
-        <v>319.1441153425082</v>
+        <v>321.4312640320202</v>
       </c>
       <c r="D147" t="n">
-        <v>310.6746106421415</v>
+        <v>315.9281112234418</v>
       </c>
       <c r="E147" t="n">
-        <v>318.0953979492188</v>
+        <v>316.8469543457031</v>
       </c>
       <c r="F147" t="n">
-        <v>23739200</v>
+        <v>19152600</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B148" t="n">
-        <v>319.6235089208506</v>
+        <v>316.7471095555252</v>
       </c>
       <c r="C148" t="n">
-        <v>321.4312640320202</v>
+        <v>321.2315371363443</v>
       </c>
       <c r="D148" t="n">
-        <v>315.9281112234418</v>
+        <v>315.0791651091577</v>
       </c>
       <c r="E148" t="n">
-        <v>316.8469543457031</v>
+        <v>320.9119262695312</v>
       </c>
       <c r="F148" t="n">
-        <v>19152600</v>
+        <v>18866400</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B149" t="n">
-        <v>316.7471095555252</v>
+        <v>324.3876234083889</v>
       </c>
       <c r="C149" t="n">
-        <v>321.2315371363443</v>
+        <v>332.8770926852431</v>
       </c>
       <c r="D149" t="n">
-        <v>315.0791651091577</v>
+        <v>323.3489033390031</v>
       </c>
       <c r="E149" t="n">
-        <v>320.9119262695312</v>
+        <v>332.49755859375</v>
       </c>
       <c r="F149" t="n">
-        <v>18866400</v>
+        <v>27721400</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B150" t="n">
-        <v>324.3876234083889</v>
+        <v>332.4775916674409</v>
       </c>
       <c r="C150" t="n">
-        <v>332.8770926852431</v>
+        <v>337.0619013824557</v>
       </c>
       <c r="D150" t="n">
-        <v>323.3489033390031</v>
+        <v>330.4900363853266</v>
       </c>
       <c r="E150" t="n">
-        <v>332.49755859375</v>
+        <v>336.7023315429688</v>
       </c>
       <c r="F150" t="n">
-        <v>27721400</v>
+        <v>24918800</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B151" t="n">
-        <v>332.4775916674409</v>
+        <v>338.3302967803236</v>
       </c>
       <c r="C151" t="n">
-        <v>337.0619013824557</v>
+        <v>339.458901613874</v>
       </c>
       <c r="D151" t="n">
-        <v>330.4900363853266</v>
+        <v>334.105526677332</v>
       </c>
       <c r="E151" t="n">
-        <v>336.7023315429688</v>
+        <v>335.6036682128906</v>
       </c>
       <c r="F151" t="n">
-        <v>24918800</v>
+        <v>20541500</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B152" t="n">
-        <v>338.3302967803236</v>
+        <v>337.2316773591919</v>
       </c>
       <c r="C152" t="n">
-        <v>339.458901613874</v>
+        <v>341.895905080184</v>
       </c>
       <c r="D152" t="n">
-        <v>334.105526677332</v>
+        <v>335.8234205588037</v>
       </c>
       <c r="E152" t="n">
-        <v>335.6036682128906</v>
+        <v>341.2566833496094</v>
       </c>
       <c r="F152" t="n">
-        <v>20541500</v>
+        <v>25581900</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B153" t="n">
-        <v>337.2316773591919</v>
+        <v>340.3378420577138</v>
       </c>
       <c r="C153" t="n">
-        <v>341.895905080184</v>
+        <v>340.9770333119858</v>
       </c>
       <c r="D153" t="n">
-        <v>335.8234205588037</v>
+        <v>336.1929591105031</v>
       </c>
       <c r="E153" t="n">
-        <v>341.2566833496094</v>
+        <v>337.0019836425781</v>
       </c>
       <c r="F153" t="n">
-        <v>25581900</v>
+        <v>18784200</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B154" t="n">
-        <v>340.3378420577138</v>
+        <v>337.2716301294484</v>
       </c>
       <c r="C154" t="n">
-        <v>340.9770333119858</v>
+        <v>338.9195798085849</v>
       </c>
       <c r="D154" t="n">
-        <v>336.1929591105031</v>
+        <v>330.9394885663705</v>
       </c>
       <c r="E154" t="n">
-        <v>337.0019836425781</v>
+        <v>331.8783264160156</v>
       </c>
       <c r="F154" t="n">
-        <v>18784200</v>
+        <v>23123800</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B155" t="n">
-        <v>337.2716301294484</v>
+        <v>336.6024588411248</v>
       </c>
       <c r="C155" t="n">
-        <v>338.9195798085849</v>
+        <v>339.3990082413208</v>
       </c>
       <c r="D155" t="n">
-        <v>330.9394885663705</v>
+        <v>334.7547751685775</v>
       </c>
       <c r="E155" t="n">
-        <v>331.8783264160156</v>
+        <v>338.8996276855469</v>
       </c>
       <c r="F155" t="n">
-        <v>23123800</v>
+        <v>20293000</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B156" t="n">
-        <v>336.6024588411248</v>
+        <v>340.7572947145818</v>
       </c>
       <c r="C156" t="n">
-        <v>339.3990082413208</v>
+        <v>341.5363271303731</v>
       </c>
       <c r="D156" t="n">
-        <v>334.7547751685775</v>
+        <v>335.7634893621326</v>
       </c>
       <c r="E156" t="n">
-        <v>338.8996276855469</v>
+        <v>338.4701538085938</v>
       </c>
       <c r="F156" t="n">
-        <v>20293000</v>
+        <v>18650300</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B157" t="n">
-        <v>340.7572947145818</v>
+        <v>338.3103390739037</v>
       </c>
       <c r="C157" t="n">
-        <v>341.5363271303731</v>
+        <v>344.8422143498026</v>
       </c>
       <c r="D157" t="n">
-        <v>335.7634893621326</v>
+        <v>334.9744808477988</v>
       </c>
       <c r="E157" t="n">
-        <v>338.4701538085938</v>
+        <v>343.9732971191406</v>
       </c>
       <c r="F157" t="n">
-        <v>18650300</v>
+        <v>26426100</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B158" t="n">
-        <v>338.3103690890599</v>
+        <v>345.55136124882</v>
       </c>
       <c r="C158" t="n">
-        <v>344.8422449444718</v>
+        <v>352.7424225666816</v>
       </c>
       <c r="D158" t="n">
-        <v>334.9745105669949</v>
+        <v>342.3053878156813</v>
       </c>
       <c r="E158" t="n">
-        <v>343.9733276367188</v>
+        <v>349.9059448242188</v>
       </c>
       <c r="F158" t="n">
-        <v>26426100</v>
+        <v>28576900</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B159" t="n">
-        <v>345.5513913866066</v>
+        <v>348.1181620694143</v>
       </c>
       <c r="C159" t="n">
-        <v>352.7424533316474</v>
+        <v>351.9833930501032</v>
       </c>
       <c r="D159" t="n">
-        <v>342.3054176703653</v>
+        <v>345.6911799613628</v>
       </c>
       <c r="E159" t="n">
-        <v>349.9059753417969</v>
+        <v>349.3466491699219</v>
       </c>
       <c r="F159" t="n">
-        <v>28576900</v>
+        <v>27824100</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B160" t="n">
-        <v>348.1181924796765</v>
+        <v>347.1394107424554</v>
       </c>
       <c r="C160" t="n">
-        <v>351.9834237980171</v>
+        <v>355.3492283904879</v>
       </c>
       <c r="D160" t="n">
-        <v>345.6912101596132</v>
+        <v>343.7835575206014</v>
       </c>
       <c r="E160" t="n">
-        <v>349.3466796875</v>
+        <v>349.5064697265625</v>
       </c>
       <c r="F160" t="n">
-        <v>27824100</v>
+        <v>35376300</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B161" t="n">
-        <v>347.1393804315599</v>
+        <v>373.6065555628184</v>
       </c>
       <c r="C161" t="n">
-        <v>355.3491973627422</v>
+        <v>385.3619622201579</v>
       </c>
       <c r="D161" t="n">
-        <v>343.7835275027263</v>
+        <v>365.3667768501622</v>
       </c>
       <c r="E161" t="n">
-        <v>349.5064392089844</v>
+        <v>384.3232421875</v>
       </c>
       <c r="F161" t="n">
-        <v>35376300</v>
+        <v>72040000</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B162" t="n">
-        <v>373.6065555628184</v>
+        <v>381.1572209075714</v>
       </c>
       <c r="C162" t="n">
-        <v>385.3619622201579</v>
+        <v>386.2808704617397</v>
       </c>
       <c r="D162" t="n">
-        <v>365.3667768501622</v>
+        <v>378.5804000830116</v>
       </c>
       <c r="E162" t="n">
-        <v>384.3232421875</v>
+        <v>385.2121887207031</v>
       </c>
       <c r="F162" t="n">
-        <v>72040000</v>
+        <v>30105200</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B163" t="n">
-        <v>381.1572209075714</v>
+        <v>385.1522332062169</v>
       </c>
       <c r="C163" t="n">
-        <v>386.2808704617397</v>
+        <v>386.9000650646732</v>
       </c>
       <c r="D163" t="n">
-        <v>378.5804000830116</v>
+        <v>379.3194722618546</v>
       </c>
       <c r="E163" t="n">
-        <v>385.2121887207031</v>
+        <v>382.7751770019531</v>
       </c>
       <c r="F163" t="n">
-        <v>30105200</v>
+        <v>26298600</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B164" t="n">
-        <v>385.1522332062169</v>
+        <v>385.7515048868787</v>
       </c>
       <c r="C164" t="n">
-        <v>386.9000650646732</v>
+        <v>392.3333367803882</v>
       </c>
       <c r="D164" t="n">
-        <v>379.3194722618546</v>
+        <v>383.5442209432822</v>
       </c>
       <c r="E164" t="n">
-        <v>382.7751770019531</v>
+        <v>387.9487609863281</v>
       </c>
       <c r="F164" t="n">
-        <v>26298600</v>
+        <v>23878600</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B165" t="n">
-        <v>385.7515048868787</v>
+        <v>393.7615619135972</v>
       </c>
       <c r="C165" t="n">
-        <v>392.3333367803882</v>
+        <v>399.3546301445318</v>
       </c>
       <c r="D165" t="n">
-        <v>383.5442209432822</v>
+        <v>392.2734176347804</v>
       </c>
       <c r="E165" t="n">
-        <v>387.9487609863281</v>
+        <v>397.546875</v>
       </c>
       <c r="F165" t="n">
-        <v>23878600</v>
+        <v>31308500</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B166" t="n">
-        <v>393.7615619135972</v>
+        <v>399.4245497990884</v>
       </c>
       <c r="C166" t="n">
-        <v>399.3546301445318</v>
+        <v>399.6043194807176</v>
       </c>
       <c r="D166" t="n">
-        <v>392.2734176347804</v>
+        <v>392.1934987581594</v>
       </c>
       <c r="E166" t="n">
-        <v>397.546875</v>
+        <v>397.4969177246094</v>
       </c>
       <c r="F166" t="n">
-        <v>31308500</v>
+        <v>24433500</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B167" t="n">
-        <v>399.4245497990884</v>
+        <v>396.5081562950806</v>
       </c>
       <c r="C167" t="n">
-        <v>399.6043194807176</v>
+        <v>401.5019617899809</v>
       </c>
       <c r="D167" t="n">
-        <v>392.1934987581594</v>
+        <v>395.8689345614438</v>
       </c>
       <c r="E167" t="n">
-        <v>397.4969177246094</v>
+        <v>400.3034362792969</v>
       </c>
       <c r="F167" t="n">
-        <v>24433500</v>
+        <v>21461800</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B168" t="n">
-        <v>396.5081562950806</v>
+        <v>393.1622804247065</v>
       </c>
       <c r="C168" t="n">
-        <v>401.5019617899809</v>
+        <v>396.9475933307253</v>
       </c>
       <c r="D168" t="n">
-        <v>395.8689345614438</v>
+        <v>387.9887055115338</v>
       </c>
       <c r="E168" t="n">
-        <v>400.3034362792969</v>
+        <v>388.1585083007812</v>
       </c>
       <c r="F168" t="n">
-        <v>21461800</v>
+        <v>30753700</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B169" t="n">
-        <v>393.1623113356883</v>
+        <v>386.8601198229993</v>
       </c>
       <c r="C169" t="n">
-        <v>396.9476245393139</v>
+        <v>388.0386506028281</v>
       </c>
       <c r="D169" t="n">
-        <v>387.9887360157618</v>
+        <v>382.2957742925754</v>
       </c>
       <c r="E169" t="n">
-        <v>388.1585388183594</v>
+        <v>386.8701171875</v>
       </c>
       <c r="F169" t="n">
-        <v>30753700</v>
+        <v>26017500</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B170" t="n">
-        <v>386.8601198229993</v>
+        <v>385.1222825184223</v>
       </c>
       <c r="C170" t="n">
-        <v>388.0386506028281</v>
+        <v>403.1998643489371</v>
       </c>
       <c r="D170" t="n">
-        <v>382.2957742925754</v>
+        <v>384.5230197682841</v>
       </c>
       <c r="E170" t="n">
-        <v>386.8701171875</v>
+        <v>402.1211853027344</v>
       </c>
       <c r="F170" t="n">
-        <v>26017500</v>
+        <v>28144600</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B171" t="n">
-        <v>385.1222825184223</v>
+        <v>396.7878070287349</v>
       </c>
       <c r="C171" t="n">
-        <v>403.1998643489371</v>
+        <v>402.430801125594</v>
       </c>
       <c r="D171" t="n">
-        <v>384.5230197682841</v>
+        <v>395.349588612008</v>
       </c>
       <c r="E171" t="n">
-        <v>402.1211853027344</v>
+        <v>400.5731201171875</v>
       </c>
       <c r="F171" t="n">
-        <v>28144600</v>
+        <v>21136700</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B172" t="n">
-        <v>396.7878070287349</v>
+        <v>395.8290000666237</v>
       </c>
       <c r="C172" t="n">
-        <v>402.430801125594</v>
+        <v>399.0450119758119</v>
       </c>
       <c r="D172" t="n">
-        <v>395.349588612008</v>
+        <v>392.692875633045</v>
       </c>
       <c r="E172" t="n">
-        <v>400.5731201171875</v>
+        <v>396.2884216308594</v>
       </c>
       <c r="F172" t="n">
-        <v>21136700</v>
+        <v>20309700</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B173" t="n">
-        <v>395.8290000666237</v>
+        <v>395.1997907850553</v>
       </c>
       <c r="C173" t="n">
-        <v>399.0450119758119</v>
+        <v>408.1037674120522</v>
       </c>
       <c r="D173" t="n">
-        <v>392.692875633045</v>
+        <v>394.0412242260142</v>
       </c>
       <c r="E173" t="n">
-        <v>396.2884216308594</v>
+        <v>396.4482421875</v>
       </c>
       <c r="F173" t="n">
-        <v>20309700</v>
+        <v>26837200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B174" t="n">
-        <v>395.1997907850553</v>
+        <v>396.4681837278221</v>
       </c>
       <c r="C174" t="n">
-        <v>408.1037674120522</v>
+        <v>396.6579507685057</v>
       </c>
       <c r="D174" t="n">
-        <v>394.0412242260142</v>
+        <v>385.6316200793582</v>
       </c>
       <c r="E174" t="n">
-        <v>396.4482421875</v>
+        <v>387.1797180175781</v>
       </c>
       <c r="F174" t="n">
-        <v>26837200</v>
+        <v>39545700</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B175" t="n">
-        <v>396.4681837278221</v>
+        <v>387.2196997137571</v>
       </c>
       <c r="C175" t="n">
-        <v>396.6579507685057</v>
+        <v>393.3720414113799</v>
       </c>
       <c r="D175" t="n">
-        <v>385.6316200793582</v>
+        <v>382.4256280338265</v>
       </c>
       <c r="E175" t="n">
-        <v>387.1797180175781</v>
+        <v>388.4281921386719</v>
       </c>
       <c r="F175" t="n">
-        <v>39545700</v>
+        <v>31744400</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B176" t="n">
-        <v>387.2196997137571</v>
+        <v>385.2221548650083</v>
       </c>
       <c r="C176" t="n">
-        <v>393.3720414113799</v>
+        <v>392.0137179133836</v>
       </c>
       <c r="D176" t="n">
-        <v>382.4256280338265</v>
+        <v>382.5454520468608</v>
       </c>
       <c r="E176" t="n">
-        <v>388.4281921386719</v>
+        <v>387.1797180175781</v>
       </c>
       <c r="F176" t="n">
-        <v>31744400</v>
+        <v>24852800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B177" t="n">
-        <v>385.2221548650083</v>
+        <v>386.8701229826527</v>
       </c>
       <c r="C177" t="n">
-        <v>392.0137179133836</v>
+        <v>388.258385079403</v>
       </c>
       <c r="D177" t="n">
-        <v>382.5454520468608</v>
+        <v>381.2970189068101</v>
       </c>
       <c r="E177" t="n">
-        <v>387.1797180175781</v>
+        <v>382.4955444335938</v>
       </c>
       <c r="F177" t="n">
-        <v>24852800</v>
+        <v>20442100</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B178" t="n">
-        <v>386.8701229826527</v>
+        <v>384.0336125447445</v>
       </c>
       <c r="C178" t="n">
-        <v>388.258385079403</v>
+        <v>388.7777274266938</v>
       </c>
       <c r="D178" t="n">
-        <v>381.2970189068101</v>
+        <v>382.125975324115</v>
       </c>
       <c r="E178" t="n">
-        <v>382.4955444335938</v>
+        <v>388.398193359375</v>
       </c>
       <c r="F178" t="n">
-        <v>20442100</v>
+        <v>27747400</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B179" t="n">
-        <v>384.0336427193848</v>
+        <v>386.1909390913781</v>
       </c>
       <c r="C179" t="n">
-        <v>388.777757974093</v>
+        <v>393.3919975499695</v>
       </c>
       <c r="D179" t="n">
-        <v>382.1260053488666</v>
+        <v>385.421873594791</v>
       </c>
       <c r="E179" t="n">
-        <v>388.3982238769531</v>
+        <v>388.3482360839844</v>
       </c>
       <c r="F179" t="n">
-        <v>27747400</v>
+        <v>23087300</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B180" t="n">
-        <v>386.1909694394293</v>
+        <v>387.5193014898567</v>
       </c>
       <c r="C180" t="n">
-        <v>393.3920284639016</v>
+        <v>391.384502017129</v>
       </c>
       <c r="D180" t="n">
-        <v>385.4219038824068</v>
+        <v>384.682823662297</v>
       </c>
       <c r="E180" t="n">
-        <v>388.3482666015625</v>
+        <v>389.6466674804688</v>
       </c>
       <c r="F180" t="n">
-        <v>23087300</v>
+        <v>24357500</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B181" t="n">
-        <v>387.5193014898567</v>
+        <v>384.7626974671623</v>
       </c>
       <c r="C181" t="n">
-        <v>391.384502017129</v>
+        <v>384.7626974671623</v>
       </c>
       <c r="D181" t="n">
-        <v>384.682823662297</v>
+        <v>377.9910987617443</v>
       </c>
       <c r="E181" t="n">
-        <v>389.6466674804688</v>
+        <v>379.8687744140625</v>
       </c>
       <c r="F181" t="n">
-        <v>24357500</v>
+        <v>44415800</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B182" t="n">
-        <v>384.7626974671623</v>
+        <v>376.0535251127361</v>
       </c>
       <c r="C182" t="n">
-        <v>384.7626974671623</v>
+        <v>378.0910063274455</v>
       </c>
       <c r="D182" t="n">
-        <v>377.9910987617443</v>
+        <v>373.0572417592452</v>
       </c>
       <c r="E182" t="n">
-        <v>379.8687744140625</v>
+        <v>375.9037170410156</v>
       </c>
       <c r="F182" t="n">
-        <v>44415800</v>
+        <v>28672100</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B183" t="n">
-        <v>376.0535251127361</v>
+        <v>366.1358206463617</v>
       </c>
       <c r="C183" t="n">
-        <v>378.0910063274455</v>
+        <v>373.0772223440179</v>
       </c>
       <c r="D183" t="n">
-        <v>373.0572417592452</v>
+        <v>357.9959239406105</v>
       </c>
       <c r="E183" t="n">
-        <v>375.9037170410156</v>
+        <v>361.4017028808594</v>
       </c>
       <c r="F183" t="n">
-        <v>28672100</v>
+        <v>50412300</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B184" t="n">
-        <v>366.1358206463617</v>
+        <v>361.5814692403301</v>
       </c>
       <c r="C184" t="n">
-        <v>373.0772223440179</v>
+        <v>365.9960065843375</v>
       </c>
       <c r="D184" t="n">
-        <v>357.9959239406105</v>
+        <v>357.6363508187865</v>
       </c>
       <c r="E184" t="n">
-        <v>361.4017028808594</v>
+        <v>358.5452270507812</v>
       </c>
       <c r="F184" t="n">
-        <v>50412300</v>
+        <v>55441600</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B185" t="n">
-        <v>361.5814692403301</v>
+        <v>358.4553682250688</v>
       </c>
       <c r="C185" t="n">
-        <v>365.9960065843375</v>
+        <v>372.7875967270043</v>
       </c>
       <c r="D185" t="n">
-        <v>357.6363508187865</v>
+        <v>357.7662205978281</v>
       </c>
       <c r="E185" t="n">
-        <v>358.5452270507812</v>
+        <v>371.7289123535156</v>
       </c>
       <c r="F185" t="n">
-        <v>55441600</v>
+        <v>44055500</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B186" t="n">
-        <v>358.4553387971999</v>
+        <v>365.8861360555161</v>
       </c>
       <c r="C186" t="n">
-        <v>372.7875661225121</v>
+        <v>371.6190149899659</v>
       </c>
       <c r="D186" t="n">
-        <v>357.7661912265356</v>
+        <v>363.6688852043904</v>
       </c>
       <c r="E186" t="n">
-        <v>371.7288818359375</v>
+        <v>368.0734252929688</v>
       </c>
       <c r="F186" t="n">
-        <v>44055500</v>
+        <v>37471200</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,25 +5279,25 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B187" t="n">
-        <v>365.8861360555161</v>
+        <v>364.9454235864071</v>
       </c>
       <c r="C187" t="n">
-        <v>371.6190149899659</v>
+        <v>365.9647879200631</v>
       </c>
       <c r="D187" t="n">
-        <v>363.6688852043904</v>
+        <v>360.2984165590168</v>
       </c>
       <c r="E187" t="n">
-        <v>368.0734252929688</v>
+        <v>363.0766296386719</v>
       </c>
       <c r="F187" t="n">
-        <v>37471200</v>
+        <v>27942500</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5305,25 +5305,25 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B188" t="n">
-        <v>364.9454235864071</v>
+        <v>366.8542002567407</v>
       </c>
       <c r="C188" t="n">
-        <v>365.9647879200631</v>
+        <v>371.8409852276818</v>
       </c>
       <c r="D188" t="n">
-        <v>360.2984165590168</v>
+        <v>357.0704802123837</v>
       </c>
       <c r="E188" t="n">
-        <v>363.0766296386719</v>
+        <v>364.0260314941406</v>
       </c>
       <c r="F188" t="n">
-        <v>27942500</v>
+        <v>29535100</v>
       </c>
       <c r="G188" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B189" t="n">
-        <v>366.8542002567407</v>
+        <v>362.9567158453764</v>
       </c>
       <c r="C189" t="n">
-        <v>371.8409852276818</v>
+        <v>368.3232616719084</v>
       </c>
       <c r="D189" t="n">
-        <v>357.0704802123837</v>
+        <v>354.9718577941881</v>
       </c>
       <c r="E189" t="n">
-        <v>364.0260314941406</v>
+        <v>356.1510925292969</v>
       </c>
       <c r="F189" t="n">
-        <v>29535100</v>
+        <v>32357100</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B190" t="n">
-        <v>362.9567158453764</v>
+        <v>355.7013467902599</v>
       </c>
       <c r="C190" t="n">
-        <v>368.3232616719084</v>
+        <v>358.5694982511428</v>
       </c>
       <c r="D190" t="n">
-        <v>354.9718577941881</v>
+        <v>346.1374871435174</v>
       </c>
       <c r="E190" t="n">
-        <v>356.1510925292969</v>
+        <v>357.5401611328125</v>
       </c>
       <c r="F190" t="n">
-        <v>32357100</v>
+        <v>35538200</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B191" t="n">
-        <v>355.7013467902599</v>
+        <v>362.3870579560934</v>
       </c>
       <c r="C191" t="n">
-        <v>358.5694982511428</v>
+        <v>366.3345327833823</v>
       </c>
       <c r="D191" t="n">
-        <v>346.1374871435174</v>
+        <v>354.7119986974298</v>
       </c>
       <c r="E191" t="n">
-        <v>357.5401611328125</v>
+        <v>359.4489440917969</v>
       </c>
       <c r="F191" t="n">
-        <v>35538200</v>
+        <v>24704600</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B192" t="n">
-        <v>362.3870579560934</v>
+        <v>367.6936611370598</v>
       </c>
       <c r="C192" t="n">
-        <v>366.3345327833823</v>
+        <v>372.7504085202595</v>
       </c>
       <c r="D192" t="n">
-        <v>354.7119986974298</v>
+        <v>366.3145426692825</v>
       </c>
       <c r="E192" t="n">
-        <v>359.4489440917969</v>
+        <v>369.1127624511719</v>
       </c>
       <c r="F192" t="n">
-        <v>24704600</v>
+        <v>27727500</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B193" t="n">
-        <v>367.6936611370598</v>
+        <v>369.3626044753487</v>
       </c>
       <c r="C193" t="n">
-        <v>372.7504085202595</v>
+        <v>375.7584875251172</v>
       </c>
       <c r="D193" t="n">
-        <v>366.3145426692825</v>
+        <v>366.8242274297617</v>
       </c>
       <c r="E193" t="n">
-        <v>369.1127624511719</v>
+        <v>373.01025390625</v>
       </c>
       <c r="F193" t="n">
-        <v>27727500</v>
+        <v>24876100</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B194" t="n">
-        <v>369.3626044753487</v>
+        <v>368.8929017493238</v>
       </c>
       <c r="C194" t="n">
-        <v>375.7584875251172</v>
+        <v>372.0908279957741</v>
       </c>
       <c r="D194" t="n">
-        <v>366.8242274297617</v>
+        <v>361.7874528539307</v>
       </c>
       <c r="E194" t="n">
-        <v>373.01025390625</v>
+        <v>363.5563354492188</v>
       </c>
       <c r="F194" t="n">
-        <v>24876100</v>
+        <v>24543600</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B195" t="n">
-        <v>368.8929017493238</v>
+        <v>365.5150449761754</v>
       </c>
       <c r="C195" t="n">
-        <v>372.0908279957741</v>
+        <v>369.2426598317581</v>
       </c>
       <c r="D195" t="n">
-        <v>361.7874528539307</v>
+        <v>358.4396065335441</v>
       </c>
       <c r="E195" t="n">
-        <v>363.5563354492188</v>
+        <v>367.7935791015625</v>
       </c>
       <c r="F195" t="n">
-        <v>24543600</v>
+        <v>44470100</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B196" t="n">
-        <v>365.5150449761754</v>
+        <v>357.7200907639775</v>
       </c>
       <c r="C196" t="n">
-        <v>369.2426598317581</v>
+        <v>358.6894689253907</v>
       </c>
       <c r="D196" t="n">
-        <v>358.4396065335441</v>
+        <v>341.5005047739323</v>
       </c>
       <c r="E196" t="n">
-        <v>367.7935791015625</v>
+        <v>349.4553833007812</v>
       </c>
       <c r="F196" t="n">
-        <v>44470100</v>
+        <v>52814800</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B197" t="n">
-        <v>357.7200907639775</v>
+        <v>340.4711459801061</v>
       </c>
       <c r="C197" t="n">
-        <v>358.6894689253907</v>
+        <v>349.0656275102868</v>
       </c>
       <c r="D197" t="n">
-        <v>341.5005047739323</v>
+        <v>339.981470511436</v>
       </c>
       <c r="E197" t="n">
-        <v>349.4553833007812</v>
+        <v>345.9076538085938</v>
       </c>
       <c r="F197" t="n">
-        <v>52814800</v>
+        <v>34007700</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B198" t="n">
-        <v>340.4711459801061</v>
+        <v>348.8157979233392</v>
       </c>
       <c r="C198" t="n">
-        <v>349.0656275102868</v>
+        <v>353.2529482684732</v>
       </c>
       <c r="D198" t="n">
-        <v>339.981470511436</v>
+        <v>341.7103492701006</v>
       </c>
       <c r="E198" t="n">
-        <v>345.9076538085938</v>
+        <v>345.0682067871094</v>
       </c>
       <c r="F198" t="n">
-        <v>34007700</v>
+        <v>44997300</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B199" t="n">
-        <v>348.8157979233392</v>
+        <v>336.5137001542092</v>
       </c>
       <c r="C199" t="n">
-        <v>353.2529482684732</v>
+        <v>345.3480177972958</v>
       </c>
       <c r="D199" t="n">
-        <v>341.7103492701006</v>
+        <v>335.6242572392167</v>
       </c>
       <c r="E199" t="n">
-        <v>345.0682067871094</v>
+        <v>343.4891967773438</v>
       </c>
       <c r="F199" t="n">
-        <v>44997300</v>
+        <v>44491400</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B200" t="n">
-        <v>336.5137001542092</v>
+        <v>342.3299372399903</v>
       </c>
       <c r="C200" t="n">
-        <v>345.3480177972958</v>
+        <v>346.1374872957393</v>
       </c>
       <c r="D200" t="n">
-        <v>335.6242572392167</v>
+        <v>329.98789515005</v>
       </c>
       <c r="E200" t="n">
-        <v>343.4891967773438</v>
+        <v>337.1732788085938</v>
       </c>
       <c r="F200" t="n">
-        <v>44491400</v>
+        <v>114706300</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B201" t="n">
-        <v>342.3299372399903</v>
+        <v>341.6104064955248</v>
       </c>
       <c r="C201" t="n">
-        <v>346.1374872957393</v>
+        <v>354.122383587675</v>
       </c>
       <c r="D201" t="n">
-        <v>329.98789515005</v>
+        <v>340.4511784786947</v>
       </c>
       <c r="E201" t="n">
-        <v>337.1732788085938</v>
+        <v>353.4228210449219</v>
       </c>
       <c r="F201" t="n">
-        <v>114706300</v>
+        <v>34213900</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B202" t="n">
-        <v>341.6104064955248</v>
+        <v>353.6426900862941</v>
       </c>
       <c r="C202" t="n">
-        <v>354.122383587675</v>
+        <v>358.3896389689017</v>
       </c>
       <c r="D202" t="n">
-        <v>340.4511784786947</v>
+        <v>350.1749177879227</v>
       </c>
       <c r="E202" t="n">
-        <v>353.4228210449219</v>
+        <v>357.1404418945312</v>
       </c>
       <c r="F202" t="n">
-        <v>34213900</v>
+        <v>35237200</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B203" t="n">
-        <v>353.6426900862941</v>
+        <v>358.1397942573561</v>
       </c>
       <c r="C203" t="n">
-        <v>358.3896389689017</v>
+        <v>362.7368455226467</v>
       </c>
       <c r="D203" t="n">
-        <v>350.1749177879227</v>
+        <v>356.2010379867681</v>
       </c>
       <c r="E203" t="n">
-        <v>357.1404418945312</v>
+        <v>360.9779663085938</v>
       </c>
       <c r="F203" t="n">
-        <v>35237200</v>
+        <v>26736400</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B204" t="n">
-        <v>358.1397942573561</v>
+        <v>359.2490860357571</v>
       </c>
       <c r="C204" t="n">
-        <v>362.7368455226467</v>
+        <v>363.9760280309549</v>
       </c>
       <c r="D204" t="n">
-        <v>356.2010379867681</v>
+        <v>353.1929813351636</v>
       </c>
       <c r="E204" t="n">
-        <v>360.9779663085938</v>
+        <v>359.6788024902344</v>
       </c>
       <c r="F204" t="n">
-        <v>26736400</v>
+        <v>25974800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B205" t="n">
-        <v>359.2490860357571</v>
+        <v>361.3177293642356</v>
       </c>
       <c r="C205" t="n">
-        <v>363.9760280309549</v>
+        <v>367.693635754559</v>
       </c>
       <c r="D205" t="n">
-        <v>353.1929813351636</v>
+        <v>357.1504252362982</v>
       </c>
       <c r="E205" t="n">
-        <v>359.6788024902344</v>
+        <v>366.2245788574219</v>
       </c>
       <c r="F205" t="n">
-        <v>25974800</v>
+        <v>26915800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B206" t="n">
-        <v>361.3177293642356</v>
+        <v>368.8329180211536</v>
       </c>
       <c r="C206" t="n">
-        <v>367.693635754559</v>
+        <v>372.9202869594668</v>
       </c>
       <c r="D206" t="n">
-        <v>357.1504252362982</v>
+        <v>365.2652040573587</v>
       </c>
       <c r="E206" t="n">
-        <v>366.2245788574219</v>
+        <v>366.7942199707031</v>
       </c>
       <c r="F206" t="n">
-        <v>26915800</v>
+        <v>24045600</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B207" t="n">
-        <v>368.8329180211536</v>
+        <v>364.525702555654</v>
       </c>
       <c r="C207" t="n">
-        <v>372.9202869594668</v>
+        <v>367.6037106679975</v>
       </c>
       <c r="D207" t="n">
-        <v>365.2652040573587</v>
+        <v>357.7900113228786</v>
       </c>
       <c r="E207" t="n">
-        <v>366.7942199707031</v>
+        <v>361.6875305175781</v>
       </c>
       <c r="F207" t="n">
-        <v>24045600</v>
+        <v>22094800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B208" t="n">
-        <v>364.525702555654</v>
+        <v>354.0824097063769</v>
       </c>
       <c r="C208" t="n">
-        <v>367.6037106679975</v>
+        <v>359.4189759454678</v>
       </c>
       <c r="D208" t="n">
-        <v>357.7900113228786</v>
+        <v>350.8544734886641</v>
       </c>
       <c r="E208" t="n">
-        <v>361.6875305175781</v>
+        <v>358.6594848632812</v>
       </c>
       <c r="F208" t="n">
-        <v>22094800</v>
+        <v>24729100</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B209" t="n">
-        <v>354.0824097063769</v>
+        <v>357.3003428038799</v>
       </c>
       <c r="C209" t="n">
-        <v>359.4189759454678</v>
+        <v>357.5901650645865</v>
       </c>
       <c r="D209" t="n">
-        <v>350.8544734886641</v>
+        <v>352.5234144110846</v>
       </c>
       <c r="E209" t="n">
-        <v>358.6594848632812</v>
+        <v>356.9505615234375</v>
       </c>
       <c r="F209" t="n">
-        <v>24729100</v>
+        <v>18146100</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B210" t="n">
-        <v>357.3003428038799</v>
+        <v>355.9611981097028</v>
       </c>
       <c r="C210" t="n">
-        <v>357.5901650645865</v>
+        <v>357.8999543595846</v>
       </c>
       <c r="D210" t="n">
-        <v>352.5234144110846</v>
+        <v>351.5240477747128</v>
       </c>
       <c r="E210" t="n">
-        <v>356.9505615234375</v>
+        <v>352.2835693359375</v>
       </c>
       <c r="F210" t="n">
-        <v>18146100</v>
+        <v>15901700</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B211" t="n">
-        <v>355.9611981097028</v>
+        <v>350.9744235107016</v>
       </c>
       <c r="C211" t="n">
-        <v>357.8999543595846</v>
+        <v>359.92865963343</v>
       </c>
       <c r="D211" t="n">
-        <v>351.5240477747128</v>
+        <v>350.8644783088037</v>
       </c>
       <c r="E211" t="n">
-        <v>352.2835693359375</v>
+        <v>359.2790832519531</v>
       </c>
       <c r="F211" t="n">
-        <v>15901700</v>
+        <v>18259400</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B212" t="n">
-        <v>350.9744235107016</v>
+        <v>357.7400685886304</v>
       </c>
       <c r="C212" t="n">
-        <v>359.92865963343</v>
+        <v>373.4099896327818</v>
       </c>
       <c r="D212" t="n">
-        <v>350.8644783088037</v>
+        <v>357.5302120160503</v>
       </c>
       <c r="E212" t="n">
-        <v>359.2790832519531</v>
+        <v>370.6817626953125</v>
       </c>
       <c r="F212" t="n">
-        <v>18259400</v>
+        <v>28284600</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B213" t="n">
-        <v>357.7400685886304</v>
+        <v>372.8203579699616</v>
       </c>
       <c r="C213" t="n">
-        <v>373.4099896327818</v>
+        <v>375.0289298103755</v>
       </c>
       <c r="D213" t="n">
-        <v>357.5302120160503</v>
+        <v>352.0736836469807</v>
       </c>
       <c r="E213" t="n">
-        <v>370.6817626953125</v>
+        <v>354.2322998046875</v>
       </c>
       <c r="F213" t="n">
-        <v>28284600</v>
+        <v>41158500</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B214" t="n">
-        <v>372.8203579699616</v>
+        <v>345.7777467999313</v>
       </c>
       <c r="C214" t="n">
-        <v>375.0289298103755</v>
+        <v>348.2961170979314</v>
       </c>
       <c r="D214" t="n">
-        <v>352.0736836469807</v>
+        <v>341.1407126662452</v>
       </c>
       <c r="E214" t="n">
-        <v>354.2322998046875</v>
+        <v>346.5472412109375</v>
       </c>
       <c r="F214" t="n">
-        <v>41158500</v>
+        <v>29959300</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B215" t="n">
-        <v>345.7777467999313</v>
+        <v>350.6546131580819</v>
       </c>
       <c r="C215" t="n">
-        <v>348.2961170979314</v>
+        <v>359.4489481797366</v>
       </c>
       <c r="D215" t="n">
-        <v>341.1407126662452</v>
+        <v>350.2948285491913</v>
       </c>
       <c r="E215" t="n">
-        <v>346.5472412109375</v>
+        <v>351.7638854980469</v>
       </c>
       <c r="F215" t="n">
-        <v>29959300</v>
+        <v>24736600</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B216" t="n">
-        <v>350.6546131580819</v>
+        <v>351.094336770995</v>
       </c>
       <c r="C216" t="n">
-        <v>359.4489481797366</v>
+        <v>351.094336770995</v>
       </c>
       <c r="D216" t="n">
-        <v>350.2948285491913</v>
+        <v>346.7771044052826</v>
       </c>
       <c r="E216" t="n">
-        <v>351.7638854980469</v>
+        <v>346.927001953125</v>
       </c>
       <c r="F216" t="n">
-        <v>24736600</v>
+        <v>23369800</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B217" t="n">
-        <v>351.094336770995</v>
+        <v>347.9363472365376</v>
       </c>
       <c r="C217" t="n">
-        <v>351.094336770995</v>
+        <v>349.7152025525983</v>
       </c>
       <c r="D217" t="n">
-        <v>346.7771044052826</v>
+        <v>341.5104851592261</v>
       </c>
       <c r="E217" t="n">
-        <v>346.927001953125</v>
+        <v>341.8702392578125</v>
       </c>
       <c r="F217" t="n">
-        <v>23369800</v>
+        <v>39334100</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B218" t="n">
-        <v>347.9363472365376</v>
+        <v>320.9237241212255</v>
       </c>
       <c r="C218" t="n">
-        <v>349.7152025525983</v>
+        <v>324.2815511558238</v>
       </c>
       <c r="D218" t="n">
-        <v>341.5104851592261</v>
+        <v>314.6977150387725</v>
       </c>
       <c r="E218" t="n">
-        <v>341.8702392578125</v>
+        <v>317.4859313964844</v>
       </c>
       <c r="F218" t="n">
-        <v>39334100</v>
+        <v>69419700</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B219" t="n">
-        <v>320.9237241212255</v>
+        <v>318.2154780071113</v>
       </c>
       <c r="C219" t="n">
-        <v>324.2815511558238</v>
+        <v>323.9717573627877</v>
       </c>
       <c r="D219" t="n">
-        <v>314.6977150387725</v>
+        <v>317.1161784867298</v>
       </c>
       <c r="E219" t="n">
-        <v>317.4859313964844</v>
+        <v>319.5346069335938</v>
       </c>
       <c r="F219" t="n">
-        <v>69419700</v>
+        <v>31806600</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B220" t="n">
-        <v>318.2154780071113</v>
+        <v>324.83120713377</v>
       </c>
       <c r="C220" t="n">
-        <v>323.9717573627877</v>
+        <v>330.2077559724587</v>
       </c>
       <c r="D220" t="n">
-        <v>317.1161784867298</v>
+        <v>324.2415898017393</v>
       </c>
       <c r="E220" t="n">
-        <v>319.5346069335938</v>
+        <v>326.3502197265625</v>
       </c>
       <c r="F220" t="n">
-        <v>31806600</v>
+        <v>28471600</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B221" t="n">
-        <v>324.83120713377</v>
+        <v>327.6893704249235</v>
       </c>
       <c r="C221" t="n">
-        <v>330.2077559724587</v>
+        <v>335.6642555263833</v>
       </c>
       <c r="D221" t="n">
-        <v>324.2415898017393</v>
+        <v>324.2316014627561</v>
       </c>
       <c r="E221" t="n">
-        <v>326.3502197265625</v>
+        <v>333.4956359863281</v>
       </c>
       <c r="F221" t="n">
-        <v>28471600</v>
+        <v>29511900</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B222" t="n">
-        <v>327.6893704249235</v>
+        <v>334.455045685483</v>
       </c>
       <c r="C222" t="n">
-        <v>335.6642555263833</v>
+        <v>342.2800028423013</v>
       </c>
       <c r="D222" t="n">
-        <v>324.2316014627561</v>
+        <v>331.4069864854741</v>
       </c>
       <c r="E222" t="n">
-        <v>333.4956359863281</v>
+        <v>336.4937133789062</v>
       </c>
       <c r="F222" t="n">
-        <v>29511900</v>
+        <v>27501600</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B223" t="n">
-        <v>334.455045685483</v>
+        <v>333.9853403838827</v>
       </c>
       <c r="C223" t="n">
-        <v>342.2800028423013</v>
+        <v>336.2938541262907</v>
       </c>
       <c r="D223" t="n">
-        <v>331.4069864854741</v>
+        <v>330.1278039779788</v>
       </c>
       <c r="E223" t="n">
-        <v>336.4937133789062</v>
+        <v>333.4456787109375</v>
       </c>
       <c r="F223" t="n">
-        <v>27501600</v>
+        <v>30168000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B224" t="n">
-        <v>333.9853403838827</v>
+        <v>340.611054758666</v>
       </c>
       <c r="C224" t="n">
-        <v>336.2938541262907</v>
+        <v>358.3496530632621</v>
       </c>
       <c r="D224" t="n">
-        <v>330.1278039779788</v>
+        <v>339.7816013274756</v>
       </c>
       <c r="E224" t="n">
-        <v>333.4456787109375</v>
+        <v>355.9012451171875</v>
       </c>
       <c r="F224" t="n">
-        <v>30168000</v>
+        <v>46498000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B225" t="n">
-        <v>340.611054758666</v>
+        <v>365.2152604560987</v>
       </c>
       <c r="C225" t="n">
-        <v>358.3496530632621</v>
+        <v>376.4480305309448</v>
       </c>
       <c r="D225" t="n">
-        <v>339.7816013274756</v>
+        <v>363.1166033198653</v>
       </c>
       <c r="E225" t="n">
-        <v>355.9012451171875</v>
+        <v>373.2700805664062</v>
       </c>
       <c r="F225" t="n">
-        <v>46498000</v>
+        <v>38669700</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B226" t="n">
-        <v>365.2152604560987</v>
+        <v>367.9834743668337</v>
       </c>
       <c r="C226" t="n">
-        <v>376.4480305309448</v>
+        <v>380.2755612380555</v>
       </c>
       <c r="D226" t="n">
-        <v>363.1166033198653</v>
+        <v>367.263935640354</v>
       </c>
       <c r="E226" t="n">
-        <v>373.2700805664062</v>
+        <v>377.4074096679688</v>
       </c>
       <c r="F226" t="n">
-        <v>38669700</v>
+        <v>35705700</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B227" t="n">
-        <v>367.9834743668337</v>
+        <v>383.0937455186354</v>
       </c>
       <c r="C227" t="n">
-        <v>380.2755612380555</v>
+        <v>384.2330278418686</v>
       </c>
       <c r="D227" t="n">
-        <v>367.263935640354</v>
+        <v>356.5408062961898</v>
       </c>
       <c r="E227" t="n">
-        <v>377.4074096679688</v>
+        <v>362.1971740722656</v>
       </c>
       <c r="F227" t="n">
-        <v>35705700</v>
+        <v>46926300</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B228" t="n">
-        <v>383.0937455186354</v>
+        <v>360.5382517887205</v>
       </c>
       <c r="C228" t="n">
-        <v>384.2330278418686</v>
+        <v>363.8961093831237</v>
       </c>
       <c r="D228" t="n">
-        <v>356.5408062961898</v>
+        <v>356.6507663527499</v>
       </c>
       <c r="E228" t="n">
-        <v>362.1971740722656</v>
+        <v>357.5202026367188</v>
       </c>
       <c r="F228" t="n">
-        <v>46926300</v>
+        <v>25235900</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B229" t="n">
-        <v>360.5382517887205</v>
+        <v>356.4908465215469</v>
       </c>
       <c r="C229" t="n">
-        <v>363.8961093831237</v>
+        <v>358.6694387836589</v>
       </c>
       <c r="D229" t="n">
-        <v>356.6507663527499</v>
+        <v>353.5527327193329</v>
       </c>
       <c r="E229" t="n">
-        <v>357.5202026367188</v>
+        <v>354.0723876953125</v>
       </c>
       <c r="F229" t="n">
-        <v>25235900</v>
+        <v>19859900</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B230" t="n">
-        <v>356.4908465215469</v>
+        <v>354.951850943437</v>
       </c>
       <c r="C230" t="n">
-        <v>358.6694387836589</v>
+        <v>357.3802827690857</v>
       </c>
       <c r="D230" t="n">
-        <v>353.5527327193329</v>
+        <v>352.4834362714388</v>
       </c>
       <c r="E230" t="n">
-        <v>354.0723876953125</v>
+        <v>357.2903442382812</v>
       </c>
       <c r="F230" t="n">
-        <v>19859900</v>
+        <v>18991400</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B231" t="n">
-        <v>354.951850943437</v>
+        <v>355.6613923515014</v>
       </c>
       <c r="C231" t="n">
-        <v>357.3802827690857</v>
+        <v>356.5807842683805</v>
       </c>
       <c r="D231" t="n">
-        <v>352.4834362714388</v>
+        <v>343.1694223006263</v>
       </c>
       <c r="E231" t="n">
-        <v>357.2903442382812</v>
+        <v>343.5791320800781</v>
       </c>
       <c r="F231" t="n">
-        <v>18991400</v>
+        <v>29081800</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B232" t="n">
-        <v>355.6613923515014</v>
+        <v>346.0875456512855</v>
       </c>
       <c r="C232" t="n">
-        <v>356.5807842683805</v>
+        <v>346.2574498710514</v>
       </c>
       <c r="D232" t="n">
-        <v>343.1694223006263</v>
+        <v>340.661040926288</v>
       </c>
       <c r="E232" t="n">
-        <v>343.5791320800781</v>
+        <v>343.3193359375</v>
       </c>
       <c r="F232" t="n">
-        <v>29081800</v>
+        <v>25012000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B233" t="n">
-        <v>346.0875456512855</v>
+        <v>345.5478948342235</v>
       </c>
       <c r="C233" t="n">
-        <v>346.2574498710514</v>
+        <v>347.7065110877775</v>
       </c>
       <c r="D233" t="n">
-        <v>340.661040926288</v>
+        <v>343.5392066313974</v>
       </c>
       <c r="E233" t="n">
-        <v>343.3193359375</v>
+        <v>346.1375122070312</v>
       </c>
       <c r="F233" t="n">
-        <v>25012000</v>
+        <v>17866100</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B234" t="n">
-        <v>345.5478948342235</v>
+        <v>346.5772111705174</v>
       </c>
       <c r="C234" t="n">
-        <v>347.7065110877775</v>
+        <v>350.2248908898295</v>
       </c>
       <c r="D234" t="n">
-        <v>343.5392066313974</v>
+        <v>344.2787008387085</v>
       </c>
       <c r="E234" t="n">
-        <v>346.1375122070312</v>
+        <v>345.6777954101562</v>
       </c>
       <c r="F234" t="n">
-        <v>17866100</v>
+        <v>17808600</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B235" t="n">
-        <v>346.5772111705174</v>
+        <v>346.0475530411078</v>
       </c>
       <c r="C235" t="n">
-        <v>350.2248908898295</v>
+        <v>347.0269344906474</v>
       </c>
       <c r="D235" t="n">
-        <v>344.2787008387085</v>
+        <v>341.7103446182459</v>
       </c>
       <c r="E235" t="n">
-        <v>345.6777954101562</v>
+        <v>343.7790222167969</v>
       </c>
       <c r="F235" t="n">
-        <v>17808600</v>
+        <v>18291300</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B236" t="n">
-        <v>346.0475530411078</v>
+        <v>342.1900536360575</v>
       </c>
       <c r="C236" t="n">
-        <v>347.0269344906474</v>
+        <v>344.6484648943574</v>
       </c>
       <c r="D236" t="n">
-        <v>341.7103446182459</v>
+        <v>339.9714784523309</v>
       </c>
       <c r="E236" t="n">
-        <v>343.7790222167969</v>
+        <v>343.9789123535156</v>
       </c>
       <c r="F236" t="n">
-        <v>18291300</v>
+        <v>19248800</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B237" t="n">
-        <v>342.1900536360575</v>
+        <v>342.2400076559886</v>
       </c>
       <c r="C237" t="n">
-        <v>344.6484648943574</v>
+        <v>346.5072842825429</v>
       </c>
       <c r="D237" t="n">
-        <v>339.9714784523309</v>
+        <v>340.4411761094805</v>
       </c>
       <c r="E237" t="n">
-        <v>343.9789123535156</v>
+        <v>344.4985656738281</v>
       </c>
       <c r="F237" t="n">
-        <v>19248800</v>
+        <v>19733800</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B238" t="n">
-        <v>342.2400076559886</v>
+        <v>342.8396207141765</v>
       </c>
       <c r="C238" t="n">
-        <v>346.5072842825429</v>
+        <v>343.6790774504127</v>
       </c>
       <c r="D238" t="n">
-        <v>340.4411761094805</v>
+        <v>338.3525147854226</v>
       </c>
       <c r="E238" t="n">
-        <v>344.4985656738281</v>
+        <v>340.451171875</v>
       </c>
       <c r="F238" t="n">
-        <v>19733800</v>
+        <v>18570400</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B239" t="n">
-        <v>342.8396207141765</v>
+        <v>342.359928876986</v>
       </c>
       <c r="C239" t="n">
-        <v>343.6790774504127</v>
+        <v>345.9776291730591</v>
       </c>
       <c r="D239" t="n">
-        <v>338.3525147854226</v>
+        <v>340.1813365286692</v>
       </c>
       <c r="E239" t="n">
-        <v>340.451171875</v>
+        <v>344.5985107421875</v>
       </c>
       <c r="F239" t="n">
-        <v>18570400</v>
+        <v>20849800</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B240" t="n">
-        <v>342.359928876986</v>
+        <v>343.3992753172161</v>
       </c>
       <c r="C240" t="n">
-        <v>345.9776291730591</v>
+        <v>351.3741604480826</v>
       </c>
       <c r="D240" t="n">
-        <v>340.1813365286692</v>
+        <v>342.2699962782288</v>
       </c>
       <c r="E240" t="n">
-        <v>344.5985107421875</v>
+        <v>347.83642578125</v>
       </c>
       <c r="F240" t="n">
-        <v>20849800</v>
+        <v>26338200</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B241" t="n">
-        <v>343.3992753172161</v>
+        <v>349.4154232615459</v>
       </c>
       <c r="C241" t="n">
-        <v>351.3741604480826</v>
+        <v>349.9350782600912</v>
       </c>
       <c r="D241" t="n">
-        <v>342.2699962782288</v>
+        <v>345.3780098175396</v>
       </c>
       <c r="E241" t="n">
-        <v>347.83642578125</v>
+        <v>346.7371215820312</v>
       </c>
       <c r="F241" t="n">
-        <v>26338200</v>
+        <v>20649700</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B242" t="n">
-        <v>349.4154232615459</v>
+        <v>346.3973312516375</v>
       </c>
       <c r="C242" t="n">
-        <v>349.9350782600912</v>
+        <v>346.6571739906042</v>
       </c>
       <c r="D242" t="n">
-        <v>345.3780098175396</v>
+        <v>339.9614657782595</v>
       </c>
       <c r="E242" t="n">
-        <v>346.7371215820312</v>
+        <v>341.7803039550781</v>
       </c>
       <c r="F242" t="n">
-        <v>20649700</v>
+        <v>20420300</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B243" t="n">
-        <v>346.3973312516375</v>
+        <v>339.4518318672431</v>
       </c>
       <c r="C243" t="n">
-        <v>346.6571739906042</v>
+        <v>341.4705233735174</v>
       </c>
       <c r="D243" t="n">
-        <v>339.9614657782595</v>
+        <v>338.3025461528343</v>
       </c>
       <c r="E243" t="n">
-        <v>341.7803039550781</v>
+        <v>340.4311828613281</v>
       </c>
       <c r="F243" t="n">
-        <v>20420300</v>
+        <v>23391400</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B244" t="n">
-        <v>339.4518318672431</v>
+        <v>340.4911426360338</v>
       </c>
       <c r="C244" t="n">
-        <v>341.4705233735174</v>
+        <v>348.9157509584863</v>
       </c>
       <c r="D244" t="n">
-        <v>338.3025461528343</v>
+        <v>340.0514228221321</v>
       </c>
       <c r="E244" t="n">
-        <v>340.4311828613281</v>
+        <v>346.3673706054688</v>
       </c>
       <c r="F244" t="n">
-        <v>23391400</v>
+        <v>25347200</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B245" t="n">
-        <v>340.4911426360338</v>
+        <v>343.609121722545</v>
       </c>
       <c r="C245" t="n">
-        <v>348.9157509584863</v>
+        <v>344.3686432833908</v>
       </c>
       <c r="D245" t="n">
-        <v>340.0514228221321</v>
+        <v>336.943423385668</v>
       </c>
       <c r="E245" t="n">
-        <v>346.3673706054688</v>
+        <v>339.1320190429688</v>
       </c>
       <c r="F245" t="n">
-        <v>25347200</v>
+        <v>33493600</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B246" t="n">
-        <v>343.609121722545</v>
+        <v>335.7841605001305</v>
       </c>
       <c r="C246" t="n">
-        <v>344.3686432833908</v>
+        <v>336.9834018439635</v>
       </c>
       <c r="D246" t="n">
-        <v>336.943423385668</v>
+        <v>332.8360433203593</v>
       </c>
       <c r="E246" t="n">
-        <v>339.1320190429688</v>
+        <v>334.8047790527344</v>
       </c>
       <c r="F246" t="n">
-        <v>33493600</v>
+        <v>23342700</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B247" t="n">
-        <v>335.7841605001305</v>
+        <v>333.845410447285</v>
       </c>
       <c r="C247" t="n">
-        <v>336.9834018439635</v>
+        <v>339.7815972628325</v>
       </c>
       <c r="D247" t="n">
-        <v>332.8360433203593</v>
+        <v>332.6062167342666</v>
       </c>
       <c r="E247" t="n">
-        <v>334.8047790527344</v>
+        <v>336.9034423828125</v>
       </c>
       <c r="F247" t="n">
-        <v>23342700</v>
+        <v>22582300</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B248" t="n">
-        <v>333.845410447285</v>
+        <v>340.3412297100126</v>
       </c>
       <c r="C248" t="n">
-        <v>339.7815972628325</v>
+        <v>344.4585782378343</v>
       </c>
       <c r="D248" t="n">
-        <v>332.6062167342666</v>
+        <v>339.841550898423</v>
       </c>
       <c r="E248" t="n">
-        <v>336.9034423828125</v>
+        <v>342.260009765625</v>
       </c>
       <c r="F248" t="n">
-        <v>22582300</v>
+        <v>20726900</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,25 +6891,25 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B249" t="n">
-        <v>340.3412297100126</v>
+        <v>342.4700012207031</v>
       </c>
       <c r="C249" t="n">
-        <v>344.4585782378343</v>
+        <v>343.5299987792969</v>
       </c>
       <c r="D249" t="n">
-        <v>339.841550898423</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="E249" t="n">
-        <v>342.260009765625</v>
+        <v>338.4599914550781</v>
       </c>
       <c r="F249" t="n">
-        <v>20726900</v>
+        <v>23189300</v>
       </c>
       <c r="G249" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -6917,25 +6917,25 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B250" t="n">
-        <v>342.4700012207031</v>
+        <v>335.4200134277344</v>
       </c>
       <c r="C250" t="n">
-        <v>343.5299987792969</v>
+        <v>339.6799926757812</v>
       </c>
       <c r="D250" t="n">
-        <v>337.0899963378906</v>
+        <v>333.2200012207031</v>
       </c>
       <c r="E250" t="n">
-        <v>338.4599914550781</v>
+        <v>338.3599853515625</v>
       </c>
       <c r="F250" t="n">
-        <v>23189300</v>
+        <v>22915800</v>
       </c>
       <c r="G250" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B251" t="n">
-        <v>335.4200134277344</v>
+        <v>331.6499938964844</v>
       </c>
       <c r="C251" t="n">
-        <v>339.6799926757812</v>
+        <v>331.8500061035156</v>
       </c>
       <c r="D251" t="n">
-        <v>333.2200012207031</v>
+        <v>327.8999938964844</v>
       </c>
       <c r="E251" t="n">
-        <v>338.3599853515625</v>
+        <v>330.6499938964844</v>
       </c>
       <c r="F251" t="n">
-        <v>22915800</v>
+        <v>33151600</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B252" t="n">
-        <v>331.6499938964844</v>
+        <v>328.2300109863281</v>
       </c>
       <c r="C252" t="n">
-        <v>331.8500061035156</v>
+        <v>333.2300109863281</v>
       </c>
       <c r="D252" t="n">
-        <v>327.8999938964844</v>
+        <v>327.739990234375</v>
       </c>
       <c r="E252" t="n">
-        <v>330.6499938964844</v>
+        <v>332.6000061035156</v>
       </c>
       <c r="F252" t="n">
-        <v>33081300</v>
+        <v>23508500</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10772,37 +10772,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>332.6</v>
+      </c>
+      <c r="D2" t="n">
         <v>330.65</v>
       </c>
-      <c r="D2" t="n">
-        <v>338.36</v>
-      </c>
       <c r="E2" t="n">
-        <v>331.69</v>
+        <v>328.01</v>
       </c>
       <c r="F2" t="n">
-        <v>331.85</v>
+        <v>333.23</v>
       </c>
       <c r="G2" t="n">
-        <v>327.9</v>
+        <v>327.7465</v>
       </c>
       <c r="H2" t="n">
-        <v>32730889</v>
+        <v>22782704</v>
       </c>
       <c r="I2" t="n">
-        <v>30031591</v>
+        <v>29954344</v>
       </c>
       <c r="J2" t="n">
-        <v>4043827838976</v>
+        <v>4067676389376</v>
       </c>
       <c r="K2" t="n">
-        <v>16.97382</v>
+        <v>16.696787</v>
       </c>
       <c r="L2" t="n">
-        <v>22.259953</v>
+        <v>22.361423</v>
       </c>
       <c r="M2" t="n">
-        <v>19.48</v>
+        <v>19.92</v>
       </c>
       <c r="N2" t="n">
         <v>408.61</v>
@@ -10814,7 +10814,7 @@
         <v>1.225</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="R2" t="n">
         <v>0.54771</v>
@@ -10838,7 +10838,7 @@
         <v>50.896</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.496581</v>
+        <v>6.534895</v>
       </c>
       <c r="Z2" t="n">
         <v>2.94</v>
@@ -10850,7 +10850,7 @@
         <v>445865984000</v>
       </c>
       <c r="AC2" t="n">
-        <v>3940189470720</v>
+        <v>3964038021120</v>
       </c>
       <c r="AD2" t="n">
         <v>173164003328</v>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-10 18:59:07</t>
+          <t>2026-09-11 19:02:42</t>
         </is>
       </c>
     </row>

--- a/data/GOOGL_data.xlsx
+++ b/data/GOOGL_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B2" t="n">
-        <v>239.2577712479691</v>
+        <v>239.746507229255</v>
       </c>
       <c r="C2" t="n">
-        <v>241.6216187469878</v>
+        <v>241.4520784124984</v>
       </c>
       <c r="D2" t="n">
-        <v>235.6371823693535</v>
+        <v>237.3826595650776</v>
       </c>
       <c r="E2" t="n">
-        <v>239.7464904785156</v>
+        <v>240.1753997802734</v>
       </c>
       <c r="F2" t="n">
-        <v>30599300</v>
+        <v>26771600</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B3" t="n">
-        <v>239.746507229255</v>
+        <v>244.0253674338205</v>
       </c>
       <c r="C3" t="n">
-        <v>241.4520784124984</v>
+        <v>251.7552643082765</v>
       </c>
       <c r="D3" t="n">
-        <v>237.3826595650776</v>
+        <v>244.0253674338205</v>
       </c>
       <c r="E3" t="n">
-        <v>240.1753997802734</v>
+        <v>250.9573364257812</v>
       </c>
       <c r="F3" t="n">
-        <v>26771600</v>
+        <v>58383800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B4" t="n">
-        <v>244.0253674338205</v>
+        <v>251.4261108558069</v>
       </c>
       <c r="C4" t="n">
-        <v>251.7552643082765</v>
+        <v>252.3836121103763</v>
       </c>
       <c r="D4" t="n">
-        <v>244.0253674338205</v>
+        <v>248.8228805399337</v>
       </c>
       <c r="E4" t="n">
-        <v>250.9573364257812</v>
+        <v>250.5084991455078</v>
       </c>
       <c r="F4" t="n">
-        <v>58383800</v>
+        <v>34109700</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B5" t="n">
-        <v>251.4261108558069</v>
+        <v>250.5683549046871</v>
       </c>
       <c r="C5" t="n">
-        <v>252.3836121103763</v>
+        <v>250.9473740826164</v>
       </c>
       <c r="D5" t="n">
-        <v>248.8228805399337</v>
+        <v>245.6411664684413</v>
       </c>
       <c r="E5" t="n">
-        <v>250.5084991455078</v>
+        <v>248.8827362060547</v>
       </c>
       <c r="F5" t="n">
-        <v>34109700</v>
+        <v>34108000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B6" t="n">
-        <v>250.5683549046871</v>
+        <v>251.0271530076639</v>
       </c>
       <c r="C6" t="n">
-        <v>250.9473740826164</v>
+        <v>253.3311738191467</v>
       </c>
       <c r="D6" t="n">
-        <v>245.6411664684413</v>
+        <v>249.1520399405299</v>
       </c>
       <c r="E6" t="n">
-        <v>248.8827362060547</v>
+        <v>251.3762512207031</v>
       </c>
       <c r="F6" t="n">
-        <v>34108000</v>
+        <v>31239500</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B7" t="n">
-        <v>251.0271530076639</v>
+        <v>252.5930922260568</v>
       </c>
       <c r="C7" t="n">
-        <v>253.3311738191467</v>
+        <v>255.3359589728353</v>
       </c>
       <c r="D7" t="n">
-        <v>249.1520399405299</v>
+        <v>251.1568250217611</v>
       </c>
       <c r="E7" t="n">
-        <v>251.3762512207031</v>
+        <v>254.0592803955078</v>
       </c>
       <c r="F7" t="n">
-        <v>31239500</v>
+        <v>55571400</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B8" t="n">
-        <v>252.5930922260568</v>
+        <v>253.7700350469374</v>
       </c>
       <c r="C8" t="n">
-        <v>255.3359589728353</v>
+        <v>255.1165394138156</v>
       </c>
       <c r="D8" t="n">
-        <v>251.1568250217611</v>
+        <v>249.6507580677981</v>
       </c>
       <c r="E8" t="n">
-        <v>254.0592803955078</v>
+        <v>251.8749694824219</v>
       </c>
       <c r="F8" t="n">
-        <v>55571400</v>
+        <v>32290500</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B9" t="n">
-        <v>253.7700350469374</v>
+        <v>252.38362744671</v>
       </c>
       <c r="C9" t="n">
-        <v>255.1165394138156</v>
+        <v>253.7002107757565</v>
       </c>
       <c r="D9" t="n">
-        <v>249.6507580677981</v>
+        <v>249.8302703204236</v>
       </c>
       <c r="E9" t="n">
-        <v>251.8749694824219</v>
+        <v>251.0072174072266</v>
       </c>
       <c r="F9" t="n">
-        <v>32290500</v>
+        <v>26628000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B10" t="n">
-        <v>252.38362744671</v>
+        <v>251.0071959779958</v>
       </c>
       <c r="C10" t="n">
-        <v>253.7002107757565</v>
+        <v>251.6954085485873</v>
       </c>
       <c r="D10" t="n">
-        <v>249.8302703204236</v>
+        <v>245.8007354743648</v>
       </c>
       <c r="E10" t="n">
-        <v>251.0072174072266</v>
+        <v>246.4989166259766</v>
       </c>
       <c r="F10" t="n">
-        <v>26628000</v>
+        <v>28201000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B11" t="n">
-        <v>251.0072115158567</v>
+        <v>243.7660414512771</v>
       </c>
       <c r="C11" t="n">
-        <v>251.6954241290499</v>
+        <v>245.8506317386469</v>
       </c>
       <c r="D11" t="n">
-        <v>245.8007506899351</v>
+        <v>240.1155467413105</v>
       </c>
       <c r="E11" t="n">
-        <v>246.4989318847656</v>
+        <v>245.1524353027344</v>
       </c>
       <c r="F11" t="n">
-        <v>28201000</v>
+        <v>31020400</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B12" t="n">
-        <v>243.76602627878</v>
+        <v>246.429136680309</v>
       </c>
       <c r="C12" t="n">
-        <v>245.8506164364007</v>
+        <v>248.7730319241888</v>
       </c>
       <c r="D12" t="n">
-        <v>240.1155317960277</v>
+        <v>245.3319838637119</v>
       </c>
       <c r="E12" t="n">
-        <v>245.1524200439453</v>
+        <v>245.9004974365234</v>
       </c>
       <c r="F12" t="n">
-        <v>31020400</v>
+        <v>18503200</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B13" t="n">
-        <v>246.429136680309</v>
+        <v>247.2071078925349</v>
       </c>
       <c r="C13" t="n">
-        <v>248.7730319241888</v>
+        <v>250.4985358461003</v>
       </c>
       <c r="D13" t="n">
-        <v>245.3319838637119</v>
+        <v>242.1402830798725</v>
       </c>
       <c r="E13" t="n">
-        <v>245.9004974365234</v>
+        <v>243.4169616699219</v>
       </c>
       <c r="F13" t="n">
-        <v>18503200</v>
+        <v>32505800</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B14" t="n">
-        <v>247.2071078925349</v>
+        <v>242.1801651040411</v>
       </c>
       <c r="C14" t="n">
-        <v>250.4985358461003</v>
+        <v>242.6589157556348</v>
       </c>
       <c r="D14" t="n">
-        <v>242.1402830798725</v>
+        <v>238.6294019345709</v>
       </c>
       <c r="E14" t="n">
-        <v>243.4169616699219</v>
+        <v>242.4694213867188</v>
       </c>
       <c r="F14" t="n">
-        <v>32505800</v>
+        <v>34724300</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B15" t="n">
-        <v>242.1801651040411</v>
+        <v>240.125510895299</v>
       </c>
       <c r="C15" t="n">
-        <v>242.6589157556348</v>
+        <v>245.661117617101</v>
       </c>
       <c r="D15" t="n">
-        <v>238.6294019345709</v>
+        <v>237.9910625183314</v>
       </c>
       <c r="E15" t="n">
-        <v>242.4694213867188</v>
+        <v>244.2647399902344</v>
       </c>
       <c r="F15" t="n">
-        <v>34724300</v>
+        <v>31658200</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B16" t="n">
-        <v>240.1254958950803</v>
+        <v>244.5140808226371</v>
       </c>
       <c r="C16" t="n">
-        <v>245.6611022710827</v>
+        <v>246.1697784759451</v>
       </c>
       <c r="D16" t="n">
-        <v>237.991047651448</v>
+        <v>241.6714827842888</v>
       </c>
       <c r="E16" t="n">
-        <v>244.2647247314453</v>
+        <v>245.0526885986328</v>
       </c>
       <c r="F16" t="n">
-        <v>31658200</v>
+        <v>25483300</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B17" t="n">
-        <v>244.5140808226371</v>
+        <v>243.8558226752064</v>
       </c>
       <c r="C17" t="n">
-        <v>246.1697784759451</v>
+        <v>245.6611252797062</v>
       </c>
       <c r="D17" t="n">
-        <v>241.6714827842888</v>
+        <v>241.0331615881319</v>
       </c>
       <c r="E17" t="n">
-        <v>245.0526885986328</v>
+        <v>244.7135925292969</v>
       </c>
       <c r="F17" t="n">
-        <v>25483300</v>
+        <v>30249600</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B18" t="n">
-        <v>243.8558378805103</v>
+        <v>244.1450721986699</v>
       </c>
       <c r="C18" t="n">
-        <v>245.6611405975774</v>
+        <v>250.6681168360691</v>
       </c>
       <c r="D18" t="n">
-        <v>241.0331766174326</v>
+        <v>243.9455940157645</v>
       </c>
       <c r="E18" t="n">
-        <v>244.7136077880859</v>
+        <v>249.7804107666016</v>
       </c>
       <c r="F18" t="n">
-        <v>30249600</v>
+        <v>28894700</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B19" t="n">
-        <v>244.1450721986699</v>
+        <v>247.6259964046166</v>
       </c>
       <c r="C19" t="n">
-        <v>250.6681168360691</v>
+        <v>249.790365637847</v>
       </c>
       <c r="D19" t="n">
-        <v>243.9455940157645</v>
+        <v>244.8831298545143</v>
       </c>
       <c r="E19" t="n">
-        <v>249.7804107666016</v>
+        <v>245.1224975585938</v>
       </c>
       <c r="F19" t="n">
-        <v>28894700</v>
+        <v>23181300</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B20" t="n">
-        <v>247.6260118192477</v>
+        <v>244.3246032710778</v>
       </c>
       <c r="C20" t="n">
-        <v>249.7903811872092</v>
+        <v>245.3718674935034</v>
       </c>
       <c r="D20" t="n">
-        <v>244.8831450984028</v>
+        <v>243.187560933671</v>
       </c>
       <c r="E20" t="n">
-        <v>245.1225128173828</v>
+        <v>243.9854736328125</v>
       </c>
       <c r="F20" t="n">
-        <v>23181300</v>
+        <v>21307100</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B21" t="n">
-        <v>244.3245879910796</v>
+        <v>243.8358644557508</v>
       </c>
       <c r="C21" t="n">
-        <v>245.3718521480096</v>
+        <v>244.1251055211473</v>
       </c>
       <c r="D21" t="n">
-        <v>243.1875457247831</v>
+        <v>238.5296568297252</v>
       </c>
       <c r="E21" t="n">
-        <v>243.9854583740234</v>
+        <v>240.9034881591797</v>
       </c>
       <c r="F21" t="n">
-        <v>21307100</v>
+        <v>27892100</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B22" t="n">
-        <v>243.8358644557508</v>
+        <v>240.8037542960898</v>
       </c>
       <c r="C22" t="n">
-        <v>244.1251055211473</v>
+        <v>243.4568582504832</v>
       </c>
       <c r="D22" t="n">
-        <v>238.5296568297252</v>
+        <v>235.2282576904417</v>
       </c>
       <c r="E22" t="n">
-        <v>240.9034881591797</v>
+        <v>235.9563751220703</v>
       </c>
       <c r="F22" t="n">
-        <v>27892100</v>
+        <v>33180300</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B23" t="n">
-        <v>240.8037387238312</v>
+        <v>239.5869108546296</v>
       </c>
       <c r="C23" t="n">
-        <v>243.4568425066541</v>
+        <v>243.8657760570938</v>
       </c>
       <c r="D23" t="n">
-        <v>235.2282424787384</v>
+        <v>239.0882078361079</v>
       </c>
       <c r="E23" t="n">
-        <v>235.9563598632812</v>
+        <v>243.5166778564453</v>
       </c>
       <c r="F23" t="n">
-        <v>33180300</v>
+        <v>24995000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B24" t="n">
-        <v>239.5869258671789</v>
+        <v>240.6042540225217</v>
       </c>
       <c r="C24" t="n">
-        <v>243.8657913377574</v>
+        <v>246.4789749711557</v>
       </c>
       <c r="D24" t="n">
-        <v>239.0882228174084</v>
+        <v>239.8861204584095</v>
       </c>
       <c r="E24" t="n">
-        <v>243.5166931152344</v>
+        <v>244.8133087158203</v>
       </c>
       <c r="F24" t="n">
-        <v>24995000</v>
+        <v>22111600</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B25" t="n">
-        <v>240.6042690189676</v>
+        <v>246.6086514775368</v>
       </c>
       <c r="C25" t="n">
-        <v>246.4789903337629</v>
+        <v>251.4560455996756</v>
       </c>
       <c r="D25" t="n">
-        <v>239.8861354100955</v>
+        <v>245.3519253048375</v>
       </c>
       <c r="E25" t="n">
-        <v>244.8133239746094</v>
+        <v>250.3788452148438</v>
       </c>
       <c r="F25" t="n">
-        <v>22111600</v>
+        <v>27007700</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B26" t="n">
-        <v>246.6086514775368</v>
+        <v>251.1169327071502</v>
       </c>
       <c r="C26" t="n">
-        <v>251.4560455996756</v>
+        <v>256.2934574717041</v>
       </c>
       <c r="D26" t="n">
-        <v>245.3519253048375</v>
+        <v>249.4512663819502</v>
       </c>
       <c r="E26" t="n">
-        <v>250.3788452148438</v>
+        <v>250.8077392578125</v>
       </c>
       <c r="F26" t="n">
-        <v>27007700</v>
+        <v>27997200</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B27" t="n">
-        <v>251.1169327071502</v>
+        <v>250.1095396639979</v>
       </c>
       <c r="C27" t="n">
-        <v>256.2934574717041</v>
+        <v>253.5605713492617</v>
       </c>
       <c r="D27" t="n">
-        <v>249.4512663819502</v>
+        <v>247.1671948127543</v>
       </c>
       <c r="E27" t="n">
-        <v>250.8077392578125</v>
+        <v>252.6429595947266</v>
       </c>
       <c r="F27" t="n">
-        <v>27997200</v>
+        <v>29671600</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B28" t="n">
-        <v>250.1095396639979</v>
+        <v>254.0293456100436</v>
       </c>
       <c r="C28" t="n">
-        <v>253.5605713492617</v>
+        <v>256.6624817157193</v>
       </c>
       <c r="D28" t="n">
-        <v>247.1671948127543</v>
+        <v>253.5705321372737</v>
       </c>
       <c r="E28" t="n">
-        <v>252.6429595947266</v>
+        <v>255.8845062255859</v>
       </c>
       <c r="F28" t="n">
-        <v>29671600</v>
+        <v>22350200</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B29" t="n">
-        <v>254.0293759063695</v>
+        <v>254.079230052693</v>
       </c>
       <c r="C29" t="n">
-        <v>256.6625123260812</v>
+        <v>254.2188662949897</v>
       </c>
       <c r="D29" t="n">
-        <v>253.5705623788801</v>
+        <v>243.5166881090968</v>
       </c>
       <c r="E29" t="n">
-        <v>255.8845367431641</v>
+        <v>249.8103332519531</v>
       </c>
       <c r="F29" t="n">
-        <v>22350200</v>
+        <v>47312100</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B30" t="n">
-        <v>254.079230052693</v>
+        <v>253.7101963156115</v>
       </c>
       <c r="C30" t="n">
-        <v>254.2188662949897</v>
+        <v>255.6950248045094</v>
       </c>
       <c r="D30" t="n">
-        <v>243.5166881090968</v>
+        <v>248.6433712710665</v>
       </c>
       <c r="E30" t="n">
-        <v>249.8103332519531</v>
+        <v>251.0371551513672</v>
       </c>
       <c r="F30" t="n">
-        <v>47312100</v>
+        <v>35029400</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B31" t="n">
-        <v>253.7101963156115</v>
+        <v>252.3237915100895</v>
       </c>
       <c r="C31" t="n">
-        <v>255.6950248045094</v>
+        <v>254.3784456458486</v>
       </c>
       <c r="D31" t="n">
-        <v>248.6433712710665</v>
+        <v>251.196732963501</v>
       </c>
       <c r="E31" t="n">
-        <v>251.0371551513672</v>
+        <v>252.4235382080078</v>
       </c>
       <c r="F31" t="n">
-        <v>35029400</v>
+        <v>19901400</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B32" t="n">
-        <v>252.3237915100895</v>
+        <v>255.9144557753844</v>
       </c>
       <c r="C32" t="n">
-        <v>254.3784456458486</v>
+        <v>261.0012332121926</v>
       </c>
       <c r="D32" t="n">
-        <v>251.196732963501</v>
+        <v>254.6577447284323</v>
       </c>
       <c r="E32" t="n">
-        <v>252.4235382080078</v>
+        <v>259.2458190917969</v>
       </c>
       <c r="F32" t="n">
-        <v>19901400</v>
+        <v>28655100</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B33" t="n">
-        <v>255.9144557753844</v>
+        <v>264.1330942614516</v>
       </c>
       <c r="C33" t="n">
-        <v>261.0012332121926</v>
+        <v>269.4393020900735</v>
       </c>
       <c r="D33" t="n">
-        <v>254.6577447284323</v>
+        <v>263.5944864374467</v>
       </c>
       <c r="E33" t="n">
-        <v>259.2458190917969</v>
+        <v>268.571533203125</v>
       </c>
       <c r="F33" t="n">
-        <v>28655100</v>
+        <v>35235200</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B34" t="n">
-        <v>264.1330942614516</v>
+        <v>268.9904573908112</v>
       </c>
       <c r="C34" t="n">
-        <v>269.4393020900735</v>
+        <v>270.0277682724026</v>
       </c>
       <c r="D34" t="n">
-        <v>263.5944864374467</v>
+        <v>265.808729451237</v>
       </c>
       <c r="E34" t="n">
-        <v>268.571533203125</v>
+        <v>266.7762145996094</v>
       </c>
       <c r="F34" t="n">
-        <v>35235200</v>
+        <v>29738600</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B35" t="n">
-        <v>268.9904266199372</v>
+        <v>267.055471479175</v>
       </c>
       <c r="C35" t="n">
-        <v>270.0277373828665</v>
+        <v>274.6257797911847</v>
       </c>
       <c r="D35" t="n">
-        <v>265.8086990443333</v>
+        <v>266.975692387603</v>
       </c>
       <c r="E35" t="n">
-        <v>266.7761840820312</v>
+        <v>273.8577880859375</v>
       </c>
       <c r="F35" t="n">
-        <v>29738600</v>
+        <v>43580300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B36" t="n">
-        <v>267.055471479175</v>
+        <v>290.8336705300809</v>
       </c>
       <c r="C36" t="n">
-        <v>274.6257797911847</v>
+        <v>290.8336705300809</v>
       </c>
       <c r="D36" t="n">
-        <v>266.975692387603</v>
+        <v>279.3335782487789</v>
       </c>
       <c r="E36" t="n">
-        <v>273.8577880859375</v>
+        <v>280.7499084472656</v>
       </c>
       <c r="F36" t="n">
-        <v>43580300</v>
+        <v>74876000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B37" t="n">
-        <v>290.8336705300809</v>
+        <v>282.4753817503845</v>
       </c>
       <c r="C37" t="n">
-        <v>290.8336705300809</v>
+        <v>285.2581533777714</v>
       </c>
       <c r="D37" t="n">
-        <v>279.3335782487789</v>
+        <v>276.3114191679317</v>
       </c>
       <c r="E37" t="n">
-        <v>280.7499084472656</v>
+        <v>280.4606323242188</v>
       </c>
       <c r="F37" t="n">
-        <v>74876000</v>
+        <v>39267900</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B38" t="n">
-        <v>282.4753817503845</v>
+        <v>281.4480558536455</v>
       </c>
       <c r="C38" t="n">
-        <v>285.2581533777714</v>
+        <v>284.7893724933962</v>
       </c>
       <c r="D38" t="n">
-        <v>276.3114191679317</v>
+        <v>279.0742243823285</v>
       </c>
       <c r="E38" t="n">
-        <v>280.4606323242188</v>
+        <v>282.9840698242188</v>
       </c>
       <c r="F38" t="n">
-        <v>39267900</v>
+        <v>29786000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B39" t="n">
-        <v>281.4480558536455</v>
+        <v>276.0321395313242</v>
       </c>
       <c r="C39" t="n">
-        <v>284.7893724933962</v>
+        <v>280.5404041676455</v>
       </c>
       <c r="D39" t="n">
-        <v>279.0742243823285</v>
+        <v>275.5434202802167</v>
       </c>
       <c r="E39" t="n">
-        <v>282.9840698242188</v>
+        <v>276.8200988769531</v>
       </c>
       <c r="F39" t="n">
-        <v>29786000</v>
+        <v>30078400</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B40" t="n">
-        <v>276.0321395313242</v>
+        <v>278.1466184544242</v>
       </c>
       <c r="C40" t="n">
-        <v>280.5404041676455</v>
+        <v>285.677052345188</v>
       </c>
       <c r="D40" t="n">
-        <v>275.5434202802167</v>
+        <v>276.62058842555</v>
       </c>
       <c r="E40" t="n">
-        <v>276.8200988769531</v>
+        <v>283.572509765625</v>
       </c>
       <c r="F40" t="n">
-        <v>30078400</v>
+        <v>31010300</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B41" t="n">
-        <v>278.1466184544242</v>
+        <v>284.5898651937554</v>
       </c>
       <c r="C41" t="n">
-        <v>285.677052345188</v>
+        <v>287.6020510547858</v>
       </c>
       <c r="D41" t="n">
-        <v>276.62058842555</v>
+        <v>280.4107616957575</v>
       </c>
       <c r="E41" t="n">
-        <v>283.572509765625</v>
+        <v>284.0113830566406</v>
       </c>
       <c r="F41" t="n">
-        <v>31010300</v>
+        <v>37173600</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B42" t="n">
-        <v>284.5898651937554</v>
+        <v>282.4753634096288</v>
       </c>
       <c r="C42" t="n">
-        <v>287.6020510547858</v>
+        <v>283.0438921724298</v>
       </c>
       <c r="D42" t="n">
-        <v>280.4107616957575</v>
+        <v>274.4761777186906</v>
       </c>
       <c r="E42" t="n">
-        <v>284.0113830566406</v>
+        <v>278.1067199707031</v>
       </c>
       <c r="F42" t="n">
-        <v>37173600</v>
+        <v>34479600</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B43" t="n">
-        <v>282.4753634096288</v>
+        <v>283.6822445549795</v>
       </c>
       <c r="C43" t="n">
-        <v>283.0438921724298</v>
+        <v>290.0456696400176</v>
       </c>
       <c r="D43" t="n">
-        <v>274.4761777186906</v>
+        <v>282.1262631003564</v>
       </c>
       <c r="E43" t="n">
-        <v>278.1067199707031</v>
+        <v>289.3475036621094</v>
       </c>
       <c r="F43" t="n">
-        <v>34479600</v>
+        <v>29557300</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B44" t="n">
-        <v>283.6822445549795</v>
+        <v>287.0035887304013</v>
       </c>
       <c r="C44" t="n">
-        <v>290.0456696400176</v>
+        <v>291.1627853205446</v>
       </c>
       <c r="D44" t="n">
-        <v>282.1262631003564</v>
+        <v>286.5747114373448</v>
       </c>
       <c r="E44" t="n">
-        <v>289.3475036621094</v>
+        <v>290.5543518066406</v>
       </c>
       <c r="F44" t="n">
-        <v>29557300</v>
+        <v>19842100</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B45" t="n">
-        <v>287.0035887304013</v>
+        <v>290.9234183741868</v>
       </c>
       <c r="C45" t="n">
-        <v>291.1627853205446</v>
+        <v>291.2525794490294</v>
       </c>
       <c r="D45" t="n">
-        <v>286.5747114373448</v>
+        <v>282.9541529801612</v>
       </c>
       <c r="E45" t="n">
-        <v>290.5543518066406</v>
+        <v>285.96630859375</v>
       </c>
       <c r="F45" t="n">
-        <v>19842100</v>
+        <v>24829900</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B46" t="n">
-        <v>290.9234183741868</v>
+        <v>281.6076529103283</v>
       </c>
       <c r="C46" t="n">
-        <v>291.2525794490294</v>
+        <v>282.1063559927165</v>
       </c>
       <c r="D46" t="n">
-        <v>282.9541529801612</v>
+        <v>276.5208753822851</v>
       </c>
       <c r="E46" t="n">
-        <v>285.96630859375</v>
+        <v>277.8474426269531</v>
       </c>
       <c r="F46" t="n">
-        <v>24829900</v>
+        <v>29494000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B47" t="n">
-        <v>281.6076529103283</v>
+        <v>270.7059931829425</v>
       </c>
       <c r="C47" t="n">
-        <v>282.1063559927165</v>
+        <v>277.8374407083971</v>
       </c>
       <c r="D47" t="n">
-        <v>276.5208753822851</v>
+        <v>269.9978433748846</v>
       </c>
       <c r="E47" t="n">
-        <v>277.8474426269531</v>
+        <v>275.6930236816406</v>
       </c>
       <c r="F47" t="n">
-        <v>29494000</v>
+        <v>31647200</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B48" t="n">
-        <v>270.705963217399</v>
+        <v>285.0387085276487</v>
       </c>
       <c r="C48" t="n">
-        <v>277.8374099534448</v>
+        <v>293.1875295999499</v>
       </c>
       <c r="D48" t="n">
-        <v>269.997813487729</v>
+        <v>282.8344496120375</v>
       </c>
       <c r="E48" t="n">
-        <v>275.6929931640625</v>
+        <v>284.2806701660156</v>
       </c>
       <c r="F48" t="n">
-        <v>31647200</v>
+        <v>52670200</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B49" t="n">
-        <v>285.0387085276487</v>
+        <v>287.1731753233953</v>
       </c>
       <c r="C49" t="n">
-        <v>293.1875295999499</v>
+        <v>288.0508671158451</v>
       </c>
       <c r="D49" t="n">
-        <v>282.8344496120375</v>
+        <v>277.4783868942568</v>
       </c>
       <c r="E49" t="n">
-        <v>284.2806701660156</v>
+        <v>283.5426025390625</v>
       </c>
       <c r="F49" t="n">
-        <v>52670200</v>
+        <v>49158700</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B50" t="n">
-        <v>287.1731753233953</v>
+        <v>286.4151676571055</v>
       </c>
       <c r="C50" t="n">
-        <v>288.0508671158451</v>
+        <v>303.0219747769531</v>
       </c>
       <c r="D50" t="n">
-        <v>277.4783868942568</v>
+        <v>285.8865435893576</v>
       </c>
       <c r="E50" t="n">
-        <v>283.5426025390625</v>
+        <v>292.0505065917969</v>
       </c>
       <c r="F50" t="n">
-        <v>49158700</v>
+        <v>68198900</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B51" t="n">
-        <v>286.4151377283875</v>
+        <v>303.7500416076266</v>
       </c>
       <c r="C51" t="n">
-        <v>303.0219431129204</v>
+        <v>305.625169818548</v>
       </c>
       <c r="D51" t="n">
-        <v>285.8865137158778</v>
+        <v>287.9212127447435</v>
       </c>
       <c r="E51" t="n">
-        <v>292.0504760742188</v>
+        <v>288.6991882324219</v>
       </c>
       <c r="F51" t="n">
-        <v>68198900</v>
+        <v>62025200</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B52" t="n">
-        <v>303.7500416076266</v>
+        <v>295.6511650531278</v>
       </c>
       <c r="C52" t="n">
-        <v>305.625169818548</v>
+        <v>303.1317117013016</v>
       </c>
       <c r="D52" t="n">
-        <v>287.9212127447435</v>
+        <v>293.0878237631323</v>
       </c>
       <c r="E52" t="n">
-        <v>288.6991882324219</v>
+        <v>298.8827514648438</v>
       </c>
       <c r="F52" t="n">
-        <v>62025200</v>
+        <v>74137700</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B53" t="n">
-        <v>295.6511348655125</v>
+        <v>310.3229443803346</v>
       </c>
       <c r="C53" t="n">
-        <v>303.1316807498811</v>
+        <v>318.651290855991</v>
       </c>
       <c r="D53" t="n">
-        <v>293.0877938372482</v>
+        <v>308.796914365105</v>
       </c>
       <c r="E53" t="n">
-        <v>298.8827209472656</v>
+        <v>317.7536010742188</v>
       </c>
       <c r="F53" t="n">
-        <v>74137700</v>
+        <v>85165100</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B54" t="n">
-        <v>310.3229443803346</v>
+        <v>325.3638169665917</v>
       </c>
       <c r="C54" t="n">
-        <v>318.651290855991</v>
+        <v>327.9770159307299</v>
       </c>
       <c r="D54" t="n">
-        <v>308.796914365105</v>
+        <v>316.826023668276</v>
       </c>
       <c r="E54" t="n">
-        <v>317.7536010742188</v>
+        <v>322.6010131835938</v>
       </c>
       <c r="F54" t="n">
-        <v>85165100</v>
+        <v>88632100</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B55" t="n">
-        <v>325.3638169665917</v>
+        <v>319.8482042131112</v>
       </c>
       <c r="C55" t="n">
-        <v>327.9770159307299</v>
+        <v>323.658303098724</v>
       </c>
       <c r="D55" t="n">
-        <v>316.826023668276</v>
+        <v>315.9683100285969</v>
       </c>
       <c r="E55" t="n">
-        <v>322.6010131835938</v>
+        <v>319.1201171875</v>
       </c>
       <c r="F55" t="n">
-        <v>88632100</v>
+        <v>51373400</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B56" t="n">
-        <v>319.8482042131112</v>
+        <v>322.531246115159</v>
       </c>
       <c r="C56" t="n">
-        <v>323.658303098724</v>
+        <v>326.002230736067</v>
       </c>
       <c r="D56" t="n">
-        <v>315.9683100285969</v>
+        <v>315.9683265474213</v>
       </c>
       <c r="E56" t="n">
-        <v>319.1201171875</v>
+        <v>319.3495178222656</v>
       </c>
       <c r="F56" t="n">
-        <v>51373400</v>
+        <v>26018600</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B57" t="n">
-        <v>322.5312152935296</v>
+        <v>316.8759510785769</v>
       </c>
       <c r="C57" t="n">
-        <v>326.0021995827445</v>
+        <v>319.020368247556</v>
       </c>
       <c r="D57" t="n">
-        <v>315.9682963529555</v>
+        <v>313.0758360216101</v>
       </c>
       <c r="E57" t="n">
-        <v>319.3494873046875</v>
+        <v>314.0732421875</v>
       </c>
       <c r="F57" t="n">
-        <v>26018600</v>
+        <v>41183000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B58" t="n">
-        <v>316.8759510785769</v>
+        <v>315.9183945655827</v>
       </c>
       <c r="C58" t="n">
-        <v>319.020368247556</v>
+        <v>317.554155160306</v>
       </c>
       <c r="D58" t="n">
-        <v>313.0758360216101</v>
+        <v>313.0957487295115</v>
       </c>
       <c r="E58" t="n">
-        <v>314.0732421875</v>
+        <v>314.9908142089844</v>
       </c>
       <c r="F58" t="n">
-        <v>41183000</v>
+        <v>35854700</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B59" t="n">
-        <v>315.9184251730286</v>
+        <v>315.0705842416539</v>
       </c>
       <c r="C59" t="n">
-        <v>317.5541859262309</v>
+        <v>320.745796167407</v>
       </c>
       <c r="D59" t="n">
-        <v>313.095779063488</v>
+        <v>313.285219045246</v>
       </c>
       <c r="E59" t="n">
-        <v>314.9908447265625</v>
+        <v>318.8008728027344</v>
       </c>
       <c r="F59" t="n">
-        <v>35854700</v>
+        <v>41838300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B60" t="n">
-        <v>315.0706144021458</v>
+        <v>321.3942008459266</v>
       </c>
       <c r="C60" t="n">
-        <v>320.7458268711651</v>
+        <v>321.5238380796439</v>
       </c>
       <c r="D60" t="n">
-        <v>313.2852490348319</v>
+        <v>313.8837336096964</v>
       </c>
       <c r="E60" t="n">
-        <v>318.8009033203125</v>
+        <v>316.796142578125</v>
       </c>
       <c r="F60" t="n">
-        <v>41838300</v>
+        <v>31240900</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B61" t="n">
-        <v>321.3941698854088</v>
+        <v>318.6612335259534</v>
       </c>
       <c r="C61" t="n">
-        <v>321.5238071066378</v>
+        <v>322.3217269426038</v>
       </c>
       <c r="D61" t="n">
-        <v>313.8837033726762</v>
+        <v>318.3420867388224</v>
       </c>
       <c r="E61" t="n">
-        <v>316.7961120605469</v>
+        <v>320.4366149902344</v>
       </c>
       <c r="F61" t="n">
-        <v>31240900</v>
+        <v>28851700</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,25 +2029,25 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B62" t="n">
-        <v>318.6612638744486</v>
+        <v>319.428628654094</v>
       </c>
       <c r="C62" t="n">
-        <v>322.3217576397153</v>
+        <v>319.8178861109197</v>
       </c>
       <c r="D62" t="n">
-        <v>318.3421170569229</v>
+        <v>310.6157850065654</v>
       </c>
       <c r="E62" t="n">
-        <v>320.4366455078125</v>
+        <v>313.1109313964844</v>
       </c>
       <c r="F62" t="n">
-        <v>28851700</v>
+        <v>33909400</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2055,25 +2055,25 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B63" t="n">
-        <v>319.4285975207571</v>
+        <v>311.7635388280278</v>
       </c>
       <c r="C63" t="n">
-        <v>319.8178549396436</v>
+        <v>317.3726229056239</v>
       </c>
       <c r="D63" t="n">
-        <v>310.6157547321785</v>
+        <v>311.2944500995635</v>
       </c>
       <c r="E63" t="n">
-        <v>313.1109008789062</v>
+        <v>316.4643859863281</v>
       </c>
       <c r="F63" t="n">
-        <v>33909400</v>
+        <v>30194000</v>
       </c>
       <c r="G63" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B64" t="n">
-        <v>311.7635388280278</v>
+        <v>315.2168165746965</v>
       </c>
       <c r="C64" t="n">
-        <v>317.3726229056239</v>
+        <v>320.6861883612462</v>
       </c>
       <c r="D64" t="n">
-        <v>311.2944500995635</v>
+        <v>314.069055340672</v>
       </c>
       <c r="E64" t="n">
-        <v>316.4643859863281</v>
+        <v>319.5883178710938</v>
       </c>
       <c r="F64" t="n">
-        <v>30194000</v>
+        <v>33428900</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B65" t="n">
-        <v>315.2168165746965</v>
+        <v>319.4585358397385</v>
       </c>
       <c r="C65" t="n">
-        <v>320.6861883612462</v>
+        <v>320.4965251579071</v>
       </c>
       <c r="D65" t="n">
-        <v>314.069055340672</v>
+        <v>308.0008443067889</v>
       </c>
       <c r="E65" t="n">
-        <v>319.5883178710938</v>
+        <v>311.8233947753906</v>
       </c>
       <c r="F65" t="n">
-        <v>33428900</v>
+        <v>42353700</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B66" t="n">
-        <v>319.4585671045538</v>
+        <v>313.0909556884665</v>
       </c>
       <c r="C66" t="n">
-        <v>320.4965565243085</v>
+        <v>314.2586670471713</v>
       </c>
       <c r="D66" t="n">
-        <v>308.0008744502611</v>
+        <v>304.9667450846255</v>
       </c>
       <c r="E66" t="n">
-        <v>311.8234252929688</v>
+        <v>308.6895141601562</v>
       </c>
       <c r="F66" t="n">
-        <v>42353700</v>
+        <v>35940200</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B67" t="n">
-        <v>313.0909556884665</v>
+        <v>310.7155693717638</v>
       </c>
       <c r="C67" t="n">
-        <v>314.2586670471713</v>
+        <v>310.8153813101663</v>
       </c>
       <c r="D67" t="n">
-        <v>304.9667450846255</v>
+        <v>304.288070405232</v>
       </c>
       <c r="E67" t="n">
-        <v>308.6895141601562</v>
+        <v>307.62158203125</v>
       </c>
       <c r="F67" t="n">
-        <v>35940200</v>
+        <v>29151900</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B68" t="n">
-        <v>310.7156001962807</v>
+        <v>304.3579426322819</v>
       </c>
       <c r="C68" t="n">
-        <v>310.8154121445851</v>
+        <v>310.1666197797816</v>
       </c>
       <c r="D68" t="n">
-        <v>304.2881005921093</v>
+        <v>302.0025088045779</v>
       </c>
       <c r="E68" t="n">
-        <v>307.6216125488281</v>
+        <v>305.9747924804688</v>
       </c>
       <c r="F68" t="n">
-        <v>29151900</v>
+        <v>30585000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B69" t="n">
-        <v>304.3579426322819</v>
+        <v>307.4120099511304</v>
       </c>
       <c r="C69" t="n">
-        <v>310.1666197797816</v>
+        <v>307.4918412298865</v>
       </c>
       <c r="D69" t="n">
-        <v>302.0025088045779</v>
+        <v>295.5450797036171</v>
       </c>
       <c r="E69" t="n">
-        <v>305.9747924804688</v>
+        <v>296.1439208984375</v>
       </c>
       <c r="F69" t="n">
-        <v>30585000</v>
+        <v>43930400</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B70" t="n">
-        <v>307.4120099511304</v>
+        <v>301.1342186567393</v>
       </c>
       <c r="C70" t="n">
-        <v>307.4918412298865</v>
+        <v>303.3698600006946</v>
       </c>
       <c r="D70" t="n">
-        <v>295.5450797036171</v>
+        <v>298.6490626821344</v>
       </c>
       <c r="E70" t="n">
-        <v>296.1439208984375</v>
+        <v>301.8727722167969</v>
       </c>
       <c r="F70" t="n">
-        <v>43930400</v>
+        <v>33518000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B71" t="n">
-        <v>301.1342186567393</v>
+        <v>301.1442091965169</v>
       </c>
       <c r="C71" t="n">
-        <v>303.3698600006946</v>
+        <v>306.6534812800651</v>
       </c>
       <c r="D71" t="n">
-        <v>298.6490626821344</v>
+        <v>300.3856749721532</v>
       </c>
       <c r="E71" t="n">
-        <v>301.8727722167969</v>
+        <v>306.5636596679688</v>
       </c>
       <c r="F71" t="n">
-        <v>33518000</v>
+        <v>59943200</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B72" t="n">
-        <v>301.1442091965169</v>
+        <v>309.2783702904479</v>
       </c>
       <c r="C72" t="n">
-        <v>306.6534812800651</v>
+        <v>309.5278849133803</v>
       </c>
       <c r="D72" t="n">
-        <v>300.3856749721532</v>
+        <v>304.7072453416635</v>
       </c>
       <c r="E72" t="n">
-        <v>306.5636596679688</v>
+        <v>309.1785583496094</v>
       </c>
       <c r="F72" t="n">
-        <v>59943200</v>
+        <v>26429900</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B73" t="n">
-        <v>309.278400817878</v>
+        <v>309.0288478780406</v>
       </c>
       <c r="C73" t="n">
-        <v>309.5279154654388</v>
+        <v>314.328535898872</v>
       </c>
       <c r="D73" t="n">
-        <v>304.707275417899</v>
+        <v>308.7194521900694</v>
       </c>
       <c r="E73" t="n">
-        <v>309.1785888671875</v>
+        <v>313.7396850585938</v>
       </c>
       <c r="F73" t="n">
-        <v>26429900</v>
+        <v>25478700</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B74" t="n">
-        <v>309.0288478780406</v>
+        <v>314.1588665693361</v>
       </c>
       <c r="C74" t="n">
-        <v>314.328535898872</v>
+        <v>314.4682622711062</v>
       </c>
       <c r="D74" t="n">
-        <v>308.7194521900694</v>
+        <v>311.3144241794057</v>
       </c>
       <c r="E74" t="n">
-        <v>313.7396850585938</v>
+        <v>313.4801940917969</v>
       </c>
       <c r="F74" t="n">
-        <v>25478700</v>
+        <v>10097400</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B75" t="n">
-        <v>314.1588359856885</v>
+        <v>313.8694546536391</v>
       </c>
       <c r="C75" t="n">
-        <v>314.4682316573388</v>
+        <v>314.4782557314601</v>
       </c>
       <c r="D75" t="n">
-        <v>311.3143938726672</v>
+        <v>311.6737137240756</v>
       </c>
       <c r="E75" t="n">
-        <v>313.4801635742188</v>
+        <v>312.9013366699219</v>
       </c>
       <c r="F75" t="n">
-        <v>10097400</v>
+        <v>10899000</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B76" t="n">
-        <v>313.8694852656387</v>
+        <v>310.7654822740718</v>
       </c>
       <c r="C76" t="n">
-        <v>314.4782864028367</v>
+        <v>313.4103313095557</v>
       </c>
       <c r="D76" t="n">
-        <v>311.6737441219225</v>
+        <v>310.0169383701615</v>
       </c>
       <c r="E76" t="n">
-        <v>312.9013671875</v>
+        <v>312.9512329101562</v>
       </c>
       <c r="F76" t="n">
-        <v>10899000</v>
+        <v>19621800</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B77" t="n">
-        <v>310.7655125785055</v>
+        <v>311.8932765746258</v>
       </c>
       <c r="C77" t="n">
-        <v>313.410361871903</v>
+        <v>316.3346490163796</v>
       </c>
       <c r="D77" t="n">
-        <v>310.0169686016006</v>
+        <v>311.8533457068925</v>
       </c>
       <c r="E77" t="n">
-        <v>312.9512634277344</v>
+        <v>313.2406616210938</v>
       </c>
       <c r="F77" t="n">
-        <v>19621800</v>
+        <v>17380900</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B78" t="n">
-        <v>311.8932765746258</v>
+        <v>312.2426007868329</v>
       </c>
       <c r="C78" t="n">
-        <v>316.3346490163796</v>
+        <v>313.9692224596297</v>
       </c>
       <c r="D78" t="n">
-        <v>311.8533457068925</v>
+        <v>310.8353346785167</v>
       </c>
       <c r="E78" t="n">
-        <v>313.2406616210938</v>
+        <v>312.3923034667969</v>
       </c>
       <c r="F78" t="n">
-        <v>17380900</v>
+        <v>16377700</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B79" t="n">
-        <v>312.2426007868329</v>
+        <v>316.2847494408858</v>
       </c>
       <c r="C79" t="n">
-        <v>313.9692224596297</v>
+        <v>321.8738834308866</v>
       </c>
       <c r="D79" t="n">
-        <v>310.8353346785167</v>
+        <v>309.727497435876</v>
       </c>
       <c r="E79" t="n">
-        <v>312.3923034667969</v>
+        <v>314.5381469726562</v>
       </c>
       <c r="F79" t="n">
-        <v>16377700</v>
+        <v>32009400</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B80" t="n">
-        <v>316.2847187538463</v>
+        <v>317.0432968268774</v>
       </c>
       <c r="C80" t="n">
-        <v>321.87385220157</v>
+        <v>318.4006418955826</v>
       </c>
       <c r="D80" t="n">
-        <v>309.7274673850438</v>
+        <v>314.0191805034655</v>
       </c>
       <c r="E80" t="n">
-        <v>314.5381164550781</v>
+        <v>315.9254760742188</v>
       </c>
       <c r="F80" t="n">
-        <v>32009400</v>
+        <v>30195600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B81" t="n">
-        <v>317.0432662013207</v>
+        <v>315.7857038876524</v>
       </c>
       <c r="C81" t="n">
-        <v>318.4006111389099</v>
+        <v>320.3168980142969</v>
       </c>
       <c r="D81" t="n">
-        <v>314.0191501700305</v>
+        <v>311.1746784825258</v>
       </c>
       <c r="E81" t="n">
-        <v>315.9254455566406</v>
+        <v>313.7297058105469</v>
       </c>
       <c r="F81" t="n">
-        <v>30195600</v>
+        <v>31212100</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B82" t="n">
-        <v>315.7857038876524</v>
+        <v>313.7496575108236</v>
       </c>
       <c r="C82" t="n">
-        <v>320.3168980142969</v>
+        <v>325.5167758318212</v>
       </c>
       <c r="D82" t="n">
-        <v>311.1746784825258</v>
+        <v>313.5800046213677</v>
       </c>
       <c r="E82" t="n">
-        <v>313.7297058105469</v>
+        <v>321.3548889160156</v>
       </c>
       <c r="F82" t="n">
-        <v>31212100</v>
+        <v>35104400</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B83" t="n">
-        <v>313.7496873061683</v>
+        <v>328.3313118537803</v>
       </c>
       <c r="C83" t="n">
-        <v>325.5168067446344</v>
+        <v>329.6786969446188</v>
       </c>
       <c r="D83" t="n">
-        <v>313.5800344006012</v>
+        <v>320.8758135066914</v>
       </c>
       <c r="E83" t="n">
-        <v>321.3549194335938</v>
+        <v>324.8081665039062</v>
       </c>
       <c r="F83" t="n">
-        <v>35104400</v>
+        <v>31896100</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B84" t="n">
-        <v>328.3313118537803</v>
+        <v>326.4549607998293</v>
       </c>
       <c r="C84" t="n">
-        <v>329.6786969446188</v>
+        <v>330.1876899539591</v>
       </c>
       <c r="D84" t="n">
-        <v>320.8758135066914</v>
+        <v>325.1674567682817</v>
       </c>
       <c r="E84" t="n">
-        <v>324.8081665039062</v>
+        <v>327.9320983886719</v>
       </c>
       <c r="F84" t="n">
-        <v>31896100</v>
+        <v>26214200</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B85" t="n">
-        <v>326.4549607998293</v>
+        <v>325.1674358606418</v>
       </c>
       <c r="C85" t="n">
-        <v>330.1876899539591</v>
+        <v>333.3914583276215</v>
       </c>
       <c r="D85" t="n">
-        <v>325.1674567682817</v>
+        <v>324.3690012716118</v>
       </c>
       <c r="E85" t="n">
-        <v>327.9320983886719</v>
+        <v>331.2156677246094</v>
       </c>
       <c r="F85" t="n">
-        <v>26214200</v>
+        <v>33923900</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B86" t="n">
-        <v>325.1674658209474</v>
+        <v>334.2997097916206</v>
       </c>
       <c r="C86" t="n">
-        <v>333.3914890456728</v>
+        <v>339.828932001794</v>
       </c>
       <c r="D86" t="n">
-        <v>324.3690311583512</v>
+        <v>332.9722749179122</v>
       </c>
       <c r="E86" t="n">
-        <v>331.2156982421875</v>
+        <v>335.3177185058594</v>
       </c>
       <c r="F86" t="n">
-        <v>33923900</v>
+        <v>33517600</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B87" t="n">
-        <v>334.2996793666924</v>
+        <v>334.4094733641317</v>
       </c>
       <c r="C87" t="n">
-        <v>339.8289010736461</v>
+        <v>335.8666302231012</v>
       </c>
       <c r="D87" t="n">
-        <v>332.9722446137951</v>
+        <v>329.8383789070015</v>
       </c>
       <c r="E87" t="n">
-        <v>335.3176879882812</v>
+        <v>335.1879577636719</v>
       </c>
       <c r="F87" t="n">
-        <v>33517600</v>
+        <v>28525600</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B88" t="n">
-        <v>334.4094733641317</v>
+        <v>336.9944202593897</v>
       </c>
       <c r="C88" t="n">
-        <v>335.8666302231012</v>
+        <v>337.0343511246202</v>
       </c>
       <c r="D88" t="n">
-        <v>329.8383789070015</v>
+        <v>330.0978329050398</v>
       </c>
       <c r="E88" t="n">
-        <v>335.1879577636719</v>
+        <v>332.1338806152344</v>
       </c>
       <c r="F88" t="n">
-        <v>28525600</v>
+        <v>28442400</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B89" t="n">
-        <v>336.9944512235705</v>
+        <v>333.7607557246461</v>
       </c>
       <c r="C89" t="n">
-        <v>337.03438209247</v>
+        <v>334.0002800245007</v>
       </c>
       <c r="D89" t="n">
-        <v>330.097863235539</v>
+        <v>327.0637915356931</v>
       </c>
       <c r="E89" t="n">
-        <v>332.1339111328125</v>
+        <v>329.3593139648438</v>
       </c>
       <c r="F89" t="n">
-        <v>28442400</v>
+        <v>40341600</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B90" t="n">
-        <v>333.7607557246461</v>
+        <v>320.2470363972373</v>
       </c>
       <c r="C90" t="n">
-        <v>334.0002800245007</v>
+        <v>327.0937337673917</v>
       </c>
       <c r="D90" t="n">
-        <v>327.0637915356931</v>
+        <v>319.8078882063433</v>
       </c>
       <c r="E90" t="n">
-        <v>329.3593139648438</v>
+        <v>321.3748474121094</v>
       </c>
       <c r="F90" t="n">
-        <v>40341600</v>
+        <v>35361000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B91" t="n">
-        <v>320.2470363972373</v>
+        <v>320.2969541162656</v>
       </c>
       <c r="C91" t="n">
-        <v>327.0937337673917</v>
+        <v>331.8345081879527</v>
       </c>
       <c r="D91" t="n">
-        <v>319.8078882063433</v>
+        <v>318.729994927537</v>
       </c>
       <c r="E91" t="n">
-        <v>321.3748474121094</v>
+        <v>327.7424621582031</v>
       </c>
       <c r="F91" t="n">
-        <v>35361000</v>
+        <v>35386600</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B92" t="n">
-        <v>320.2969541162656</v>
+        <v>333.8006975362521</v>
       </c>
       <c r="C92" t="n">
-        <v>331.8345081879527</v>
+        <v>334.4993202531722</v>
       </c>
       <c r="D92" t="n">
-        <v>318.729994927537</v>
+        <v>328.1117515615861</v>
       </c>
       <c r="E92" t="n">
-        <v>327.7424621582031</v>
+        <v>329.8982849121094</v>
       </c>
       <c r="F92" t="n">
-        <v>35386600</v>
+        <v>26253600</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B93" t="n">
-        <v>333.8006666576773</v>
+        <v>331.8444485977197</v>
       </c>
       <c r="C93" t="n">
-        <v>334.4992893099707</v>
+        <v>333.0421309365838</v>
       </c>
       <c r="D93" t="n">
-        <v>328.1117212092731</v>
+        <v>326.8142558744754</v>
       </c>
       <c r="E93" t="n">
-        <v>329.8982543945312</v>
+        <v>327.2933044433594</v>
       </c>
       <c r="F93" t="n">
-        <v>26253600</v>
+        <v>27280000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B94" t="n">
-        <v>331.8444485977197</v>
+        <v>327.1735452193246</v>
       </c>
       <c r="C94" t="n">
-        <v>333.0421309365838</v>
+        <v>335.1879535299186</v>
       </c>
       <c r="D94" t="n">
-        <v>326.8142558744754</v>
+        <v>326.3651202937951</v>
       </c>
       <c r="E94" t="n">
-        <v>327.2933044433594</v>
+        <v>332.6129760742188</v>
       </c>
       <c r="F94" t="n">
-        <v>27280000</v>
+        <v>26042100</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B95" t="n">
-        <v>327.1735452193246</v>
+        <v>334.7188669221849</v>
       </c>
       <c r="C95" t="n">
-        <v>335.1879535299186</v>
+        <v>337.2539439848537</v>
       </c>
       <c r="D95" t="n">
-        <v>326.3651202937951</v>
+        <v>332.8325522369338</v>
       </c>
       <c r="E95" t="n">
-        <v>332.6129760742188</v>
+        <v>333.9004516601562</v>
       </c>
       <c r="F95" t="n">
-        <v>26042100</v>
+        <v>21636200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B96" t="n">
-        <v>334.7188669221849</v>
+        <v>335.4075567602221</v>
       </c>
       <c r="C96" t="n">
-        <v>337.2539439848537</v>
+        <v>336.8846943919215</v>
       </c>
       <c r="D96" t="n">
-        <v>332.8325522369338</v>
+        <v>331.2955603721992</v>
       </c>
       <c r="E96" t="n">
-        <v>333.9004516601562</v>
+        <v>335.357666015625</v>
       </c>
       <c r="F96" t="n">
-        <v>21636200</v>
+        <v>27434400</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B97" t="n">
-        <v>335.4075262381039</v>
+        <v>339.639269303412</v>
       </c>
       <c r="C97" t="n">
-        <v>336.8846637353836</v>
+        <v>341.6254262776615</v>
       </c>
       <c r="D97" t="n">
-        <v>331.2955302242731</v>
+        <v>325.9060061089392</v>
       </c>
       <c r="E97" t="n">
-        <v>335.3576354980469</v>
+        <v>337.59326171875</v>
       </c>
       <c r="F97" t="n">
-        <v>27434400</v>
+        <v>39785600</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B98" t="n">
-        <v>339.6393000059441</v>
+        <v>339.3398975620609</v>
       </c>
       <c r="C98" t="n">
-        <v>341.625457159737</v>
+        <v>339.3398975620609</v>
       </c>
       <c r="D98" t="n">
-        <v>325.9060355700189</v>
+        <v>331.6448748839121</v>
       </c>
       <c r="E98" t="n">
-        <v>337.5932922363281</v>
+        <v>337.3437805175781</v>
       </c>
       <c r="F98" t="n">
-        <v>39785600</v>
+        <v>31024000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B99" t="n">
-        <v>339.3398975620609</v>
+        <v>335.5672372238362</v>
       </c>
       <c r="C99" t="n">
-        <v>339.3398975620609</v>
+        <v>344.160506471566</v>
       </c>
       <c r="D99" t="n">
-        <v>331.6448748839121</v>
+        <v>334.9783863513143</v>
       </c>
       <c r="E99" t="n">
-        <v>337.3437805175781</v>
+        <v>343.0227355957031</v>
       </c>
       <c r="F99" t="n">
-        <v>31024000</v>
+        <v>32006100</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B100" t="n">
-        <v>335.5672073695487</v>
+        <v>346.6656368085559</v>
       </c>
       <c r="C100" t="n">
-        <v>344.1604758527643</v>
+        <v>348.322417578686</v>
       </c>
       <c r="D100" t="n">
-        <v>334.9783565494149</v>
+        <v>336.8148042563823</v>
       </c>
       <c r="E100" t="n">
-        <v>343.022705078125</v>
+        <v>339.0504455566406</v>
       </c>
       <c r="F100" t="n">
-        <v>32006100</v>
+        <v>36506700</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B101" t="n">
-        <v>346.6656368085559</v>
+        <v>342.2941250868659</v>
       </c>
       <c r="C101" t="n">
-        <v>348.322417578686</v>
+        <v>342.6434516437907</v>
       </c>
       <c r="D101" t="n">
-        <v>336.8148042563823</v>
+        <v>327.8821583120744</v>
       </c>
       <c r="E101" t="n">
-        <v>339.0504455566406</v>
+        <v>332.3934020996094</v>
       </c>
       <c r="F101" t="n">
-        <v>36506700</v>
+        <v>70618400</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B102" t="n">
-        <v>342.2941565134455</v>
+        <v>311.6138208417116</v>
       </c>
       <c r="C102" t="n">
-        <v>342.6434831024425</v>
+        <v>332.0440792110618</v>
       </c>
       <c r="D102" t="n">
-        <v>327.8821884154679</v>
+        <v>305.8649942318392</v>
       </c>
       <c r="E102" t="n">
-        <v>332.3934326171875</v>
+        <v>330.6068725585938</v>
       </c>
       <c r="F102" t="n">
-        <v>70618400</v>
+        <v>88205800</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B103" t="n">
-        <v>311.6138496060838</v>
+        <v>326.5447743483745</v>
       </c>
       <c r="C103" t="n">
-        <v>332.0441098613053</v>
+        <v>329.7385737476322</v>
       </c>
       <c r="D103" t="n">
-        <v>305.8650224655501</v>
+        <v>319.2988903139048</v>
       </c>
       <c r="E103" t="n">
-        <v>330.6069030761719</v>
+        <v>322.233154296875</v>
       </c>
       <c r="F103" t="n">
-        <v>88205800</v>
+        <v>56380500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B104" t="n">
-        <v>326.5447743483745</v>
+        <v>320.3069052195784</v>
       </c>
       <c r="C104" t="n">
-        <v>329.7385737476322</v>
+        <v>327.0637807183464</v>
       </c>
       <c r="D104" t="n">
-        <v>319.2988903139048</v>
+        <v>316.6440476026885</v>
       </c>
       <c r="E104" t="n">
-        <v>322.233154296875</v>
+        <v>323.6903381347656</v>
       </c>
       <c r="F104" t="n">
-        <v>56380500</v>
+        <v>39640100</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B105" t="n">
-        <v>320.3069052195784</v>
+        <v>320.3468306795893</v>
       </c>
       <c r="C105" t="n">
-        <v>327.0637807183464</v>
+        <v>321.0454837970353</v>
       </c>
       <c r="D105" t="n">
-        <v>316.6440476026885</v>
+        <v>313.9991629255859</v>
       </c>
       <c r="E105" t="n">
-        <v>323.6903381347656</v>
+        <v>317.9614562988281</v>
       </c>
       <c r="F105" t="n">
-        <v>39640100</v>
+        <v>39170000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B106" t="n">
-        <v>320.3468306795893</v>
+        <v>318.3507205277581</v>
       </c>
       <c r="C106" t="n">
-        <v>321.0454837970353</v>
+        <v>320.4366591349046</v>
       </c>
       <c r="D106" t="n">
-        <v>313.9991629255859</v>
+        <v>309.0587983421378</v>
       </c>
       <c r="E106" t="n">
-        <v>317.9614562988281</v>
+        <v>310.3562622070312</v>
       </c>
       <c r="F106" t="n">
-        <v>39170000</v>
+        <v>45406400</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B107" t="n">
-        <v>318.3506892240785</v>
+        <v>311.4840518259579</v>
       </c>
       <c r="C107" t="n">
-        <v>320.4366276261131</v>
+        <v>315.6259882196205</v>
       </c>
       <c r="D107" t="n">
-        <v>309.0587679521403</v>
+        <v>306.603561940612</v>
       </c>
       <c r="E107" t="n">
-        <v>310.3562316894531</v>
+        <v>308.4000549316406</v>
       </c>
       <c r="F107" t="n">
-        <v>45406400</v>
+        <v>47761300</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B108" t="n">
-        <v>311.4840826487114</v>
+        <v>307.1325415821482</v>
       </c>
       <c r="C108" t="n">
-        <v>315.6260194522374</v>
+        <v>308.0307881065925</v>
       </c>
       <c r="D108" t="n">
-        <v>306.603592280419</v>
+        <v>303.1203270701956</v>
       </c>
       <c r="E108" t="n">
-        <v>308.4000854492188</v>
+        <v>305.1264343261719</v>
       </c>
       <c r="F108" t="n">
-        <v>47761300</v>
+        <v>38499700</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B109" t="n">
-        <v>307.1325415821482</v>
+        <v>299.4574575670962</v>
       </c>
       <c r="C109" t="n">
-        <v>308.0307881065925</v>
+        <v>303.8489085337251</v>
       </c>
       <c r="D109" t="n">
-        <v>303.1203270701956</v>
+        <v>295.674807618098</v>
       </c>
       <c r="E109" t="n">
-        <v>305.1264343261719</v>
+        <v>301.43359375</v>
       </c>
       <c r="F109" t="n">
-        <v>38499700</v>
+        <v>39247600</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B110" t="n">
-        <v>299.4574575670962</v>
+        <v>301.5035060024616</v>
       </c>
       <c r="C110" t="n">
-        <v>303.8489085337251</v>
+        <v>304.7871271852118</v>
       </c>
       <c r="D110" t="n">
-        <v>295.674807618098</v>
+        <v>300.6651404690992</v>
       </c>
       <c r="E110" t="n">
-        <v>301.43359375</v>
+        <v>302.7410888671875</v>
       </c>
       <c r="F110" t="n">
-        <v>39247600</v>
+        <v>28482100</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B111" t="n">
-        <v>301.5035060024616</v>
+        <v>301.2340248853423</v>
       </c>
       <c r="C111" t="n">
-        <v>304.7871271852118</v>
+        <v>304.8769323320439</v>
       </c>
       <c r="D111" t="n">
-        <v>300.6651404690992</v>
+        <v>299.4574819671566</v>
       </c>
       <c r="E111" t="n">
-        <v>302.7410888671875</v>
+        <v>302.2620239257812</v>
       </c>
       <c r="F111" t="n">
-        <v>28482100</v>
+        <v>25834400</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B112" t="n">
-        <v>301.2340248853423</v>
+        <v>303.7291622459488</v>
       </c>
       <c r="C112" t="n">
-        <v>304.8769323320439</v>
+        <v>315.885507154404</v>
       </c>
       <c r="D112" t="n">
-        <v>299.4574819671566</v>
+        <v>303.3099642850277</v>
       </c>
       <c r="E112" t="n">
-        <v>302.2620239257812</v>
+        <v>314.3684692382812</v>
       </c>
       <c r="F112" t="n">
-        <v>25834400</v>
+        <v>53210800</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B113" t="n">
-        <v>303.7291917307074</v>
+        <v>318.4305429928518</v>
       </c>
       <c r="C113" t="n">
-        <v>315.8855378192499</v>
+        <v>318.8996316925602</v>
       </c>
       <c r="D113" t="n">
-        <v>303.3099937290923</v>
+        <v>309.2683735389658</v>
       </c>
       <c r="E113" t="n">
-        <v>314.3684997558594</v>
+        <v>310.8852233886719</v>
       </c>
       <c r="F113" t="n">
-        <v>53210800</v>
+        <v>31423000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B114" t="n">
-        <v>318.4305429928518</v>
+        <v>309.91711960911</v>
       </c>
       <c r="C114" t="n">
-        <v>318.8996316925602</v>
+        <v>311.6637220131571</v>
       </c>
       <c r="D114" t="n">
-        <v>309.2683735389658</v>
+        <v>305.3360346729232</v>
       </c>
       <c r="E114" t="n">
-        <v>310.8852233886719</v>
+        <v>310.29638671875</v>
       </c>
       <c r="F114" t="n">
-        <v>31423000</v>
+        <v>25615600</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B115" t="n">
-        <v>309.91711960911</v>
+        <v>311.4541150323118</v>
       </c>
       <c r="C115" t="n">
-        <v>311.6637220131571</v>
+        <v>313.0310644276307</v>
       </c>
       <c r="D115" t="n">
-        <v>305.3360346729232</v>
+        <v>308.8392067871133</v>
       </c>
       <c r="E115" t="n">
-        <v>310.29638671875</v>
+        <v>312.29248046875</v>
       </c>
       <c r="F115" t="n">
-        <v>25615600</v>
+        <v>29963600</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B116" t="n">
-        <v>311.4541454679639</v>
+        <v>312.0330312197015</v>
       </c>
       <c r="C116" t="n">
-        <v>313.031095017384</v>
+        <v>312.5320604811519</v>
       </c>
       <c r="D116" t="n">
-        <v>308.8392369672335</v>
+        <v>301.7630004907203</v>
       </c>
       <c r="E116" t="n">
-        <v>312.2925109863281</v>
+        <v>306.7832336425781</v>
       </c>
       <c r="F116" t="n">
-        <v>29963600</v>
+        <v>36431200</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B117" t="n">
-        <v>312.0330001798944</v>
+        <v>303.5495233120643</v>
       </c>
       <c r="C117" t="n">
-        <v>312.5320293917034</v>
+        <v>311.7635251790807</v>
       </c>
       <c r="D117" t="n">
-        <v>301.762970472535</v>
+        <v>303.2101566226461</v>
       </c>
       <c r="E117" t="n">
-        <v>306.783203125</v>
+        <v>311.1547241210938</v>
       </c>
       <c r="F117" t="n">
-        <v>36431200</v>
+        <v>44640600</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B118" t="n">
-        <v>303.5495233120643</v>
+        <v>302.6413055358027</v>
       </c>
       <c r="C118" t="n">
-        <v>311.7635251790807</v>
+        <v>307.8910728050191</v>
       </c>
       <c r="D118" t="n">
-        <v>303.2101566226461</v>
+        <v>300.7150293830805</v>
       </c>
       <c r="E118" t="n">
-        <v>311.1547241210938</v>
+        <v>305.9248962402344</v>
       </c>
       <c r="F118" t="n">
-        <v>44640600</v>
+        <v>34790200</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B119" t="n">
-        <v>302.6413055358027</v>
+        <v>298.0102681623609</v>
       </c>
       <c r="C119" t="n">
-        <v>307.8910728050191</v>
+        <v>303.3498869477631</v>
       </c>
       <c r="D119" t="n">
-        <v>300.7150293830805</v>
+        <v>296.1339134078651</v>
       </c>
       <c r="E119" t="n">
-        <v>305.9248962402344</v>
+        <v>302.9905700683594</v>
       </c>
       <c r="F119" t="n">
-        <v>34790200</v>
+        <v>35497000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B120" t="n">
-        <v>298.0102681623609</v>
+        <v>302.3019795923877</v>
       </c>
       <c r="C120" t="n">
-        <v>303.3498869477631</v>
+        <v>304.8769573413998</v>
       </c>
       <c r="D120" t="n">
-        <v>296.1339134078651</v>
+        <v>300.1661195993462</v>
       </c>
       <c r="E120" t="n">
-        <v>302.9905700683594</v>
+        <v>302.54150390625</v>
       </c>
       <c r="F120" t="n">
-        <v>35497000</v>
+        <v>29536200</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B121" t="n">
-        <v>302.3019795923877</v>
+        <v>302.4516473530844</v>
       </c>
       <c r="C121" t="n">
-        <v>304.8769573413998</v>
+        <v>302.711121843687</v>
       </c>
       <c r="D121" t="n">
-        <v>300.1661195993462</v>
+        <v>297.4114338033223</v>
       </c>
       <c r="E121" t="n">
-        <v>302.54150390625</v>
+        <v>300.2958374023438</v>
       </c>
       <c r="F121" t="n">
-        <v>29536200</v>
+        <v>35752300</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B122" t="n">
-        <v>302.4516780897468</v>
+        <v>295.5151547022239</v>
       </c>
       <c r="C122" t="n">
-        <v>302.7111526067185</v>
+        <v>299.9465371351957</v>
       </c>
       <c r="D122" t="n">
-        <v>297.4114640277728</v>
+        <v>294.6069177596933</v>
       </c>
       <c r="E122" t="n">
-        <v>300.2958679199219</v>
+        <v>297.9404296875</v>
       </c>
       <c r="F122" t="n">
-        <v>35752300</v>
+        <v>25576900</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,25 +3615,25 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B123" t="n">
-        <v>295.5151547022239</v>
+        <v>293.9952756214191</v>
       </c>
       <c r="C123" t="n">
-        <v>299.9465371351957</v>
+        <v>306.4198649966507</v>
       </c>
       <c r="D123" t="n">
-        <v>294.6069177596933</v>
+        <v>293.7156237584298</v>
       </c>
       <c r="E123" t="n">
-        <v>297.9404296875</v>
+        <v>305.9804077148438</v>
       </c>
       <c r="F123" t="n">
-        <v>25576900</v>
+        <v>29312100</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -3641,25 +3641,25 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B124" t="n">
-        <v>293.9952756214191</v>
+        <v>305.7906896809686</v>
       </c>
       <c r="C124" t="n">
-        <v>306.4198649966507</v>
+        <v>309.1265479913924</v>
       </c>
       <c r="D124" t="n">
-        <v>293.7156237584298</v>
+        <v>305.1914269440574</v>
       </c>
       <c r="E124" t="n">
-        <v>305.9804077148438</v>
+        <v>306.6596069335938</v>
       </c>
       <c r="F124" t="n">
-        <v>29312100</v>
+        <v>23239700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B125" t="n">
-        <v>305.7906896809686</v>
+        <v>306.3699695674413</v>
       </c>
       <c r="C125" t="n">
-        <v>309.1265479913924</v>
+        <v>311.0341973481569</v>
       </c>
       <c r="D125" t="n">
-        <v>305.1914269440574</v>
+        <v>305.5410112597431</v>
       </c>
       <c r="E125" t="n">
-        <v>306.6596069335938</v>
+        <v>308.3175659179688</v>
       </c>
       <c r="F125" t="n">
-        <v>23239700</v>
+        <v>24125700</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B126" t="n">
-        <v>306.3699695674413</v>
+        <v>306.4398571350748</v>
       </c>
       <c r="C126" t="n">
-        <v>311.0341973481569</v>
+        <v>308.5572255769297</v>
       </c>
       <c r="D126" t="n">
-        <v>305.5410112597431</v>
+        <v>300.6570224145156</v>
       </c>
       <c r="E126" t="n">
-        <v>308.3175659179688</v>
+        <v>303.1738891601562</v>
       </c>
       <c r="F126" t="n">
-        <v>24125700</v>
+        <v>24928300</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B127" t="n">
-        <v>306.4398571350748</v>
+        <v>306.6296377698095</v>
       </c>
       <c r="C127" t="n">
-        <v>308.5572255769297</v>
+        <v>307.3087879643589</v>
       </c>
       <c r="D127" t="n">
-        <v>300.6570224145156</v>
+        <v>300.0677703977713</v>
       </c>
       <c r="E127" t="n">
-        <v>303.1738891601562</v>
+        <v>301.9054870605469</v>
       </c>
       <c r="F127" t="n">
-        <v>24928300</v>
+        <v>23693100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B128" t="n">
-        <v>306.6296377698095</v>
+        <v>303.9729346538992</v>
       </c>
       <c r="C128" t="n">
-        <v>307.3087879643589</v>
+        <v>306.1102674724465</v>
       </c>
       <c r="D128" t="n">
-        <v>300.0677703977713</v>
+        <v>302.6445653756606</v>
       </c>
       <c r="E128" t="n">
-        <v>301.9054870605469</v>
+        <v>305.1814270019531</v>
       </c>
       <c r="F128" t="n">
-        <v>23693100</v>
+        <v>23519700</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B129" t="n">
-        <v>303.9729346538992</v>
+        <v>305.481031231764</v>
       </c>
       <c r="C129" t="n">
-        <v>306.1102674724465</v>
+        <v>311.0341705495281</v>
       </c>
       <c r="D129" t="n">
-        <v>302.6445653756606</v>
+        <v>305.1214918945171</v>
       </c>
       <c r="E129" t="n">
-        <v>305.1814270019531</v>
+        <v>310.5347900390625</v>
       </c>
       <c r="F129" t="n">
-        <v>23519700</v>
+        <v>21955200</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B130" t="n">
-        <v>305.481031231764</v>
+        <v>308.8868058363209</v>
       </c>
       <c r="C130" t="n">
-        <v>311.0341705495281</v>
+        <v>312.0828532524296</v>
       </c>
       <c r="D130" t="n">
-        <v>305.1214918945171</v>
+        <v>306.5497087361953</v>
       </c>
       <c r="E130" t="n">
-        <v>310.5347900390625</v>
+        <v>307.3087768554688</v>
       </c>
       <c r="F130" t="n">
-        <v>21955200</v>
+        <v>20009800</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B131" t="n">
-        <v>308.8868058363209</v>
+        <v>303.6333516523425</v>
       </c>
       <c r="C131" t="n">
-        <v>312.0828532524296</v>
+        <v>307.6783216475022</v>
       </c>
       <c r="D131" t="n">
-        <v>306.5497087361953</v>
+        <v>301.9754046785898</v>
       </c>
       <c r="E131" t="n">
-        <v>307.3087768554688</v>
+        <v>306.7494812011719</v>
       </c>
       <c r="F131" t="n">
-        <v>20009800</v>
+        <v>25075800</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B132" t="n">
-        <v>303.6333516523425</v>
+        <v>305.0815409313132</v>
       </c>
       <c r="C132" t="n">
-        <v>307.6783216475022</v>
+        <v>305.620880431115</v>
       </c>
       <c r="D132" t="n">
-        <v>301.9754046785898</v>
+        <v>297.9004465638477</v>
       </c>
       <c r="E132" t="n">
-        <v>306.7494812011719</v>
+        <v>300.6270751953125</v>
       </c>
       <c r="F132" t="n">
-        <v>25075800</v>
+        <v>44364100</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B133" t="n">
-        <v>305.0815409313132</v>
+        <v>301.7357168812967</v>
       </c>
       <c r="C133" t="n">
-        <v>305.620880431115</v>
+        <v>305.6009481410186</v>
       </c>
       <c r="D133" t="n">
-        <v>297.9004465638477</v>
+        <v>300.5571860375472</v>
       </c>
       <c r="E133" t="n">
-        <v>300.6270751953125</v>
+        <v>301.685791015625</v>
       </c>
       <c r="F133" t="n">
-        <v>44364100</v>
+        <v>29326900</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B134" t="n">
-        <v>301.7357168812967</v>
+        <v>298.8293264668504</v>
       </c>
       <c r="C134" t="n">
-        <v>305.6009481410186</v>
+        <v>299.5484356615691</v>
       </c>
       <c r="D134" t="n">
-        <v>300.5571860375472</v>
+        <v>289.9702901097709</v>
       </c>
       <c r="E134" t="n">
-        <v>301.685791015625</v>
+        <v>290.0801696777344</v>
       </c>
       <c r="F134" t="n">
-        <v>29326900</v>
+        <v>36864300</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B135" t="n">
-        <v>298.8293264668504</v>
+        <v>293.0764495892524</v>
       </c>
       <c r="C135" t="n">
-        <v>299.5484356615691</v>
+        <v>295.6332754793409</v>
       </c>
       <c r="D135" t="n">
-        <v>289.9702901097709</v>
+        <v>288.8816409209488</v>
       </c>
       <c r="E135" t="n">
-        <v>290.0801696777344</v>
+        <v>290.5695495605469</v>
       </c>
       <c r="F135" t="n">
-        <v>36864300</v>
+        <v>29460700</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B136" t="n">
-        <v>293.0764495892524</v>
+        <v>287.5532902578335</v>
       </c>
       <c r="C136" t="n">
-        <v>295.6332754793409</v>
+        <v>287.5932492331535</v>
       </c>
       <c r="D136" t="n">
-        <v>288.8816409209488</v>
+        <v>278.1549453585245</v>
       </c>
       <c r="E136" t="n">
-        <v>290.5695495605469</v>
+        <v>280.5719604492188</v>
       </c>
       <c r="F136" t="n">
-        <v>29460700</v>
+        <v>39080600</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B137" t="n">
-        <v>287.5532902578335</v>
+        <v>276.9364822022131</v>
       </c>
       <c r="C137" t="n">
-        <v>287.5932492331535</v>
+        <v>279.0238892859517</v>
       </c>
       <c r="D137" t="n">
-        <v>278.1549453585245</v>
+        <v>273.6106210828978</v>
       </c>
       <c r="E137" t="n">
-        <v>280.5719604492188</v>
+        <v>274.0001220703125</v>
       </c>
       <c r="F137" t="n">
-        <v>39080600</v>
+        <v>35890600</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B138" t="n">
-        <v>276.9364822022131</v>
+        <v>276.0775591796553</v>
       </c>
       <c r="C138" t="n">
-        <v>279.0238892859517</v>
+        <v>276.7467120540596</v>
       </c>
       <c r="D138" t="n">
-        <v>273.6106210828978</v>
+        <v>271.772870758184</v>
       </c>
       <c r="E138" t="n">
-        <v>274.0001220703125</v>
+        <v>273.1611633300781</v>
       </c>
       <c r="F138" t="n">
-        <v>35890600</v>
+        <v>35141200</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B139" t="n">
-        <v>276.0775591796553</v>
+        <v>277.6955407888773</v>
       </c>
       <c r="C139" t="n">
-        <v>276.7467120540596</v>
+        <v>287.7230801433843</v>
       </c>
       <c r="D139" t="n">
-        <v>271.772870758184</v>
+        <v>276.7467055656006</v>
       </c>
       <c r="E139" t="n">
-        <v>273.1611633300781</v>
+        <v>287.2037353515625</v>
       </c>
       <c r="F139" t="n">
-        <v>35141200</v>
+        <v>43875400</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B140" t="n">
-        <v>277.6955407888773</v>
+        <v>290.4796724840224</v>
       </c>
       <c r="C140" t="n">
-        <v>287.7230801433843</v>
+        <v>300.1476725442409</v>
       </c>
       <c r="D140" t="n">
-        <v>276.7467055656006</v>
+        <v>290.0502125293938</v>
       </c>
       <c r="E140" t="n">
-        <v>287.2037353515625</v>
+        <v>297.0215759277344</v>
       </c>
       <c r="F140" t="n">
-        <v>43875400</v>
+        <v>37684500</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B141" t="n">
-        <v>290.4796724840224</v>
+        <v>290.3298713924274</v>
       </c>
       <c r="C141" t="n">
-        <v>300.1476725442409</v>
+        <v>297.7107001938477</v>
       </c>
       <c r="D141" t="n">
-        <v>290.0502125293938</v>
+        <v>289.0914173614996</v>
       </c>
       <c r="E141" t="n">
-        <v>297.0215759277344</v>
+        <v>295.403564453125</v>
       </c>
       <c r="F141" t="n">
-        <v>37684500</v>
+        <v>21666500</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B142" t="n">
-        <v>290.3298713924274</v>
+        <v>295.5034260146894</v>
       </c>
       <c r="C142" t="n">
-        <v>297.7107001938477</v>
+        <v>300.2475409865838</v>
       </c>
       <c r="D142" t="n">
-        <v>289.0914173614996</v>
+        <v>294.8142784540748</v>
       </c>
       <c r="E142" t="n">
-        <v>295.403564453125</v>
+        <v>299.6183166503906</v>
       </c>
       <c r="F142" t="n">
-        <v>21666500</v>
+        <v>16945500</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B143" t="n">
-        <v>295.5034260146894</v>
+        <v>302.3549447988444</v>
       </c>
       <c r="C143" t="n">
-        <v>300.2475409865838</v>
+        <v>305.2513457589993</v>
       </c>
       <c r="D143" t="n">
-        <v>294.8142784540748</v>
+        <v>297.3511421656273</v>
       </c>
       <c r="E143" t="n">
-        <v>299.6183166503906</v>
+        <v>305.08154296875</v>
       </c>
       <c r="F143" t="n">
-        <v>16945500</v>
+        <v>23205400</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B144" t="n">
-        <v>302.3549447988444</v>
+        <v>320.0530070056894</v>
       </c>
       <c r="C144" t="n">
-        <v>305.2513457589993</v>
+        <v>321.6809619973042</v>
       </c>
       <c r="D144" t="n">
-        <v>297.3511421656273</v>
+        <v>314.6297110626625</v>
       </c>
       <c r="E144" t="n">
-        <v>305.08154296875</v>
+        <v>316.9268798828125</v>
       </c>
       <c r="F144" t="n">
-        <v>23205400</v>
+        <v>33547100</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B145" t="n">
-        <v>320.0530070056894</v>
+        <v>315.5186078441214</v>
       </c>
       <c r="C145" t="n">
-        <v>321.6809619973042</v>
+        <v>319.1441153425082</v>
       </c>
       <c r="D145" t="n">
-        <v>314.6297110626625</v>
+        <v>310.6746106421415</v>
       </c>
       <c r="E145" t="n">
-        <v>316.9268798828125</v>
+        <v>318.0953979492188</v>
       </c>
       <c r="F145" t="n">
-        <v>33547100</v>
+        <v>23739200</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B146" t="n">
-        <v>315.5186078441214</v>
+        <v>319.6235089208506</v>
       </c>
       <c r="C146" t="n">
-        <v>319.1441153425082</v>
+        <v>321.4312640320202</v>
       </c>
       <c r="D146" t="n">
-        <v>310.6746106421415</v>
+        <v>315.9281112234418</v>
       </c>
       <c r="E146" t="n">
-        <v>318.0953979492188</v>
+        <v>316.8469543457031</v>
       </c>
       <c r="F146" t="n">
-        <v>23739200</v>
+        <v>19152600</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B147" t="n">
-        <v>319.6235089208506</v>
+        <v>316.7471095555252</v>
       </c>
       <c r="C147" t="n">
-        <v>321.4312640320202</v>
+        <v>321.2315371363443</v>
       </c>
       <c r="D147" t="n">
-        <v>315.9281112234418</v>
+        <v>315.0791651091577</v>
       </c>
       <c r="E147" t="n">
-        <v>316.8469543457031</v>
+        <v>320.9119262695312</v>
       </c>
       <c r="F147" t="n">
-        <v>19152600</v>
+        <v>18866400</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B148" t="n">
-        <v>316.7471095555252</v>
+        <v>324.3876234083889</v>
       </c>
       <c r="C148" t="n">
-        <v>321.2315371363443</v>
+        <v>332.8770926852431</v>
       </c>
       <c r="D148" t="n">
-        <v>315.0791651091577</v>
+        <v>323.3489033390031</v>
       </c>
       <c r="E148" t="n">
-        <v>320.9119262695312</v>
+        <v>332.49755859375</v>
       </c>
       <c r="F148" t="n">
-        <v>18866400</v>
+        <v>27721400</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B149" t="n">
-        <v>324.3876234083889</v>
+        <v>332.4775916674409</v>
       </c>
       <c r="C149" t="n">
-        <v>332.8770926852431</v>
+        <v>337.0619013824557</v>
       </c>
       <c r="D149" t="n">
-        <v>323.3489033390031</v>
+        <v>330.4900363853266</v>
       </c>
       <c r="E149" t="n">
-        <v>332.49755859375</v>
+        <v>336.7023315429688</v>
       </c>
       <c r="F149" t="n">
-        <v>27721400</v>
+        <v>24918800</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B150" t="n">
-        <v>332.4775916674409</v>
+        <v>338.3302967803236</v>
       </c>
       <c r="C150" t="n">
-        <v>337.0619013824557</v>
+        <v>339.458901613874</v>
       </c>
       <c r="D150" t="n">
-        <v>330.4900363853266</v>
+        <v>334.105526677332</v>
       </c>
       <c r="E150" t="n">
-        <v>336.7023315429688</v>
+        <v>335.6036682128906</v>
       </c>
       <c r="F150" t="n">
-        <v>24918800</v>
+        <v>20541500</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B151" t="n">
-        <v>338.3302967803236</v>
+        <v>337.2316773591919</v>
       </c>
       <c r="C151" t="n">
-        <v>339.458901613874</v>
+        <v>341.895905080184</v>
       </c>
       <c r="D151" t="n">
-        <v>334.105526677332</v>
+        <v>335.8234205588037</v>
       </c>
       <c r="E151" t="n">
-        <v>335.6036682128906</v>
+        <v>341.2566833496094</v>
       </c>
       <c r="F151" t="n">
-        <v>20541500</v>
+        <v>25581900</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B152" t="n">
-        <v>337.2316773591919</v>
+        <v>340.3378420577138</v>
       </c>
       <c r="C152" t="n">
-        <v>341.895905080184</v>
+        <v>340.9770333119858</v>
       </c>
       <c r="D152" t="n">
-        <v>335.8234205588037</v>
+        <v>336.1929591105031</v>
       </c>
       <c r="E152" t="n">
-        <v>341.2566833496094</v>
+        <v>337.0019836425781</v>
       </c>
       <c r="F152" t="n">
-        <v>25581900</v>
+        <v>18784200</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B153" t="n">
-        <v>340.3378420577138</v>
+        <v>337.2716301294484</v>
       </c>
       <c r="C153" t="n">
-        <v>340.9770333119858</v>
+        <v>338.9195798085849</v>
       </c>
       <c r="D153" t="n">
-        <v>336.1929591105031</v>
+        <v>330.9394885663705</v>
       </c>
       <c r="E153" t="n">
-        <v>337.0019836425781</v>
+        <v>331.8783264160156</v>
       </c>
       <c r="F153" t="n">
-        <v>18784200</v>
+        <v>23123800</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B154" t="n">
-        <v>337.2716301294484</v>
+        <v>336.6024588411248</v>
       </c>
       <c r="C154" t="n">
-        <v>338.9195798085849</v>
+        <v>339.3990082413208</v>
       </c>
       <c r="D154" t="n">
-        <v>330.9394885663705</v>
+        <v>334.7547751685775</v>
       </c>
       <c r="E154" t="n">
-        <v>331.8783264160156</v>
+        <v>338.8996276855469</v>
       </c>
       <c r="F154" t="n">
-        <v>23123800</v>
+        <v>20293000</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B155" t="n">
-        <v>336.6024588411248</v>
+        <v>340.7572947145818</v>
       </c>
       <c r="C155" t="n">
-        <v>339.3990082413208</v>
+        <v>341.5363271303731</v>
       </c>
       <c r="D155" t="n">
-        <v>334.7547751685775</v>
+        <v>335.7634893621326</v>
       </c>
       <c r="E155" t="n">
-        <v>338.8996276855469</v>
+        <v>338.4701538085938</v>
       </c>
       <c r="F155" t="n">
-        <v>20293000</v>
+        <v>18650300</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B156" t="n">
-        <v>340.7572947145818</v>
+        <v>338.3103390739037</v>
       </c>
       <c r="C156" t="n">
-        <v>341.5363271303731</v>
+        <v>344.8422143498026</v>
       </c>
       <c r="D156" t="n">
-        <v>335.7634893621326</v>
+        <v>334.9744808477988</v>
       </c>
       <c r="E156" t="n">
-        <v>338.4701538085938</v>
+        <v>343.9732971191406</v>
       </c>
       <c r="F156" t="n">
-        <v>18650300</v>
+        <v>26426100</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B157" t="n">
-        <v>338.3103390739037</v>
+        <v>345.55136124882</v>
       </c>
       <c r="C157" t="n">
-        <v>344.8422143498026</v>
+        <v>352.7424225666816</v>
       </c>
       <c r="D157" t="n">
-        <v>334.9744808477988</v>
+        <v>342.3053878156813</v>
       </c>
       <c r="E157" t="n">
-        <v>343.9732971191406</v>
+        <v>349.9059448242188</v>
       </c>
       <c r="F157" t="n">
-        <v>26426100</v>
+        <v>28576900</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B158" t="n">
-        <v>345.55136124882</v>
+        <v>348.1181620694143</v>
       </c>
       <c r="C158" t="n">
-        <v>352.7424225666816</v>
+        <v>351.9833930501032</v>
       </c>
       <c r="D158" t="n">
-        <v>342.3053878156813</v>
+        <v>345.6911799613628</v>
       </c>
       <c r="E158" t="n">
-        <v>349.9059448242188</v>
+        <v>349.3466491699219</v>
       </c>
       <c r="F158" t="n">
-        <v>28576900</v>
+        <v>27824100</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B159" t="n">
-        <v>348.1181620694143</v>
+        <v>347.1394107424554</v>
       </c>
       <c r="C159" t="n">
-        <v>351.9833930501032</v>
+        <v>355.3492283904879</v>
       </c>
       <c r="D159" t="n">
-        <v>345.6911799613628</v>
+        <v>343.7835575206014</v>
       </c>
       <c r="E159" t="n">
-        <v>349.3466491699219</v>
+        <v>349.5064697265625</v>
       </c>
       <c r="F159" t="n">
-        <v>27824100</v>
+        <v>35376300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B160" t="n">
-        <v>347.1394107424554</v>
+        <v>373.6065555628184</v>
       </c>
       <c r="C160" t="n">
-        <v>355.3492283904879</v>
+        <v>385.3619622201579</v>
       </c>
       <c r="D160" t="n">
-        <v>343.7835575206014</v>
+        <v>365.3667768501622</v>
       </c>
       <c r="E160" t="n">
-        <v>349.5064697265625</v>
+        <v>384.3232421875</v>
       </c>
       <c r="F160" t="n">
-        <v>35376300</v>
+        <v>72040000</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B161" t="n">
-        <v>373.6065555628184</v>
+        <v>381.1572209075714</v>
       </c>
       <c r="C161" t="n">
-        <v>385.3619622201579</v>
+        <v>386.2808704617397</v>
       </c>
       <c r="D161" t="n">
-        <v>365.3667768501622</v>
+        <v>378.5804000830116</v>
       </c>
       <c r="E161" t="n">
-        <v>384.3232421875</v>
+        <v>385.2121887207031</v>
       </c>
       <c r="F161" t="n">
-        <v>72040000</v>
+        <v>30105200</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B162" t="n">
-        <v>381.1572209075714</v>
+        <v>385.1522332062169</v>
       </c>
       <c r="C162" t="n">
-        <v>386.2808704617397</v>
+        <v>386.9000650646732</v>
       </c>
       <c r="D162" t="n">
-        <v>378.5804000830116</v>
+        <v>379.3194722618546</v>
       </c>
       <c r="E162" t="n">
-        <v>385.2121887207031</v>
+        <v>382.7751770019531</v>
       </c>
       <c r="F162" t="n">
-        <v>30105200</v>
+        <v>26298600</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B163" t="n">
-        <v>385.1522332062169</v>
+        <v>385.7515048868787</v>
       </c>
       <c r="C163" t="n">
-        <v>386.9000650646732</v>
+        <v>392.3333367803882</v>
       </c>
       <c r="D163" t="n">
-        <v>379.3194722618546</v>
+        <v>383.5442209432822</v>
       </c>
       <c r="E163" t="n">
-        <v>382.7751770019531</v>
+        <v>387.9487609863281</v>
       </c>
       <c r="F163" t="n">
-        <v>26298600</v>
+        <v>23878600</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B164" t="n">
-        <v>385.7515048868787</v>
+        <v>393.7615619135972</v>
       </c>
       <c r="C164" t="n">
-        <v>392.3333367803882</v>
+        <v>399.3546301445318</v>
       </c>
       <c r="D164" t="n">
-        <v>383.5442209432822</v>
+        <v>392.2734176347804</v>
       </c>
       <c r="E164" t="n">
-        <v>387.9487609863281</v>
+        <v>397.546875</v>
       </c>
       <c r="F164" t="n">
-        <v>23878600</v>
+        <v>31308500</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B165" t="n">
-        <v>393.7615619135972</v>
+        <v>399.4245497990884</v>
       </c>
       <c r="C165" t="n">
-        <v>399.3546301445318</v>
+        <v>399.6043194807176</v>
       </c>
       <c r="D165" t="n">
-        <v>392.2734176347804</v>
+        <v>392.1934987581594</v>
       </c>
       <c r="E165" t="n">
-        <v>397.546875</v>
+        <v>397.4969177246094</v>
       </c>
       <c r="F165" t="n">
-        <v>31308500</v>
+        <v>24433500</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B166" t="n">
-        <v>399.4245497990884</v>
+        <v>396.5081562950806</v>
       </c>
       <c r="C166" t="n">
-        <v>399.6043194807176</v>
+        <v>401.5019617899809</v>
       </c>
       <c r="D166" t="n">
-        <v>392.1934987581594</v>
+        <v>395.8689345614438</v>
       </c>
       <c r="E166" t="n">
-        <v>397.4969177246094</v>
+        <v>400.3034362792969</v>
       </c>
       <c r="F166" t="n">
-        <v>24433500</v>
+        <v>21461800</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B167" t="n">
-        <v>396.5081562950806</v>
+        <v>393.1622804247065</v>
       </c>
       <c r="C167" t="n">
-        <v>401.5019617899809</v>
+        <v>396.9475933307253</v>
       </c>
       <c r="D167" t="n">
-        <v>395.8689345614438</v>
+        <v>387.9887055115338</v>
       </c>
       <c r="E167" t="n">
-        <v>400.3034362792969</v>
+        <v>388.1585083007812</v>
       </c>
       <c r="F167" t="n">
-        <v>21461800</v>
+        <v>30753700</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B168" t="n">
-        <v>393.1622804247065</v>
+        <v>386.8601198229993</v>
       </c>
       <c r="C168" t="n">
-        <v>396.9475933307253</v>
+        <v>388.0386506028281</v>
       </c>
       <c r="D168" t="n">
-        <v>387.9887055115338</v>
+        <v>382.2957742925754</v>
       </c>
       <c r="E168" t="n">
-        <v>388.1585083007812</v>
+        <v>386.8701171875</v>
       </c>
       <c r="F168" t="n">
-        <v>30753700</v>
+        <v>26017500</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B169" t="n">
-        <v>386.8601198229993</v>
+        <v>385.1222825184223</v>
       </c>
       <c r="C169" t="n">
-        <v>388.0386506028281</v>
+        <v>403.1998643489371</v>
       </c>
       <c r="D169" t="n">
-        <v>382.2957742925754</v>
+        <v>384.5230197682841</v>
       </c>
       <c r="E169" t="n">
-        <v>386.8701171875</v>
+        <v>402.1211853027344</v>
       </c>
       <c r="F169" t="n">
-        <v>26017500</v>
+        <v>28144600</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B170" t="n">
-        <v>385.1222825184223</v>
+        <v>396.7878070287349</v>
       </c>
       <c r="C170" t="n">
-        <v>403.1998643489371</v>
+        <v>402.430801125594</v>
       </c>
       <c r="D170" t="n">
-        <v>384.5230197682841</v>
+        <v>395.349588612008</v>
       </c>
       <c r="E170" t="n">
-        <v>402.1211853027344</v>
+        <v>400.5731201171875</v>
       </c>
       <c r="F170" t="n">
-        <v>28144600</v>
+        <v>21136700</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B171" t="n">
-        <v>396.7878070287349</v>
+        <v>395.8290000666237</v>
       </c>
       <c r="C171" t="n">
-        <v>402.430801125594</v>
+        <v>399.0450119758119</v>
       </c>
       <c r="D171" t="n">
-        <v>395.349588612008</v>
+        <v>392.692875633045</v>
       </c>
       <c r="E171" t="n">
-        <v>400.5731201171875</v>
+        <v>396.2884216308594</v>
       </c>
       <c r="F171" t="n">
-        <v>21136700</v>
+        <v>20309700</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B172" t="n">
-        <v>395.8290000666237</v>
+        <v>395.1997907850553</v>
       </c>
       <c r="C172" t="n">
-        <v>399.0450119758119</v>
+        <v>408.1037674120522</v>
       </c>
       <c r="D172" t="n">
-        <v>392.692875633045</v>
+        <v>394.0412242260142</v>
       </c>
       <c r="E172" t="n">
-        <v>396.2884216308594</v>
+        <v>396.4482421875</v>
       </c>
       <c r="F172" t="n">
-        <v>20309700</v>
+        <v>26837200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B173" t="n">
-        <v>395.1997907850553</v>
+        <v>396.4681837278221</v>
       </c>
       <c r="C173" t="n">
-        <v>408.1037674120522</v>
+        <v>396.6579507685057</v>
       </c>
       <c r="D173" t="n">
-        <v>394.0412242260142</v>
+        <v>385.6316200793582</v>
       </c>
       <c r="E173" t="n">
-        <v>396.4482421875</v>
+        <v>387.1797180175781</v>
       </c>
       <c r="F173" t="n">
-        <v>26837200</v>
+        <v>39545700</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B174" t="n">
-        <v>396.4681837278221</v>
+        <v>387.2196997137571</v>
       </c>
       <c r="C174" t="n">
-        <v>396.6579507685057</v>
+        <v>393.3720414113799</v>
       </c>
       <c r="D174" t="n">
-        <v>385.6316200793582</v>
+        <v>382.4256280338265</v>
       </c>
       <c r="E174" t="n">
-        <v>387.1797180175781</v>
+        <v>388.4281921386719</v>
       </c>
       <c r="F174" t="n">
-        <v>39545700</v>
+        <v>31744400</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B175" t="n">
-        <v>387.2196997137571</v>
+        <v>385.2221548650083</v>
       </c>
       <c r="C175" t="n">
-        <v>393.3720414113799</v>
+        <v>392.0137179133836</v>
       </c>
       <c r="D175" t="n">
-        <v>382.4256280338265</v>
+        <v>382.5454520468608</v>
       </c>
       <c r="E175" t="n">
-        <v>388.4281921386719</v>
+        <v>387.1797180175781</v>
       </c>
       <c r="F175" t="n">
-        <v>31744400</v>
+        <v>24852800</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B176" t="n">
-        <v>385.2221548650083</v>
+        <v>386.8701229826527</v>
       </c>
       <c r="C176" t="n">
-        <v>392.0137179133836</v>
+        <v>388.258385079403</v>
       </c>
       <c r="D176" t="n">
-        <v>382.5454520468608</v>
+        <v>381.2970189068101</v>
       </c>
       <c r="E176" t="n">
-        <v>387.1797180175781</v>
+        <v>382.4955444335938</v>
       </c>
       <c r="F176" t="n">
-        <v>24852800</v>
+        <v>20442100</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B177" t="n">
-        <v>386.8701229826527</v>
+        <v>384.0336125447445</v>
       </c>
       <c r="C177" t="n">
-        <v>388.258385079403</v>
+        <v>388.7777274266938</v>
       </c>
       <c r="D177" t="n">
-        <v>381.2970189068101</v>
+        <v>382.125975324115</v>
       </c>
       <c r="E177" t="n">
-        <v>382.4955444335938</v>
+        <v>388.398193359375</v>
       </c>
       <c r="F177" t="n">
-        <v>20442100</v>
+        <v>27747400</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B178" t="n">
-        <v>384.0336125447445</v>
+        <v>386.1909390913781</v>
       </c>
       <c r="C178" t="n">
-        <v>388.7777274266938</v>
+        <v>393.3919975499695</v>
       </c>
       <c r="D178" t="n">
-        <v>382.125975324115</v>
+        <v>385.421873594791</v>
       </c>
       <c r="E178" t="n">
-        <v>388.398193359375</v>
+        <v>388.3482360839844</v>
       </c>
       <c r="F178" t="n">
-        <v>27747400</v>
+        <v>23087300</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B179" t="n">
-        <v>386.1909390913781</v>
+        <v>387.5193014898567</v>
       </c>
       <c r="C179" t="n">
-        <v>393.3919975499695</v>
+        <v>391.384502017129</v>
       </c>
       <c r="D179" t="n">
-        <v>385.421873594791</v>
+        <v>384.682823662297</v>
       </c>
       <c r="E179" t="n">
-        <v>388.3482360839844</v>
+        <v>389.6466674804688</v>
       </c>
       <c r="F179" t="n">
-        <v>23087300</v>
+        <v>24357500</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B180" t="n">
-        <v>387.5193014898567</v>
+        <v>384.7626974671623</v>
       </c>
       <c r="C180" t="n">
-        <v>391.384502017129</v>
+        <v>384.7626974671623</v>
       </c>
       <c r="D180" t="n">
-        <v>384.682823662297</v>
+        <v>377.9910987617443</v>
       </c>
       <c r="E180" t="n">
-        <v>389.6466674804688</v>
+        <v>379.8687744140625</v>
       </c>
       <c r="F180" t="n">
-        <v>24357500</v>
+        <v>44415800</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B181" t="n">
-        <v>384.7626974671623</v>
+        <v>376.0535251127361</v>
       </c>
       <c r="C181" t="n">
-        <v>384.7626974671623</v>
+        <v>378.0910063274455</v>
       </c>
       <c r="D181" t="n">
-        <v>377.9910987617443</v>
+        <v>373.0572417592452</v>
       </c>
       <c r="E181" t="n">
-        <v>379.8687744140625</v>
+        <v>375.9037170410156</v>
       </c>
       <c r="F181" t="n">
-        <v>44415800</v>
+        <v>28672100</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B182" t="n">
-        <v>376.0535251127361</v>
+        <v>366.1358206463617</v>
       </c>
       <c r="C182" t="n">
-        <v>378.0910063274455</v>
+        <v>373.0772223440179</v>
       </c>
       <c r="D182" t="n">
-        <v>373.0572417592452</v>
+        <v>357.9959239406105</v>
       </c>
       <c r="E182" t="n">
-        <v>375.9037170410156</v>
+        <v>361.4017028808594</v>
       </c>
       <c r="F182" t="n">
-        <v>28672100</v>
+        <v>50412300</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B183" t="n">
-        <v>366.1358206463617</v>
+        <v>361.5814692403301</v>
       </c>
       <c r="C183" t="n">
-        <v>373.0772223440179</v>
+        <v>365.9960065843375</v>
       </c>
       <c r="D183" t="n">
-        <v>357.9959239406105</v>
+        <v>357.6363508187865</v>
       </c>
       <c r="E183" t="n">
-        <v>361.4017028808594</v>
+        <v>358.5452270507812</v>
       </c>
       <c r="F183" t="n">
-        <v>50412300</v>
+        <v>55441600</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B184" t="n">
-        <v>361.5814692403301</v>
+        <v>358.4553682250688</v>
       </c>
       <c r="C184" t="n">
-        <v>365.9960065843375</v>
+        <v>372.7875967270043</v>
       </c>
       <c r="D184" t="n">
-        <v>357.6363508187865</v>
+        <v>357.7662205978281</v>
       </c>
       <c r="E184" t="n">
-        <v>358.5452270507812</v>
+        <v>371.7289123535156</v>
       </c>
       <c r="F184" t="n">
-        <v>55441600</v>
+        <v>44055500</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B185" t="n">
-        <v>358.4553682250688</v>
+        <v>365.8861360555161</v>
       </c>
       <c r="C185" t="n">
-        <v>372.7875967270043</v>
+        <v>371.6190149899659</v>
       </c>
       <c r="D185" t="n">
-        <v>357.7662205978281</v>
+        <v>363.6688852043904</v>
       </c>
       <c r="E185" t="n">
-        <v>371.7289123535156</v>
+        <v>368.0734252929688</v>
       </c>
       <c r="F185" t="n">
-        <v>44055500</v>
+        <v>37471200</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,25 +5253,25 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B186" t="n">
-        <v>365.8861360555161</v>
+        <v>364.9454235864071</v>
       </c>
       <c r="C186" t="n">
-        <v>371.6190149899659</v>
+        <v>365.9647879200631</v>
       </c>
       <c r="D186" t="n">
-        <v>363.6688852043904</v>
+        <v>360.2984165590168</v>
       </c>
       <c r="E186" t="n">
-        <v>368.0734252929688</v>
+        <v>363.0766296386719</v>
       </c>
       <c r="F186" t="n">
-        <v>37471200</v>
+        <v>27942500</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5279,25 +5279,25 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B187" t="n">
-        <v>364.9454235864071</v>
+        <v>366.8542002567407</v>
       </c>
       <c r="C187" t="n">
-        <v>365.9647879200631</v>
+        <v>371.8409852276818</v>
       </c>
       <c r="D187" t="n">
-        <v>360.2984165590168</v>
+        <v>357.0704802123837</v>
       </c>
       <c r="E187" t="n">
-        <v>363.0766296386719</v>
+        <v>364.0260314941406</v>
       </c>
       <c r="F187" t="n">
-        <v>27942500</v>
+        <v>29535100</v>
       </c>
       <c r="G187" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B188" t="n">
-        <v>366.8542002567407</v>
+        <v>362.9567158453764</v>
       </c>
       <c r="C188" t="n">
-        <v>371.8409852276818</v>
+        <v>368.3232616719084</v>
       </c>
       <c r="D188" t="n">
-        <v>357.0704802123837</v>
+        <v>354.9718577941881</v>
       </c>
       <c r="E188" t="n">
-        <v>364.0260314941406</v>
+        <v>356.1510925292969</v>
       </c>
       <c r="F188" t="n">
-        <v>29535100</v>
+        <v>32357100</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B189" t="n">
-        <v>362.9567158453764</v>
+        <v>355.7013467902599</v>
       </c>
       <c r="C189" t="n">
-        <v>368.3232616719084</v>
+        <v>358.5694982511428</v>
       </c>
       <c r="D189" t="n">
-        <v>354.9718577941881</v>
+        <v>346.1374871435174</v>
       </c>
       <c r="E189" t="n">
-        <v>356.1510925292969</v>
+        <v>357.5401611328125</v>
       </c>
       <c r="F189" t="n">
-        <v>32357100</v>
+        <v>35538200</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B190" t="n">
-        <v>355.7013467902599</v>
+        <v>362.3870579560934</v>
       </c>
       <c r="C190" t="n">
-        <v>358.5694982511428</v>
+        <v>366.3345327833823</v>
       </c>
       <c r="D190" t="n">
-        <v>346.1374871435174</v>
+        <v>354.7119986974298</v>
       </c>
       <c r="E190" t="n">
-        <v>357.5401611328125</v>
+        <v>359.4489440917969</v>
       </c>
       <c r="F190" t="n">
-        <v>35538200</v>
+        <v>24704600</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B191" t="n">
-        <v>362.3870579560934</v>
+        <v>367.6936611370598</v>
       </c>
       <c r="C191" t="n">
-        <v>366.3345327833823</v>
+        <v>372.7504085202595</v>
       </c>
       <c r="D191" t="n">
-        <v>354.7119986974298</v>
+        <v>366.3145426692825</v>
       </c>
       <c r="E191" t="n">
-        <v>359.4489440917969</v>
+        <v>369.1127624511719</v>
       </c>
       <c r="F191" t="n">
-        <v>24704600</v>
+        <v>27727500</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B192" t="n">
-        <v>367.6936611370598</v>
+        <v>369.3626044753487</v>
       </c>
       <c r="C192" t="n">
-        <v>372.7504085202595</v>
+        <v>375.7584875251172</v>
       </c>
       <c r="D192" t="n">
-        <v>366.3145426692825</v>
+        <v>366.8242274297617</v>
       </c>
       <c r="E192" t="n">
-        <v>369.1127624511719</v>
+        <v>373.01025390625</v>
       </c>
       <c r="F192" t="n">
-        <v>27727500</v>
+        <v>24876100</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B193" t="n">
-        <v>369.3626044753487</v>
+        <v>368.8929017493238</v>
       </c>
       <c r="C193" t="n">
-        <v>375.7584875251172</v>
+        <v>372.0908279957741</v>
       </c>
       <c r="D193" t="n">
-        <v>366.8242274297617</v>
+        <v>361.7874528539307</v>
       </c>
       <c r="E193" t="n">
-        <v>373.01025390625</v>
+        <v>363.5563354492188</v>
       </c>
       <c r="F193" t="n">
-        <v>24876100</v>
+        <v>24543600</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B194" t="n">
-        <v>368.8929017493238</v>
+        <v>365.5150449761754</v>
       </c>
       <c r="C194" t="n">
-        <v>372.0908279957741</v>
+        <v>369.2426598317581</v>
       </c>
       <c r="D194" t="n">
-        <v>361.7874528539307</v>
+        <v>358.4396065335441</v>
       </c>
       <c r="E194" t="n">
-        <v>363.5563354492188</v>
+        <v>367.7935791015625</v>
       </c>
       <c r="F194" t="n">
-        <v>24543600</v>
+        <v>44470100</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B195" t="n">
-        <v>365.5150449761754</v>
+        <v>357.7200907639775</v>
       </c>
       <c r="C195" t="n">
-        <v>369.2426598317581</v>
+        <v>358.6894689253907</v>
       </c>
       <c r="D195" t="n">
-        <v>358.4396065335441</v>
+        <v>341.5005047739323</v>
       </c>
       <c r="E195" t="n">
-        <v>367.7935791015625</v>
+        <v>349.4553833007812</v>
       </c>
       <c r="F195" t="n">
-        <v>44470100</v>
+        <v>52814800</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B196" t="n">
-        <v>357.7200907639775</v>
+        <v>340.4711459801061</v>
       </c>
       <c r="C196" t="n">
-        <v>358.6894689253907</v>
+        <v>349.0656275102868</v>
       </c>
       <c r="D196" t="n">
-        <v>341.5005047739323</v>
+        <v>339.981470511436</v>
       </c>
       <c r="E196" t="n">
-        <v>349.4553833007812</v>
+        <v>345.9076538085938</v>
       </c>
       <c r="F196" t="n">
-        <v>52814800</v>
+        <v>34007700</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B197" t="n">
-        <v>340.4711459801061</v>
+        <v>348.8157979233392</v>
       </c>
       <c r="C197" t="n">
-        <v>349.0656275102868</v>
+        <v>353.2529482684732</v>
       </c>
       <c r="D197" t="n">
-        <v>339.981470511436</v>
+        <v>341.7103492701006</v>
       </c>
       <c r="E197" t="n">
-        <v>345.9076538085938</v>
+        <v>345.0682067871094</v>
       </c>
       <c r="F197" t="n">
-        <v>34007700</v>
+        <v>44997300</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B198" t="n">
-        <v>348.8157979233392</v>
+        <v>336.5137001542092</v>
       </c>
       <c r="C198" t="n">
-        <v>353.2529482684732</v>
+        <v>345.3480177972958</v>
       </c>
       <c r="D198" t="n">
-        <v>341.7103492701006</v>
+        <v>335.6242572392167</v>
       </c>
       <c r="E198" t="n">
-        <v>345.0682067871094</v>
+        <v>343.4891967773438</v>
       </c>
       <c r="F198" t="n">
-        <v>44997300</v>
+        <v>44491400</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B199" t="n">
-        <v>336.5137001542092</v>
+        <v>342.3299372399903</v>
       </c>
       <c r="C199" t="n">
-        <v>345.3480177972958</v>
+        <v>346.1374872957393</v>
       </c>
       <c r="D199" t="n">
-        <v>335.6242572392167</v>
+        <v>329.98789515005</v>
       </c>
       <c r="E199" t="n">
-        <v>343.4891967773438</v>
+        <v>337.1732788085938</v>
       </c>
       <c r="F199" t="n">
-        <v>44491400</v>
+        <v>114706300</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B200" t="n">
-        <v>342.3299372399903</v>
+        <v>341.6104064955248</v>
       </c>
       <c r="C200" t="n">
-        <v>346.1374872957393</v>
+        <v>354.122383587675</v>
       </c>
       <c r="D200" t="n">
-        <v>329.98789515005</v>
+        <v>340.4511784786947</v>
       </c>
       <c r="E200" t="n">
-        <v>337.1732788085938</v>
+        <v>353.4228210449219</v>
       </c>
       <c r="F200" t="n">
-        <v>114706300</v>
+        <v>34213900</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B201" t="n">
-        <v>341.6104064955248</v>
+        <v>353.6426900862941</v>
       </c>
       <c r="C201" t="n">
-        <v>354.122383587675</v>
+        <v>358.3896389689017</v>
       </c>
       <c r="D201" t="n">
-        <v>340.4511784786947</v>
+        <v>350.1749177879227</v>
       </c>
       <c r="E201" t="n">
-        <v>353.4228210449219</v>
+        <v>357.1404418945312</v>
       </c>
       <c r="F201" t="n">
-        <v>34213900</v>
+        <v>35237200</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B202" t="n">
-        <v>353.6426900862941</v>
+        <v>358.1397942573561</v>
       </c>
       <c r="C202" t="n">
-        <v>358.3896389689017</v>
+        <v>362.7368455226467</v>
       </c>
       <c r="D202" t="n">
-        <v>350.1749177879227</v>
+        <v>356.2010379867681</v>
       </c>
       <c r="E202" t="n">
-        <v>357.1404418945312</v>
+        <v>360.9779663085938</v>
       </c>
       <c r="F202" t="n">
-        <v>35237200</v>
+        <v>26736400</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B203" t="n">
-        <v>358.1397942573561</v>
+        <v>359.2490860357571</v>
       </c>
       <c r="C203" t="n">
-        <v>362.7368455226467</v>
+        <v>363.9760280309549</v>
       </c>
       <c r="D203" t="n">
-        <v>356.2010379867681</v>
+        <v>353.1929813351636</v>
       </c>
       <c r="E203" t="n">
-        <v>360.9779663085938</v>
+        <v>359.6788024902344</v>
       </c>
       <c r="F203" t="n">
-        <v>26736400</v>
+        <v>25974800</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B204" t="n">
-        <v>359.2490860357571</v>
+        <v>361.3177293642356</v>
       </c>
       <c r="C204" t="n">
-        <v>363.9760280309549</v>
+        <v>367.693635754559</v>
       </c>
       <c r="D204" t="n">
-        <v>353.1929813351636</v>
+        <v>357.1504252362982</v>
       </c>
       <c r="E204" t="n">
-        <v>359.6788024902344</v>
+        <v>366.2245788574219</v>
       </c>
       <c r="F204" t="n">
-        <v>25974800</v>
+        <v>26915800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B205" t="n">
-        <v>361.3177293642356</v>
+        <v>368.8329180211536</v>
       </c>
       <c r="C205" t="n">
-        <v>367.693635754559</v>
+        <v>372.9202869594668</v>
       </c>
       <c r="D205" t="n">
-        <v>357.1504252362982</v>
+        <v>365.2652040573587</v>
       </c>
       <c r="E205" t="n">
-        <v>366.2245788574219</v>
+        <v>366.7942199707031</v>
       </c>
       <c r="F205" t="n">
-        <v>26915800</v>
+        <v>24045600</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B206" t="n">
-        <v>368.8329180211536</v>
+        <v>364.525702555654</v>
       </c>
       <c r="C206" t="n">
-        <v>372.9202869594668</v>
+        <v>367.6037106679975</v>
       </c>
       <c r="D206" t="n">
-        <v>365.2652040573587</v>
+        <v>357.7900113228786</v>
       </c>
       <c r="E206" t="n">
-        <v>366.7942199707031</v>
+        <v>361.6875305175781</v>
       </c>
       <c r="F206" t="n">
-        <v>24045600</v>
+        <v>22094800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B207" t="n">
-        <v>364.525702555654</v>
+        <v>354.0824097063769</v>
       </c>
       <c r="C207" t="n">
-        <v>367.6037106679975</v>
+        <v>359.4189759454678</v>
       </c>
       <c r="D207" t="n">
-        <v>357.7900113228786</v>
+        <v>350.8544734886641</v>
       </c>
       <c r="E207" t="n">
-        <v>361.6875305175781</v>
+        <v>358.6594848632812</v>
       </c>
       <c r="F207" t="n">
-        <v>22094800</v>
+        <v>24729100</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B208" t="n">
-        <v>354.0824097063769</v>
+        <v>357.3003428038799</v>
       </c>
       <c r="C208" t="n">
-        <v>359.4189759454678</v>
+        <v>357.5901650645865</v>
       </c>
       <c r="D208" t="n">
-        <v>350.8544734886641</v>
+        <v>352.5234144110846</v>
       </c>
       <c r="E208" t="n">
-        <v>358.6594848632812</v>
+        <v>356.9505615234375</v>
       </c>
       <c r="F208" t="n">
-        <v>24729100</v>
+        <v>18146100</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B209" t="n">
-        <v>357.3003428038799</v>
+        <v>355.9611981097028</v>
       </c>
       <c r="C209" t="n">
-        <v>357.5901650645865</v>
+        <v>357.8999543595846</v>
       </c>
       <c r="D209" t="n">
-        <v>352.5234144110846</v>
+        <v>351.5240477747128</v>
       </c>
       <c r="E209" t="n">
-        <v>356.9505615234375</v>
+        <v>352.2835693359375</v>
       </c>
       <c r="F209" t="n">
-        <v>18146100</v>
+        <v>15901700</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B210" t="n">
-        <v>355.9611981097028</v>
+        <v>350.9744235107016</v>
       </c>
       <c r="C210" t="n">
-        <v>357.8999543595846</v>
+        <v>359.92865963343</v>
       </c>
       <c r="D210" t="n">
-        <v>351.5240477747128</v>
+        <v>350.8644783088037</v>
       </c>
       <c r="E210" t="n">
-        <v>352.2835693359375</v>
+        <v>359.2790832519531</v>
       </c>
       <c r="F210" t="n">
-        <v>15901700</v>
+        <v>18259400</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B211" t="n">
-        <v>350.9744235107016</v>
+        <v>357.7400685886304</v>
       </c>
       <c r="C211" t="n">
-        <v>359.92865963343</v>
+        <v>373.4099896327818</v>
       </c>
       <c r="D211" t="n">
-        <v>350.8644783088037</v>
+        <v>357.5302120160503</v>
       </c>
       <c r="E211" t="n">
-        <v>359.2790832519531</v>
+        <v>370.6817626953125</v>
       </c>
       <c r="F211" t="n">
-        <v>18259400</v>
+        <v>28284600</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B212" t="n">
-        <v>357.7400685886304</v>
+        <v>372.8203579699616</v>
       </c>
       <c r="C212" t="n">
-        <v>373.4099896327818</v>
+        <v>375.0289298103755</v>
       </c>
       <c r="D212" t="n">
-        <v>357.5302120160503</v>
+        <v>352.0736836469807</v>
       </c>
       <c r="E212" t="n">
-        <v>370.6817626953125</v>
+        <v>354.2322998046875</v>
       </c>
       <c r="F212" t="n">
-        <v>28284600</v>
+        <v>41158500</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B213" t="n">
-        <v>372.8203579699616</v>
+        <v>345.7777467999313</v>
       </c>
       <c r="C213" t="n">
-        <v>375.0289298103755</v>
+        <v>348.2961170979314</v>
       </c>
       <c r="D213" t="n">
-        <v>352.0736836469807</v>
+        <v>341.1407126662452</v>
       </c>
       <c r="E213" t="n">
-        <v>354.2322998046875</v>
+        <v>346.5472412109375</v>
       </c>
       <c r="F213" t="n">
-        <v>41158500</v>
+        <v>29959300</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B214" t="n">
-        <v>345.7777467999313</v>
+        <v>350.6546131580819</v>
       </c>
       <c r="C214" t="n">
-        <v>348.2961170979314</v>
+        <v>359.4489481797366</v>
       </c>
       <c r="D214" t="n">
-        <v>341.1407126662452</v>
+        <v>350.2948285491913</v>
       </c>
       <c r="E214" t="n">
-        <v>346.5472412109375</v>
+        <v>351.7638854980469</v>
       </c>
       <c r="F214" t="n">
-        <v>29959300</v>
+        <v>24736600</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B215" t="n">
-        <v>350.6546131580819</v>
+        <v>351.094336770995</v>
       </c>
       <c r="C215" t="n">
-        <v>359.4489481797366</v>
+        <v>351.094336770995</v>
       </c>
       <c r="D215" t="n">
-        <v>350.2948285491913</v>
+        <v>346.7771044052826</v>
       </c>
       <c r="E215" t="n">
-        <v>351.7638854980469</v>
+        <v>346.927001953125</v>
       </c>
       <c r="F215" t="n">
-        <v>24736600</v>
+        <v>23369800</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B216" t="n">
-        <v>351.094336770995</v>
+        <v>347.9363472365376</v>
       </c>
       <c r="C216" t="n">
-        <v>351.094336770995</v>
+        <v>349.7152025525983</v>
       </c>
       <c r="D216" t="n">
-        <v>346.7771044052826</v>
+        <v>341.5104851592261</v>
       </c>
       <c r="E216" t="n">
-        <v>346.927001953125</v>
+        <v>341.8702392578125</v>
       </c>
       <c r="F216" t="n">
-        <v>23369800</v>
+        <v>39334100</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B217" t="n">
-        <v>347.9363472365376</v>
+        <v>320.9237241212255</v>
       </c>
       <c r="C217" t="n">
-        <v>349.7152025525983</v>
+        <v>324.2815511558238</v>
       </c>
       <c r="D217" t="n">
-        <v>341.5104851592261</v>
+        <v>314.6977150387725</v>
       </c>
       <c r="E217" t="n">
-        <v>341.8702392578125</v>
+        <v>317.4859313964844</v>
       </c>
       <c r="F217" t="n">
-        <v>39334100</v>
+        <v>69419700</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B218" t="n">
-        <v>320.9237241212255</v>
+        <v>318.2154780071113</v>
       </c>
       <c r="C218" t="n">
-        <v>324.2815511558238</v>
+        <v>323.9717573627877</v>
       </c>
       <c r="D218" t="n">
-        <v>314.6977150387725</v>
+        <v>317.1161784867298</v>
       </c>
       <c r="E218" t="n">
-        <v>317.4859313964844</v>
+        <v>319.5346069335938</v>
       </c>
       <c r="F218" t="n">
-        <v>69419700</v>
+        <v>31806600</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B219" t="n">
-        <v>318.2154780071113</v>
+        <v>324.83120713377</v>
       </c>
       <c r="C219" t="n">
-        <v>323.9717573627877</v>
+        <v>330.2077559724587</v>
       </c>
       <c r="D219" t="n">
-        <v>317.1161784867298</v>
+        <v>324.2415898017393</v>
       </c>
       <c r="E219" t="n">
-        <v>319.5346069335938</v>
+        <v>326.3502197265625</v>
       </c>
       <c r="F219" t="n">
-        <v>31806600</v>
+        <v>28471600</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B220" t="n">
-        <v>324.83120713377</v>
+        <v>327.6893704249235</v>
       </c>
       <c r="C220" t="n">
-        <v>330.2077559724587</v>
+        <v>335.6642555263833</v>
       </c>
       <c r="D220" t="n">
-        <v>324.2415898017393</v>
+        <v>324.2316014627561</v>
       </c>
       <c r="E220" t="n">
-        <v>326.3502197265625</v>
+        <v>333.4956359863281</v>
       </c>
       <c r="F220" t="n">
-        <v>28471600</v>
+        <v>29511900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B221" t="n">
-        <v>327.6893704249235</v>
+        <v>334.455045685483</v>
       </c>
       <c r="C221" t="n">
-        <v>335.6642555263833</v>
+        <v>342.2800028423013</v>
       </c>
       <c r="D221" t="n">
-        <v>324.2316014627561</v>
+        <v>331.4069864854741</v>
       </c>
       <c r="E221" t="n">
-        <v>333.4956359863281</v>
+        <v>336.4937133789062</v>
       </c>
       <c r="F221" t="n">
-        <v>29511900</v>
+        <v>27501600</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B222" t="n">
-        <v>334.455045685483</v>
+        <v>333.9853403838827</v>
       </c>
       <c r="C222" t="n">
-        <v>342.2800028423013</v>
+        <v>336.2938541262907</v>
       </c>
       <c r="D222" t="n">
-        <v>331.4069864854741</v>
+        <v>330.1278039779788</v>
       </c>
       <c r="E222" t="n">
-        <v>336.4937133789062</v>
+        <v>333.4456787109375</v>
       </c>
       <c r="F222" t="n">
-        <v>27501600</v>
+        <v>30168000</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B223" t="n">
-        <v>333.9853403838827</v>
+        <v>340.611054758666</v>
       </c>
       <c r="C223" t="n">
-        <v>336.2938541262907</v>
+        <v>358.3496530632621</v>
       </c>
       <c r="D223" t="n">
-        <v>330.1278039779788</v>
+        <v>339.7816013274756</v>
       </c>
       <c r="E223" t="n">
-        <v>333.4456787109375</v>
+        <v>355.9012451171875</v>
       </c>
       <c r="F223" t="n">
-        <v>30168000</v>
+        <v>46498000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B224" t="n">
-        <v>340.611054758666</v>
+        <v>365.2152604560987</v>
       </c>
       <c r="C224" t="n">
-        <v>358.3496530632621</v>
+        <v>376.4480305309448</v>
       </c>
       <c r="D224" t="n">
-        <v>339.7816013274756</v>
+        <v>363.1166033198653</v>
       </c>
       <c r="E224" t="n">
-        <v>355.9012451171875</v>
+        <v>373.2700805664062</v>
       </c>
       <c r="F224" t="n">
-        <v>46498000</v>
+        <v>38669700</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B225" t="n">
-        <v>365.2152604560987</v>
+        <v>367.9834743668337</v>
       </c>
       <c r="C225" t="n">
-        <v>376.4480305309448</v>
+        <v>380.2755612380555</v>
       </c>
       <c r="D225" t="n">
-        <v>363.1166033198653</v>
+        <v>367.263935640354</v>
       </c>
       <c r="E225" t="n">
-        <v>373.2700805664062</v>
+        <v>377.4074096679688</v>
       </c>
       <c r="F225" t="n">
-        <v>38669700</v>
+        <v>35705700</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B226" t="n">
-        <v>367.9834743668337</v>
+        <v>383.0937455186354</v>
       </c>
       <c r="C226" t="n">
-        <v>380.2755612380555</v>
+        <v>384.2330278418686</v>
       </c>
       <c r="D226" t="n">
-        <v>367.263935640354</v>
+        <v>356.5408062961898</v>
       </c>
       <c r="E226" t="n">
-        <v>377.4074096679688</v>
+        <v>362.1971740722656</v>
       </c>
       <c r="F226" t="n">
-        <v>35705700</v>
+        <v>46926300</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B227" t="n">
-        <v>383.0937455186354</v>
+        <v>360.5382517887205</v>
       </c>
       <c r="C227" t="n">
-        <v>384.2330278418686</v>
+        <v>363.8961093831237</v>
       </c>
       <c r="D227" t="n">
-        <v>356.5408062961898</v>
+        <v>356.6507663527499</v>
       </c>
       <c r="E227" t="n">
-        <v>362.1971740722656</v>
+        <v>357.5202026367188</v>
       </c>
       <c r="F227" t="n">
-        <v>46926300</v>
+        <v>25235900</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B228" t="n">
-        <v>360.5382517887205</v>
+        <v>356.4908465215469</v>
       </c>
       <c r="C228" t="n">
-        <v>363.8961093831237</v>
+        <v>358.6694387836589</v>
       </c>
       <c r="D228" t="n">
-        <v>356.6507663527499</v>
+        <v>353.5527327193329</v>
       </c>
       <c r="E228" t="n">
-        <v>357.5202026367188</v>
+        <v>354.0723876953125</v>
       </c>
       <c r="F228" t="n">
-        <v>25235900</v>
+        <v>19859900</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B229" t="n">
-        <v>356.4908465215469</v>
+        <v>354.951850943437</v>
       </c>
       <c r="C229" t="n">
-        <v>358.6694387836589</v>
+        <v>357.3802827690857</v>
       </c>
       <c r="D229" t="n">
-        <v>353.5527327193329</v>
+        <v>352.4834362714388</v>
       </c>
       <c r="E229" t="n">
-        <v>354.0723876953125</v>
+        <v>357.2903442382812</v>
       </c>
       <c r="F229" t="n">
-        <v>19859900</v>
+        <v>18991400</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B230" t="n">
-        <v>354.951850943437</v>
+        <v>355.6613923515014</v>
       </c>
       <c r="C230" t="n">
-        <v>357.3802827690857</v>
+        <v>356.5807842683805</v>
       </c>
       <c r="D230" t="n">
-        <v>352.4834362714388</v>
+        <v>343.1694223006263</v>
       </c>
       <c r="E230" t="n">
-        <v>357.2903442382812</v>
+        <v>343.5791320800781</v>
       </c>
       <c r="F230" t="n">
-        <v>18991400</v>
+        <v>29081800</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B231" t="n">
-        <v>355.6613923515014</v>
+        <v>346.0875456512855</v>
       </c>
       <c r="C231" t="n">
-        <v>356.5807842683805</v>
+        <v>346.2574498710514</v>
       </c>
       <c r="D231" t="n">
-        <v>343.1694223006263</v>
+        <v>340.661040926288</v>
       </c>
       <c r="E231" t="n">
-        <v>343.5791320800781</v>
+        <v>343.3193359375</v>
       </c>
       <c r="F231" t="n">
-        <v>29081800</v>
+        <v>25012000</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B232" t="n">
-        <v>346.0875456512855</v>
+        <v>345.5478948342235</v>
       </c>
       <c r="C232" t="n">
-        <v>346.2574498710514</v>
+        <v>347.7065110877775</v>
       </c>
       <c r="D232" t="n">
-        <v>340.661040926288</v>
+        <v>343.5392066313974</v>
       </c>
       <c r="E232" t="n">
-        <v>343.3193359375</v>
+        <v>346.1375122070312</v>
       </c>
       <c r="F232" t="n">
-        <v>25012000</v>
+        <v>17866100</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B233" t="n">
-        <v>345.5478948342235</v>
+        <v>346.5772111705174</v>
       </c>
       <c r="C233" t="n">
-        <v>347.7065110877775</v>
+        <v>350.2248908898295</v>
       </c>
       <c r="D233" t="n">
-        <v>343.5392066313974</v>
+        <v>344.2787008387085</v>
       </c>
       <c r="E233" t="n">
-        <v>346.1375122070312</v>
+        <v>345.6777954101562</v>
       </c>
       <c r="F233" t="n">
-        <v>17866100</v>
+        <v>17808600</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B234" t="n">
-        <v>346.5772111705174</v>
+        <v>346.0475530411078</v>
       </c>
       <c r="C234" t="n">
-        <v>350.2248908898295</v>
+        <v>347.0269344906474</v>
       </c>
       <c r="D234" t="n">
-        <v>344.2787008387085</v>
+        <v>341.7103446182459</v>
       </c>
       <c r="E234" t="n">
-        <v>345.6777954101562</v>
+        <v>343.7790222167969</v>
       </c>
       <c r="F234" t="n">
-        <v>17808600</v>
+        <v>18291300</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B235" t="n">
-        <v>346.0475530411078</v>
+        <v>342.1900536360575</v>
       </c>
       <c r="C235" t="n">
-        <v>347.0269344906474</v>
+        <v>344.6484648943574</v>
       </c>
       <c r="D235" t="n">
-        <v>341.7103446182459</v>
+        <v>339.9714784523309</v>
       </c>
       <c r="E235" t="n">
-        <v>343.7790222167969</v>
+        <v>343.9789123535156</v>
       </c>
       <c r="F235" t="n">
-        <v>18291300</v>
+        <v>19248800</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B236" t="n">
-        <v>342.1900536360575</v>
+        <v>342.2400076559886</v>
       </c>
       <c r="C236" t="n">
-        <v>344.6484648943574</v>
+        <v>346.5072842825429</v>
       </c>
       <c r="D236" t="n">
-        <v>339.9714784523309</v>
+        <v>340.4411761094805</v>
       </c>
       <c r="E236" t="n">
-        <v>343.9789123535156</v>
+        <v>344.4985656738281</v>
       </c>
       <c r="F236" t="n">
-        <v>19248800</v>
+        <v>19733800</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B237" t="n">
-        <v>342.2400076559886</v>
+        <v>342.8396207141765</v>
       </c>
       <c r="C237" t="n">
-        <v>346.5072842825429</v>
+        <v>343.6790774504127</v>
       </c>
       <c r="D237" t="n">
-        <v>340.4411761094805</v>
+        <v>338.3525147854226</v>
       </c>
       <c r="E237" t="n">
-        <v>344.4985656738281</v>
+        <v>340.451171875</v>
       </c>
       <c r="F237" t="n">
-        <v>19733800</v>
+        <v>18570400</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B238" t="n">
-        <v>342.8396207141765</v>
+        <v>342.359928876986</v>
       </c>
       <c r="C238" t="n">
-        <v>343.6790774504127</v>
+        <v>345.9776291730591</v>
       </c>
       <c r="D238" t="n">
-        <v>338.3525147854226</v>
+        <v>340.1813365286692</v>
       </c>
       <c r="E238" t="n">
-        <v>340.451171875</v>
+        <v>344.5985107421875</v>
       </c>
       <c r="F238" t="n">
-        <v>18570400</v>
+        <v>20849800</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B239" t="n">
-        <v>342.359928876986</v>
+        <v>343.3992753172161</v>
       </c>
       <c r="C239" t="n">
-        <v>345.9776291730591</v>
+        <v>351.3741604480826</v>
       </c>
       <c r="D239" t="n">
-        <v>340.1813365286692</v>
+        <v>342.2699962782288</v>
       </c>
       <c r="E239" t="n">
-        <v>344.5985107421875</v>
+        <v>347.83642578125</v>
       </c>
       <c r="F239" t="n">
-        <v>20849800</v>
+        <v>26338200</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B240" t="n">
-        <v>343.3992753172161</v>
+        <v>349.4154232615459</v>
       </c>
       <c r="C240" t="n">
-        <v>351.3741604480826</v>
+        <v>349.9350782600912</v>
       </c>
       <c r="D240" t="n">
-        <v>342.2699962782288</v>
+        <v>345.3780098175396</v>
       </c>
       <c r="E240" t="n">
-        <v>347.83642578125</v>
+        <v>346.7371215820312</v>
       </c>
       <c r="F240" t="n">
-        <v>26338200</v>
+        <v>20649700</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B241" t="n">
-        <v>349.4154232615459</v>
+        <v>346.3973312516375</v>
       </c>
       <c r="C241" t="n">
-        <v>349.9350782600912</v>
+        <v>346.6571739906042</v>
       </c>
       <c r="D241" t="n">
-        <v>345.3780098175396</v>
+        <v>339.9614657782595</v>
       </c>
       <c r="E241" t="n">
-        <v>346.7371215820312</v>
+        <v>341.7803039550781</v>
       </c>
       <c r="F241" t="n">
-        <v>20649700</v>
+        <v>20420300</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B242" t="n">
-        <v>346.3973312516375</v>
+        <v>339.4518318672431</v>
       </c>
       <c r="C242" t="n">
-        <v>346.6571739906042</v>
+        <v>341.4705233735174</v>
       </c>
       <c r="D242" t="n">
-        <v>339.9614657782595</v>
+        <v>338.3025461528343</v>
       </c>
       <c r="E242" t="n">
-        <v>341.7803039550781</v>
+        <v>340.4311828613281</v>
       </c>
       <c r="F242" t="n">
-        <v>20420300</v>
+        <v>23391400</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B243" t="n">
-        <v>339.4518318672431</v>
+        <v>340.4911426360338</v>
       </c>
       <c r="C243" t="n">
-        <v>341.4705233735174</v>
+        <v>348.9157509584863</v>
       </c>
       <c r="D243" t="n">
-        <v>338.3025461528343</v>
+        <v>340.0514228221321</v>
       </c>
       <c r="E243" t="n">
-        <v>340.4311828613281</v>
+        <v>346.3673706054688</v>
       </c>
       <c r="F243" t="n">
-        <v>23391400</v>
+        <v>25347200</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B244" t="n">
-        <v>340.4911426360338</v>
+        <v>343.609121722545</v>
       </c>
       <c r="C244" t="n">
-        <v>348.9157509584863</v>
+        <v>344.3686432833908</v>
       </c>
       <c r="D244" t="n">
-        <v>340.0514228221321</v>
+        <v>336.943423385668</v>
       </c>
       <c r="E244" t="n">
-        <v>346.3673706054688</v>
+        <v>339.1320190429688</v>
       </c>
       <c r="F244" t="n">
-        <v>25347200</v>
+        <v>33493600</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B245" t="n">
-        <v>343.609121722545</v>
+        <v>335.7841605001305</v>
       </c>
       <c r="C245" t="n">
-        <v>344.3686432833908</v>
+        <v>336.9834018439635</v>
       </c>
       <c r="D245" t="n">
-        <v>336.943423385668</v>
+        <v>332.8360433203593</v>
       </c>
       <c r="E245" t="n">
-        <v>339.1320190429688</v>
+        <v>334.8047790527344</v>
       </c>
       <c r="F245" t="n">
-        <v>33493600</v>
+        <v>23342700</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B246" t="n">
-        <v>335.7841605001305</v>
+        <v>333.845410447285</v>
       </c>
       <c r="C246" t="n">
-        <v>336.9834018439635</v>
+        <v>339.7815972628325</v>
       </c>
       <c r="D246" t="n">
-        <v>332.8360433203593</v>
+        <v>332.6062167342666</v>
       </c>
       <c r="E246" t="n">
-        <v>334.8047790527344</v>
+        <v>336.9034423828125</v>
       </c>
       <c r="F246" t="n">
-        <v>23342700</v>
+        <v>22582300</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B247" t="n">
-        <v>333.845410447285</v>
+        <v>340.3412297100126</v>
       </c>
       <c r="C247" t="n">
-        <v>339.7815972628325</v>
+        <v>344.4585782378343</v>
       </c>
       <c r="D247" t="n">
-        <v>332.6062167342666</v>
+        <v>339.841550898423</v>
       </c>
       <c r="E247" t="n">
-        <v>336.9034423828125</v>
+        <v>342.260009765625</v>
       </c>
       <c r="F247" t="n">
-        <v>22582300</v>
+        <v>20726900</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,25 +6865,25 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B248" t="n">
-        <v>340.3412297100126</v>
+        <v>342.4700012207031</v>
       </c>
       <c r="C248" t="n">
-        <v>344.4585782378343</v>
+        <v>343.5299987792969</v>
       </c>
       <c r="D248" t="n">
-        <v>339.841550898423</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="E248" t="n">
-        <v>342.260009765625</v>
+        <v>338.4599914550781</v>
       </c>
       <c r="F248" t="n">
-        <v>20726900</v>
+        <v>23189300</v>
       </c>
       <c r="G248" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -6891,25 +6891,25 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B249" t="n">
-        <v>342.4700012207031</v>
+        <v>335.4200134277344</v>
       </c>
       <c r="C249" t="n">
-        <v>343.5299987792969</v>
+        <v>339.6799926757812</v>
       </c>
       <c r="D249" t="n">
-        <v>337.0899963378906</v>
+        <v>333.2200012207031</v>
       </c>
       <c r="E249" t="n">
-        <v>338.4599914550781</v>
+        <v>338.3599853515625</v>
       </c>
       <c r="F249" t="n">
-        <v>23189300</v>
+        <v>22915800</v>
       </c>
       <c r="G249" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B250" t="n">
-        <v>335.4200134277344</v>
+        <v>331.6499938964844</v>
       </c>
       <c r="C250" t="n">
-        <v>339.6799926757812</v>
+        <v>331.8500061035156</v>
       </c>
       <c r="D250" t="n">
-        <v>333.2200012207031</v>
+        <v>327.8999938964844</v>
       </c>
       <c r="E250" t="n">
-        <v>338.3599853515625</v>
+        <v>330.6499938964844</v>
       </c>
       <c r="F250" t="n">
-        <v>22915800</v>
+        <v>33151600</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B251" t="n">
-        <v>331.6499938964844</v>
+        <v>328.2300109863281</v>
       </c>
       <c r="C251" t="n">
-        <v>331.8500061035156</v>
+        <v>333.2300109863281</v>
       </c>
       <c r="D251" t="n">
-        <v>327.8999938964844</v>
+        <v>327.739990234375</v>
       </c>
       <c r="E251" t="n">
-        <v>330.6499938964844</v>
+        <v>332.6000061035156</v>
       </c>
       <c r="F251" t="n">
-        <v>33151600</v>
+        <v>23557600</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B252" t="n">
-        <v>328.2300109863281</v>
+        <v>335.0299987792969</v>
       </c>
       <c r="C252" t="n">
-        <v>333.2300109863281</v>
+        <v>342.9800109863281</v>
       </c>
       <c r="D252" t="n">
-        <v>327.739990234375</v>
+        <v>335.0299987792969</v>
       </c>
       <c r="E252" t="n">
-        <v>332.6000061035156</v>
+        <v>338.5</v>
       </c>
       <c r="F252" t="n">
-        <v>23508500</v>
+        <v>24677500</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10772,37 +10772,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="D2" t="n">
         <v>332.6</v>
       </c>
-      <c r="D2" t="n">
-        <v>330.65</v>
-      </c>
       <c r="E2" t="n">
-        <v>328.01</v>
+        <v>335.065</v>
       </c>
       <c r="F2" t="n">
-        <v>333.23</v>
+        <v>342.97</v>
       </c>
       <c r="G2" t="n">
-        <v>327.7465</v>
+        <v>335.065</v>
       </c>
       <c r="H2" t="n">
-        <v>22782704</v>
+        <v>24283830</v>
       </c>
       <c r="I2" t="n">
-        <v>29954344</v>
+        <v>29850733</v>
       </c>
       <c r="J2" t="n">
-        <v>4067676389376</v>
+        <v>4139833098240</v>
       </c>
       <c r="K2" t="n">
-        <v>16.696787</v>
+        <v>16.975927</v>
       </c>
       <c r="L2" t="n">
-        <v>22.361423</v>
+        <v>22.758093</v>
       </c>
       <c r="M2" t="n">
-        <v>19.92</v>
+        <v>20.28</v>
       </c>
       <c r="N2" t="n">
         <v>408.61</v>
@@ -10838,7 +10838,7 @@
         <v>50.896</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.534895</v>
+        <v>6.6508174</v>
       </c>
       <c r="Z2" t="n">
         <v>2.94</v>
@@ -10850,7 +10850,7 @@
         <v>445865984000</v>
       </c>
       <c r="AC2" t="n">
-        <v>3964038021120</v>
+        <v>4036194992128</v>
       </c>
       <c r="AD2" t="n">
         <v>173164003328</v>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:02:42</t>
+          <t>2026-09-12 21:46:49</t>
         </is>
       </c>
     </row>
